--- a/youzi/小鳄鱼/index.xlsx
+++ b/youzi/小鳄鱼/index.xlsx
@@ -39,6 +39,60 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
@@ -51,73 +105,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA91D2B"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FA94B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CD"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,37 +183,355 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2FA94B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6707C"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C1C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15664"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4E0BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -171,7 +543,859 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC969E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A712F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A143"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -183,19 +1407,517 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFBEE4C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9818B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1E2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F2E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C1C6"/>
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9858F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -213,7 +1935,997 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CDD1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8790"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CD95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B96B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04D5B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -225,97 +2937,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15664"/>
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -327,649 +2961,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB4E0BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC969E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A712F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C41"/>
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CE"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -981,73 +3039,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1059,2017 +3069,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A143"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9818B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBEE4C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1E2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F2E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9858F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CDD1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8790"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF54B96B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CD95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04D5B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFEC949D"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEC949D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3081,12 +3105,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEBF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF7D3D7"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB9E2C2"/>
         <bgColor/>
       </patternFill>
@@ -3094,54 +3142,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -8682,7 +8682,7 @@
       <c r="C2" t="str">
         <v>603881</v>
       </c>
-      <c r="D2" s="1" t="str">
+      <c r="D2" s="10" t="str">
         <v>净买: 1.27亿</v>
       </c>
       <c r="E2">
@@ -8697,37 +8697,37 @@
       <c r="H2">
         <v>8.87</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="1">
         <v>1.04</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="2">
         <v>11.14</v>
       </c>
       <c r="K2" s="3">
         <v>0.03</v>
       </c>
-      <c r="L2" s="11">
+      <c r="L2" s="7">
         <v>7.5</v>
       </c>
-      <c r="M2" s="12">
+      <c r="M2" s="8">
         <v>8.74</v>
       </c>
-      <c r="N2" s="2">
+      <c r="N2" s="9">
         <v>19.61</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O2" s="11">
         <v>25.9</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="4">
         <v>21.45</v>
       </c>
-      <c r="Q2" s="6">
+      <c r="Q2" s="5">
         <v>15.56</v>
       </c>
-      <c r="R2" s="7">
+      <c r="R2" s="12">
         <v>9.81</v>
       </c>
-      <c r="S2" s="8">
+      <c r="S2" s="6">
         <v>-0.74</v>
       </c>
       <c r="T2" s="13">
@@ -8759,37 +8759,37 @@
       <c r="H3">
         <v>-4.56</v>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="26">
         <v>-5.7</v>
       </c>
-      <c r="J3" s="26">
+      <c r="J3" s="23">
         <v>1.34</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="14">
         <v>2.51</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="18">
         <v>12.77</v>
       </c>
       <c r="M3" s="19">
         <v>18.69</v>
       </c>
-      <c r="N3" s="20">
+      <c r="N3" s="21">
         <v>14.5</v>
       </c>
-      <c r="O3" s="24">
+      <c r="O3" s="15">
         <v>8.94</v>
       </c>
-      <c r="P3" s="21">
+      <c r="P3" s="16">
         <v>3.52</v>
       </c>
-      <c r="Q3" s="22">
+      <c r="Q3" s="20">
         <v>-6.42</v>
       </c>
-      <c r="R3" s="16">
+      <c r="R3" s="22">
         <v>-4.83</v>
       </c>
-      <c r="S3" s="15">
+      <c r="S3" s="24">
         <v>-3.18</v>
       </c>
       <c r="T3" s="17">
@@ -8806,7 +8806,7 @@
       <c r="C4" t="str">
         <v>603511</v>
       </c>
-      <c r="D4" s="29" t="str">
+      <c r="D4" s="35" t="str">
         <v>净卖: -457.10万</v>
       </c>
       <c r="E4">
@@ -8821,19 +8821,19 @@
       <c r="H4">
         <v>0.22</v>
       </c>
-      <c r="I4" s="35">
+      <c r="I4" s="30">
         <v>9.8</v>
       </c>
-      <c r="J4" s="36">
+      <c r="J4" s="31">
         <v>13.04</v>
       </c>
-      <c r="K4" s="30">
+      <c r="K4" s="39">
         <v>17.87</v>
       </c>
-      <c r="L4" s="37">
+      <c r="L4" s="32">
         <v>11.31</v>
       </c>
-      <c r="M4" s="32">
+      <c r="M4" s="27">
         <v>12.39</v>
       </c>
       <c r="N4" s="33">
@@ -8842,19 +8842,19 @@
       <c r="O4" s="38">
         <v>7.93</v>
       </c>
-      <c r="P4" s="31">
+      <c r="P4" s="28">
         <v>8.36</v>
       </c>
-      <c r="Q4" s="34">
+      <c r="Q4" s="36">
         <v>9.44</v>
       </c>
-      <c r="R4" s="28">
+      <c r="R4" s="37">
         <v>11.38</v>
       </c>
-      <c r="S4" s="39">
+      <c r="S4" s="34">
         <v>11.1</v>
       </c>
-      <c r="T4" s="27">
+      <c r="T4" s="29">
         <v>1.51</v>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       <c r="C5" t="str">
         <v>002639</v>
       </c>
-      <c r="D5" s="48" t="str">
+      <c r="D5" s="42" t="str">
         <v>净买: 6286.22万</v>
       </c>
       <c r="E5">
@@ -8883,40 +8883,40 @@
       <c r="H5">
         <v>-1.66</v>
       </c>
-      <c r="I5" s="42">
+      <c r="I5" s="47">
         <v>11.82</v>
       </c>
       <c r="J5" s="43">
         <v>12.21</v>
       </c>
-      <c r="K5" s="44">
+      <c r="K5" s="50">
         <v>5.32</v>
       </c>
       <c r="L5" s="49">
         <v>15.84</v>
       </c>
-      <c r="M5" s="45">
+      <c r="M5" s="51">
         <v>10.91</v>
       </c>
-      <c r="N5" s="46">
+      <c r="N5" s="52">
         <v>18.96</v>
       </c>
-      <c r="O5" s="50">
+      <c r="O5" s="44">
         <v>22.6</v>
       </c>
-      <c r="P5" s="41">
+      <c r="P5" s="45">
         <v>15.71</v>
       </c>
-      <c r="Q5" s="47">
+      <c r="Q5" s="46">
         <v>4.16</v>
       </c>
-      <c r="R5" s="51">
+      <c r="R5" s="40">
         <v>-6.23</v>
       </c>
-      <c r="S5" s="52">
+      <c r="S5" s="41">
         <v>-8.18</v>
       </c>
-      <c r="T5" s="40">
+      <c r="T5" s="48">
         <v>151.69</v>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
       <c r="C6" t="str">
         <v>603226</v>
       </c>
-      <c r="D6" s="58" t="str">
+      <c r="D6" s="59" t="str">
         <v>净卖: -590.66万</v>
       </c>
       <c r="E6">
@@ -8948,37 +8948,37 @@
       <c r="I6" s="63">
         <v>10.05</v>
       </c>
-      <c r="J6" s="55">
+      <c r="J6" s="60">
         <v>4.08</v>
       </c>
       <c r="K6" s="56">
         <v>4.08</v>
       </c>
-      <c r="L6" s="59">
+      <c r="L6" s="64">
         <v>4.08</v>
       </c>
-      <c r="M6" s="53">
+      <c r="M6" s="65">
         <v>7.06</v>
       </c>
-      <c r="N6" s="60">
+      <c r="N6" s="57">
         <v>5.02</v>
       </c>
-      <c r="O6" s="61">
+      <c r="O6" s="53">
         <v>-5.49</v>
       </c>
-      <c r="P6" s="57">
+      <c r="P6" s="54">
         <v>-14.6</v>
       </c>
-      <c r="Q6" s="62">
+      <c r="Q6" s="58">
         <v>-9.26</v>
       </c>
-      <c r="R6" s="64">
+      <c r="R6" s="61">
         <v>-5.81</v>
       </c>
-      <c r="S6" s="65">
+      <c r="S6" s="55">
         <v>3.61</v>
       </c>
-      <c r="T6" s="54">
+      <c r="T6" s="62">
         <v>530.3</v>
       </c>
     </row>
@@ -8992,7 +8992,7 @@
       <c r="C7" t="str">
         <v>603011</v>
       </c>
-      <c r="D7" s="75" t="str">
+      <c r="D7" s="73" t="str">
         <v>净卖: -2450.00万</v>
       </c>
       <c r="E7">
@@ -9007,16 +9007,16 @@
       <c r="H7">
         <v>-0.78</v>
       </c>
-      <c r="I7" s="77">
+      <c r="I7" s="74">
         <v>10.9</v>
       </c>
-      <c r="J7" s="66">
+      <c r="J7" s="67">
         <v>5.29</v>
       </c>
-      <c r="K7" s="67">
+      <c r="K7" s="75">
         <v>-1.74</v>
       </c>
-      <c r="L7" s="72">
+      <c r="L7" s="71">
         <v>-11.53</v>
       </c>
       <c r="M7" s="68">
@@ -9025,22 +9025,22 @@
       <c r="N7" s="69">
         <v>-24.17</v>
       </c>
-      <c r="O7" s="76">
+      <c r="O7" s="78">
         <v>-21.8</v>
       </c>
-      <c r="P7" s="73">
+      <c r="P7" s="76">
         <v>-20.46</v>
       </c>
-      <c r="Q7" s="78">
+      <c r="Q7" s="70">
         <v>-12.48</v>
       </c>
-      <c r="R7" s="74">
+      <c r="R7" s="77">
         <v>-15.24</v>
       </c>
-      <c r="S7" s="70">
+      <c r="S7" s="66">
         <v>-22.12</v>
       </c>
-      <c r="T7" s="71">
+      <c r="T7" s="72">
         <v>72.51</v>
       </c>
     </row>
@@ -9054,7 +9054,7 @@
       <c r="C8" t="str">
         <v>000989</v>
       </c>
-      <c r="D8" s="89" t="str">
+      <c r="D8" s="87" t="str">
         <v>净卖: -4522.23万</v>
       </c>
       <c r="E8">
@@ -9069,40 +9069,40 @@
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="82">
+      <c r="I8" s="88">
         <v>-6.8</v>
       </c>
-      <c r="J8" s="90">
+      <c r="J8" s="89">
         <v>-8.95</v>
       </c>
-      <c r="K8" s="83">
+      <c r="K8" s="81">
         <v>-12.73</v>
       </c>
-      <c r="L8" s="91">
+      <c r="L8" s="82">
         <v>-12.41</v>
       </c>
-      <c r="M8" s="79">
+      <c r="M8" s="83">
         <v>-9.82</v>
       </c>
-      <c r="N8" s="86">
+      <c r="N8" s="90">
         <v>-6.8</v>
       </c>
-      <c r="O8" s="87">
+      <c r="O8" s="91">
         <v>-1.29</v>
       </c>
-      <c r="P8" s="84">
+      <c r="P8" s="79">
         <v>-3.78</v>
       </c>
-      <c r="Q8" s="85">
+      <c r="Q8" s="84">
         <v>-6.36</v>
       </c>
-      <c r="R8" s="88">
+      <c r="R8" s="85">
         <v>-5.83</v>
       </c>
       <c r="S8" s="80">
         <v>-8.2</v>
       </c>
-      <c r="T8" s="81">
+      <c r="T8" s="86">
         <v>2.59</v>
       </c>
     </row>
@@ -9116,7 +9116,7 @@
       <c r="C9" t="str">
         <v>603488</v>
       </c>
-      <c r="D9" s="93" t="str">
+      <c r="D9" s="102" t="str">
         <v>净卖: -414.45万</v>
       </c>
       <c r="E9">
@@ -9131,40 +9131,40 @@
       <c r="H9">
         <v>-0.82</v>
       </c>
-      <c r="I9" s="100">
+      <c r="I9" s="98">
         <v>10.89</v>
       </c>
-      <c r="J9" s="98">
+      <c r="J9" s="99">
         <v>2.01</v>
       </c>
-      <c r="K9" s="94">
+      <c r="K9" s="103">
         <v>-0.12</v>
       </c>
-      <c r="L9" s="101">
+      <c r="L9" s="104">
         <v>-4.5</v>
       </c>
-      <c r="M9" s="95">
+      <c r="M9" s="93">
         <v>-4.73</v>
       </c>
-      <c r="N9" s="104">
+      <c r="N9" s="92">
         <v>-6.27</v>
       </c>
-      <c r="O9" s="102">
+      <c r="O9" s="100">
         <v>-5.56</v>
       </c>
-      <c r="P9" s="99">
+      <c r="P9" s="94">
         <v>-9.11</v>
       </c>
-      <c r="Q9" s="96">
+      <c r="Q9" s="95">
         <v>-8.52</v>
       </c>
-      <c r="R9" s="103">
+      <c r="R9" s="101">
         <v>-7.1</v>
       </c>
-      <c r="S9" s="97">
+      <c r="S9" s="96">
         <v>-7.81</v>
       </c>
-      <c r="T9" s="92">
+      <c r="T9" s="97">
         <v>32.54</v>
       </c>
     </row>
@@ -9178,7 +9178,7 @@
       <c r="C10" t="str">
         <v>603429</v>
       </c>
-      <c r="D10" s="117" t="str">
+      <c r="D10" s="113" t="str">
         <v>净卖: -775.14万</v>
       </c>
       <c r="E10">
@@ -9193,40 +9193,40 @@
       <c r="H10">
         <v>-0.46</v>
       </c>
-      <c r="I10" s="105">
+      <c r="I10" s="112">
         <v>-9.58</v>
       </c>
-      <c r="J10" s="106">
+      <c r="J10" s="105">
         <v>-17.02</v>
       </c>
-      <c r="K10" s="112">
+      <c r="K10" s="106">
         <v>-15.53</v>
       </c>
-      <c r="L10" s="109">
+      <c r="L10" s="107">
         <v>-17.02</v>
       </c>
-      <c r="M10" s="113">
+      <c r="M10" s="114">
         <v>-25.3</v>
       </c>
-      <c r="N10" s="115">
+      <c r="N10" s="108">
         <v>-26.33</v>
       </c>
-      <c r="O10" s="116">
+      <c r="O10" s="109">
         <v>-22.79</v>
       </c>
-      <c r="P10" s="107">
+      <c r="P10" s="115">
         <v>-22.7</v>
       </c>
-      <c r="Q10" s="114">
+      <c r="Q10" s="116">
         <v>-24.47</v>
       </c>
       <c r="R10" s="110">
         <v>-23.91</v>
       </c>
-      <c r="S10" s="111">
+      <c r="S10" s="117">
         <v>-24.74</v>
       </c>
-      <c r="T10" s="108">
+      <c r="T10" s="111">
         <v>-7.16</v>
       </c>
     </row>
@@ -9240,7 +9240,7 @@
       <c r="C11" t="str">
         <v>600735</v>
       </c>
-      <c r="D11" s="128" t="str">
+      <c r="D11" s="121" t="str">
         <v>净买: 1079.52万</v>
       </c>
       <c r="E11">
@@ -9255,40 +9255,40 @@
       <c r="H11">
         <v>-5.01</v>
       </c>
-      <c r="I11" s="129">
+      <c r="I11" s="122">
         <v>5.4</v>
       </c>
-      <c r="J11" s="130">
+      <c r="J11" s="123">
         <v>4.08</v>
       </c>
-      <c r="K11" s="118">
+      <c r="K11" s="124">
         <v>1.32</v>
       </c>
-      <c r="L11" s="121">
+      <c r="L11" s="127">
         <v>2.37</v>
       </c>
-      <c r="M11" s="119">
+      <c r="M11" s="130">
         <v>7.64</v>
       </c>
-      <c r="N11" s="124">
+      <c r="N11" s="118">
         <v>6.19</v>
       </c>
-      <c r="O11" s="120">
+      <c r="O11" s="119">
         <v>3.43</v>
       </c>
-      <c r="P11" s="125">
+      <c r="P11" s="128">
         <v>8.7</v>
       </c>
-      <c r="Q11" s="126">
+      <c r="Q11" s="125">
         <v>10.28</v>
       </c>
-      <c r="R11" s="122">
+      <c r="R11" s="129">
         <v>6.59</v>
       </c>
-      <c r="S11" s="127">
+      <c r="S11" s="126">
         <v>3.43</v>
       </c>
-      <c r="T11" s="123">
+      <c r="T11" s="120">
         <v>-11.33</v>
       </c>
     </row>
@@ -9320,34 +9320,34 @@
       <c r="I12" s="135">
         <v>-4.19</v>
       </c>
-      <c r="J12" s="136">
+      <c r="J12" s="139">
         <v>-2.47</v>
       </c>
-      <c r="K12" s="132">
+      <c r="K12" s="141">
         <v>-4.19</v>
       </c>
-      <c r="L12" s="142">
+      <c r="L12" s="140">
         <v>-13.75</v>
       </c>
-      <c r="M12" s="143">
+      <c r="M12" s="136">
         <v>-14.93</v>
       </c>
-      <c r="N12" s="131">
+      <c r="N12" s="142">
         <v>-10.85</v>
       </c>
-      <c r="O12" s="137">
+      <c r="O12" s="143">
         <v>-10.74</v>
       </c>
-      <c r="P12" s="140">
+      <c r="P12" s="137">
         <v>-12.78</v>
       </c>
-      <c r="Q12" s="138">
+      <c r="Q12" s="132">
         <v>-12.14</v>
       </c>
-      <c r="R12" s="139">
+      <c r="R12" s="138">
         <v>-13.1</v>
       </c>
-      <c r="S12" s="141">
+      <c r="S12" s="131">
         <v>-14.18</v>
       </c>
       <c r="T12" s="133">
@@ -9364,7 +9364,7 @@
       <c r="C13" t="str">
         <v>603429</v>
       </c>
-      <c r="D13" s="152" t="str">
+      <c r="D13" s="146" t="str">
         <v>净卖: -2033.97万</v>
       </c>
       <c r="E13">
@@ -9379,40 +9379,40 @@
       <c r="H13">
         <v>-0.45</v>
       </c>
-      <c r="I13" s="146">
+      <c r="I13" s="151">
         <v>-9.57</v>
       </c>
-      <c r="J13" s="153">
+      <c r="J13" s="155">
         <v>-10.81</v>
       </c>
-      <c r="K13" s="147">
+      <c r="K13" s="149">
         <v>-6.53</v>
       </c>
-      <c r="L13" s="144">
+      <c r="L13" s="152">
         <v>-6.42</v>
       </c>
-      <c r="M13" s="154">
+      <c r="M13" s="156">
         <v>-8.56</v>
       </c>
-      <c r="N13" s="155">
+      <c r="N13" s="153">
         <v>-7.88</v>
       </c>
-      <c r="O13" s="148">
+      <c r="O13" s="150">
         <v>-8.9</v>
       </c>
-      <c r="P13" s="149">
+      <c r="P13" s="147">
         <v>-10.02</v>
       </c>
-      <c r="Q13" s="150">
+      <c r="Q13" s="144">
         <v>-8.78</v>
       </c>
-      <c r="R13" s="151">
+      <c r="R13" s="148">
         <v>-8.78</v>
       </c>
-      <c r="S13" s="156">
+      <c r="S13" s="145">
         <v>-5.86</v>
       </c>
-      <c r="T13" s="145">
+      <c r="T13" s="154">
         <v>12.39</v>
       </c>
     </row>
@@ -9426,7 +9426,7 @@
       <c r="C14" t="str">
         <v>600735</v>
       </c>
-      <c r="D14" s="164" t="str">
+      <c r="D14" s="165" t="str">
         <v>净买: 450.48万</v>
       </c>
       <c r="E14">
@@ -9441,40 +9441,40 @@
       <c r="H14">
         <v>-9.95</v>
       </c>
-      <c r="I14" s="157">
+      <c r="I14" s="169">
         <v>0</v>
       </c>
-      <c r="J14" s="158">
+      <c r="J14" s="166">
         <v>-0.12</v>
       </c>
-      <c r="K14" s="159">
+      <c r="K14" s="167">
         <v>0.6</v>
       </c>
-      <c r="L14" s="160">
+      <c r="L14" s="168">
         <v>2.04</v>
       </c>
-      <c r="M14" s="165">
+      <c r="M14" s="162">
         <v>-0.96</v>
       </c>
-      <c r="N14" s="166">
+      <c r="N14" s="157">
         <v>-3.72</v>
       </c>
-      <c r="O14" s="161">
+      <c r="O14" s="159">
         <v>2.4</v>
       </c>
-      <c r="P14" s="162">
+      <c r="P14" s="158">
         <v>2.88</v>
       </c>
       <c r="Q14" s="163">
         <v>3.48</v>
       </c>
-      <c r="R14" s="167">
+      <c r="R14" s="160">
         <v>2.76</v>
       </c>
-      <c r="S14" s="168">
+      <c r="S14" s="161">
         <v>4.32</v>
       </c>
-      <c r="T14" s="169">
+      <c r="T14" s="164">
         <v>-19.21</v>
       </c>
     </row>
@@ -9488,7 +9488,7 @@
       <c r="C15" t="str">
         <v>605198</v>
       </c>
-      <c r="D15" s="174" t="str">
+      <c r="D15" s="176" t="str">
         <v>净买: 424.10万</v>
       </c>
       <c r="E15">
@@ -9503,40 +9503,40 @@
       <c r="H15">
         <v>-3.44</v>
       </c>
-      <c r="I15" s="176">
+      <c r="I15" s="177">
         <v>-6.79</v>
       </c>
-      <c r="J15" s="179">
+      <c r="J15" s="170">
         <v>-11.34</v>
       </c>
-      <c r="K15" s="177">
+      <c r="K15" s="171">
         <v>-12.86</v>
       </c>
-      <c r="L15" s="171">
+      <c r="L15" s="181">
         <v>-11.52</v>
       </c>
-      <c r="M15" s="178">
+      <c r="M15" s="173">
         <v>-11.25</v>
       </c>
-      <c r="N15" s="175">
+      <c r="N15" s="174">
         <v>-11.47</v>
       </c>
       <c r="O15" s="172">
         <v>-11.43</v>
       </c>
-      <c r="P15" s="180">
+      <c r="P15" s="182">
         <v>-11.41</v>
       </c>
-      <c r="Q15" s="181">
+      <c r="Q15" s="175">
         <v>-9.78</v>
       </c>
-      <c r="R15" s="182">
+      <c r="R15" s="178">
         <v>-11.65</v>
       </c>
-      <c r="S15" s="173">
+      <c r="S15" s="179">
         <v>-11.96</v>
       </c>
-      <c r="T15" s="170">
+      <c r="T15" s="180">
         <v>5.27</v>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
       <c r="C16" t="str">
         <v>600208</v>
       </c>
-      <c r="D16" s="184" t="str">
+      <c r="D16" s="191" t="str">
         <v>净卖: -1100.93万</v>
       </c>
       <c r="E16">
@@ -9565,40 +9565,40 @@
       <c r="H16">
         <v>9.93</v>
       </c>
-      <c r="I16" s="190">
+      <c r="I16" s="188">
         <v>0</v>
       </c>
-      <c r="J16" s="185">
+      <c r="J16" s="192">
         <v>10.04</v>
       </c>
-      <c r="K16" s="186">
+      <c r="K16" s="184">
         <v>7.23</v>
       </c>
-      <c r="L16" s="194">
+      <c r="L16" s="183">
         <v>11.24</v>
       </c>
-      <c r="M16" s="195">
+      <c r="M16" s="185">
         <v>0.2</v>
       </c>
-      <c r="N16" s="183">
+      <c r="N16" s="193">
         <v>-4.42</v>
       </c>
-      <c r="O16" s="191">
+      <c r="O16" s="194">
         <v>-2.81</v>
       </c>
-      <c r="P16" s="187">
+      <c r="P16" s="186">
         <v>3.41</v>
       </c>
-      <c r="Q16" s="188">
+      <c r="Q16" s="195">
         <v>0.4</v>
       </c>
-      <c r="R16" s="189">
+      <c r="R16" s="187">
         <v>-5.82</v>
       </c>
-      <c r="S16" s="192">
+      <c r="S16" s="189">
         <v>-3.21</v>
       </c>
-      <c r="T16" s="193">
+      <c r="T16" s="190">
         <v>-28.11</v>
       </c>
     </row>
@@ -9612,7 +9612,7 @@
       <c r="C17" t="str">
         <v>600590</v>
       </c>
-      <c r="D17" s="202" t="str">
+      <c r="D17" s="207" t="str">
         <v>净买: 1371.16万</v>
       </c>
       <c r="E17">
@@ -9627,40 +9627,40 @@
       <c r="H17">
         <v>9.98</v>
       </c>
-      <c r="I17" s="196">
+      <c r="I17" s="198">
         <v>0</v>
       </c>
-      <c r="J17" s="203">
+      <c r="J17" s="208">
         <v>-3.03</v>
       </c>
-      <c r="K17" s="204">
+      <c r="K17" s="199">
         <v>-5.43</v>
       </c>
-      <c r="L17" s="197">
+      <c r="L17" s="203">
         <v>-8.3</v>
       </c>
-      <c r="M17" s="199">
+      <c r="M17" s="204">
         <v>-9.54</v>
       </c>
-      <c r="N17" s="205">
+      <c r="N17" s="196">
         <v>-11.64</v>
       </c>
-      <c r="O17" s="206">
+      <c r="O17" s="200">
         <v>-10.4</v>
       </c>
-      <c r="P17" s="198">
+      <c r="P17" s="201">
         <v>-12.57</v>
       </c>
-      <c r="Q17" s="207">
+      <c r="Q17" s="205">
         <v>-13.03</v>
       </c>
-      <c r="R17" s="200">
+      <c r="R17" s="197">
         <v>-14.82</v>
       </c>
-      <c r="S17" s="201">
+      <c r="S17" s="202">
         <v>-21.26</v>
       </c>
-      <c r="T17" s="208">
+      <c r="T17" s="206">
         <v>22.89</v>
       </c>
     </row>
@@ -9689,40 +9689,40 @@
       <c r="H18">
         <v>2.21</v>
       </c>
-      <c r="I18" s="213">
+      <c r="I18" s="216">
         <v>7.01</v>
       </c>
-      <c r="J18" s="221">
+      <c r="J18" s="219">
         <v>5.38</v>
       </c>
-      <c r="K18" s="214">
+      <c r="K18" s="213">
         <v>3.49</v>
       </c>
-      <c r="L18" s="211">
+      <c r="L18" s="214">
         <v>1.38</v>
       </c>
       <c r="M18" s="217">
         <v>9.01</v>
       </c>
-      <c r="N18" s="212">
+      <c r="N18" s="221">
         <v>4.46</v>
       </c>
       <c r="O18" s="209">
         <v>10.34</v>
       </c>
-      <c r="P18" s="215">
+      <c r="P18" s="210">
         <v>3.06</v>
       </c>
-      <c r="Q18" s="210">
+      <c r="Q18" s="215">
         <v>1.01</v>
       </c>
-      <c r="R18" s="218">
+      <c r="R18" s="211">
         <v>-6.11</v>
       </c>
-      <c r="S18" s="219">
+      <c r="S18" s="212">
         <v>-3.86</v>
       </c>
-      <c r="T18" s="216">
+      <c r="T18" s="218">
         <v>-18.78</v>
       </c>
     </row>
@@ -9736,7 +9736,7 @@
       <c r="C19" t="str">
         <v>000061</v>
       </c>
-      <c r="D19" s="231" t="str">
+      <c r="D19" s="223" t="str">
         <v>净买: 2178.30万</v>
       </c>
       <c r="E19">
@@ -9751,40 +9751,40 @@
       <c r="H19">
         <v>5.09</v>
       </c>
-      <c r="I19" s="233">
+      <c r="I19" s="227">
         <v>4.72</v>
       </c>
-      <c r="J19" s="223">
+      <c r="J19" s="228">
         <v>8.94</v>
       </c>
-      <c r="K19" s="229">
+      <c r="K19" s="233">
         <v>3.73</v>
       </c>
       <c r="L19" s="224">
         <v>-1.99</v>
       </c>
-      <c r="M19" s="225">
+      <c r="M19" s="229">
         <v>-1.49</v>
       </c>
-      <c r="N19" s="234">
+      <c r="N19" s="230">
         <v>-0.25</v>
       </c>
-      <c r="O19" s="230">
+      <c r="O19" s="234">
         <v>-0.12</v>
       </c>
-      <c r="P19" s="222">
+      <c r="P19" s="231">
         <v>3.11</v>
       </c>
-      <c r="Q19" s="226">
+      <c r="Q19" s="225">
         <v>4.84</v>
       </c>
-      <c r="R19" s="227">
+      <c r="R19" s="232">
         <v>15.28</v>
       </c>
-      <c r="S19" s="228">
+      <c r="S19" s="222">
         <v>14.53</v>
       </c>
-      <c r="T19" s="232">
+      <c r="T19" s="226">
         <v>-7.7</v>
       </c>
     </row>
@@ -9798,7 +9798,7 @@
       <c r="C20" t="str">
         <v>837174</v>
       </c>
-      <c r="D20" s="244" t="str">
+      <c r="D20" s="238" t="str">
         <v>净买: 1878.87万</v>
       </c>
       <c r="E20">
@@ -9816,34 +9816,34 @@
       <c r="I20" s="245">
         <v>31.1</v>
       </c>
-      <c r="J20" s="246">
+      <c r="J20" s="235">
         <v>25.62</v>
       </c>
-      <c r="K20" s="237">
+      <c r="K20" s="239">
         <v>0.1</v>
       </c>
-      <c r="L20" s="242">
+      <c r="L20" s="236">
         <v>-14.6</v>
       </c>
-      <c r="M20" s="243">
+      <c r="M20" s="237">
         <v>-15.25</v>
       </c>
-      <c r="N20" s="240">
+      <c r="N20" s="242">
         <v>-17.98</v>
       </c>
-      <c r="O20" s="247">
+      <c r="O20" s="243">
         <v>-19.46</v>
       </c>
-      <c r="P20" s="238">
+      <c r="P20" s="240">
         <v>-18.77</v>
       </c>
-      <c r="Q20" s="239">
+      <c r="Q20" s="246">
         <v>-23.13</v>
       </c>
-      <c r="R20" s="235">
+      <c r="R20" s="244">
         <v>-22.25</v>
       </c>
-      <c r="S20" s="236">
+      <c r="S20" s="247">
         <v>-22.58</v>
       </c>
       <c r="T20" s="241">
@@ -9860,7 +9860,7 @@
       <c r="C21" t="str">
         <v>002050</v>
       </c>
-      <c r="D21" s="257" t="str">
+      <c r="D21" s="255" t="str">
         <v>净买: 2.36亿</v>
       </c>
       <c r="E21">
@@ -9875,19 +9875,19 @@
       <c r="H21">
         <v>2.54</v>
       </c>
-      <c r="I21" s="258">
+      <c r="I21" s="256">
         <v>7.27</v>
       </c>
-      <c r="J21" s="260">
+      <c r="J21" s="257">
         <v>8.13</v>
       </c>
-      <c r="K21" s="248">
+      <c r="K21" s="249">
         <v>6.42</v>
       </c>
-      <c r="L21" s="255">
+      <c r="L21" s="260">
         <v>10.42</v>
       </c>
-      <c r="M21" s="249">
+      <c r="M21" s="258">
         <v>9.59</v>
       </c>
       <c r="N21" s="250">
@@ -9896,19 +9896,19 @@
       <c r="O21" s="259">
         <v>24.62</v>
       </c>
-      <c r="P21" s="251">
+      <c r="P21" s="253">
         <v>33.1</v>
       </c>
-      <c r="Q21" s="256">
+      <c r="Q21" s="251">
         <v>44.7</v>
       </c>
-      <c r="R21" s="252">
+      <c r="R21" s="254">
         <v>32.31</v>
       </c>
-      <c r="S21" s="253">
+      <c r="S21" s="248">
         <v>36.5</v>
       </c>
-      <c r="T21" s="254">
+      <c r="T21" s="252">
         <v>44.66</v>
       </c>
     </row>
@@ -9922,7 +9922,7 @@
       <c r="C22" t="str">
         <v>603429</v>
       </c>
-      <c r="D22" s="273" t="str">
+      <c r="D22" s="270" t="str">
         <v>净买: 1423.30万</v>
       </c>
       <c r="E22">
@@ -9937,40 +9937,40 @@
       <c r="H22">
         <v>-0.38</v>
       </c>
-      <c r="I22" s="269">
+      <c r="I22" s="271">
         <v>-6.68</v>
       </c>
-      <c r="J22" s="266">
+      <c r="J22" s="273">
         <v>-8.22</v>
       </c>
       <c r="K22" s="261">
         <v>-10.52</v>
       </c>
-      <c r="L22" s="262">
+      <c r="L22" s="268">
         <v>-8.76</v>
       </c>
-      <c r="M22" s="267">
+      <c r="M22" s="262">
         <v>-10.37</v>
       </c>
-      <c r="N22" s="263">
+      <c r="N22" s="265">
         <v>-10.68</v>
       </c>
-      <c r="O22" s="264">
+      <c r="O22" s="272">
         <v>-12.75</v>
       </c>
-      <c r="P22" s="270">
+      <c r="P22" s="266">
         <v>-9.75</v>
       </c>
-      <c r="Q22" s="265">
+      <c r="Q22" s="267">
         <v>-0.69</v>
       </c>
-      <c r="R22" s="271">
+      <c r="R22" s="263">
         <v>-0.92</v>
       </c>
-      <c r="S22" s="268">
+      <c r="S22" s="269">
         <v>2</v>
       </c>
-      <c r="T22" s="272">
+      <c r="T22" s="264">
         <v>-23.35</v>
       </c>
     </row>
@@ -9984,7 +9984,7 @@
       <c r="C23" t="str">
         <v>002475</v>
       </c>
-      <c r="D23" s="280" t="str">
+      <c r="D23" s="286" t="str">
         <v>净买: 2.00亿</v>
       </c>
       <c r="E23">
@@ -10002,37 +10002,37 @@
       <c r="I23" s="274">
         <v>12.08</v>
       </c>
-      <c r="J23" s="284">
+      <c r="J23" s="285">
         <v>11.67</v>
       </c>
-      <c r="K23" s="281">
+      <c r="K23" s="279">
         <v>11.74</v>
       </c>
-      <c r="L23" s="275">
+      <c r="L23" s="280">
         <v>11</v>
       </c>
-      <c r="M23" s="276">
+      <c r="M23" s="281">
         <v>10.19</v>
       </c>
-      <c r="N23" s="277">
+      <c r="N23" s="276">
         <v>12.52</v>
       </c>
-      <c r="O23" s="285">
+      <c r="O23" s="282">
         <v>17.39</v>
       </c>
-      <c r="P23" s="282">
+      <c r="P23" s="277">
         <v>29.13</v>
       </c>
-      <c r="Q23" s="286">
+      <c r="Q23" s="275">
         <v>39.19</v>
       </c>
       <c r="R23" s="283">
         <v>48.73</v>
       </c>
-      <c r="S23" s="278">
+      <c r="S23" s="284">
         <v>45.64</v>
       </c>
-      <c r="T23" s="279">
+      <c r="T23" s="278">
         <v>26.59</v>
       </c>
     </row>
@@ -10046,7 +10046,7 @@
       <c r="C24" t="str">
         <v>002146</v>
       </c>
-      <c r="D24" s="298" t="str">
+      <c r="D24" s="299" t="str">
         <v>净买: 2134.01万</v>
       </c>
       <c r="E24">
@@ -10061,40 +10061,40 @@
       <c r="H24">
         <v>0.5</v>
       </c>
-      <c r="I24" s="292">
+      <c r="I24" s="287">
         <v>-9</v>
       </c>
-      <c r="J24" s="293">
+      <c r="J24" s="288">
         <v>-11</v>
       </c>
-      <c r="K24" s="288">
+      <c r="K24" s="289">
         <v>-14.5</v>
       </c>
-      <c r="L24" s="289">
+      <c r="L24" s="295">
         <v>-17.5</v>
       </c>
-      <c r="M24" s="299">
+      <c r="M24" s="290">
         <v>-16.5</v>
       </c>
-      <c r="N24" s="290">
+      <c r="N24" s="297">
         <v>-19</v>
       </c>
-      <c r="O24" s="287">
+      <c r="O24" s="291">
         <v>-20</v>
       </c>
-      <c r="P24" s="296">
+      <c r="P24" s="293">
         <v>-19.5</v>
       </c>
-      <c r="Q24" s="291">
+      <c r="Q24" s="294">
         <v>-19.5</v>
       </c>
-      <c r="R24" s="297">
+      <c r="R24" s="298">
         <v>-19</v>
       </c>
-      <c r="S24" s="294">
+      <c r="S24" s="296">
         <v>-18.5</v>
       </c>
-      <c r="T24" s="295">
+      <c r="T24" s="292">
         <v>-31.5</v>
       </c>
     </row>
@@ -10108,7 +10108,7 @@
       <c r="C25" t="str">
         <v>002743</v>
       </c>
-      <c r="D25" s="309" t="str">
+      <c r="D25" s="301" t="str">
         <v>净卖: -133.27万</v>
       </c>
       <c r="E25">
@@ -10123,40 +10123,40 @@
       <c r="H25">
         <v>-9.98</v>
       </c>
-      <c r="I25" s="302">
+      <c r="I25" s="311">
         <v>0</v>
       </c>
-      <c r="J25" s="310">
+      <c r="J25" s="309">
         <v>-5.83</v>
       </c>
-      <c r="K25" s="303">
+      <c r="K25" s="310">
         <v>-3.38</v>
       </c>
-      <c r="L25" s="311">
+      <c r="L25" s="302">
         <v>0.75</v>
       </c>
-      <c r="M25" s="312">
+      <c r="M25" s="305">
         <v>1.88</v>
       </c>
-      <c r="N25" s="305">
+      <c r="N25" s="303">
         <v>3.01</v>
       </c>
-      <c r="O25" s="300">
+      <c r="O25" s="306">
         <v>3.95</v>
       </c>
-      <c r="P25" s="306">
+      <c r="P25" s="304">
         <v>0.75</v>
       </c>
-      <c r="Q25" s="304">
+      <c r="Q25" s="307">
         <v>-0.19</v>
       </c>
-      <c r="R25" s="307">
+      <c r="R25" s="308">
         <v>1.5</v>
       </c>
-      <c r="S25" s="301">
+      <c r="S25" s="312">
         <v>5.83</v>
       </c>
-      <c r="T25" s="308">
+      <c r="T25" s="300">
         <v>0</v>
       </c>
     </row>
@@ -10188,37 +10188,37 @@
       <c r="I26" s="317">
         <v>6.51</v>
       </c>
-      <c r="J26" s="318">
+      <c r="J26" s="321">
         <v>17.26</v>
       </c>
-      <c r="K26" s="323">
+      <c r="K26" s="318">
         <v>28.99</v>
       </c>
       <c r="L26" s="322">
         <v>16.94</v>
       </c>
-      <c r="M26" s="324">
+      <c r="M26" s="323">
         <v>28.66</v>
       </c>
       <c r="N26" s="325">
         <v>30.29</v>
       </c>
-      <c r="O26" s="319">
+      <c r="O26" s="324">
         <v>43.32</v>
       </c>
       <c r="P26" s="313">
         <v>33.55</v>
       </c>
-      <c r="Q26" s="320">
+      <c r="Q26" s="314">
         <v>25.08</v>
       </c>
-      <c r="R26" s="321">
+      <c r="R26" s="319">
         <v>29.97</v>
       </c>
-      <c r="S26" s="314">
+      <c r="S26" s="315">
         <v>21.5</v>
       </c>
-      <c r="T26" s="315">
+      <c r="T26" s="320">
         <v>2.61</v>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       <c r="C27" t="str">
         <v>601011</v>
       </c>
-      <c r="D27" s="334" t="str">
+      <c r="D27" s="331" t="str">
         <v>净卖: -659.33万</v>
       </c>
       <c r="E27">
@@ -10247,40 +10247,40 @@
       <c r="H27">
         <v>10.09</v>
       </c>
-      <c r="I27" s="329">
+      <c r="I27" s="332">
         <v>0</v>
       </c>
-      <c r="J27" s="330">
+      <c r="J27" s="333">
         <v>10</v>
       </c>
-      <c r="K27" s="326">
+      <c r="K27" s="335">
         <v>-0.28</v>
       </c>
-      <c r="L27" s="335">
+      <c r="L27" s="337">
         <v>9.72</v>
       </c>
       <c r="M27" s="336">
         <v>11.11</v>
       </c>
-      <c r="N27" s="327">
+      <c r="N27" s="338">
         <v>22.22</v>
       </c>
-      <c r="O27" s="328">
+      <c r="O27" s="326">
         <v>13.89</v>
       </c>
-      <c r="P27" s="333">
+      <c r="P27" s="328">
         <v>6.67</v>
       </c>
-      <c r="Q27" s="337">
+      <c r="Q27" s="327">
         <v>10.83</v>
       </c>
-      <c r="R27" s="338">
+      <c r="R27" s="329">
         <v>3.61</v>
       </c>
-      <c r="S27" s="331">
+      <c r="S27" s="334">
         <v>4.17</v>
       </c>
-      <c r="T27" s="332">
+      <c r="T27" s="330">
         <v>-12.5</v>
       </c>
     </row>
@@ -10294,7 +10294,7 @@
       <c r="C28" t="str">
         <v>920765</v>
       </c>
-      <c r="D28" s="343" t="str">
+      <c r="D28" s="351" t="str">
         <v>净卖: -291.63万</v>
       </c>
       <c r="E28">
@@ -10309,40 +10309,40 @@
       <c r="H28">
         <v>-0.26</v>
       </c>
-      <c r="I28" s="339">
+      <c r="I28" s="347">
         <v>21.66</v>
       </c>
-      <c r="J28" s="344">
+      <c r="J28" s="348">
         <v>16.41</v>
       </c>
-      <c r="K28" s="350">
+      <c r="K28" s="340">
         <v>26.65</v>
       </c>
-      <c r="L28" s="340">
+      <c r="L28" s="341">
         <v>21.66</v>
       </c>
-      <c r="M28" s="347">
+      <c r="M28" s="343">
         <v>16.11</v>
       </c>
-      <c r="N28" s="351">
+      <c r="N28" s="349">
         <v>14.53</v>
       </c>
-      <c r="O28" s="348">
+      <c r="O28" s="344">
         <v>11.07</v>
       </c>
-      <c r="P28" s="341">
+      <c r="P28" s="345">
         <v>10.15</v>
       </c>
-      <c r="Q28" s="345">
+      <c r="Q28" s="342">
         <v>9.63</v>
       </c>
-      <c r="R28" s="346">
+      <c r="R28" s="350">
         <v>8.67</v>
       </c>
-      <c r="S28" s="349">
+      <c r="S28" s="346">
         <v>9.1</v>
       </c>
-      <c r="T28" s="342">
+      <c r="T28" s="339">
         <v>-33.7</v>
       </c>
     </row>
@@ -10371,40 +10371,40 @@
       <c r="H29">
         <v>16.03</v>
       </c>
-      <c r="I29" s="359">
+      <c r="I29" s="360">
         <v>3.42</v>
       </c>
       <c r="J29" s="355">
         <v>1.23</v>
       </c>
-      <c r="K29" s="364">
+      <c r="K29" s="362">
         <v>10.14</v>
       </c>
-      <c r="L29" s="358">
+      <c r="L29" s="356">
         <v>-0.87</v>
       </c>
-      <c r="M29" s="352">
+      <c r="M29" s="357">
         <v>5.63</v>
       </c>
-      <c r="N29" s="360">
+      <c r="N29" s="364">
         <v>-0.83</v>
       </c>
-      <c r="O29" s="361">
+      <c r="O29" s="358">
         <v>-0.62</v>
       </c>
-      <c r="P29" s="362">
+      <c r="P29" s="352">
         <v>-6.58</v>
       </c>
-      <c r="Q29" s="353">
+      <c r="Q29" s="361">
         <v>-16.49</v>
       </c>
-      <c r="R29" s="356">
+      <c r="R29" s="353">
         <v>-10.75</v>
       </c>
-      <c r="S29" s="354">
+      <c r="S29" s="359">
         <v>0.63</v>
       </c>
-      <c r="T29" s="357">
+      <c r="T29" s="354">
         <v>6.31</v>
       </c>
     </row>
@@ -10418,7 +10418,7 @@
       <c r="C30" t="str">
         <v>603130</v>
       </c>
-      <c r="D30" s="374" t="str">
+      <c r="D30" s="373" t="str">
         <v>净买: 297.33万</v>
       </c>
       <c r="E30">
@@ -10433,16 +10433,16 @@
       <c r="H30">
         <v>-0.93</v>
       </c>
-      <c r="I30" s="375">
+      <c r="I30" s="370">
         <v>-8.65</v>
       </c>
-      <c r="J30" s="372">
+      <c r="J30" s="374">
         <v>-3.96</v>
       </c>
-      <c r="K30" s="366">
+      <c r="K30" s="375">
         <v>-6.7</v>
       </c>
-      <c r="L30" s="376">
+      <c r="L30" s="366">
         <v>-2.84</v>
       </c>
       <c r="M30" s="367">
@@ -10451,22 +10451,22 @@
       <c r="N30" s="368">
         <v>-7.23</v>
       </c>
-      <c r="O30" s="370">
+      <c r="O30" s="371">
         <v>-9.19</v>
       </c>
-      <c r="P30" s="369">
+      <c r="P30" s="376">
         <v>-11.19</v>
       </c>
-      <c r="Q30" s="373">
+      <c r="Q30" s="377">
         <v>-10.76</v>
       </c>
-      <c r="R30" s="377">
+      <c r="R30" s="372">
         <v>-1.83</v>
       </c>
       <c r="S30" s="365">
         <v>2.97</v>
       </c>
-      <c r="T30" s="371">
+      <c r="T30" s="369">
         <v>2.64</v>
       </c>
     </row>
@@ -10480,7 +10480,7 @@
       <c r="C31" t="str">
         <v>000695</v>
       </c>
-      <c r="D31" s="385" t="str">
+      <c r="D31" s="384" t="str">
         <v>净买: 1731.47万</v>
       </c>
       <c r="E31">
@@ -10495,40 +10495,40 @@
       <c r="H31">
         <v>-2.44</v>
       </c>
-      <c r="I31" s="386">
+      <c r="I31" s="388">
         <v>-7.67</v>
       </c>
-      <c r="J31" s="382">
+      <c r="J31" s="389">
         <v>-10.54</v>
       </c>
-      <c r="K31" s="379">
+      <c r="K31" s="385">
         <v>-16.08</v>
       </c>
-      <c r="L31" s="383">
+      <c r="L31" s="390">
         <v>-21.88</v>
       </c>
-      <c r="M31" s="388">
+      <c r="M31" s="380">
         <v>-23.96</v>
       </c>
-      <c r="N31" s="389">
+      <c r="N31" s="386">
         <v>-24.6</v>
       </c>
-      <c r="O31" s="390">
+      <c r="O31" s="383">
         <v>-28.17</v>
       </c>
-      <c r="P31" s="384">
+      <c r="P31" s="387">
         <v>-28.81</v>
       </c>
-      <c r="Q31" s="380">
+      <c r="Q31" s="381">
         <v>-30.62</v>
       </c>
-      <c r="R31" s="381">
+      <c r="R31" s="382">
         <v>-32.37</v>
       </c>
       <c r="S31" s="378">
         <v>-32.16</v>
       </c>
-      <c r="T31" s="387">
+      <c r="T31" s="379">
         <v>-20.18</v>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       <c r="C32" t="str">
         <v>920407</v>
       </c>
-      <c r="D32" s="395" t="str">
+      <c r="D32" s="403" t="str">
         <v>净买: 722.34万</v>
       </c>
       <c r="E32">
@@ -10557,40 +10557,40 @@
       <c r="H32">
         <v>1.28</v>
       </c>
-      <c r="I32" s="393">
+      <c r="I32" s="399">
         <v>28.31</v>
       </c>
-      <c r="J32" s="397">
+      <c r="J32" s="395">
         <v>29.11</v>
       </c>
-      <c r="K32" s="401">
+      <c r="K32" s="391">
         <v>15.45</v>
       </c>
-      <c r="L32" s="398">
+      <c r="L32" s="396">
         <v>17.04</v>
       </c>
-      <c r="M32" s="399">
+      <c r="M32" s="397">
         <v>25.35</v>
       </c>
-      <c r="N32" s="396">
+      <c r="N32" s="392">
         <v>62.96</v>
       </c>
-      <c r="O32" s="402">
+      <c r="O32" s="398">
         <v>42.07</v>
       </c>
-      <c r="P32" s="400">
+      <c r="P32" s="393">
         <v>32.35</v>
       </c>
-      <c r="Q32" s="403">
+      <c r="Q32" s="400">
         <v>36.62</v>
       </c>
-      <c r="R32" s="391">
+      <c r="R32" s="401">
         <v>27.7</v>
       </c>
-      <c r="S32" s="392">
+      <c r="S32" s="394">
         <v>27.7</v>
       </c>
-      <c r="T32" s="394">
+      <c r="T32" s="402">
         <v>-11.78</v>
       </c>
     </row>
@@ -10604,7 +10604,7 @@
       <c r="C33" t="str">
         <v>920765</v>
       </c>
-      <c r="D33" s="406" t="str">
+      <c r="D33" s="407" t="str">
         <v>净卖: -3268.70万</v>
       </c>
       <c r="E33">
@@ -10619,40 +10619,40 @@
       <c r="H33">
         <v>-10.08</v>
       </c>
-      <c r="I33" s="407">
+      <c r="I33" s="411">
         <v>2.35</v>
       </c>
-      <c r="J33" s="411">
+      <c r="J33" s="412">
         <v>-1.45</v>
       </c>
-      <c r="K33" s="412">
+      <c r="K33" s="415">
         <v>-5.92</v>
       </c>
-      <c r="L33" s="413">
+      <c r="L33" s="416">
         <v>-10.71</v>
       </c>
-      <c r="M33" s="408">
+      <c r="M33" s="413">
         <v>-10.51</v>
       </c>
-      <c r="N33" s="409">
+      <c r="N33" s="408">
         <v>-12.16</v>
       </c>
-      <c r="O33" s="415">
+      <c r="O33" s="404">
         <v>-14.08</v>
       </c>
-      <c r="P33" s="410">
+      <c r="P33" s="405">
         <v>-16.59</v>
       </c>
-      <c r="Q33" s="404">
+      <c r="Q33" s="406">
         <v>-19.14</v>
       </c>
-      <c r="R33" s="414">
+      <c r="R33" s="409">
         <v>-18.63</v>
       </c>
-      <c r="S33" s="405">
+      <c r="S33" s="414">
         <v>-18.86</v>
       </c>
-      <c r="T33" s="416">
+      <c r="T33" s="410">
         <v>-40.59</v>
       </c>
     </row>
@@ -10666,7 +10666,7 @@
       <c r="C34" t="str">
         <v>603458</v>
       </c>
-      <c r="D34" s="424" t="str">
+      <c r="D34" s="427" t="str">
         <v>净买: 2084.50万</v>
       </c>
       <c r="E34">
@@ -10681,40 +10681,40 @@
       <c r="H34">
         <v>5.37</v>
       </c>
-      <c r="I34" s="429">
+      <c r="I34" s="423">
         <v>4.4</v>
       </c>
-      <c r="J34" s="425">
+      <c r="J34" s="421">
         <v>0.2</v>
       </c>
-      <c r="K34" s="417">
+      <c r="K34" s="428">
         <v>10.2</v>
       </c>
-      <c r="L34" s="426">
+      <c r="L34" s="424">
         <v>14</v>
       </c>
-      <c r="M34" s="428">
+      <c r="M34" s="429">
         <v>13.9</v>
       </c>
-      <c r="N34" s="418">
+      <c r="N34" s="417">
         <v>20.5</v>
       </c>
-      <c r="O34" s="427">
+      <c r="O34" s="418">
         <v>20.4</v>
       </c>
-      <c r="P34" s="421">
+      <c r="P34" s="419">
         <v>21.7</v>
       </c>
-      <c r="Q34" s="419">
+      <c r="Q34" s="422">
         <v>19.2</v>
       </c>
-      <c r="R34" s="422">
+      <c r="R34" s="420">
         <v>31.1</v>
       </c>
-      <c r="S34" s="420">
+      <c r="S34" s="425">
         <v>27.9</v>
       </c>
-      <c r="T34" s="423">
+      <c r="T34" s="426">
         <v>19.5</v>
       </c>
     </row>
@@ -10728,7 +10728,7 @@
       <c r="C35" t="str">
         <v>920179</v>
       </c>
-      <c r="D35" s="436" t="str">
+      <c r="D35" s="440" t="str">
         <v>净买: 1651.86万</v>
       </c>
       <c r="E35">
@@ -10743,40 +10743,40 @@
       <c r="H35">
         <v>5.59</v>
       </c>
-      <c r="I35" s="438">
+      <c r="I35" s="437">
         <v>15.88</v>
       </c>
-      <c r="J35" s="439">
+      <c r="J35" s="434">
         <v>19.24</v>
       </c>
-      <c r="K35" s="437">
+      <c r="K35" s="441">
         <v>13.24</v>
       </c>
-      <c r="L35" s="440">
+      <c r="L35" s="435">
         <v>17.03</v>
       </c>
-      <c r="M35" s="441">
+      <c r="M35" s="430">
         <v>8.58</v>
       </c>
-      <c r="N35" s="442">
+      <c r="N35" s="438">
         <v>8.97</v>
       </c>
-      <c r="O35" s="430">
+      <c r="O35" s="431">
         <v>10.54</v>
       </c>
-      <c r="P35" s="431">
+      <c r="P35" s="436">
         <v>7.38</v>
       </c>
       <c r="Q35" s="432">
         <v>13.87</v>
       </c>
-      <c r="R35" s="433">
+      <c r="R35" s="439">
         <v>36.96</v>
       </c>
-      <c r="S35" s="434">
+      <c r="S35" s="433">
         <v>37.84</v>
       </c>
-      <c r="T35" s="435">
+      <c r="T35" s="442">
         <v>32.84</v>
       </c>
     </row>
@@ -10790,7 +10790,7 @@
       <c r="C36" t="str">
         <v>603488</v>
       </c>
-      <c r="D36" s="453" t="str">
+      <c r="D36" s="452" t="str">
         <v>净买: 3230.20万</v>
       </c>
       <c r="E36">
@@ -10805,40 +10805,40 @@
       <c r="H36">
         <v>-0.94</v>
       </c>
-      <c r="I36" s="450">
+      <c r="I36" s="448">
         <v>11.07</v>
       </c>
-      <c r="J36" s="451">
+      <c r="J36" s="445">
         <v>9.74</v>
       </c>
-      <c r="K36" s="445">
+      <c r="K36" s="449">
         <v>7.38</v>
       </c>
-      <c r="L36" s="449">
+      <c r="L36" s="455">
         <v>2.93</v>
       </c>
-      <c r="M36" s="454">
+      <c r="M36" s="453">
         <v>-3.12</v>
       </c>
-      <c r="N36" s="455">
+      <c r="N36" s="454">
         <v>-5.01</v>
       </c>
-      <c r="O36" s="446">
+      <c r="O36" s="443">
         <v>-4.92</v>
       </c>
-      <c r="P36" s="443">
+      <c r="P36" s="444">
         <v>-5.11</v>
       </c>
-      <c r="Q36" s="452">
+      <c r="Q36" s="446">
         <v>-5.3</v>
       </c>
-      <c r="R36" s="444">
+      <c r="R36" s="450">
         <v>-8.89</v>
       </c>
       <c r="S36" s="447">
         <v>0.19</v>
       </c>
-      <c r="T36" s="448">
+      <c r="T36" s="451">
         <v>5.96</v>
       </c>
     </row>
@@ -10852,7 +10852,7 @@
       <c r="C37" t="str">
         <v>688115</v>
       </c>
-      <c r="D37" s="458" t="str">
+      <c r="D37" s="459" t="str">
         <v>净买: 534.48万</v>
       </c>
       <c r="E37">
@@ -10867,40 +10867,40 @@
       <c r="H37">
         <v>-0.49</v>
       </c>
-      <c r="I37" s="465">
+      <c r="I37" s="456">
         <v>-15.96</v>
       </c>
-      <c r="J37" s="459">
+      <c r="J37" s="460">
         <v>-24.38</v>
       </c>
-      <c r="K37" s="462">
+      <c r="K37" s="466">
         <v>-27.28</v>
       </c>
-      <c r="L37" s="460">
+      <c r="L37" s="461">
         <v>-26.26</v>
       </c>
-      <c r="M37" s="466">
+      <c r="M37" s="462">
         <v>-29.33</v>
       </c>
       <c r="N37" s="467">
         <v>-33.51</v>
       </c>
-      <c r="O37" s="468">
+      <c r="O37" s="464">
         <v>-34.12</v>
       </c>
       <c r="P37" s="463">
         <v>-35.51</v>
       </c>
-      <c r="Q37" s="456">
+      <c r="Q37" s="457">
         <v>-35.8</v>
       </c>
-      <c r="R37" s="464">
+      <c r="R37" s="468">
         <v>-33.88</v>
       </c>
-      <c r="S37" s="457">
+      <c r="S37" s="458">
         <v>-35.38</v>
       </c>
-      <c r="T37" s="461">
+      <c r="T37" s="465">
         <v>-36.54</v>
       </c>
     </row>
@@ -10914,7 +10914,7 @@
       <c r="C38" t="str">
         <v>600671</v>
       </c>
-      <c r="D38" s="477" t="str">
+      <c r="D38" s="478" t="str">
         <v>净卖: -271.42万</v>
       </c>
       <c r="E38">
@@ -10929,40 +10929,40 @@
       <c r="H38">
         <v>-1.3</v>
       </c>
-      <c r="I38" s="474">
+      <c r="I38" s="479">
         <v>-8.5</v>
       </c>
-      <c r="J38" s="470">
+      <c r="J38" s="473">
         <v>-11.05</v>
       </c>
-      <c r="K38" s="471">
+      <c r="K38" s="480">
         <v>-13.41</v>
       </c>
-      <c r="L38" s="478">
+      <c r="L38" s="470">
         <v>-13.14</v>
       </c>
-      <c r="M38" s="475">
+      <c r="M38" s="474">
         <v>-15.18</v>
       </c>
-      <c r="N38" s="479">
+      <c r="N38" s="481">
         <v>-15.68</v>
       </c>
-      <c r="O38" s="476">
+      <c r="O38" s="471">
         <v>-13.05</v>
       </c>
-      <c r="P38" s="480">
+      <c r="P38" s="475">
         <v>-15.68</v>
       </c>
-      <c r="Q38" s="481">
+      <c r="Q38" s="476">
         <v>-14.45</v>
       </c>
-      <c r="R38" s="472">
+      <c r="R38" s="469">
         <v>-13.27</v>
       </c>
-      <c r="S38" s="473">
+      <c r="S38" s="477">
         <v>-11.23</v>
       </c>
-      <c r="T38" s="469">
+      <c r="T38" s="472">
         <v>-11.45</v>
       </c>
     </row>
@@ -10976,7 +10976,7 @@
       <c r="C39" t="str">
         <v>300017</v>
       </c>
-      <c r="D39" s="491" t="str">
+      <c r="D39" s="487" t="str">
         <v>净买: 3.37亿</v>
       </c>
       <c r="E39">
@@ -10991,40 +10991,40 @@
       <c r="H39">
         <v>15.07</v>
       </c>
-      <c r="I39" s="483">
+      <c r="I39" s="494">
         <v>0.06</v>
       </c>
-      <c r="J39" s="484">
+      <c r="J39" s="488">
         <v>7.83</v>
       </c>
-      <c r="K39" s="492">
+      <c r="K39" s="482">
         <v>6.29</v>
       </c>
-      <c r="L39" s="488">
+      <c r="L39" s="483">
         <v>8.34</v>
       </c>
       <c r="M39" s="489">
         <v>23.94</v>
       </c>
-      <c r="N39" s="486">
+      <c r="N39" s="484">
         <v>7.32</v>
       </c>
-      <c r="O39" s="493">
+      <c r="O39" s="490">
         <v>15.34</v>
       </c>
-      <c r="P39" s="487">
+      <c r="P39" s="491">
         <v>15.08</v>
       </c>
-      <c r="Q39" s="494">
+      <c r="Q39" s="492">
         <v>21.31</v>
       </c>
-      <c r="R39" s="482">
+      <c r="R39" s="493">
         <v>19.9</v>
       </c>
       <c r="S39" s="485">
         <v>31.26</v>
       </c>
-      <c r="T39" s="490">
+      <c r="T39" s="486">
         <v>21.31</v>
       </c>
     </row>
@@ -11087,40 +11087,40 @@
       <c r="F41" t="str"/>
       <c r="G41" t="str"/>
       <c r="H41" t="str"/>
-      <c r="I41" s="500">
+      <c r="I41" s="506">
         <v>55.26</v>
       </c>
-      <c r="J41" s="497">
+      <c r="J41" s="505">
         <v>60.53</v>
       </c>
-      <c r="K41" s="501">
+      <c r="K41" s="498">
         <v>55.26</v>
       </c>
-      <c r="L41" s="504">
+      <c r="L41" s="499">
         <v>52.63</v>
       </c>
-      <c r="M41" s="498">
+      <c r="M41" s="500">
         <v>50</v>
       </c>
-      <c r="N41" s="502">
+      <c r="N41" s="495">
         <v>44.74</v>
       </c>
-      <c r="O41" s="506">
+      <c r="O41" s="496">
         <v>44.74</v>
       </c>
-      <c r="P41" s="495">
+      <c r="P41" s="501">
         <v>50</v>
       </c>
-      <c r="Q41" s="496">
+      <c r="Q41" s="502">
         <v>44.74</v>
       </c>
-      <c r="R41" s="499">
+      <c r="R41" s="503">
         <v>39.47</v>
       </c>
-      <c r="S41" s="503">
+      <c r="S41" s="504">
         <v>50</v>
       </c>
-      <c r="T41" s="505">
+      <c r="T41" s="497">
         <v>55.26</v>
       </c>
     </row>
@@ -11135,40 +11135,40 @@
       <c r="F42" t="str"/>
       <c r="G42" t="str"/>
       <c r="H42" t="str"/>
-      <c r="I42" s="511">
+      <c r="I42" s="516">
         <v>3.07</v>
       </c>
-      <c r="J42" s="513">
+      <c r="J42" s="507">
         <v>2.73</v>
       </c>
-      <c r="K42" s="518">
+      <c r="K42" s="510">
         <v>0.67</v>
       </c>
-      <c r="L42" s="507">
+      <c r="L42" s="511">
         <v>-0.15</v>
       </c>
-      <c r="M42" s="514">
+      <c r="M42" s="512">
         <v>-0.18</v>
       </c>
       <c r="N42" s="515">
         <v>0.5</v>
       </c>
-      <c r="O42" s="516">
+      <c r="O42" s="513">
         <v>0.7</v>
       </c>
-      <c r="P42" s="509">
+      <c r="P42" s="517">
         <v>-0.65</v>
       </c>
-      <c r="Q42" s="512">
+      <c r="Q42" s="508">
         <v>-0.47</v>
       </c>
-      <c r="R42" s="517">
+      <c r="R42" s="509">
         <v>-0.13</v>
       </c>
-      <c r="S42" s="508">
+      <c r="S42" s="514">
         <v>0.43</v>
       </c>
-      <c r="T42" s="510">
+      <c r="T42" s="518">
         <v>18.24</v>
       </c>
     </row>

--- a/youzi/小鳄鱼/index.xlsx
+++ b/youzi/小鳄鱼/index.xlsx
@@ -39,37 +39,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF7D4D8"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -81,13 +111,235 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C788"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FA94B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C1C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15664"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -99,25 +351,1027 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4E0BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC969E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A712F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A143"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,55 +1383,505 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6707C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2FA94B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF76C788"/>
+        <fgColor rgb="FFE9818B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBEE4C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1E2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F2E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9858F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -189,13 +1893,1045 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CDD1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B96B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CD95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8790"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04D5B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -207,79 +2943,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4C1C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -297,817 +3003,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15664"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB4E0BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC969E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A712F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1119,1957 +3075,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A143"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBEE4C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9818B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1E2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F2E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9858F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CDD1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8790"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CD95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF54B96B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04D5B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949D"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3081,6 +3093,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCCEAD3"/>
         <bgColor/>
       </patternFill>
@@ -3093,30 +3123,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFEEF8F1"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEBF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF7D3D7"/>
         <bgColor/>
       </patternFill>
@@ -3129,19 +3141,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB9E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -8682,7 +8682,7 @@
       <c r="C2" t="str">
         <v>603881</v>
       </c>
-      <c r="D2" s="10" t="str">
+      <c r="D2" s="5" t="str">
         <v>净买: 1.27亿</v>
       </c>
       <c r="E2">
@@ -8697,40 +8697,40 @@
       <c r="H2">
         <v>8.87</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="8">
         <v>1.04</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="11">
         <v>11.14</v>
       </c>
       <c r="K2" s="3">
         <v>0.03</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="12">
         <v>7.5</v>
       </c>
-      <c r="M2" s="8">
+      <c r="M2" s="9">
         <v>8.74</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="10">
         <v>19.61</v>
       </c>
-      <c r="O2" s="11">
+      <c r="O2" s="13">
         <v>25.9</v>
       </c>
-      <c r="P2" s="4">
+      <c r="P2" s="1">
         <v>21.45</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="6">
         <v>15.56</v>
       </c>
-      <c r="R2" s="12">
+      <c r="R2" s="7">
         <v>9.81</v>
       </c>
-      <c r="S2" s="6">
+      <c r="S2" s="2">
         <v>-0.74</v>
       </c>
-      <c r="T2" s="13">
+      <c r="T2" s="4">
         <v>21.21</v>
       </c>
     </row>
@@ -8744,7 +8744,7 @@
       <c r="C3" t="str">
         <v>603881</v>
       </c>
-      <c r="D3" s="25" t="str">
+      <c r="D3" s="21" t="str">
         <v>净卖: -9150.08万</v>
       </c>
       <c r="E3">
@@ -8762,7 +8762,7 @@
       <c r="I3" s="26">
         <v>-5.7</v>
       </c>
-      <c r="J3" s="23">
+      <c r="J3" s="22">
         <v>1.34</v>
       </c>
       <c r="K3" s="14">
@@ -8771,28 +8771,28 @@
       <c r="L3" s="18">
         <v>12.77</v>
       </c>
-      <c r="M3" s="19">
+      <c r="M3" s="23">
         <v>18.69</v>
       </c>
-      <c r="N3" s="21">
+      <c r="N3" s="16">
         <v>14.5</v>
       </c>
-      <c r="O3" s="15">
+      <c r="O3" s="19">
         <v>8.94</v>
       </c>
-      <c r="P3" s="16">
+      <c r="P3" s="24">
         <v>3.52</v>
       </c>
-      <c r="Q3" s="20">
+      <c r="Q3" s="17">
         <v>-6.42</v>
       </c>
-      <c r="R3" s="22">
+      <c r="R3" s="25">
         <v>-4.83</v>
       </c>
-      <c r="S3" s="24">
+      <c r="S3" s="15">
         <v>-3.18</v>
       </c>
-      <c r="T3" s="17">
+      <c r="T3" s="20">
         <v>14.27</v>
       </c>
     </row>
@@ -8806,7 +8806,7 @@
       <c r="C4" t="str">
         <v>603511</v>
       </c>
-      <c r="D4" s="35" t="str">
+      <c r="D4" s="38" t="str">
         <v>净卖: -457.10万</v>
       </c>
       <c r="E4">
@@ -8821,40 +8821,40 @@
       <c r="H4">
         <v>0.22</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="32">
         <v>9.8</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="39">
         <v>13.04</v>
       </c>
-      <c r="K4" s="39">
+      <c r="K4" s="35">
         <v>17.87</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="27">
         <v>11.31</v>
       </c>
-      <c r="M4" s="27">
+      <c r="M4" s="36">
         <v>12.39</v>
       </c>
-      <c r="N4" s="33">
+      <c r="N4" s="28">
         <v>15.13</v>
       </c>
-      <c r="O4" s="38">
+      <c r="O4" s="29">
         <v>7.93</v>
       </c>
-      <c r="P4" s="28">
+      <c r="P4" s="30">
         <v>8.36</v>
       </c>
-      <c r="Q4" s="36">
+      <c r="Q4" s="33">
         <v>9.44</v>
       </c>
-      <c r="R4" s="37">
+      <c r="R4" s="34">
         <v>11.38</v>
       </c>
-      <c r="S4" s="34">
+      <c r="S4" s="31">
         <v>11.1</v>
       </c>
-      <c r="T4" s="29">
+      <c r="T4" s="37">
         <v>1.51</v>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       <c r="C5" t="str">
         <v>002639</v>
       </c>
-      <c r="D5" s="42" t="str">
+      <c r="D5" s="52" t="str">
         <v>净买: 6286.22万</v>
       </c>
       <c r="E5">
@@ -8889,34 +8889,34 @@
       <c r="J5" s="43">
         <v>12.21</v>
       </c>
-      <c r="K5" s="50">
+      <c r="K5" s="48">
         <v>5.32</v>
       </c>
       <c r="L5" s="49">
         <v>15.84</v>
       </c>
-      <c r="M5" s="51">
+      <c r="M5" s="44">
         <v>10.91</v>
       </c>
-      <c r="N5" s="52">
+      <c r="N5" s="50">
         <v>18.96</v>
       </c>
-      <c r="O5" s="44">
+      <c r="O5" s="40">
         <v>22.6</v>
       </c>
       <c r="P5" s="45">
         <v>15.71</v>
       </c>
-      <c r="Q5" s="46">
+      <c r="Q5" s="41">
         <v>4.16</v>
       </c>
-      <c r="R5" s="40">
+      <c r="R5" s="46">
         <v>-6.23</v>
       </c>
-      <c r="S5" s="41">
+      <c r="S5" s="51">
         <v>-8.18</v>
       </c>
-      <c r="T5" s="48">
+      <c r="T5" s="42">
         <v>151.69</v>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
       <c r="C6" t="str">
         <v>603226</v>
       </c>
-      <c r="D6" s="59" t="str">
+      <c r="D6" s="58" t="str">
         <v>净卖: -590.66万</v>
       </c>
       <c r="E6">
@@ -8945,40 +8945,40 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="63">
+      <c r="I6" s="65">
         <v>10.05</v>
       </c>
-      <c r="J6" s="60">
+      <c r="J6" s="53">
         <v>4.08</v>
       </c>
-      <c r="K6" s="56">
+      <c r="K6" s="54">
         <v>4.08</v>
       </c>
-      <c r="L6" s="64">
+      <c r="L6" s="59">
         <v>4.08</v>
       </c>
-      <c r="M6" s="65">
+      <c r="M6" s="60">
         <v>7.06</v>
       </c>
-      <c r="N6" s="57">
+      <c r="N6" s="61">
         <v>5.02</v>
       </c>
-      <c r="O6" s="53">
+      <c r="O6" s="62">
         <v>-5.49</v>
       </c>
-      <c r="P6" s="54">
+      <c r="P6" s="63">
         <v>-14.6</v>
       </c>
-      <c r="Q6" s="58">
+      <c r="Q6" s="57">
         <v>-9.26</v>
       </c>
-      <c r="R6" s="61">
+      <c r="R6" s="64">
         <v>-5.81</v>
       </c>
       <c r="S6" s="55">
         <v>3.61</v>
       </c>
-      <c r="T6" s="62">
+      <c r="T6" s="56">
         <v>530.3</v>
       </c>
     </row>
@@ -8992,7 +8992,7 @@
       <c r="C7" t="str">
         <v>603011</v>
       </c>
-      <c r="D7" s="73" t="str">
+      <c r="D7" s="71" t="str">
         <v>净卖: -2450.00万</v>
       </c>
       <c r="E7">
@@ -9007,40 +9007,40 @@
       <c r="H7">
         <v>-0.78</v>
       </c>
-      <c r="I7" s="74">
+      <c r="I7" s="67">
         <v>10.9</v>
       </c>
-      <c r="J7" s="67">
+      <c r="J7" s="76">
         <v>5.29</v>
       </c>
-      <c r="K7" s="75">
+      <c r="K7" s="72">
         <v>-1.74</v>
       </c>
-      <c r="L7" s="71">
+      <c r="L7" s="73">
         <v>-11.53</v>
       </c>
-      <c r="M7" s="68">
+      <c r="M7" s="77">
         <v>-20.38</v>
       </c>
-      <c r="N7" s="69">
+      <c r="N7" s="68">
         <v>-24.17</v>
       </c>
-      <c r="O7" s="78">
+      <c r="O7" s="74">
         <v>-21.8</v>
       </c>
-      <c r="P7" s="76">
+      <c r="P7" s="75">
         <v>-20.46</v>
       </c>
-      <c r="Q7" s="70">
+      <c r="Q7" s="78">
         <v>-12.48</v>
       </c>
-      <c r="R7" s="77">
+      <c r="R7" s="66">
         <v>-15.24</v>
       </c>
-      <c r="S7" s="66">
+      <c r="S7" s="69">
         <v>-22.12</v>
       </c>
-      <c r="T7" s="72">
+      <c r="T7" s="70">
         <v>72.51</v>
       </c>
     </row>
@@ -9054,7 +9054,7 @@
       <c r="C8" t="str">
         <v>000989</v>
       </c>
-      <c r="D8" s="87" t="str">
+      <c r="D8" s="85" t="str">
         <v>净卖: -4522.23万</v>
       </c>
       <c r="E8">
@@ -9069,40 +9069,40 @@
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="88">
+      <c r="I8" s="86">
         <v>-6.8</v>
       </c>
-      <c r="J8" s="89">
+      <c r="J8" s="91">
         <v>-8.95</v>
       </c>
-      <c r="K8" s="81">
+      <c r="K8" s="79">
         <v>-12.73</v>
       </c>
-      <c r="L8" s="82">
+      <c r="L8" s="87">
         <v>-12.41</v>
       </c>
-      <c r="M8" s="83">
+      <c r="M8" s="88">
         <v>-9.82</v>
       </c>
-      <c r="N8" s="90">
+      <c r="N8" s="89">
         <v>-6.8</v>
       </c>
-      <c r="O8" s="91">
+      <c r="O8" s="80">
         <v>-1.29</v>
       </c>
-      <c r="P8" s="79">
+      <c r="P8" s="82">
         <v>-3.78</v>
       </c>
-      <c r="Q8" s="84">
+      <c r="Q8" s="81">
         <v>-6.36</v>
       </c>
-      <c r="R8" s="85">
+      <c r="R8" s="90">
         <v>-5.83</v>
       </c>
-      <c r="S8" s="80">
+      <c r="S8" s="83">
         <v>-8.2</v>
       </c>
-      <c r="T8" s="86">
+      <c r="T8" s="84">
         <v>2.59</v>
       </c>
     </row>
@@ -9116,7 +9116,7 @@
       <c r="C9" t="str">
         <v>603488</v>
       </c>
-      <c r="D9" s="102" t="str">
+      <c r="D9" s="104" t="str">
         <v>净卖: -414.45万</v>
       </c>
       <c r="E9">
@@ -9131,40 +9131,40 @@
       <c r="H9">
         <v>-0.82</v>
       </c>
-      <c r="I9" s="98">
+      <c r="I9" s="102">
         <v>10.89</v>
       </c>
-      <c r="J9" s="99">
+      <c r="J9" s="103">
         <v>2.01</v>
       </c>
-      <c r="K9" s="103">
+      <c r="K9" s="100">
         <v>-0.12</v>
       </c>
-      <c r="L9" s="104">
+      <c r="L9" s="96">
         <v>-4.5</v>
       </c>
-      <c r="M9" s="93">
+      <c r="M9" s="101">
         <v>-4.73</v>
       </c>
-      <c r="N9" s="92">
+      <c r="N9" s="97">
         <v>-6.27</v>
       </c>
-      <c r="O9" s="100">
+      <c r="O9" s="98">
         <v>-5.56</v>
       </c>
-      <c r="P9" s="94">
+      <c r="P9" s="92">
         <v>-9.11</v>
       </c>
-      <c r="Q9" s="95">
+      <c r="Q9" s="93">
         <v>-8.52</v>
       </c>
-      <c r="R9" s="101">
+      <c r="R9" s="94">
         <v>-7.1</v>
       </c>
-      <c r="S9" s="96">
+      <c r="S9" s="95">
         <v>-7.81</v>
       </c>
-      <c r="T9" s="97">
+      <c r="T9" s="99">
         <v>32.54</v>
       </c>
     </row>
@@ -9178,7 +9178,7 @@
       <c r="C10" t="str">
         <v>603429</v>
       </c>
-      <c r="D10" s="113" t="str">
+      <c r="D10" s="109" t="str">
         <v>净卖: -775.14万</v>
       </c>
       <c r="E10">
@@ -9193,40 +9193,40 @@
       <c r="H10">
         <v>-0.46</v>
       </c>
-      <c r="I10" s="112">
+      <c r="I10" s="110">
         <v>-9.58</v>
       </c>
-      <c r="J10" s="105">
+      <c r="J10" s="114">
         <v>-17.02</v>
       </c>
-      <c r="K10" s="106">
+      <c r="K10" s="105">
         <v>-15.53</v>
       </c>
-      <c r="L10" s="107">
+      <c r="L10" s="111">
         <v>-17.02</v>
       </c>
-      <c r="M10" s="114">
+      <c r="M10" s="106">
         <v>-25.3</v>
       </c>
-      <c r="N10" s="108">
+      <c r="N10" s="107">
         <v>-26.33</v>
       </c>
-      <c r="O10" s="109">
+      <c r="O10" s="108">
         <v>-22.79</v>
       </c>
-      <c r="P10" s="115">
+      <c r="P10" s="112">
         <v>-22.7</v>
       </c>
-      <c r="Q10" s="116">
+      <c r="Q10" s="115">
         <v>-24.47</v>
       </c>
-      <c r="R10" s="110">
+      <c r="R10" s="113">
         <v>-23.91</v>
       </c>
-      <c r="S10" s="117">
+      <c r="S10" s="116">
         <v>-24.74</v>
       </c>
-      <c r="T10" s="111">
+      <c r="T10" s="117">
         <v>-7.16</v>
       </c>
     </row>
@@ -9240,7 +9240,7 @@
       <c r="C11" t="str">
         <v>600735</v>
       </c>
-      <c r="D11" s="121" t="str">
+      <c r="D11" s="123" t="str">
         <v>净买: 1079.52万</v>
       </c>
       <c r="E11">
@@ -9255,40 +9255,40 @@
       <c r="H11">
         <v>-5.01</v>
       </c>
-      <c r="I11" s="122">
+      <c r="I11" s="124">
         <v>5.4</v>
       </c>
-      <c r="J11" s="123">
+      <c r="J11" s="129">
         <v>4.08</v>
       </c>
-      <c r="K11" s="124">
+      <c r="K11" s="118">
         <v>1.32</v>
       </c>
-      <c r="L11" s="127">
+      <c r="L11" s="125">
         <v>2.37</v>
       </c>
       <c r="M11" s="130">
         <v>7.64</v>
       </c>
-      <c r="N11" s="118">
+      <c r="N11" s="119">
         <v>6.19</v>
       </c>
-      <c r="O11" s="119">
+      <c r="O11" s="126">
         <v>3.43</v>
       </c>
-      <c r="P11" s="128">
+      <c r="P11" s="127">
         <v>8.7</v>
       </c>
-      <c r="Q11" s="125">
+      <c r="Q11" s="121">
         <v>10.28</v>
       </c>
-      <c r="R11" s="129">
+      <c r="R11" s="122">
         <v>6.59</v>
       </c>
-      <c r="S11" s="126">
+      <c r="S11" s="120">
         <v>3.43</v>
       </c>
-      <c r="T11" s="120">
+      <c r="T11" s="128">
         <v>-11.33</v>
       </c>
     </row>
@@ -9302,7 +9302,7 @@
       <c r="C12" t="str">
         <v>603429</v>
       </c>
-      <c r="D12" s="134" t="str">
+      <c r="D12" s="139" t="str">
         <v>净买: 2015.22万</v>
       </c>
       <c r="E12">
@@ -9317,40 +9317,40 @@
       <c r="H12">
         <v>-4.22</v>
       </c>
-      <c r="I12" s="135">
+      <c r="I12" s="133">
         <v>-4.19</v>
       </c>
-      <c r="J12" s="139">
+      <c r="J12" s="134">
         <v>-2.47</v>
       </c>
-      <c r="K12" s="141">
+      <c r="K12" s="140">
         <v>-4.19</v>
       </c>
-      <c r="L12" s="140">
+      <c r="L12" s="135">
         <v>-13.75</v>
       </c>
-      <c r="M12" s="136">
+      <c r="M12" s="141">
         <v>-14.93</v>
       </c>
       <c r="N12" s="142">
         <v>-10.85</v>
       </c>
-      <c r="O12" s="143">
+      <c r="O12" s="136">
         <v>-10.74</v>
       </c>
-      <c r="P12" s="137">
+      <c r="P12" s="143">
         <v>-12.78</v>
       </c>
-      <c r="Q12" s="132">
+      <c r="Q12" s="131">
         <v>-12.14</v>
       </c>
-      <c r="R12" s="138">
+      <c r="R12" s="132">
         <v>-13.1</v>
       </c>
-      <c r="S12" s="131">
+      <c r="S12" s="138">
         <v>-14.18</v>
       </c>
-      <c r="T12" s="133">
+      <c r="T12" s="137">
         <v>7.2</v>
       </c>
     </row>
@@ -9364,7 +9364,7 @@
       <c r="C13" t="str">
         <v>603429</v>
       </c>
-      <c r="D13" s="146" t="str">
+      <c r="D13" s="148" t="str">
         <v>净卖: -2033.97万</v>
       </c>
       <c r="E13">
@@ -9379,40 +9379,40 @@
       <c r="H13">
         <v>-0.45</v>
       </c>
-      <c r="I13" s="151">
+      <c r="I13" s="144">
         <v>-9.57</v>
       </c>
-      <c r="J13" s="155">
+      <c r="J13" s="153">
         <v>-10.81</v>
       </c>
       <c r="K13" s="149">
         <v>-6.53</v>
       </c>
-      <c r="L13" s="152">
+      <c r="L13" s="145">
         <v>-6.42</v>
       </c>
-      <c r="M13" s="156">
+      <c r="M13" s="150">
         <v>-8.56</v>
       </c>
-      <c r="N13" s="153">
+      <c r="N13" s="151">
         <v>-7.88</v>
       </c>
-      <c r="O13" s="150">
+      <c r="O13" s="146">
         <v>-8.9</v>
       </c>
-      <c r="P13" s="147">
+      <c r="P13" s="154">
         <v>-10.02</v>
       </c>
-      <c r="Q13" s="144">
+      <c r="Q13" s="155">
         <v>-8.78</v>
       </c>
-      <c r="R13" s="148">
+      <c r="R13" s="156">
         <v>-8.78</v>
       </c>
-      <c r="S13" s="145">
+      <c r="S13" s="152">
         <v>-5.86</v>
       </c>
-      <c r="T13" s="154">
+      <c r="T13" s="147">
         <v>12.39</v>
       </c>
     </row>
@@ -9426,7 +9426,7 @@
       <c r="C14" t="str">
         <v>600735</v>
       </c>
-      <c r="D14" s="165" t="str">
+      <c r="D14" s="160" t="str">
         <v>净买: 450.48万</v>
       </c>
       <c r="E14">
@@ -9441,40 +9441,40 @@
       <c r="H14">
         <v>-9.95</v>
       </c>
-      <c r="I14" s="169">
+      <c r="I14" s="161">
         <v>0</v>
       </c>
-      <c r="J14" s="166">
+      <c r="J14" s="158">
         <v>-0.12</v>
       </c>
-      <c r="K14" s="167">
+      <c r="K14" s="162">
         <v>0.6</v>
       </c>
-      <c r="L14" s="168">
+      <c r="L14" s="167">
         <v>2.04</v>
       </c>
-      <c r="M14" s="162">
+      <c r="M14" s="168">
         <v>-0.96</v>
       </c>
-      <c r="N14" s="157">
+      <c r="N14" s="169">
         <v>-3.72</v>
       </c>
-      <c r="O14" s="159">
+      <c r="O14" s="163">
         <v>2.4</v>
       </c>
-      <c r="P14" s="158">
+      <c r="P14" s="164">
         <v>2.88</v>
       </c>
-      <c r="Q14" s="163">
+      <c r="Q14" s="165">
         <v>3.48</v>
       </c>
-      <c r="R14" s="160">
+      <c r="R14" s="166">
         <v>2.76</v>
       </c>
-      <c r="S14" s="161">
+      <c r="S14" s="157">
         <v>4.32</v>
       </c>
-      <c r="T14" s="164">
+      <c r="T14" s="159">
         <v>-19.21</v>
       </c>
     </row>
@@ -9488,7 +9488,7 @@
       <c r="C15" t="str">
         <v>605198</v>
       </c>
-      <c r="D15" s="176" t="str">
+      <c r="D15" s="179" t="str">
         <v>净买: 424.10万</v>
       </c>
       <c r="E15">
@@ -9503,40 +9503,40 @@
       <c r="H15">
         <v>-3.44</v>
       </c>
-      <c r="I15" s="177">
+      <c r="I15" s="182">
         <v>-6.79</v>
       </c>
       <c r="J15" s="170">
         <v>-11.34</v>
       </c>
-      <c r="K15" s="171">
+      <c r="K15" s="178">
         <v>-12.86</v>
       </c>
-      <c r="L15" s="181">
+      <c r="L15" s="175">
         <v>-11.52</v>
       </c>
-      <c r="M15" s="173">
+      <c r="M15" s="176">
         <v>-11.25</v>
       </c>
-      <c r="N15" s="174">
+      <c r="N15" s="171">
         <v>-11.47</v>
       </c>
       <c r="O15" s="172">
         <v>-11.43</v>
       </c>
-      <c r="P15" s="182">
+      <c r="P15" s="173">
         <v>-11.41</v>
       </c>
-      <c r="Q15" s="175">
+      <c r="Q15" s="180">
         <v>-9.78</v>
       </c>
-      <c r="R15" s="178">
+      <c r="R15" s="181">
         <v>-11.65</v>
       </c>
-      <c r="S15" s="179">
+      <c r="S15" s="177">
         <v>-11.96</v>
       </c>
-      <c r="T15" s="180">
+      <c r="T15" s="174">
         <v>5.27</v>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
       <c r="C16" t="str">
         <v>600208</v>
       </c>
-      <c r="D16" s="191" t="str">
+      <c r="D16" s="185" t="str">
         <v>净卖: -1100.93万</v>
       </c>
       <c r="E16">
@@ -9565,40 +9565,40 @@
       <c r="H16">
         <v>9.93</v>
       </c>
-      <c r="I16" s="188">
+      <c r="I16" s="186">
         <v>0</v>
       </c>
       <c r="J16" s="192">
         <v>10.04</v>
       </c>
-      <c r="K16" s="184">
+      <c r="K16" s="187">
         <v>7.23</v>
       </c>
-      <c r="L16" s="183">
+      <c r="L16" s="193">
         <v>11.24</v>
       </c>
-      <c r="M16" s="185">
+      <c r="M16" s="195">
         <v>0.2</v>
       </c>
-      <c r="N16" s="193">
+      <c r="N16" s="183">
         <v>-4.42</v>
       </c>
-      <c r="O16" s="194">
+      <c r="O16" s="188">
         <v>-2.81</v>
       </c>
-      <c r="P16" s="186">
+      <c r="P16" s="189">
         <v>3.41</v>
       </c>
-      <c r="Q16" s="195">
+      <c r="Q16" s="190">
         <v>0.4</v>
       </c>
-      <c r="R16" s="187">
+      <c r="R16" s="194">
         <v>-5.82</v>
       </c>
-      <c r="S16" s="189">
+      <c r="S16" s="184">
         <v>-3.21</v>
       </c>
-      <c r="T16" s="190">
+      <c r="T16" s="191">
         <v>-28.11</v>
       </c>
     </row>
@@ -9612,7 +9612,7 @@
       <c r="C17" t="str">
         <v>600590</v>
       </c>
-      <c r="D17" s="207" t="str">
+      <c r="D17" s="202" t="str">
         <v>净买: 1371.16万</v>
       </c>
       <c r="E17">
@@ -9627,40 +9627,40 @@
       <c r="H17">
         <v>9.98</v>
       </c>
-      <c r="I17" s="198">
+      <c r="I17" s="200">
         <v>0</v>
       </c>
-      <c r="J17" s="208">
+      <c r="J17" s="206">
         <v>-3.03</v>
       </c>
-      <c r="K17" s="199">
+      <c r="K17" s="203">
         <v>-5.43</v>
       </c>
-      <c r="L17" s="203">
+      <c r="L17" s="208">
         <v>-8.3</v>
       </c>
-      <c r="M17" s="204">
+      <c r="M17" s="207">
         <v>-9.54</v>
       </c>
-      <c r="N17" s="196">
+      <c r="N17" s="204">
         <v>-11.64</v>
       </c>
-      <c r="O17" s="200">
+      <c r="O17" s="205">
         <v>-10.4</v>
       </c>
-      <c r="P17" s="201">
+      <c r="P17" s="196">
         <v>-12.57</v>
       </c>
-      <c r="Q17" s="205">
+      <c r="Q17" s="197">
         <v>-13.03</v>
       </c>
-      <c r="R17" s="197">
+      <c r="R17" s="198">
         <v>-14.82</v>
       </c>
-      <c r="S17" s="202">
+      <c r="S17" s="201">
         <v>-21.26</v>
       </c>
-      <c r="T17" s="206">
+      <c r="T17" s="199">
         <v>22.89</v>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
       <c r="C18" t="str">
         <v>000063</v>
       </c>
-      <c r="D18" s="220" t="str">
+      <c r="D18" s="216" t="str">
         <v>净买: 5.93亿</v>
       </c>
       <c r="E18">
@@ -9689,40 +9689,40 @@
       <c r="H18">
         <v>2.21</v>
       </c>
-      <c r="I18" s="216">
+      <c r="I18" s="209">
         <v>7.01</v>
       </c>
-      <c r="J18" s="219">
+      <c r="J18" s="210">
         <v>5.38</v>
       </c>
-      <c r="K18" s="213">
+      <c r="K18" s="217">
         <v>3.49</v>
       </c>
-      <c r="L18" s="214">
+      <c r="L18" s="218">
         <v>1.38</v>
       </c>
-      <c r="M18" s="217">
+      <c r="M18" s="219">
         <v>9.01</v>
       </c>
-      <c r="N18" s="221">
+      <c r="N18" s="211">
         <v>4.46</v>
       </c>
-      <c r="O18" s="209">
+      <c r="O18" s="221">
         <v>10.34</v>
       </c>
-      <c r="P18" s="210">
+      <c r="P18" s="212">
         <v>3.06</v>
       </c>
-      <c r="Q18" s="215">
+      <c r="Q18" s="220">
         <v>1.01</v>
       </c>
-      <c r="R18" s="211">
+      <c r="R18" s="213">
         <v>-6.11</v>
       </c>
-      <c r="S18" s="212">
+      <c r="S18" s="214">
         <v>-3.86</v>
       </c>
-      <c r="T18" s="218">
+      <c r="T18" s="215">
         <v>-18.78</v>
       </c>
     </row>
@@ -9736,7 +9736,7 @@
       <c r="C19" t="str">
         <v>000061</v>
       </c>
-      <c r="D19" s="223" t="str">
+      <c r="D19" s="227" t="str">
         <v>净买: 2178.30万</v>
       </c>
       <c r="E19">
@@ -9751,40 +9751,40 @@
       <c r="H19">
         <v>5.09</v>
       </c>
-      <c r="I19" s="227">
+      <c r="I19" s="223">
         <v>4.72</v>
       </c>
-      <c r="J19" s="228">
+      <c r="J19" s="224">
         <v>8.94</v>
       </c>
-      <c r="K19" s="233">
+      <c r="K19" s="228">
         <v>3.73</v>
       </c>
-      <c r="L19" s="224">
+      <c r="L19" s="229">
         <v>-1.99</v>
       </c>
-      <c r="M19" s="229">
+      <c r="M19" s="226">
         <v>-1.49</v>
       </c>
       <c r="N19" s="230">
         <v>-0.25</v>
       </c>
-      <c r="O19" s="234">
+      <c r="O19" s="233">
         <v>-0.12</v>
       </c>
-      <c r="P19" s="231">
+      <c r="P19" s="225">
         <v>3.11</v>
       </c>
-      <c r="Q19" s="225">
+      <c r="Q19" s="234">
         <v>4.84</v>
       </c>
-      <c r="R19" s="232">
+      <c r="R19" s="222">
         <v>15.28</v>
       </c>
-      <c r="S19" s="222">
+      <c r="S19" s="231">
         <v>14.53</v>
       </c>
-      <c r="T19" s="226">
+      <c r="T19" s="232">
         <v>-7.7</v>
       </c>
     </row>
@@ -9813,40 +9813,40 @@
       <c r="H20">
         <v>-0.85</v>
       </c>
-      <c r="I20" s="245">
+      <c r="I20" s="247">
         <v>31.1</v>
       </c>
-      <c r="J20" s="235">
+      <c r="J20" s="239">
         <v>25.62</v>
       </c>
-      <c r="K20" s="239">
+      <c r="K20" s="241">
         <v>0.1</v>
       </c>
-      <c r="L20" s="236">
+      <c r="L20" s="242">
         <v>-14.6</v>
       </c>
-      <c r="M20" s="237">
+      <c r="M20" s="243">
         <v>-15.25</v>
       </c>
-      <c r="N20" s="242">
+      <c r="N20" s="244">
         <v>-17.98</v>
       </c>
-      <c r="O20" s="243">
+      <c r="O20" s="235">
         <v>-19.46</v>
       </c>
-      <c r="P20" s="240">
+      <c r="P20" s="245">
         <v>-18.77</v>
       </c>
       <c r="Q20" s="246">
         <v>-23.13</v>
       </c>
-      <c r="R20" s="244">
+      <c r="R20" s="236">
         <v>-22.25</v>
       </c>
-      <c r="S20" s="247">
+      <c r="S20" s="237">
         <v>-22.58</v>
       </c>
-      <c r="T20" s="241">
+      <c r="T20" s="240">
         <v>-29.79</v>
       </c>
     </row>
@@ -9860,7 +9860,7 @@
       <c r="C21" t="str">
         <v>002050</v>
       </c>
-      <c r="D21" s="255" t="str">
+      <c r="D21" s="256" t="str">
         <v>净买: 2.36亿</v>
       </c>
       <c r="E21">
@@ -9875,40 +9875,40 @@
       <c r="H21">
         <v>2.54</v>
       </c>
-      <c r="I21" s="256">
+      <c r="I21" s="248">
         <v>7.27</v>
       </c>
       <c r="J21" s="257">
         <v>8.13</v>
       </c>
-      <c r="K21" s="249">
+      <c r="K21" s="255">
         <v>6.42</v>
       </c>
-      <c r="L21" s="260">
+      <c r="L21" s="249">
         <v>10.42</v>
       </c>
-      <c r="M21" s="258">
+      <c r="M21" s="250">
         <v>9.59</v>
       </c>
-      <c r="N21" s="250">
+      <c r="N21" s="251">
         <v>13.28</v>
       </c>
-      <c r="O21" s="259">
+      <c r="O21" s="258">
         <v>24.62</v>
       </c>
-      <c r="P21" s="253">
+      <c r="P21" s="259">
         <v>33.1</v>
       </c>
-      <c r="Q21" s="251">
+      <c r="Q21" s="252">
         <v>44.7</v>
       </c>
-      <c r="R21" s="254">
+      <c r="R21" s="253">
         <v>32.31</v>
       </c>
-      <c r="S21" s="248">
+      <c r="S21" s="254">
         <v>36.5</v>
       </c>
-      <c r="T21" s="252">
+      <c r="T21" s="260">
         <v>44.66</v>
       </c>
     </row>
@@ -9940,37 +9940,37 @@
       <c r="I22" s="271">
         <v>-6.68</v>
       </c>
-      <c r="J22" s="273">
+      <c r="J22" s="272">
         <v>-8.22</v>
       </c>
-      <c r="K22" s="261">
+      <c r="K22" s="263">
         <v>-10.52</v>
       </c>
-      <c r="L22" s="268">
+      <c r="L22" s="264">
         <v>-8.76</v>
       </c>
-      <c r="M22" s="262">
+      <c r="M22" s="273">
         <v>-10.37</v>
       </c>
-      <c r="N22" s="265">
+      <c r="N22" s="261">
         <v>-10.68</v>
       </c>
-      <c r="O22" s="272">
+      <c r="O22" s="268">
         <v>-12.75</v>
       </c>
-      <c r="P22" s="266">
+      <c r="P22" s="262">
         <v>-9.75</v>
       </c>
-      <c r="Q22" s="267">
+      <c r="Q22" s="265">
         <v>-0.69</v>
       </c>
-      <c r="R22" s="263">
+      <c r="R22" s="266">
         <v>-0.92</v>
       </c>
-      <c r="S22" s="269">
+      <c r="S22" s="267">
         <v>2</v>
       </c>
-      <c r="T22" s="264">
+      <c r="T22" s="269">
         <v>-23.35</v>
       </c>
     </row>
@@ -9984,7 +9984,7 @@
       <c r="C23" t="str">
         <v>002475</v>
       </c>
-      <c r="D23" s="286" t="str">
+      <c r="D23" s="284" t="str">
         <v>净买: 2.00亿</v>
       </c>
       <c r="E23">
@@ -9999,40 +9999,40 @@
       <c r="H23">
         <v>-1.85</v>
       </c>
-      <c r="I23" s="274">
+      <c r="I23" s="285">
         <v>12.08</v>
       </c>
-      <c r="J23" s="285">
+      <c r="J23" s="276">
         <v>11.67</v>
       </c>
-      <c r="K23" s="279">
+      <c r="K23" s="277">
         <v>11.74</v>
       </c>
-      <c r="L23" s="280">
+      <c r="L23" s="278">
         <v>11</v>
       </c>
       <c r="M23" s="281">
         <v>10.19</v>
       </c>
-      <c r="N23" s="276">
+      <c r="N23" s="279">
         <v>12.52</v>
       </c>
-      <c r="O23" s="282">
+      <c r="O23" s="280">
         <v>17.39</v>
       </c>
-      <c r="P23" s="277">
+      <c r="P23" s="282">
         <v>29.13</v>
       </c>
-      <c r="Q23" s="275">
+      <c r="Q23" s="286">
         <v>39.19</v>
       </c>
-      <c r="R23" s="283">
+      <c r="R23" s="274">
         <v>48.73</v>
       </c>
-      <c r="S23" s="284">
+      <c r="S23" s="275">
         <v>45.64</v>
       </c>
-      <c r="T23" s="278">
+      <c r="T23" s="283">
         <v>26.59</v>
       </c>
     </row>
@@ -10046,7 +10046,7 @@
       <c r="C24" t="str">
         <v>002146</v>
       </c>
-      <c r="D24" s="299" t="str">
+      <c r="D24" s="293" t="str">
         <v>净买: 2134.01万</v>
       </c>
       <c r="E24">
@@ -10061,40 +10061,40 @@
       <c r="H24">
         <v>0.5</v>
       </c>
-      <c r="I24" s="287">
+      <c r="I24" s="297">
         <v>-9</v>
       </c>
-      <c r="J24" s="288">
+      <c r="J24" s="294">
         <v>-11</v>
       </c>
-      <c r="K24" s="289">
+      <c r="K24" s="290">
         <v>-14.5</v>
       </c>
-      <c r="L24" s="295">
+      <c r="L24" s="298">
         <v>-17.5</v>
       </c>
-      <c r="M24" s="290">
+      <c r="M24" s="288">
         <v>-16.5</v>
       </c>
-      <c r="N24" s="297">
+      <c r="N24" s="291">
         <v>-19</v>
       </c>
-      <c r="O24" s="291">
+      <c r="O24" s="292">
         <v>-20</v>
       </c>
-      <c r="P24" s="293">
+      <c r="P24" s="299">
         <v>-19.5</v>
       </c>
-      <c r="Q24" s="294">
+      <c r="Q24" s="295">
         <v>-19.5</v>
       </c>
-      <c r="R24" s="298">
+      <c r="R24" s="287">
         <v>-19</v>
       </c>
       <c r="S24" s="296">
         <v>-18.5</v>
       </c>
-      <c r="T24" s="292">
+      <c r="T24" s="289">
         <v>-31.5</v>
       </c>
     </row>
@@ -10108,7 +10108,7 @@
       <c r="C25" t="str">
         <v>002743</v>
       </c>
-      <c r="D25" s="301" t="str">
+      <c r="D25" s="309" t="str">
         <v>净卖: -133.27万</v>
       </c>
       <c r="E25">
@@ -10123,40 +10123,40 @@
       <c r="H25">
         <v>-9.98</v>
       </c>
-      <c r="I25" s="311">
+      <c r="I25" s="310">
         <v>0</v>
       </c>
-      <c r="J25" s="309">
+      <c r="J25" s="307">
         <v>-5.83</v>
       </c>
-      <c r="K25" s="310">
+      <c r="K25" s="303">
         <v>-3.38</v>
       </c>
-      <c r="L25" s="302">
+      <c r="L25" s="311">
         <v>0.75</v>
       </c>
-      <c r="M25" s="305">
+      <c r="M25" s="312">
         <v>1.88</v>
       </c>
-      <c r="N25" s="303">
+      <c r="N25" s="300">
         <v>3.01</v>
       </c>
-      <c r="O25" s="306">
+      <c r="O25" s="304">
         <v>3.95</v>
       </c>
-      <c r="P25" s="304">
+      <c r="P25" s="301">
         <v>0.75</v>
       </c>
-      <c r="Q25" s="307">
+      <c r="Q25" s="302">
         <v>-0.19</v>
       </c>
       <c r="R25" s="308">
         <v>1.5</v>
       </c>
-      <c r="S25" s="312">
+      <c r="S25" s="305">
         <v>5.83</v>
       </c>
-      <c r="T25" s="300">
+      <c r="T25" s="306">
         <v>0</v>
       </c>
     </row>
@@ -10170,7 +10170,7 @@
       <c r="C26" t="str">
         <v>601011</v>
       </c>
-      <c r="D26" s="316" t="str">
+      <c r="D26" s="318" t="str">
         <v>净卖: -479.33万</v>
       </c>
       <c r="E26">
@@ -10185,40 +10185,40 @@
       <c r="H26">
         <v>3.37</v>
       </c>
-      <c r="I26" s="317">
+      <c r="I26" s="319">
         <v>6.51</v>
       </c>
-      <c r="J26" s="321">
+      <c r="J26" s="323">
         <v>17.26</v>
       </c>
-      <c r="K26" s="318">
+      <c r="K26" s="314">
         <v>28.99</v>
       </c>
-      <c r="L26" s="322">
+      <c r="L26" s="315">
         <v>16.94</v>
       </c>
-      <c r="M26" s="323">
+      <c r="M26" s="320">
         <v>28.66</v>
       </c>
-      <c r="N26" s="325">
+      <c r="N26" s="324">
         <v>30.29</v>
       </c>
-      <c r="O26" s="324">
+      <c r="O26" s="325">
         <v>43.32</v>
       </c>
-      <c r="P26" s="313">
+      <c r="P26" s="316">
         <v>33.55</v>
       </c>
-      <c r="Q26" s="314">
+      <c r="Q26" s="317">
         <v>25.08</v>
       </c>
-      <c r="R26" s="319">
+      <c r="R26" s="321">
         <v>29.97</v>
       </c>
-      <c r="S26" s="315">
+      <c r="S26" s="322">
         <v>21.5</v>
       </c>
-      <c r="T26" s="320">
+      <c r="T26" s="313">
         <v>2.61</v>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       <c r="C27" t="str">
         <v>601011</v>
       </c>
-      <c r="D27" s="331" t="str">
+      <c r="D27" s="336" t="str">
         <v>净卖: -659.33万</v>
       </c>
       <c r="E27">
@@ -10247,40 +10247,40 @@
       <c r="H27">
         <v>10.09</v>
       </c>
-      <c r="I27" s="332">
+      <c r="I27" s="337">
         <v>0</v>
       </c>
-      <c r="J27" s="333">
+      <c r="J27" s="338">
         <v>10</v>
       </c>
-      <c r="K27" s="335">
+      <c r="K27" s="327">
         <v>-0.28</v>
       </c>
-      <c r="L27" s="337">
+      <c r="L27" s="328">
         <v>9.72</v>
       </c>
-      <c r="M27" s="336">
+      <c r="M27" s="331">
         <v>11.11</v>
       </c>
-      <c r="N27" s="338">
+      <c r="N27" s="333">
         <v>22.22</v>
       </c>
-      <c r="O27" s="326">
+      <c r="O27" s="332">
         <v>13.89</v>
       </c>
-      <c r="P27" s="328">
+      <c r="P27" s="329">
         <v>6.67</v>
       </c>
-      <c r="Q27" s="327">
+      <c r="Q27" s="334">
         <v>10.83</v>
       </c>
-      <c r="R27" s="329">
+      <c r="R27" s="330">
         <v>3.61</v>
       </c>
-      <c r="S27" s="334">
+      <c r="S27" s="326">
         <v>4.17</v>
       </c>
-      <c r="T27" s="330">
+      <c r="T27" s="335">
         <v>-12.5</v>
       </c>
     </row>
@@ -10309,40 +10309,40 @@
       <c r="H28">
         <v>-0.26</v>
       </c>
-      <c r="I28" s="347">
+      <c r="I28" s="344">
         <v>21.66</v>
       </c>
-      <c r="J28" s="348">
+      <c r="J28" s="345">
         <v>16.41</v>
       </c>
-      <c r="K28" s="340">
+      <c r="K28" s="348">
         <v>26.65</v>
       </c>
-      <c r="L28" s="341">
+      <c r="L28" s="346">
         <v>21.66</v>
       </c>
-      <c r="M28" s="343">
+      <c r="M28" s="349">
         <v>16.11</v>
       </c>
-      <c r="N28" s="349">
+      <c r="N28" s="340">
         <v>14.53</v>
       </c>
-      <c r="O28" s="344">
+      <c r="O28" s="347">
         <v>11.07</v>
       </c>
-      <c r="P28" s="345">
+      <c r="P28" s="341">
         <v>10.15</v>
       </c>
-      <c r="Q28" s="342">
+      <c r="Q28" s="350">
         <v>9.63</v>
       </c>
-      <c r="R28" s="350">
+      <c r="R28" s="339">
         <v>8.67</v>
       </c>
-      <c r="S28" s="346">
+      <c r="S28" s="342">
         <v>9.1</v>
       </c>
-      <c r="T28" s="339">
+      <c r="T28" s="343">
         <v>-33.7</v>
       </c>
     </row>
@@ -10356,7 +10356,7 @@
       <c r="C29" t="str">
         <v>688233</v>
       </c>
-      <c r="D29" s="363" t="str">
+      <c r="D29" s="362" t="str">
         <v>净买: 4489.13万</v>
       </c>
       <c r="E29">
@@ -10371,40 +10371,40 @@
       <c r="H29">
         <v>16.03</v>
       </c>
-      <c r="I29" s="360">
+      <c r="I29" s="359">
         <v>3.42</v>
       </c>
-      <c r="J29" s="355">
+      <c r="J29" s="363">
         <v>1.23</v>
       </c>
-      <c r="K29" s="362">
+      <c r="K29" s="357">
         <v>10.14</v>
       </c>
-      <c r="L29" s="356">
+      <c r="L29" s="353">
         <v>-0.87</v>
       </c>
-      <c r="M29" s="357">
+      <c r="M29" s="354">
         <v>5.63</v>
       </c>
-      <c r="N29" s="364">
+      <c r="N29" s="358">
         <v>-0.83</v>
       </c>
-      <c r="O29" s="358">
+      <c r="O29" s="364">
         <v>-0.62</v>
       </c>
-      <c r="P29" s="352">
+      <c r="P29" s="355">
         <v>-6.58</v>
       </c>
-      <c r="Q29" s="361">
+      <c r="Q29" s="352">
         <v>-16.49</v>
       </c>
-      <c r="R29" s="353">
+      <c r="R29" s="360">
         <v>-10.75</v>
       </c>
-      <c r="S29" s="359">
+      <c r="S29" s="361">
         <v>0.63</v>
       </c>
-      <c r="T29" s="354">
+      <c r="T29" s="356">
         <v>6.31</v>
       </c>
     </row>
@@ -10418,7 +10418,7 @@
       <c r="C30" t="str">
         <v>603130</v>
       </c>
-      <c r="D30" s="373" t="str">
+      <c r="D30" s="368" t="str">
         <v>净买: 297.33万</v>
       </c>
       <c r="E30">
@@ -10433,40 +10433,40 @@
       <c r="H30">
         <v>-0.93</v>
       </c>
-      <c r="I30" s="370">
+      <c r="I30" s="376">
         <v>-8.65</v>
       </c>
-      <c r="J30" s="374">
+      <c r="J30" s="369">
         <v>-3.96</v>
       </c>
-      <c r="K30" s="375">
+      <c r="K30" s="370">
         <v>-6.7</v>
       </c>
-      <c r="L30" s="366">
+      <c r="L30" s="371">
         <v>-2.84</v>
       </c>
-      <c r="M30" s="367">
+      <c r="M30" s="372">
         <v>-5.33</v>
       </c>
-      <c r="N30" s="368">
+      <c r="N30" s="377">
         <v>-7.23</v>
       </c>
-      <c r="O30" s="371">
+      <c r="O30" s="366">
         <v>-9.19</v>
       </c>
-      <c r="P30" s="376">
+      <c r="P30" s="365">
         <v>-11.19</v>
       </c>
-      <c r="Q30" s="377">
+      <c r="Q30" s="367">
         <v>-10.76</v>
       </c>
-      <c r="R30" s="372">
+      <c r="R30" s="373">
         <v>-1.83</v>
       </c>
-      <c r="S30" s="365">
+      <c r="S30" s="374">
         <v>2.97</v>
       </c>
-      <c r="T30" s="369">
+      <c r="T30" s="375">
         <v>2.64</v>
       </c>
     </row>
@@ -10480,7 +10480,7 @@
       <c r="C31" t="str">
         <v>000695</v>
       </c>
-      <c r="D31" s="384" t="str">
+      <c r="D31" s="382" t="str">
         <v>净买: 1731.47万</v>
       </c>
       <c r="E31">
@@ -10495,37 +10495,37 @@
       <c r="H31">
         <v>-2.44</v>
       </c>
-      <c r="I31" s="388">
+      <c r="I31" s="383">
         <v>-7.67</v>
       </c>
-      <c r="J31" s="389">
+      <c r="J31" s="384">
         <v>-10.54</v>
       </c>
-      <c r="K31" s="385">
+      <c r="K31" s="387">
         <v>-16.08</v>
       </c>
-      <c r="L31" s="390">
+      <c r="L31" s="385">
         <v>-21.88</v>
       </c>
-      <c r="M31" s="380">
+      <c r="M31" s="386">
         <v>-23.96</v>
       </c>
-      <c r="N31" s="386">
+      <c r="N31" s="388">
         <v>-24.6</v>
       </c>
-      <c r="O31" s="383">
+      <c r="O31" s="389">
         <v>-28.17</v>
       </c>
-      <c r="P31" s="387">
+      <c r="P31" s="378">
         <v>-28.81</v>
       </c>
-      <c r="Q31" s="381">
+      <c r="Q31" s="380">
         <v>-30.62</v>
       </c>
-      <c r="R31" s="382">
+      <c r="R31" s="390">
         <v>-32.37</v>
       </c>
-      <c r="S31" s="378">
+      <c r="S31" s="381">
         <v>-32.16</v>
       </c>
       <c r="T31" s="379">
@@ -10542,7 +10542,7 @@
       <c r="C32" t="str">
         <v>920407</v>
       </c>
-      <c r="D32" s="403" t="str">
+      <c r="D32" s="398" t="str">
         <v>净买: 722.34万</v>
       </c>
       <c r="E32">
@@ -10557,40 +10557,40 @@
       <c r="H32">
         <v>1.28</v>
       </c>
-      <c r="I32" s="399">
+      <c r="I32" s="393">
         <v>28.31</v>
       </c>
-      <c r="J32" s="395">
+      <c r="J32" s="399">
         <v>29.11</v>
       </c>
-      <c r="K32" s="391">
+      <c r="K32" s="395">
         <v>15.45</v>
       </c>
-      <c r="L32" s="396">
+      <c r="L32" s="400">
         <v>17.04</v>
       </c>
-      <c r="M32" s="397">
+      <c r="M32" s="402">
         <v>25.35</v>
       </c>
-      <c r="N32" s="392">
+      <c r="N32" s="403">
         <v>62.96</v>
       </c>
-      <c r="O32" s="398">
+      <c r="O32" s="401">
         <v>42.07</v>
       </c>
-      <c r="P32" s="393">
+      <c r="P32" s="391">
         <v>32.35</v>
       </c>
-      <c r="Q32" s="400">
+      <c r="Q32" s="394">
         <v>36.62</v>
       </c>
-      <c r="R32" s="401">
+      <c r="R32" s="396">
         <v>27.7</v>
       </c>
-      <c r="S32" s="394">
+      <c r="S32" s="397">
         <v>27.7</v>
       </c>
-      <c r="T32" s="402">
+      <c r="T32" s="392">
         <v>-11.78</v>
       </c>
     </row>
@@ -10604,7 +10604,7 @@
       <c r="C33" t="str">
         <v>920765</v>
       </c>
-      <c r="D33" s="407" t="str">
+      <c r="D33" s="413" t="str">
         <v>净卖: -3268.70万</v>
       </c>
       <c r="E33">
@@ -10619,40 +10619,40 @@
       <c r="H33">
         <v>-10.08</v>
       </c>
-      <c r="I33" s="411">
+      <c r="I33" s="414">
         <v>2.35</v>
       </c>
-      <c r="J33" s="412">
+      <c r="J33" s="407">
         <v>-1.45</v>
       </c>
-      <c r="K33" s="415">
+      <c r="K33" s="408">
         <v>-5.92</v>
       </c>
-      <c r="L33" s="416">
+      <c r="L33" s="409">
         <v>-10.71</v>
       </c>
-      <c r="M33" s="413">
+      <c r="M33" s="410">
         <v>-10.51</v>
       </c>
-      <c r="N33" s="408">
+      <c r="N33" s="411">
         <v>-12.16</v>
       </c>
-      <c r="O33" s="404">
+      <c r="O33" s="405">
         <v>-14.08</v>
       </c>
-      <c r="P33" s="405">
+      <c r="P33" s="415">
         <v>-16.59</v>
       </c>
-      <c r="Q33" s="406">
+      <c r="Q33" s="412">
         <v>-19.14</v>
       </c>
-      <c r="R33" s="409">
+      <c r="R33" s="406">
         <v>-18.63</v>
       </c>
-      <c r="S33" s="414">
+      <c r="S33" s="416">
         <v>-18.86</v>
       </c>
-      <c r="T33" s="410">
+      <c r="T33" s="404">
         <v>-40.59</v>
       </c>
     </row>
@@ -10666,7 +10666,7 @@
       <c r="C34" t="str">
         <v>603458</v>
       </c>
-      <c r="D34" s="427" t="str">
+      <c r="D34" s="425" t="str">
         <v>净买: 2084.50万</v>
       </c>
       <c r="E34">
@@ -10681,40 +10681,40 @@
       <c r="H34">
         <v>5.37</v>
       </c>
-      <c r="I34" s="423">
+      <c r="I34" s="417">
         <v>4.4</v>
       </c>
-      <c r="J34" s="421">
+      <c r="J34" s="418">
         <v>0.2</v>
       </c>
-      <c r="K34" s="428">
+      <c r="K34" s="421">
         <v>10.2</v>
       </c>
-      <c r="L34" s="424">
+      <c r="L34" s="426">
         <v>14</v>
       </c>
-      <c r="M34" s="429">
+      <c r="M34" s="427">
         <v>13.9</v>
       </c>
-      <c r="N34" s="417">
+      <c r="N34" s="420">
         <v>20.5</v>
       </c>
-      <c r="O34" s="418">
+      <c r="O34" s="419">
         <v>20.4</v>
       </c>
-      <c r="P34" s="419">
+      <c r="P34" s="428">
         <v>21.7</v>
       </c>
       <c r="Q34" s="422">
         <v>19.2</v>
       </c>
-      <c r="R34" s="420">
+      <c r="R34" s="423">
         <v>31.1</v>
       </c>
-      <c r="S34" s="425">
+      <c r="S34" s="424">
         <v>27.9</v>
       </c>
-      <c r="T34" s="426">
+      <c r="T34" s="429">
         <v>19.5</v>
       </c>
     </row>
@@ -10728,7 +10728,7 @@
       <c r="C35" t="str">
         <v>920179</v>
       </c>
-      <c r="D35" s="440" t="str">
+      <c r="D35" s="434" t="str">
         <v>净买: 1651.86万</v>
       </c>
       <c r="E35">
@@ -10743,40 +10743,40 @@
       <c r="H35">
         <v>5.59</v>
       </c>
-      <c r="I35" s="437">
+      <c r="I35" s="440">
         <v>15.88</v>
       </c>
-      <c r="J35" s="434">
+      <c r="J35" s="441">
         <v>19.24</v>
       </c>
-      <c r="K35" s="441">
+      <c r="K35" s="442">
         <v>13.24</v>
       </c>
-      <c r="L35" s="435">
+      <c r="L35" s="438">
         <v>17.03</v>
       </c>
-      <c r="M35" s="430">
+      <c r="M35" s="431">
         <v>8.58</v>
       </c>
-      <c r="N35" s="438">
+      <c r="N35" s="432">
         <v>8.97</v>
       </c>
-      <c r="O35" s="431">
+      <c r="O35" s="435">
         <v>10.54</v>
       </c>
-      <c r="P35" s="436">
+      <c r="P35" s="430">
         <v>7.38</v>
       </c>
-      <c r="Q35" s="432">
+      <c r="Q35" s="436">
         <v>13.87</v>
       </c>
-      <c r="R35" s="439">
+      <c r="R35" s="433">
         <v>36.96</v>
       </c>
-      <c r="S35" s="433">
+      <c r="S35" s="439">
         <v>37.84</v>
       </c>
-      <c r="T35" s="442">
+      <c r="T35" s="437">
         <v>32.84</v>
       </c>
     </row>
@@ -10790,7 +10790,7 @@
       <c r="C36" t="str">
         <v>603488</v>
       </c>
-      <c r="D36" s="452" t="str">
+      <c r="D36" s="451" t="str">
         <v>净买: 3230.20万</v>
       </c>
       <c r="E36">
@@ -10805,40 +10805,40 @@
       <c r="H36">
         <v>-0.94</v>
       </c>
-      <c r="I36" s="448">
+      <c r="I36" s="452">
         <v>11.07</v>
       </c>
-      <c r="J36" s="445">
+      <c r="J36" s="446">
         <v>9.74</v>
       </c>
-      <c r="K36" s="449">
+      <c r="K36" s="454">
         <v>7.38</v>
       </c>
       <c r="L36" s="455">
         <v>2.93</v>
       </c>
-      <c r="M36" s="453">
+      <c r="M36" s="443">
         <v>-3.12</v>
       </c>
-      <c r="N36" s="454">
+      <c r="N36" s="449">
         <v>-5.01</v>
       </c>
-      <c r="O36" s="443">
+      <c r="O36" s="450">
         <v>-4.92</v>
       </c>
-      <c r="P36" s="444">
+      <c r="P36" s="447">
         <v>-5.11</v>
       </c>
-      <c r="Q36" s="446">
+      <c r="Q36" s="453">
         <v>-5.3</v>
       </c>
-      <c r="R36" s="450">
+      <c r="R36" s="444">
         <v>-8.89</v>
       </c>
-      <c r="S36" s="447">
+      <c r="S36" s="448">
         <v>0.19</v>
       </c>
-      <c r="T36" s="451">
+      <c r="T36" s="445">
         <v>5.96</v>
       </c>
     </row>
@@ -10867,40 +10867,40 @@
       <c r="H37">
         <v>-0.49</v>
       </c>
-      <c r="I37" s="456">
+      <c r="I37" s="460">
         <v>-15.96</v>
       </c>
-      <c r="J37" s="460">
+      <c r="J37" s="461">
         <v>-24.38</v>
       </c>
       <c r="K37" s="466">
         <v>-27.28</v>
       </c>
-      <c r="L37" s="461">
+      <c r="L37" s="463">
         <v>-26.26</v>
       </c>
-      <c r="M37" s="462">
+      <c r="M37" s="467">
         <v>-29.33</v>
       </c>
-      <c r="N37" s="467">
+      <c r="N37" s="456">
         <v>-33.51</v>
       </c>
       <c r="O37" s="464">
         <v>-34.12</v>
       </c>
-      <c r="P37" s="463">
+      <c r="P37" s="462">
         <v>-35.51</v>
       </c>
-      <c r="Q37" s="457">
+      <c r="Q37" s="465">
         <v>-35.8</v>
       </c>
-      <c r="R37" s="468">
+      <c r="R37" s="457">
         <v>-33.88</v>
       </c>
       <c r="S37" s="458">
         <v>-35.38</v>
       </c>
-      <c r="T37" s="465">
+      <c r="T37" s="468">
         <v>-36.54</v>
       </c>
     </row>
@@ -10914,7 +10914,7 @@
       <c r="C38" t="str">
         <v>600671</v>
       </c>
-      <c r="D38" s="478" t="str">
+      <c r="D38" s="471" t="str">
         <v>净卖: -271.42万</v>
       </c>
       <c r="E38">
@@ -10929,40 +10929,40 @@
       <c r="H38">
         <v>-1.3</v>
       </c>
-      <c r="I38" s="479">
+      <c r="I38" s="474">
         <v>-8.5</v>
       </c>
-      <c r="J38" s="473">
+      <c r="J38" s="477">
         <v>-11.05</v>
       </c>
       <c r="K38" s="480">
         <v>-13.41</v>
       </c>
-      <c r="L38" s="470">
+      <c r="L38" s="481">
         <v>-13.14</v>
       </c>
-      <c r="M38" s="474">
+      <c r="M38" s="478">
         <v>-15.18</v>
       </c>
-      <c r="N38" s="481">
+      <c r="N38" s="479">
         <v>-15.68</v>
       </c>
-      <c r="O38" s="471">
+      <c r="O38" s="469">
         <v>-13.05</v>
       </c>
       <c r="P38" s="475">
         <v>-15.68</v>
       </c>
-      <c r="Q38" s="476">
+      <c r="Q38" s="470">
         <v>-14.45</v>
       </c>
-      <c r="R38" s="469">
+      <c r="R38" s="472">
         <v>-13.27</v>
       </c>
-      <c r="S38" s="477">
+      <c r="S38" s="473">
         <v>-11.23</v>
       </c>
-      <c r="T38" s="472">
+      <c r="T38" s="476">
         <v>-11.45</v>
       </c>
     </row>
@@ -10976,7 +10976,7 @@
       <c r="C39" t="str">
         <v>300017</v>
       </c>
-      <c r="D39" s="487" t="str">
+      <c r="D39" s="493" t="str">
         <v>净买: 3.37亿</v>
       </c>
       <c r="E39">
@@ -10991,40 +10991,40 @@
       <c r="H39">
         <v>15.07</v>
       </c>
-      <c r="I39" s="494">
+      <c r="I39" s="490">
         <v>0.06</v>
       </c>
-      <c r="J39" s="488">
+      <c r="J39" s="487">
         <v>7.83</v>
       </c>
-      <c r="K39" s="482">
+      <c r="K39" s="483">
         <v>6.29</v>
       </c>
-      <c r="L39" s="483">
+      <c r="L39" s="484">
         <v>8.34</v>
       </c>
-      <c r="M39" s="489">
+      <c r="M39" s="494">
         <v>23.94</v>
       </c>
-      <c r="N39" s="484">
+      <c r="N39" s="485">
         <v>7.32</v>
       </c>
-      <c r="O39" s="490">
+      <c r="O39" s="486">
         <v>15.34</v>
       </c>
       <c r="P39" s="491">
         <v>15.08</v>
       </c>
-      <c r="Q39" s="492">
+      <c r="Q39" s="488">
         <v>21.31</v>
       </c>
-      <c r="R39" s="493">
+      <c r="R39" s="482">
         <v>19.9</v>
       </c>
-      <c r="S39" s="485">
+      <c r="S39" s="489">
         <v>31.26</v>
       </c>
-      <c r="T39" s="486">
+      <c r="T39" s="492">
         <v>21.31</v>
       </c>
     </row>
@@ -11087,40 +11087,40 @@
       <c r="F41" t="str"/>
       <c r="G41" t="str"/>
       <c r="H41" t="str"/>
-      <c r="I41" s="506">
+      <c r="I41" s="502">
         <v>55.26</v>
       </c>
-      <c r="J41" s="505">
+      <c r="J41" s="506">
         <v>60.53</v>
       </c>
-      <c r="K41" s="498">
+      <c r="K41" s="501">
         <v>55.26</v>
       </c>
-      <c r="L41" s="499">
+      <c r="L41" s="503">
         <v>52.63</v>
       </c>
-      <c r="M41" s="500">
+      <c r="M41" s="495">
         <v>50</v>
       </c>
-      <c r="N41" s="495">
+      <c r="N41" s="496">
         <v>44.74</v>
       </c>
-      <c r="O41" s="496">
+      <c r="O41" s="504">
         <v>44.74</v>
       </c>
-      <c r="P41" s="501">
+      <c r="P41" s="497">
         <v>50</v>
       </c>
-      <c r="Q41" s="502">
+      <c r="Q41" s="498">
         <v>44.74</v>
       </c>
-      <c r="R41" s="503">
+      <c r="R41" s="499">
         <v>39.47</v>
       </c>
-      <c r="S41" s="504">
+      <c r="S41" s="505">
         <v>50</v>
       </c>
-      <c r="T41" s="497">
+      <c r="T41" s="500">
         <v>55.26</v>
       </c>
     </row>
@@ -11135,40 +11135,40 @@
       <c r="F42" t="str"/>
       <c r="G42" t="str"/>
       <c r="H42" t="str"/>
-      <c r="I42" s="516">
+      <c r="I42" s="508">
         <v>3.07</v>
       </c>
-      <c r="J42" s="507">
+      <c r="J42" s="509">
         <v>2.73</v>
       </c>
       <c r="K42" s="510">
         <v>0.67</v>
       </c>
-      <c r="L42" s="511">
+      <c r="L42" s="515">
         <v>-0.15</v>
       </c>
       <c r="M42" s="512">
         <v>-0.18</v>
       </c>
-      <c r="N42" s="515">
+      <c r="N42" s="517">
         <v>0.5</v>
       </c>
-      <c r="O42" s="513">
+      <c r="O42" s="511">
         <v>0.7</v>
       </c>
-      <c r="P42" s="517">
+      <c r="P42" s="518">
         <v>-0.65</v>
       </c>
-      <c r="Q42" s="508">
+      <c r="Q42" s="513">
         <v>-0.47</v>
       </c>
-      <c r="R42" s="509">
+      <c r="R42" s="514">
         <v>-0.13</v>
       </c>
-      <c r="S42" s="514">
+      <c r="S42" s="516">
         <v>0.43</v>
       </c>
-      <c r="T42" s="518">
+      <c r="T42" s="507">
         <v>18.24</v>
       </c>
     </row>

--- a/youzi/小鳄鱼/index.xlsx
+++ b/youzi/小鳄鱼/index.xlsx
@@ -39,6 +39,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -57,6 +81,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FA94B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C788"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -75,61 +291,265 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF76C788"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15664"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4E0BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,7 +561,325 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA7AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -153,7 +891,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -165,49 +951,1975 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6707C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2FA94B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
+        <fgColor rgb="FF1A712F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE4E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A143"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBEE4C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9818B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1E2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F2E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9858F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56E79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CDD1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8790"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B96B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CD95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04D5B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -219,127 +2931,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C1C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15664"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -351,649 +2997,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB4E0BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC969E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A712F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1005,73 +3027,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFE35F6C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1083,67 +3039,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1155,79 +3057,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFEC949D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1239,1843 +3069,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A143"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9818B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBEE4C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1E2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F2E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9858F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CDD1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF54B96B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CD95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF27A343"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8790"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04D5B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3087,25 +3111,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF7EE"/>
+        <fgColor rgb="FFEEF8F1"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3117,31 +3123,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF1F9F2"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C2"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -8682,7 +8682,7 @@
       <c r="C2" t="str">
         <v>603881</v>
       </c>
-      <c r="D2" s="5" t="str">
+      <c r="D2" s="1" t="str">
         <v>净买: 1.27亿</v>
       </c>
       <c r="E2">
@@ -8703,35 +8703,35 @@
       <c r="J2" s="11">
         <v>11.14</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="7">
         <v>0.03</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="2">
         <v>7.5</v>
       </c>
       <c r="M2" s="9">
         <v>8.74</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="3">
         <v>19.61</v>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="12">
         <v>25.9</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="4">
         <v>21.45</v>
       </c>
-      <c r="Q2" s="6">
+      <c r="Q2" s="5">
         <v>15.56</v>
       </c>
-      <c r="R2" s="7">
+      <c r="R2" s="13">
         <v>9.81</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S2" s="6">
         <v>-0.74</v>
       </c>
-      <c r="T2" s="4">
-        <v>21.21</v>
+      <c r="T2" s="10">
+        <v>16.95</v>
       </c>
     </row>
     <row r="3">
@@ -8744,7 +8744,7 @@
       <c r="C3" t="str">
         <v>603881</v>
       </c>
-      <c r="D3" s="21" t="str">
+      <c r="D3" s="19" t="str">
         <v>净卖: -9150.08万</v>
       </c>
       <c r="E3">
@@ -8759,41 +8759,41 @@
       <c r="H3">
         <v>-4.56</v>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="25">
         <v>-5.7</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3" s="17">
         <v>1.34</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="23">
         <v>2.51</v>
       </c>
-      <c r="L3" s="18">
+      <c r="L3" s="26">
         <v>12.77</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="20">
         <v>18.69</v>
       </c>
-      <c r="N3" s="16">
+      <c r="N3" s="14">
         <v>14.5</v>
       </c>
-      <c r="O3" s="19">
+      <c r="O3" s="24">
         <v>8.94</v>
       </c>
-      <c r="P3" s="24">
+      <c r="P3" s="18">
         <v>3.52</v>
       </c>
-      <c r="Q3" s="17">
+      <c r="Q3" s="21">
         <v>-6.42</v>
       </c>
-      <c r="R3" s="25">
+      <c r="R3" s="15">
         <v>-4.83</v>
       </c>
-      <c r="S3" s="15">
+      <c r="S3" s="22">
         <v>-3.18</v>
       </c>
-      <c r="T3" s="20">
-        <v>14.27</v>
+      <c r="T3" s="16">
+        <v>10.25</v>
       </c>
     </row>
     <row r="4">
@@ -8806,7 +8806,7 @@
       <c r="C4" t="str">
         <v>603511</v>
       </c>
-      <c r="D4" s="38" t="str">
+      <c r="D4" s="29" t="str">
         <v>净卖: -457.10万</v>
       </c>
       <c r="E4">
@@ -8821,41 +8821,41 @@
       <c r="H4">
         <v>0.22</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="30">
         <v>9.8</v>
       </c>
-      <c r="J4" s="39">
+      <c r="J4" s="31">
         <v>13.04</v>
       </c>
-      <c r="K4" s="35">
+      <c r="K4" s="39">
         <v>17.87</v>
       </c>
       <c r="L4" s="27">
         <v>11.31</v>
       </c>
-      <c r="M4" s="36">
+      <c r="M4" s="35">
         <v>12.39</v>
       </c>
-      <c r="N4" s="28">
+      <c r="N4" s="32">
         <v>15.13</v>
       </c>
-      <c r="O4" s="29">
+      <c r="O4" s="36">
         <v>7.93</v>
       </c>
-      <c r="P4" s="30">
+      <c r="P4" s="33">
         <v>8.36</v>
       </c>
-      <c r="Q4" s="33">
+      <c r="Q4" s="37">
         <v>9.44</v>
       </c>
-      <c r="R4" s="34">
+      <c r="R4" s="38">
         <v>11.38</v>
       </c>
-      <c r="S4" s="31">
+      <c r="S4" s="34">
         <v>11.1</v>
       </c>
-      <c r="T4" s="37">
-        <v>1.51</v>
+      <c r="T4" s="28">
+        <v>2.67</v>
       </c>
     </row>
     <row r="5">
@@ -8868,7 +8868,7 @@
       <c r="C5" t="str">
         <v>002639</v>
       </c>
-      <c r="D5" s="52" t="str">
+      <c r="D5" s="41" t="str">
         <v>净买: 6286.22万</v>
       </c>
       <c r="E5">
@@ -8883,41 +8883,41 @@
       <c r="H5">
         <v>-1.66</v>
       </c>
-      <c r="I5" s="47">
+      <c r="I5" s="42">
         <v>11.82</v>
       </c>
-      <c r="J5" s="43">
+      <c r="J5" s="45">
         <v>12.21</v>
       </c>
-      <c r="K5" s="48">
+      <c r="K5" s="43">
         <v>5.32</v>
       </c>
-      <c r="L5" s="49">
+      <c r="L5" s="48">
         <v>15.84</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="46">
         <v>10.91</v>
       </c>
-      <c r="N5" s="50">
+      <c r="N5" s="51">
         <v>18.96</v>
       </c>
-      <c r="O5" s="40">
+      <c r="O5" s="52">
         <v>22.6</v>
       </c>
-      <c r="P5" s="45">
+      <c r="P5" s="49">
         <v>15.71</v>
       </c>
-      <c r="Q5" s="41">
+      <c r="Q5" s="50">
         <v>4.16</v>
       </c>
-      <c r="R5" s="46">
+      <c r="R5" s="44">
         <v>-6.23</v>
       </c>
-      <c r="S5" s="51">
+      <c r="S5" s="47">
         <v>-8.18</v>
       </c>
-      <c r="T5" s="42">
-        <v>151.69</v>
+      <c r="T5" s="40">
+        <v>160.65</v>
       </c>
     </row>
     <row r="6">
@@ -8930,7 +8930,7 @@
       <c r="C6" t="str">
         <v>603226</v>
       </c>
-      <c r="D6" s="58" t="str">
+      <c r="D6" s="57" t="str">
         <v>净卖: -590.66万</v>
       </c>
       <c r="E6">
@@ -8945,41 +8945,41 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="65">
+      <c r="I6" s="58">
         <v>10.05</v>
       </c>
-      <c r="J6" s="53">
+      <c r="J6" s="61">
         <v>4.08</v>
       </c>
-      <c r="K6" s="54">
+      <c r="K6" s="53">
         <v>4.08</v>
       </c>
       <c r="L6" s="59">
         <v>4.08</v>
       </c>
-      <c r="M6" s="60">
+      <c r="M6" s="62">
         <v>7.06</v>
       </c>
-      <c r="N6" s="61">
+      <c r="N6" s="54">
         <v>5.02</v>
       </c>
-      <c r="O6" s="62">
+      <c r="O6" s="64">
         <v>-5.49</v>
       </c>
-      <c r="P6" s="63">
+      <c r="P6" s="60">
         <v>-14.6</v>
       </c>
-      <c r="Q6" s="57">
+      <c r="Q6" s="55">
         <v>-9.26</v>
       </c>
-      <c r="R6" s="64">
+      <c r="R6" s="56">
         <v>-5.81</v>
       </c>
-      <c r="S6" s="55">
+      <c r="S6" s="63">
         <v>3.61</v>
       </c>
-      <c r="T6" s="56">
-        <v>530.3</v>
+      <c r="T6" s="65">
+        <v>507.85</v>
       </c>
     </row>
     <row r="7">
@@ -8992,7 +8992,7 @@
       <c r="C7" t="str">
         <v>603011</v>
       </c>
-      <c r="D7" s="71" t="str">
+      <c r="D7" s="78" t="str">
         <v>净卖: -2450.00万</v>
       </c>
       <c r="E7">
@@ -9007,41 +9007,41 @@
       <c r="H7">
         <v>-0.78</v>
       </c>
-      <c r="I7" s="67">
+      <c r="I7" s="66">
         <v>10.9</v>
       </c>
-      <c r="J7" s="76">
+      <c r="J7" s="74">
         <v>5.29</v>
       </c>
-      <c r="K7" s="72">
+      <c r="K7" s="67">
         <v>-1.74</v>
       </c>
-      <c r="L7" s="73">
+      <c r="L7" s="68">
         <v>-11.53</v>
       </c>
-      <c r="M7" s="77">
+      <c r="M7" s="69">
         <v>-20.38</v>
       </c>
-      <c r="N7" s="68">
+      <c r="N7" s="75">
         <v>-24.17</v>
       </c>
-      <c r="O7" s="74">
+      <c r="O7" s="70">
         <v>-21.8</v>
       </c>
-      <c r="P7" s="75">
+      <c r="P7" s="71">
         <v>-20.46</v>
       </c>
-      <c r="Q7" s="78">
+      <c r="Q7" s="76">
         <v>-12.48</v>
       </c>
-      <c r="R7" s="66">
+      <c r="R7" s="72">
         <v>-15.24</v>
       </c>
-      <c r="S7" s="69">
+      <c r="S7" s="73">
         <v>-22.12</v>
       </c>
-      <c r="T7" s="70">
-        <v>72.51</v>
+      <c r="T7" s="77">
+        <v>75.75</v>
       </c>
     </row>
     <row r="8">
@@ -9054,7 +9054,7 @@
       <c r="C8" t="str">
         <v>000989</v>
       </c>
-      <c r="D8" s="85" t="str">
+      <c r="D8" s="90" t="str">
         <v>净卖: -4522.23万</v>
       </c>
       <c r="E8">
@@ -9069,41 +9069,41 @@
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="86">
+      <c r="I8" s="81">
         <v>-6.8</v>
       </c>
-      <c r="J8" s="91">
+      <c r="J8" s="85">
         <v>-8.95</v>
       </c>
-      <c r="K8" s="79">
+      <c r="K8" s="82">
         <v>-12.73</v>
       </c>
-      <c r="L8" s="87">
+      <c r="L8" s="79">
         <v>-12.41</v>
       </c>
-      <c r="M8" s="88">
+      <c r="M8" s="86">
         <v>-9.82</v>
       </c>
-      <c r="N8" s="89">
+      <c r="N8" s="83">
         <v>-6.8</v>
       </c>
-      <c r="O8" s="80">
+      <c r="O8" s="84">
         <v>-1.29</v>
       </c>
-      <c r="P8" s="82">
+      <c r="P8" s="80">
         <v>-3.78</v>
       </c>
-      <c r="Q8" s="81">
+      <c r="Q8" s="87">
         <v>-6.36</v>
       </c>
-      <c r="R8" s="90">
+      <c r="R8" s="88">
         <v>-5.83</v>
       </c>
-      <c r="S8" s="83">
+      <c r="S8" s="91">
         <v>-8.2</v>
       </c>
-      <c r="T8" s="84">
-        <v>2.59</v>
+      <c r="T8" s="89">
+        <v>2.16</v>
       </c>
     </row>
     <row r="9">
@@ -9116,7 +9116,7 @@
       <c r="C9" t="str">
         <v>603488</v>
       </c>
-      <c r="D9" s="104" t="str">
+      <c r="D9" s="96" t="str">
         <v>净卖: -414.45万</v>
       </c>
       <c r="E9">
@@ -9131,41 +9131,41 @@
       <c r="H9">
         <v>-0.82</v>
       </c>
-      <c r="I9" s="102">
+      <c r="I9" s="100">
         <v>10.89</v>
       </c>
-      <c r="J9" s="103">
+      <c r="J9" s="92">
         <v>2.01</v>
       </c>
-      <c r="K9" s="100">
+      <c r="K9" s="97">
         <v>-0.12</v>
       </c>
-      <c r="L9" s="96">
+      <c r="L9" s="102">
         <v>-4.5</v>
       </c>
       <c r="M9" s="101">
         <v>-4.73</v>
       </c>
-      <c r="N9" s="97">
+      <c r="N9" s="103">
         <v>-6.27</v>
       </c>
-      <c r="O9" s="98">
+      <c r="O9" s="104">
         <v>-5.56</v>
       </c>
-      <c r="P9" s="92">
+      <c r="P9" s="93">
         <v>-9.11</v>
       </c>
-      <c r="Q9" s="93">
+      <c r="Q9" s="94">
         <v>-8.52</v>
       </c>
-      <c r="R9" s="94">
+      <c r="R9" s="98">
         <v>-7.1</v>
       </c>
-      <c r="S9" s="95">
+      <c r="S9" s="99">
         <v>-7.81</v>
       </c>
-      <c r="T9" s="99">
-        <v>32.54</v>
+      <c r="T9" s="95">
+        <v>33.25</v>
       </c>
     </row>
     <row r="10">
@@ -9178,7 +9178,7 @@
       <c r="C10" t="str">
         <v>603429</v>
       </c>
-      <c r="D10" s="109" t="str">
+      <c r="D10" s="112" t="str">
         <v>净卖: -775.14万</v>
       </c>
       <c r="E10">
@@ -9193,41 +9193,41 @@
       <c r="H10">
         <v>-0.46</v>
       </c>
-      <c r="I10" s="110">
+      <c r="I10" s="113">
         <v>-9.58</v>
       </c>
-      <c r="J10" s="114">
+      <c r="J10" s="108">
         <v>-17.02</v>
       </c>
-      <c r="K10" s="105">
+      <c r="K10" s="114">
         <v>-15.53</v>
       </c>
-      <c r="L10" s="111">
+      <c r="L10" s="109">
         <v>-17.02</v>
       </c>
-      <c r="M10" s="106">
+      <c r="M10" s="115">
         <v>-25.3</v>
       </c>
-      <c r="N10" s="107">
+      <c r="N10" s="110">
         <v>-26.33</v>
       </c>
-      <c r="O10" s="108">
+      <c r="O10" s="105">
         <v>-22.79</v>
       </c>
-      <c r="P10" s="112">
+      <c r="P10" s="106">
         <v>-22.7</v>
       </c>
-      <c r="Q10" s="115">
+      <c r="Q10" s="111">
         <v>-24.47</v>
       </c>
-      <c r="R10" s="113">
+      <c r="R10" s="116">
         <v>-23.91</v>
       </c>
-      <c r="S10" s="116">
+      <c r="S10" s="107">
         <v>-24.74</v>
       </c>
       <c r="T10" s="117">
-        <v>-7.16</v>
+        <v>-5.67</v>
       </c>
     </row>
     <row r="11">
@@ -9240,7 +9240,7 @@
       <c r="C11" t="str">
         <v>600735</v>
       </c>
-      <c r="D11" s="123" t="str">
+      <c r="D11" s="130" t="str">
         <v>净买: 1079.52万</v>
       </c>
       <c r="E11">
@@ -9255,40 +9255,40 @@
       <c r="H11">
         <v>-5.01</v>
       </c>
-      <c r="I11" s="124">
+      <c r="I11" s="118">
         <v>5.4</v>
       </c>
-      <c r="J11" s="129">
+      <c r="J11" s="128">
         <v>4.08</v>
       </c>
-      <c r="K11" s="118">
+      <c r="K11" s="119">
         <v>1.32</v>
       </c>
-      <c r="L11" s="125">
+      <c r="L11" s="129">
         <v>2.37</v>
       </c>
-      <c r="M11" s="130">
+      <c r="M11" s="125">
         <v>7.64</v>
       </c>
-      <c r="N11" s="119">
+      <c r="N11" s="123">
         <v>6.19</v>
       </c>
       <c r="O11" s="126">
         <v>3.43</v>
       </c>
-      <c r="P11" s="127">
+      <c r="P11" s="120">
         <v>8.7</v>
       </c>
-      <c r="Q11" s="121">
+      <c r="Q11" s="127">
         <v>10.28</v>
       </c>
-      <c r="R11" s="122">
+      <c r="R11" s="121">
         <v>6.59</v>
       </c>
-      <c r="S11" s="120">
+      <c r="S11" s="122">
         <v>3.43</v>
       </c>
-      <c r="T11" s="128">
+      <c r="T11" s="124">
         <v>-11.33</v>
       </c>
     </row>
@@ -9302,7 +9302,7 @@
       <c r="C12" t="str">
         <v>603429</v>
       </c>
-      <c r="D12" s="139" t="str">
+      <c r="D12" s="138" t="str">
         <v>净买: 2015.22万</v>
       </c>
       <c r="E12">
@@ -9317,41 +9317,41 @@
       <c r="H12">
         <v>-4.22</v>
       </c>
-      <c r="I12" s="133">
+      <c r="I12" s="136">
         <v>-4.19</v>
       </c>
-      <c r="J12" s="134">
+      <c r="J12" s="139">
         <v>-2.47</v>
       </c>
-      <c r="K12" s="140">
+      <c r="K12" s="132">
         <v>-4.19</v>
       </c>
-      <c r="L12" s="135">
+      <c r="L12" s="133">
         <v>-13.75</v>
       </c>
-      <c r="M12" s="141">
+      <c r="M12" s="140">
         <v>-14.93</v>
       </c>
-      <c r="N12" s="142">
+      <c r="N12" s="143">
         <v>-10.85</v>
       </c>
-      <c r="O12" s="136">
+      <c r="O12" s="131">
         <v>-10.74</v>
       </c>
-      <c r="P12" s="143">
+      <c r="P12" s="134">
         <v>-12.78</v>
       </c>
-      <c r="Q12" s="131">
+      <c r="Q12" s="135">
         <v>-12.14</v>
       </c>
-      <c r="R12" s="132">
+      <c r="R12" s="141">
         <v>-13.1</v>
       </c>
-      <c r="S12" s="138">
+      <c r="S12" s="137">
         <v>-14.18</v>
       </c>
-      <c r="T12" s="137">
-        <v>7.2</v>
+      <c r="T12" s="142">
+        <v>8.92</v>
       </c>
     </row>
     <row r="13">
@@ -9364,7 +9364,7 @@
       <c r="C13" t="str">
         <v>603429</v>
       </c>
-      <c r="D13" s="148" t="str">
+      <c r="D13" s="152" t="str">
         <v>净卖: -2033.97万</v>
       </c>
       <c r="E13">
@@ -9379,41 +9379,41 @@
       <c r="H13">
         <v>-0.45</v>
       </c>
-      <c r="I13" s="144">
+      <c r="I13" s="153">
         <v>-9.57</v>
       </c>
-      <c r="J13" s="153">
+      <c r="J13" s="148">
         <v>-10.81</v>
       </c>
-      <c r="K13" s="149">
+      <c r="K13" s="154">
         <v>-6.53</v>
       </c>
-      <c r="L13" s="145">
+      <c r="L13" s="155">
         <v>-6.42</v>
       </c>
-      <c r="M13" s="150">
+      <c r="M13" s="156">
         <v>-8.56</v>
       </c>
-      <c r="N13" s="151">
+      <c r="N13" s="144">
         <v>-7.88</v>
       </c>
-      <c r="O13" s="146">
+      <c r="O13" s="149">
         <v>-8.9</v>
       </c>
-      <c r="P13" s="154">
+      <c r="P13" s="145">
         <v>-10.02</v>
       </c>
-      <c r="Q13" s="155">
+      <c r="Q13" s="150">
         <v>-8.78</v>
       </c>
-      <c r="R13" s="156">
+      <c r="R13" s="151">
         <v>-8.78</v>
       </c>
-      <c r="S13" s="152">
+      <c r="S13" s="146">
         <v>-5.86</v>
       </c>
       <c r="T13" s="147">
-        <v>12.39</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="14">
@@ -9426,7 +9426,7 @@
       <c r="C14" t="str">
         <v>600735</v>
       </c>
-      <c r="D14" s="160" t="str">
+      <c r="D14" s="167" t="str">
         <v>净买: 450.48万</v>
       </c>
       <c r="E14">
@@ -9441,40 +9441,40 @@
       <c r="H14">
         <v>-9.95</v>
       </c>
-      <c r="I14" s="161">
+      <c r="I14" s="160">
         <v>0</v>
       </c>
-      <c r="J14" s="158">
+      <c r="J14" s="157">
         <v>-0.12</v>
       </c>
-      <c r="K14" s="162">
+      <c r="K14" s="158">
         <v>0.6</v>
       </c>
-      <c r="L14" s="167">
+      <c r="L14" s="168">
         <v>2.04</v>
       </c>
-      <c r="M14" s="168">
+      <c r="M14" s="161">
         <v>-0.96</v>
       </c>
-      <c r="N14" s="169">
+      <c r="N14" s="164">
         <v>-3.72</v>
       </c>
-      <c r="O14" s="163">
+      <c r="O14" s="159">
         <v>2.4</v>
       </c>
-      <c r="P14" s="164">
+      <c r="P14" s="162">
         <v>2.88</v>
       </c>
       <c r="Q14" s="165">
         <v>3.48</v>
       </c>
-      <c r="R14" s="166">
+      <c r="R14" s="163">
         <v>2.76</v>
       </c>
-      <c r="S14" s="157">
+      <c r="S14" s="169">
         <v>4.32</v>
       </c>
-      <c r="T14" s="159">
+      <c r="T14" s="166">
         <v>-19.21</v>
       </c>
     </row>
@@ -9488,7 +9488,7 @@
       <c r="C15" t="str">
         <v>605198</v>
       </c>
-      <c r="D15" s="179" t="str">
+      <c r="D15" s="177" t="str">
         <v>净买: 424.10万</v>
       </c>
       <c r="E15">
@@ -9503,41 +9503,41 @@
       <c r="H15">
         <v>-3.44</v>
       </c>
-      <c r="I15" s="182">
+      <c r="I15" s="178">
         <v>-6.79</v>
       </c>
-      <c r="J15" s="170">
+      <c r="J15" s="179">
         <v>-11.34</v>
       </c>
-      <c r="K15" s="178">
+      <c r="K15" s="180">
         <v>-12.86</v>
       </c>
-      <c r="L15" s="175">
+      <c r="L15" s="181">
         <v>-11.52</v>
       </c>
-      <c r="M15" s="176">
+      <c r="M15" s="182">
         <v>-11.25</v>
       </c>
-      <c r="N15" s="171">
+      <c r="N15" s="170">
         <v>-11.47</v>
       </c>
-      <c r="O15" s="172">
+      <c r="O15" s="171">
         <v>-11.43</v>
       </c>
       <c r="P15" s="173">
         <v>-11.41</v>
       </c>
-      <c r="Q15" s="180">
+      <c r="Q15" s="172">
         <v>-9.78</v>
       </c>
-      <c r="R15" s="181">
+      <c r="R15" s="174">
         <v>-11.65</v>
       </c>
-      <c r="S15" s="177">
+      <c r="S15" s="175">
         <v>-11.96</v>
       </c>
-      <c r="T15" s="174">
-        <v>5.27</v>
+      <c r="T15" s="176">
+        <v>0.66</v>
       </c>
     </row>
     <row r="16">
@@ -9550,7 +9550,7 @@
       <c r="C16" t="str">
         <v>600208</v>
       </c>
-      <c r="D16" s="185" t="str">
+      <c r="D16" s="189" t="str">
         <v>净卖: -1100.93万</v>
       </c>
       <c r="E16">
@@ -9565,41 +9565,41 @@
       <c r="H16">
         <v>9.93</v>
       </c>
-      <c r="I16" s="186">
+      <c r="I16" s="190">
         <v>0</v>
       </c>
-      <c r="J16" s="192">
+      <c r="J16" s="186">
         <v>10.04</v>
       </c>
       <c r="K16" s="187">
         <v>7.23</v>
       </c>
-      <c r="L16" s="193">
+      <c r="L16" s="191">
         <v>11.24</v>
       </c>
-      <c r="M16" s="195">
+      <c r="M16" s="183">
         <v>0.2</v>
       </c>
-      <c r="N16" s="183">
+      <c r="N16" s="184">
         <v>-4.42</v>
       </c>
-      <c r="O16" s="188">
+      <c r="O16" s="185">
         <v>-2.81</v>
       </c>
-      <c r="P16" s="189">
+      <c r="P16" s="192">
         <v>3.41</v>
       </c>
-      <c r="Q16" s="190">
+      <c r="Q16" s="193">
         <v>0.4</v>
       </c>
       <c r="R16" s="194">
         <v>-5.82</v>
       </c>
-      <c r="S16" s="184">
+      <c r="S16" s="195">
         <v>-3.21</v>
       </c>
-      <c r="T16" s="191">
-        <v>-28.11</v>
+      <c r="T16" s="188">
+        <v>-25.5</v>
       </c>
     </row>
     <row r="17">
@@ -9612,7 +9612,7 @@
       <c r="C17" t="str">
         <v>600590</v>
       </c>
-      <c r="D17" s="202" t="str">
+      <c r="D17" s="198" t="str">
         <v>净买: 1371.16万</v>
       </c>
       <c r="E17">
@@ -9627,41 +9627,41 @@
       <c r="H17">
         <v>9.98</v>
       </c>
-      <c r="I17" s="200">
+      <c r="I17" s="203">
         <v>0</v>
       </c>
       <c r="J17" s="206">
         <v>-3.03</v>
       </c>
-      <c r="K17" s="203">
+      <c r="K17" s="207">
         <v>-5.43</v>
       </c>
       <c r="L17" s="208">
         <v>-8.3</v>
       </c>
-      <c r="M17" s="207">
+      <c r="M17" s="199">
         <v>-9.54</v>
       </c>
-      <c r="N17" s="204">
+      <c r="N17" s="196">
         <v>-11.64</v>
       </c>
-      <c r="O17" s="205">
+      <c r="O17" s="201">
         <v>-10.4</v>
       </c>
-      <c r="P17" s="196">
+      <c r="P17" s="204">
         <v>-12.57</v>
       </c>
-      <c r="Q17" s="197">
+      <c r="Q17" s="200">
         <v>-13.03</v>
       </c>
-      <c r="R17" s="198">
+      <c r="R17" s="197">
         <v>-14.82</v>
       </c>
-      <c r="S17" s="201">
+      <c r="S17" s="202">
         <v>-21.26</v>
       </c>
-      <c r="T17" s="199">
-        <v>22.89</v>
+      <c r="T17" s="205">
+        <v>35.14</v>
       </c>
     </row>
     <row r="18">
@@ -9674,7 +9674,7 @@
       <c r="C18" t="str">
         <v>000063</v>
       </c>
-      <c r="D18" s="216" t="str">
+      <c r="D18" s="211" t="str">
         <v>净买: 5.93亿</v>
       </c>
       <c r="E18">
@@ -9689,41 +9689,41 @@
       <c r="H18">
         <v>2.21</v>
       </c>
-      <c r="I18" s="209">
+      <c r="I18" s="218">
         <v>7.01</v>
       </c>
-      <c r="J18" s="210">
+      <c r="J18" s="221">
         <v>5.38</v>
       </c>
-      <c r="K18" s="217">
+      <c r="K18" s="209">
         <v>3.49</v>
       </c>
-      <c r="L18" s="218">
+      <c r="L18" s="214">
         <v>1.38</v>
       </c>
-      <c r="M18" s="219">
+      <c r="M18" s="212">
         <v>9.01</v>
       </c>
-      <c r="N18" s="211">
+      <c r="N18" s="213">
         <v>4.46</v>
       </c>
-      <c r="O18" s="221">
+      <c r="O18" s="215">
         <v>10.34</v>
       </c>
-      <c r="P18" s="212">
+      <c r="P18" s="219">
         <v>3.06</v>
       </c>
-      <c r="Q18" s="220">
+      <c r="Q18" s="210">
         <v>1.01</v>
       </c>
-      <c r="R18" s="213">
+      <c r="R18" s="220">
         <v>-6.11</v>
       </c>
-      <c r="S18" s="214">
+      <c r="S18" s="216">
         <v>-3.86</v>
       </c>
-      <c r="T18" s="215">
-        <v>-18.78</v>
+      <c r="T18" s="217">
+        <v>-17.63</v>
       </c>
     </row>
     <row r="19">
@@ -9736,7 +9736,7 @@
       <c r="C19" t="str">
         <v>000061</v>
       </c>
-      <c r="D19" s="227" t="str">
+      <c r="D19" s="230" t="str">
         <v>净买: 2178.30万</v>
       </c>
       <c r="E19">
@@ -9751,41 +9751,41 @@
       <c r="H19">
         <v>5.09</v>
       </c>
-      <c r="I19" s="223">
+      <c r="I19" s="228">
         <v>4.72</v>
       </c>
-      <c r="J19" s="224">
+      <c r="J19" s="222">
         <v>8.94</v>
       </c>
-      <c r="K19" s="228">
+      <c r="K19" s="231">
         <v>3.73</v>
       </c>
-      <c r="L19" s="229">
+      <c r="L19" s="225">
         <v>-1.99</v>
       </c>
-      <c r="M19" s="226">
+      <c r="M19" s="232">
         <v>-1.49</v>
       </c>
-      <c r="N19" s="230">
+      <c r="N19" s="229">
         <v>-0.25</v>
       </c>
-      <c r="O19" s="233">
+      <c r="O19" s="223">
         <v>-0.12</v>
       </c>
-      <c r="P19" s="225">
+      <c r="P19" s="233">
         <v>3.11</v>
       </c>
-      <c r="Q19" s="234">
+      <c r="Q19" s="226">
         <v>4.84</v>
       </c>
-      <c r="R19" s="222">
+      <c r="R19" s="234">
         <v>15.28</v>
       </c>
-      <c r="S19" s="231">
+      <c r="S19" s="227">
         <v>14.53</v>
       </c>
-      <c r="T19" s="232">
-        <v>-7.7</v>
+      <c r="T19" s="224">
+        <v>-7.95</v>
       </c>
     </row>
     <row r="20">
@@ -9798,7 +9798,7 @@
       <c r="C20" t="str">
         <v>837174</v>
       </c>
-      <c r="D20" s="238" t="str">
+      <c r="D20" s="243" t="str">
         <v>净买: 1878.87万</v>
       </c>
       <c r="E20">
@@ -9813,40 +9813,40 @@
       <c r="H20">
         <v>-0.85</v>
       </c>
-      <c r="I20" s="247">
+      <c r="I20" s="235">
         <v>31.1</v>
       </c>
-      <c r="J20" s="239">
+      <c r="J20" s="237">
         <v>25.62</v>
       </c>
       <c r="K20" s="241">
         <v>0.1</v>
       </c>
-      <c r="L20" s="242">
+      <c r="L20" s="244">
         <v>-14.6</v>
       </c>
-      <c r="M20" s="243">
+      <c r="M20" s="236">
         <v>-15.25</v>
       </c>
-      <c r="N20" s="244">
+      <c r="N20" s="242">
         <v>-17.98</v>
       </c>
-      <c r="O20" s="235">
+      <c r="O20" s="245">
         <v>-19.46</v>
       </c>
-      <c r="P20" s="245">
+      <c r="P20" s="238">
         <v>-18.77</v>
       </c>
-      <c r="Q20" s="246">
+      <c r="Q20" s="239">
         <v>-23.13</v>
       </c>
-      <c r="R20" s="236">
+      <c r="R20" s="246">
         <v>-22.25</v>
       </c>
-      <c r="S20" s="237">
+      <c r="S20" s="240">
         <v>-22.58</v>
       </c>
-      <c r="T20" s="240">
+      <c r="T20" s="247">
         <v>-29.79</v>
       </c>
     </row>
@@ -9860,7 +9860,7 @@
       <c r="C21" t="str">
         <v>002050</v>
       </c>
-      <c r="D21" s="256" t="str">
+      <c r="D21" s="257" t="str">
         <v>净买: 2.36亿</v>
       </c>
       <c r="E21">
@@ -9875,41 +9875,41 @@
       <c r="H21">
         <v>2.54</v>
       </c>
-      <c r="I21" s="248">
+      <c r="I21" s="250">
         <v>7.27</v>
       </c>
-      <c r="J21" s="257">
+      <c r="J21" s="254">
         <v>8.13</v>
       </c>
       <c r="K21" s="255">
         <v>6.42</v>
       </c>
-      <c r="L21" s="249">
+      <c r="L21" s="251">
         <v>10.42</v>
       </c>
-      <c r="M21" s="250">
+      <c r="M21" s="256">
         <v>9.59</v>
       </c>
-      <c r="N21" s="251">
+      <c r="N21" s="252">
         <v>13.28</v>
       </c>
       <c r="O21" s="258">
         <v>24.62</v>
       </c>
-      <c r="P21" s="259">
+      <c r="P21" s="248">
         <v>33.1</v>
       </c>
-      <c r="Q21" s="252">
+      <c r="Q21" s="249">
         <v>44.7</v>
       </c>
       <c r="R21" s="253">
         <v>32.31</v>
       </c>
-      <c r="S21" s="254">
+      <c r="S21" s="259">
         <v>36.5</v>
       </c>
       <c r="T21" s="260">
-        <v>44.66</v>
+        <v>45.93</v>
       </c>
     </row>
     <row r="22">
@@ -9922,7 +9922,7 @@
       <c r="C22" t="str">
         <v>603429</v>
       </c>
-      <c r="D22" s="270" t="str">
+      <c r="D22" s="272" t="str">
         <v>净买: 1423.30万</v>
       </c>
       <c r="E22">
@@ -9937,41 +9937,41 @@
       <c r="H22">
         <v>-0.38</v>
       </c>
-      <c r="I22" s="271">
+      <c r="I22" s="269">
         <v>-6.68</v>
       </c>
-      <c r="J22" s="272">
+      <c r="J22" s="265">
         <v>-8.22</v>
       </c>
-      <c r="K22" s="263">
+      <c r="K22" s="266">
         <v>-10.52</v>
       </c>
-      <c r="L22" s="264">
+      <c r="L22" s="273">
         <v>-8.76</v>
       </c>
-      <c r="M22" s="273">
+      <c r="M22" s="267">
         <v>-10.37</v>
       </c>
-      <c r="N22" s="261">
+      <c r="N22" s="264">
         <v>-10.68</v>
       </c>
-      <c r="O22" s="268">
+      <c r="O22" s="261">
         <v>-12.75</v>
       </c>
-      <c r="P22" s="262">
+      <c r="P22" s="270">
         <v>-9.75</v>
       </c>
-      <c r="Q22" s="265">
+      <c r="Q22" s="262">
         <v>-0.69</v>
       </c>
-      <c r="R22" s="266">
+      <c r="R22" s="263">
         <v>-0.92</v>
       </c>
-      <c r="S22" s="267">
+      <c r="S22" s="268">
         <v>2</v>
       </c>
-      <c r="T22" s="269">
-        <v>-23.35</v>
+      <c r="T22" s="271">
+        <v>-22.12</v>
       </c>
     </row>
     <row r="23">
@@ -9984,7 +9984,7 @@
       <c r="C23" t="str">
         <v>002475</v>
       </c>
-      <c r="D23" s="284" t="str">
+      <c r="D23" s="285" t="str">
         <v>净买: 2.00亿</v>
       </c>
       <c r="E23">
@@ -9999,41 +9999,41 @@
       <c r="H23">
         <v>-1.85</v>
       </c>
-      <c r="I23" s="285">
+      <c r="I23" s="286">
         <v>12.08</v>
       </c>
-      <c r="J23" s="276">
+      <c r="J23" s="275">
         <v>11.67</v>
       </c>
-      <c r="K23" s="277">
+      <c r="K23" s="280">
         <v>11.74</v>
       </c>
-      <c r="L23" s="278">
+      <c r="L23" s="274">
         <v>11</v>
       </c>
-      <c r="M23" s="281">
+      <c r="M23" s="276">
         <v>10.19</v>
       </c>
-      <c r="N23" s="279">
+      <c r="N23" s="281">
         <v>12.52</v>
       </c>
-      <c r="O23" s="280">
+      <c r="O23" s="282">
         <v>17.39</v>
       </c>
-      <c r="P23" s="282">
+      <c r="P23" s="283">
         <v>29.13</v>
       </c>
-      <c r="Q23" s="286">
+      <c r="Q23" s="277">
         <v>39.19</v>
       </c>
-      <c r="R23" s="274">
+      <c r="R23" s="278">
         <v>48.73</v>
       </c>
-      <c r="S23" s="275">
+      <c r="S23" s="279">
         <v>45.64</v>
       </c>
-      <c r="T23" s="283">
-        <v>26.59</v>
+      <c r="T23" s="284">
+        <v>39.26</v>
       </c>
     </row>
     <row r="24">
@@ -10046,7 +10046,7 @@
       <c r="C24" t="str">
         <v>002146</v>
       </c>
-      <c r="D24" s="293" t="str">
+      <c r="D24" s="294" t="str">
         <v>净买: 2134.01万</v>
       </c>
       <c r="E24">
@@ -10061,41 +10061,41 @@
       <c r="H24">
         <v>0.5</v>
       </c>
-      <c r="I24" s="297">
+      <c r="I24" s="292">
         <v>-9</v>
       </c>
-      <c r="J24" s="294">
+      <c r="J24" s="298">
         <v>-11</v>
       </c>
-      <c r="K24" s="290">
+      <c r="K24" s="299">
         <v>-14.5</v>
       </c>
-      <c r="L24" s="298">
+      <c r="L24" s="287">
         <v>-17.5</v>
       </c>
       <c r="M24" s="288">
         <v>-16.5</v>
       </c>
-      <c r="N24" s="291">
+      <c r="N24" s="289">
         <v>-19</v>
       </c>
-      <c r="O24" s="292">
+      <c r="O24" s="290">
         <v>-20</v>
       </c>
-      <c r="P24" s="299">
+      <c r="P24" s="293">
         <v>-19.5</v>
       </c>
       <c r="Q24" s="295">
         <v>-19.5</v>
       </c>
-      <c r="R24" s="287">
+      <c r="R24" s="291">
         <v>-19</v>
       </c>
       <c r="S24" s="296">
         <v>-18.5</v>
       </c>
-      <c r="T24" s="289">
-        <v>-31.5</v>
+      <c r="T24" s="297">
+        <v>-32.5</v>
       </c>
     </row>
     <row r="25">
@@ -10108,7 +10108,7 @@
       <c r="C25" t="str">
         <v>002743</v>
       </c>
-      <c r="D25" s="309" t="str">
+      <c r="D25" s="303" t="str">
         <v>净卖: -133.27万</v>
       </c>
       <c r="E25">
@@ -10123,41 +10123,41 @@
       <c r="H25">
         <v>-9.98</v>
       </c>
-      <c r="I25" s="310">
+      <c r="I25" s="309">
         <v>0</v>
       </c>
-      <c r="J25" s="307">
+      <c r="J25" s="310">
         <v>-5.83</v>
       </c>
-      <c r="K25" s="303">
+      <c r="K25" s="304">
         <v>-3.38</v>
       </c>
-      <c r="L25" s="311">
+      <c r="L25" s="305">
         <v>0.75</v>
       </c>
-      <c r="M25" s="312">
+      <c r="M25" s="311">
         <v>1.88</v>
       </c>
-      <c r="N25" s="300">
+      <c r="N25" s="312">
         <v>3.01</v>
       </c>
-      <c r="O25" s="304">
+      <c r="O25" s="306">
         <v>3.95</v>
       </c>
-      <c r="P25" s="301">
+      <c r="P25" s="300">
         <v>0.75</v>
       </c>
-      <c r="Q25" s="302">
+      <c r="Q25" s="307">
         <v>-0.19</v>
       </c>
-      <c r="R25" s="308">
+      <c r="R25" s="301">
         <v>1.5</v>
       </c>
-      <c r="S25" s="305">
+      <c r="S25" s="302">
         <v>5.83</v>
       </c>
-      <c r="T25" s="306">
-        <v>0</v>
+      <c r="T25" s="308">
+        <v>0.19</v>
       </c>
     </row>
     <row r="26">
@@ -10170,7 +10170,7 @@
       <c r="C26" t="str">
         <v>601011</v>
       </c>
-      <c r="D26" s="318" t="str">
+      <c r="D26" s="324" t="str">
         <v>净卖: -479.33万</v>
       </c>
       <c r="E26">
@@ -10185,41 +10185,41 @@
       <c r="H26">
         <v>3.37</v>
       </c>
-      <c r="I26" s="319">
+      <c r="I26" s="314">
         <v>6.51</v>
       </c>
-      <c r="J26" s="323">
+      <c r="J26" s="320">
         <v>17.26</v>
       </c>
-      <c r="K26" s="314">
+      <c r="K26" s="321">
         <v>28.99</v>
       </c>
-      <c r="L26" s="315">
+      <c r="L26" s="313">
         <v>16.94</v>
       </c>
-      <c r="M26" s="320">
+      <c r="M26" s="315">
         <v>28.66</v>
       </c>
-      <c r="N26" s="324">
+      <c r="N26" s="316">
         <v>30.29</v>
       </c>
-      <c r="O26" s="325">
+      <c r="O26" s="317">
         <v>43.32</v>
       </c>
-      <c r="P26" s="316">
+      <c r="P26" s="322">
         <v>33.55</v>
       </c>
-      <c r="Q26" s="317">
+      <c r="Q26" s="318">
         <v>25.08</v>
       </c>
-      <c r="R26" s="321">
+      <c r="R26" s="325">
         <v>29.97</v>
       </c>
-      <c r="S26" s="322">
+      <c r="S26" s="319">
         <v>21.5</v>
       </c>
-      <c r="T26" s="313">
-        <v>2.61</v>
+      <c r="T26" s="323">
+        <v>3.58</v>
       </c>
     </row>
     <row r="27">
@@ -10232,7 +10232,7 @@
       <c r="C27" t="str">
         <v>601011</v>
       </c>
-      <c r="D27" s="336" t="str">
+      <c r="D27" s="330" t="str">
         <v>净卖: -659.33万</v>
       </c>
       <c r="E27">
@@ -10250,38 +10250,38 @@
       <c r="I27" s="337">
         <v>0</v>
       </c>
-      <c r="J27" s="338">
+      <c r="J27" s="326">
         <v>10</v>
       </c>
-      <c r="K27" s="327">
+      <c r="K27" s="334">
         <v>-0.28</v>
       </c>
-      <c r="L27" s="328">
+      <c r="L27" s="327">
         <v>9.72</v>
       </c>
       <c r="M27" s="331">
         <v>11.11</v>
       </c>
-      <c r="N27" s="333">
+      <c r="N27" s="335">
         <v>22.22</v>
       </c>
-      <c r="O27" s="332">
+      <c r="O27" s="328">
         <v>13.89</v>
       </c>
-      <c r="P27" s="329">
+      <c r="P27" s="336">
         <v>6.67</v>
       </c>
-      <c r="Q27" s="334">
+      <c r="Q27" s="329">
         <v>10.83</v>
       </c>
-      <c r="R27" s="330">
+      <c r="R27" s="332">
         <v>3.61</v>
       </c>
-      <c r="S27" s="326">
+      <c r="S27" s="333">
         <v>4.17</v>
       </c>
-      <c r="T27" s="335">
-        <v>-12.5</v>
+      <c r="T27" s="338">
+        <v>-11.67</v>
       </c>
     </row>
     <row r="28">
@@ -10294,7 +10294,7 @@
       <c r="C28" t="str">
         <v>920765</v>
       </c>
-      <c r="D28" s="351" t="str">
+      <c r="D28" s="341" t="str">
         <v>净卖: -291.63万</v>
       </c>
       <c r="E28">
@@ -10309,41 +10309,41 @@
       <c r="H28">
         <v>-0.26</v>
       </c>
-      <c r="I28" s="344">
+      <c r="I28" s="345">
         <v>21.66</v>
       </c>
-      <c r="J28" s="345">
+      <c r="J28" s="350">
         <v>16.41</v>
       </c>
-      <c r="K28" s="348">
+      <c r="K28" s="347">
         <v>26.65</v>
       </c>
       <c r="L28" s="346">
         <v>21.66</v>
       </c>
-      <c r="M28" s="349">
+      <c r="M28" s="348">
         <v>16.11</v>
       </c>
-      <c r="N28" s="340">
+      <c r="N28" s="351">
         <v>14.53</v>
       </c>
-      <c r="O28" s="347">
+      <c r="O28" s="349">
         <v>11.07</v>
       </c>
-      <c r="P28" s="341">
+      <c r="P28" s="339">
         <v>10.15</v>
       </c>
-      <c r="Q28" s="350">
+      <c r="Q28" s="342">
         <v>9.63</v>
       </c>
-      <c r="R28" s="339">
+      <c r="R28" s="343">
         <v>8.67</v>
       </c>
-      <c r="S28" s="342">
+      <c r="S28" s="340">
         <v>9.1</v>
       </c>
-      <c r="T28" s="343">
-        <v>-33.7</v>
+      <c r="T28" s="344">
+        <v>-32.91</v>
       </c>
     </row>
     <row r="29">
@@ -10356,7 +10356,7 @@
       <c r="C29" t="str">
         <v>688233</v>
       </c>
-      <c r="D29" s="362" t="str">
+      <c r="D29" s="352" t="str">
         <v>净买: 4489.13万</v>
       </c>
       <c r="E29">
@@ -10374,38 +10374,38 @@
       <c r="I29" s="359">
         <v>3.42</v>
       </c>
-      <c r="J29" s="363">
+      <c r="J29" s="353">
         <v>1.23</v>
       </c>
-      <c r="K29" s="357">
+      <c r="K29" s="354">
         <v>10.14</v>
       </c>
-      <c r="L29" s="353">
+      <c r="L29" s="355">
         <v>-0.87</v>
       </c>
-      <c r="M29" s="354">
+      <c r="M29" s="362">
         <v>5.63</v>
       </c>
-      <c r="N29" s="358">
+      <c r="N29" s="356">
         <v>-0.83</v>
       </c>
-      <c r="O29" s="364">
+      <c r="O29" s="360">
         <v>-0.62</v>
       </c>
-      <c r="P29" s="355">
+      <c r="P29" s="361">
         <v>-6.58</v>
       </c>
-      <c r="Q29" s="352">
+      <c r="Q29" s="357">
         <v>-16.49</v>
       </c>
-      <c r="R29" s="360">
+      <c r="R29" s="364">
         <v>-10.75</v>
       </c>
-      <c r="S29" s="361">
+      <c r="S29" s="363">
         <v>0.63</v>
       </c>
-      <c r="T29" s="356">
-        <v>6.31</v>
+      <c r="T29" s="358">
+        <v>7.75</v>
       </c>
     </row>
     <row r="30">
@@ -10433,41 +10433,41 @@
       <c r="H30">
         <v>-0.93</v>
       </c>
-      <c r="I30" s="376">
+      <c r="I30" s="369">
         <v>-8.65</v>
       </c>
-      <c r="J30" s="369">
+      <c r="J30" s="367">
         <v>-3.96</v>
       </c>
-      <c r="K30" s="370">
+      <c r="K30" s="366">
         <v>-6.7</v>
       </c>
-      <c r="L30" s="371">
+      <c r="L30" s="376">
         <v>-2.84</v>
       </c>
-      <c r="M30" s="372">
+      <c r="M30" s="370">
         <v>-5.33</v>
       </c>
-      <c r="N30" s="377">
+      <c r="N30" s="371">
         <v>-7.23</v>
       </c>
-      <c r="O30" s="366">
+      <c r="O30" s="372">
         <v>-9.19</v>
       </c>
-      <c r="P30" s="365">
+      <c r="P30" s="373">
         <v>-11.19</v>
       </c>
-      <c r="Q30" s="367">
+      <c r="Q30" s="377">
         <v>-10.76</v>
       </c>
-      <c r="R30" s="373">
+      <c r="R30" s="374">
         <v>-1.83</v>
       </c>
-      <c r="S30" s="374">
+      <c r="S30" s="365">
         <v>2.97</v>
       </c>
       <c r="T30" s="375">
-        <v>2.64</v>
+        <v>12.89</v>
       </c>
     </row>
     <row r="31">
@@ -10501,13 +10501,13 @@
       <c r="J31" s="384">
         <v>-10.54</v>
       </c>
-      <c r="K31" s="387">
+      <c r="K31" s="386">
         <v>-16.08</v>
       </c>
       <c r="L31" s="385">
         <v>-21.88</v>
       </c>
-      <c r="M31" s="386">
+      <c r="M31" s="387">
         <v>-23.96</v>
       </c>
       <c r="N31" s="388">
@@ -10516,20 +10516,20 @@
       <c r="O31" s="389">
         <v>-28.17</v>
       </c>
-      <c r="P31" s="378">
+      <c r="P31" s="390">
         <v>-28.81</v>
       </c>
-      <c r="Q31" s="380">
+      <c r="Q31" s="378">
         <v>-30.62</v>
       </c>
-      <c r="R31" s="390">
+      <c r="R31" s="380">
         <v>-32.37</v>
       </c>
-      <c r="S31" s="381">
+      <c r="S31" s="379">
         <v>-32.16</v>
       </c>
-      <c r="T31" s="379">
-        <v>-20.18</v>
+      <c r="T31" s="381">
+        <v>-18.69</v>
       </c>
     </row>
     <row r="32">
@@ -10542,7 +10542,7 @@
       <c r="C32" t="str">
         <v>920407</v>
       </c>
-      <c r="D32" s="398" t="str">
+      <c r="D32" s="399" t="str">
         <v>净买: 722.34万</v>
       </c>
       <c r="E32">
@@ -10557,41 +10557,41 @@
       <c r="H32">
         <v>1.28</v>
       </c>
-      <c r="I32" s="393">
+      <c r="I32" s="391">
         <v>28.31</v>
       </c>
-      <c r="J32" s="399">
+      <c r="J32" s="400">
         <v>29.11</v>
       </c>
-      <c r="K32" s="395">
+      <c r="K32" s="392">
         <v>15.45</v>
       </c>
-      <c r="L32" s="400">
+      <c r="L32" s="393">
         <v>17.04</v>
       </c>
-      <c r="M32" s="402">
+      <c r="M32" s="396">
         <v>25.35</v>
       </c>
-      <c r="N32" s="403">
+      <c r="N32" s="401">
         <v>62.96</v>
       </c>
-      <c r="O32" s="401">
+      <c r="O32" s="394">
         <v>42.07</v>
       </c>
-      <c r="P32" s="391">
+      <c r="P32" s="395">
         <v>32.35</v>
       </c>
-      <c r="Q32" s="394">
+      <c r="Q32" s="403">
         <v>36.62</v>
       </c>
-      <c r="R32" s="396">
+      <c r="R32" s="402">
         <v>27.7</v>
       </c>
       <c r="S32" s="397">
         <v>27.7</v>
       </c>
-      <c r="T32" s="392">
-        <v>-11.78</v>
+      <c r="T32" s="398">
+        <v>-9.77</v>
       </c>
     </row>
     <row r="33">
@@ -10604,7 +10604,7 @@
       <c r="C33" t="str">
         <v>920765</v>
       </c>
-      <c r="D33" s="413" t="str">
+      <c r="D33" s="405" t="str">
         <v>净卖: -3268.70万</v>
       </c>
       <c r="E33">
@@ -10619,41 +10619,41 @@
       <c r="H33">
         <v>-10.08</v>
       </c>
-      <c r="I33" s="414">
+      <c r="I33" s="406">
         <v>2.35</v>
       </c>
       <c r="J33" s="407">
         <v>-1.45</v>
       </c>
-      <c r="K33" s="408">
+      <c r="K33" s="411">
         <v>-5.92</v>
       </c>
-      <c r="L33" s="409">
+      <c r="L33" s="413">
         <v>-10.71</v>
       </c>
       <c r="M33" s="410">
         <v>-10.51</v>
       </c>
-      <c r="N33" s="411">
+      <c r="N33" s="414">
         <v>-12.16</v>
       </c>
-      <c r="O33" s="405">
+      <c r="O33" s="408">
         <v>-14.08</v>
       </c>
       <c r="P33" s="415">
         <v>-16.59</v>
       </c>
-      <c r="Q33" s="412">
+      <c r="Q33" s="416">
         <v>-19.14</v>
       </c>
-      <c r="R33" s="406">
+      <c r="R33" s="404">
         <v>-18.63</v>
       </c>
-      <c r="S33" s="416">
+      <c r="S33" s="409">
         <v>-18.86</v>
       </c>
-      <c r="T33" s="404">
-        <v>-40.59</v>
+      <c r="T33" s="412">
+        <v>-39.88</v>
       </c>
     </row>
     <row r="34">
@@ -10666,7 +10666,7 @@
       <c r="C34" t="str">
         <v>603458</v>
       </c>
-      <c r="D34" s="425" t="str">
+      <c r="D34" s="427" t="str">
         <v>净买: 2084.50万</v>
       </c>
       <c r="E34">
@@ -10681,41 +10681,41 @@
       <c r="H34">
         <v>5.37</v>
       </c>
-      <c r="I34" s="417">
+      <c r="I34" s="428">
         <v>4.4</v>
       </c>
-      <c r="J34" s="418">
+      <c r="J34" s="429">
         <v>0.2</v>
       </c>
-      <c r="K34" s="421">
+      <c r="K34" s="423">
         <v>10.2</v>
       </c>
-      <c r="L34" s="426">
+      <c r="L34" s="424">
         <v>14</v>
       </c>
-      <c r="M34" s="427">
+      <c r="M34" s="421">
         <v>13.9</v>
       </c>
-      <c r="N34" s="420">
+      <c r="N34" s="425">
         <v>20.5</v>
       </c>
-      <c r="O34" s="419">
+      <c r="O34" s="417">
         <v>20.4</v>
       </c>
-      <c r="P34" s="428">
+      <c r="P34" s="422">
         <v>21.7</v>
       </c>
-      <c r="Q34" s="422">
+      <c r="Q34" s="426">
         <v>19.2</v>
       </c>
-      <c r="R34" s="423">
+      <c r="R34" s="418">
         <v>31.1</v>
       </c>
-      <c r="S34" s="424">
+      <c r="S34" s="419">
         <v>27.9</v>
       </c>
-      <c r="T34" s="429">
-        <v>19.5</v>
+      <c r="T34" s="420">
+        <v>24</v>
       </c>
     </row>
     <row r="35">
@@ -10728,7 +10728,7 @@
       <c r="C35" t="str">
         <v>920179</v>
       </c>
-      <c r="D35" s="434" t="str">
+      <c r="D35" s="441" t="str">
         <v>净买: 1651.86万</v>
       </c>
       <c r="E35">
@@ -10743,41 +10743,41 @@
       <c r="H35">
         <v>5.59</v>
       </c>
-      <c r="I35" s="440">
+      <c r="I35" s="434">
         <v>15.88</v>
       </c>
-      <c r="J35" s="441">
+      <c r="J35" s="435">
         <v>19.24</v>
       </c>
-      <c r="K35" s="442">
+      <c r="K35" s="438">
         <v>13.24</v>
       </c>
-      <c r="L35" s="438">
+      <c r="L35" s="436">
         <v>17.03</v>
       </c>
       <c r="M35" s="431">
         <v>8.58</v>
       </c>
-      <c r="N35" s="432">
+      <c r="N35" s="442">
         <v>8.97</v>
       </c>
-      <c r="O35" s="435">
+      <c r="O35" s="437">
         <v>10.54</v>
       </c>
-      <c r="P35" s="430">
+      <c r="P35" s="432">
         <v>7.38</v>
       </c>
-      <c r="Q35" s="436">
+      <c r="Q35" s="433">
         <v>13.87</v>
       </c>
-      <c r="R35" s="433">
+      <c r="R35" s="439">
         <v>36.96</v>
       </c>
-      <c r="S35" s="439">
+      <c r="S35" s="430">
         <v>37.84</v>
       </c>
-      <c r="T35" s="437">
-        <v>32.84</v>
+      <c r="T35" s="440">
+        <v>29.14</v>
       </c>
     </row>
     <row r="36">
@@ -10805,19 +10805,19 @@
       <c r="H36">
         <v>-0.94</v>
       </c>
-      <c r="I36" s="452">
+      <c r="I36" s="448">
         <v>11.07</v>
       </c>
-      <c r="J36" s="446">
+      <c r="J36" s="452">
         <v>9.74</v>
       </c>
-      <c r="K36" s="454">
+      <c r="K36" s="445">
         <v>7.38</v>
       </c>
-      <c r="L36" s="455">
+      <c r="L36" s="454">
         <v>2.93</v>
       </c>
-      <c r="M36" s="443">
+      <c r="M36" s="455">
         <v>-3.12</v>
       </c>
       <c r="N36" s="449">
@@ -10826,20 +10826,20 @@
       <c r="O36" s="450">
         <v>-4.92</v>
       </c>
-      <c r="P36" s="447">
+      <c r="P36" s="446">
         <v>-5.11</v>
       </c>
       <c r="Q36" s="453">
         <v>-5.3</v>
       </c>
-      <c r="R36" s="444">
+      <c r="R36" s="443">
         <v>-8.89</v>
       </c>
-      <c r="S36" s="448">
+      <c r="S36" s="447">
         <v>0.19</v>
       </c>
-      <c r="T36" s="445">
-        <v>5.96</v>
+      <c r="T36" s="444">
+        <v>6.53</v>
       </c>
     </row>
     <row r="37">
@@ -10852,7 +10852,7 @@
       <c r="C37" t="str">
         <v>688115</v>
       </c>
-      <c r="D37" s="459" t="str">
+      <c r="D37" s="465" t="str">
         <v>净买: 534.48万</v>
       </c>
       <c r="E37">
@@ -10867,41 +10867,41 @@
       <c r="H37">
         <v>-0.49</v>
       </c>
-      <c r="I37" s="460">
+      <c r="I37" s="458">
         <v>-15.96</v>
       </c>
-      <c r="J37" s="461">
+      <c r="J37" s="466">
         <v>-24.38</v>
       </c>
-      <c r="K37" s="466">
+      <c r="K37" s="467">
         <v>-27.28</v>
       </c>
-      <c r="L37" s="463">
+      <c r="L37" s="462">
         <v>-26.26</v>
       </c>
-      <c r="M37" s="467">
+      <c r="M37" s="461">
         <v>-29.33</v>
       </c>
-      <c r="N37" s="456">
+      <c r="N37" s="463">
         <v>-33.51</v>
       </c>
-      <c r="O37" s="464">
+      <c r="O37" s="468">
         <v>-34.12</v>
       </c>
-      <c r="P37" s="462">
+      <c r="P37" s="464">
         <v>-35.51</v>
       </c>
-      <c r="Q37" s="465">
+      <c r="Q37" s="459">
         <v>-35.8</v>
       </c>
-      <c r="R37" s="457">
+      <c r="R37" s="460">
         <v>-33.88</v>
       </c>
-      <c r="S37" s="458">
+      <c r="S37" s="456">
         <v>-35.38</v>
       </c>
-      <c r="T37" s="468">
-        <v>-36.54</v>
+      <c r="T37" s="457">
+        <v>-36.68</v>
       </c>
     </row>
     <row r="38">
@@ -10914,7 +10914,7 @@
       <c r="C38" t="str">
         <v>600671</v>
       </c>
-      <c r="D38" s="471" t="str">
+      <c r="D38" s="470" t="str">
         <v>净卖: -271.42万</v>
       </c>
       <c r="E38">
@@ -10929,41 +10929,41 @@
       <c r="H38">
         <v>-1.3</v>
       </c>
-      <c r="I38" s="474">
+      <c r="I38" s="471">
         <v>-8.5</v>
       </c>
-      <c r="J38" s="477">
+      <c r="J38" s="472">
         <v>-11.05</v>
       </c>
-      <c r="K38" s="480">
+      <c r="K38" s="479">
         <v>-13.41</v>
       </c>
-      <c r="L38" s="481">
+      <c r="L38" s="480">
         <v>-13.14</v>
       </c>
-      <c r="M38" s="478">
+      <c r="M38" s="481">
         <v>-15.18</v>
       </c>
-      <c r="N38" s="479">
+      <c r="N38" s="473">
         <v>-15.68</v>
       </c>
-      <c r="O38" s="469">
+      <c r="O38" s="474">
         <v>-13.05</v>
       </c>
-      <c r="P38" s="475">
+      <c r="P38" s="469">
         <v>-15.68</v>
       </c>
-      <c r="Q38" s="470">
+      <c r="Q38" s="477">
         <v>-14.45</v>
       </c>
-      <c r="R38" s="472">
+      <c r="R38" s="475">
         <v>-13.27</v>
       </c>
-      <c r="S38" s="473">
+      <c r="S38" s="478">
         <v>-11.23</v>
       </c>
       <c r="T38" s="476">
-        <v>-11.45</v>
+        <v>-10.09</v>
       </c>
     </row>
     <row r="39">
@@ -10991,41 +10991,41 @@
       <c r="H39">
         <v>15.07</v>
       </c>
-      <c r="I39" s="490">
+      <c r="I39" s="494">
         <v>0.06</v>
       </c>
-      <c r="J39" s="487">
+      <c r="J39" s="490">
         <v>7.83</v>
       </c>
-      <c r="K39" s="483">
+      <c r="K39" s="492">
         <v>6.29</v>
       </c>
-      <c r="L39" s="484">
+      <c r="L39" s="482">
         <v>8.34</v>
       </c>
-      <c r="M39" s="494">
+      <c r="M39" s="487">
         <v>23.94</v>
       </c>
-      <c r="N39" s="485">
+      <c r="N39" s="483">
         <v>7.32</v>
       </c>
-      <c r="O39" s="486">
+      <c r="O39" s="484">
         <v>15.34</v>
       </c>
-      <c r="P39" s="491">
+      <c r="P39" s="485">
         <v>15.08</v>
       </c>
-      <c r="Q39" s="488">
+      <c r="Q39" s="486">
         <v>21.31</v>
       </c>
-      <c r="R39" s="482">
+      <c r="R39" s="491">
         <v>19.9</v>
       </c>
-      <c r="S39" s="489">
+      <c r="S39" s="488">
         <v>31.26</v>
       </c>
-      <c r="T39" s="492">
-        <v>21.31</v>
+      <c r="T39" s="489">
+        <v>19.77</v>
       </c>
     </row>
     <row r="40">
@@ -11090,38 +11090,38 @@
       <c r="I41" s="502">
         <v>55.26</v>
       </c>
-      <c r="J41" s="506">
+      <c r="J41" s="500">
         <v>60.53</v>
       </c>
-      <c r="K41" s="501">
+      <c r="K41" s="504">
         <v>55.26</v>
       </c>
-      <c r="L41" s="503">
+      <c r="L41" s="495">
         <v>52.63</v>
       </c>
-      <c r="M41" s="495">
+      <c r="M41" s="505">
         <v>50</v>
       </c>
-      <c r="N41" s="496">
+      <c r="N41" s="501">
         <v>44.74</v>
       </c>
-      <c r="O41" s="504">
+      <c r="O41" s="496">
         <v>44.74</v>
       </c>
-      <c r="P41" s="497">
+      <c r="P41" s="503">
         <v>50</v>
       </c>
-      <c r="Q41" s="498">
+      <c r="Q41" s="497">
         <v>44.74</v>
       </c>
-      <c r="R41" s="499">
+      <c r="R41" s="506">
         <v>39.47</v>
       </c>
-      <c r="S41" s="505">
+      <c r="S41" s="498">
         <v>50</v>
       </c>
-      <c r="T41" s="500">
-        <v>55.26</v>
+      <c r="T41" s="499">
+        <v>57.89</v>
       </c>
     </row>
     <row r="42">
@@ -11135,41 +11135,41 @@
       <c r="F42" t="str"/>
       <c r="G42" t="str"/>
       <c r="H42" t="str"/>
-      <c r="I42" s="508">
+      <c r="I42" s="512">
         <v>3.07</v>
       </c>
-      <c r="J42" s="509">
+      <c r="J42" s="507">
         <v>2.73</v>
       </c>
-      <c r="K42" s="510">
+      <c r="K42" s="508">
         <v>0.67</v>
       </c>
-      <c r="L42" s="515">
+      <c r="L42" s="513">
         <v>-0.15</v>
       </c>
-      <c r="M42" s="512">
+      <c r="M42" s="509">
         <v>-0.18</v>
       </c>
-      <c r="N42" s="517">
+      <c r="N42" s="510">
         <v>0.5</v>
       </c>
       <c r="O42" s="511">
         <v>0.7</v>
       </c>
-      <c r="P42" s="518">
+      <c r="P42" s="516">
         <v>-0.65</v>
       </c>
-      <c r="Q42" s="513">
+      <c r="Q42" s="514">
         <v>-0.47</v>
       </c>
-      <c r="R42" s="514">
+      <c r="R42" s="517">
         <v>-0.13</v>
       </c>
-      <c r="S42" s="516">
+      <c r="S42" s="515">
         <v>0.43</v>
       </c>
-      <c r="T42" s="507">
-        <v>18.24</v>
+      <c r="T42" s="518">
+        <v>19.11</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/小鳄鱼/index.xlsx
+++ b/youzi/小鳄鱼/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="520">
+  <fills count="522">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,12 +39,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC12937"/>
         <bgColor/>
       </patternFill>
@@ -57,36 +75,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF7D4D8"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB42330"/>
         <bgColor/>
       </patternFill>
@@ -105,7 +117,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C788"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FA94B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,25 +249,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2FA94B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6707C"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15664"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -153,7 +393,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4E0BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -165,13 +531,907 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF76C788"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A712F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF2E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A143"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9818B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBEE4C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -183,25 +1443,463 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1E2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F2E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9858F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -213,19 +1911,1039 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CDD1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CD95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8790"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B96B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04D5B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -249,13 +2967,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2D"/>
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -285,709 +3015,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15664"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB4E0BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA7AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A712F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA5"/>
+        <fgColor rgb="FFF5C9CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -999,175 +3051,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD5EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE4E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
+        <fgColor rgb="FFEC949D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1179,889 +3063,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A143"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBEE4C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9818B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1E2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F2E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9858F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56E79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFE87D87"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C2"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2079,997 +3105,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CDD1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8790"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF54B96B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CD95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04D5B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
+        <fgColor rgb="FFEEF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D7"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3081,6 +3141,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF3BBC0"/>
         <bgColor/>
       </patternFill>
@@ -3091,62 +3157,22 @@
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="519">
+  <borders count="521">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -6784,7 +6810,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="519">
+  <cellXfs count="521">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -8338,6 +8364,12 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="518" fillId="519" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="519" fillId="520" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="520" fillId="521" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -8682,7 +8714,7 @@
       <c r="C2" t="str">
         <v>603881</v>
       </c>
-      <c r="D2" s="1" t="str">
+      <c r="D2" s="3" t="str">
         <v>净买: 1.27亿</v>
       </c>
       <c r="E2">
@@ -8697,41 +8729,41 @@
       <c r="H2">
         <v>8.87</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="7">
         <v>1.04</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="10">
         <v>11.14</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="4">
         <v>0.03</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="5">
         <v>7.5</v>
       </c>
-      <c r="M2" s="9">
+      <c r="M2" s="11">
         <v>8.74</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="6">
         <v>19.61</v>
       </c>
       <c r="O2" s="12">
         <v>25.9</v>
       </c>
-      <c r="P2" s="4">
+      <c r="P2" s="8">
         <v>21.45</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="13">
         <v>15.56</v>
       </c>
-      <c r="R2" s="13">
+      <c r="R2" s="1">
         <v>9.81</v>
       </c>
-      <c r="S2" s="6">
+      <c r="S2" s="2">
         <v>-0.74</v>
       </c>
-      <c r="T2" s="10">
-        <v>16.95</v>
+      <c r="T2" s="9">
+        <v>12.83</v>
       </c>
     </row>
     <row r="3">
@@ -8744,7 +8776,7 @@
       <c r="C3" t="str">
         <v>603881</v>
       </c>
-      <c r="D3" s="19" t="str">
+      <c r="D3" s="24" t="str">
         <v>净卖: -9150.08万</v>
       </c>
       <c r="E3">
@@ -8759,41 +8791,41 @@
       <c r="H3">
         <v>-4.56</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="20">
         <v>-5.7</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="21">
         <v>1.34</v>
       </c>
       <c r="K3" s="23">
         <v>2.51</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="16">
         <v>12.77</v>
       </c>
-      <c r="M3" s="20">
+      <c r="M3" s="25">
         <v>18.69</v>
       </c>
-      <c r="N3" s="14">
+      <c r="N3" s="17">
         <v>14.5</v>
       </c>
-      <c r="O3" s="24">
+      <c r="O3" s="18">
         <v>8.94</v>
       </c>
-      <c r="P3" s="18">
+      <c r="P3" s="26">
         <v>3.52</v>
       </c>
-      <c r="Q3" s="21">
+      <c r="Q3" s="14">
         <v>-6.42</v>
       </c>
-      <c r="R3" s="15">
+      <c r="R3" s="19">
         <v>-4.83</v>
       </c>
-      <c r="S3" s="22">
+      <c r="S3" s="15">
         <v>-3.18</v>
       </c>
-      <c r="T3" s="16">
-        <v>10.25</v>
+      <c r="T3" s="22">
+        <v>6.37</v>
       </c>
     </row>
     <row r="4">
@@ -8821,41 +8853,41 @@
       <c r="H4">
         <v>0.22</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="34">
         <v>9.8</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="37">
         <v>13.04</v>
       </c>
-      <c r="K4" s="39">
+      <c r="K4" s="30">
         <v>17.87</v>
       </c>
-      <c r="L4" s="27">
+      <c r="L4" s="38">
         <v>11.31</v>
       </c>
       <c r="M4" s="35">
         <v>12.39</v>
       </c>
-      <c r="N4" s="32">
+      <c r="N4" s="36">
         <v>15.13</v>
       </c>
-      <c r="O4" s="36">
+      <c r="O4" s="39">
         <v>7.93</v>
       </c>
-      <c r="P4" s="33">
+      <c r="P4" s="31">
         <v>8.36</v>
       </c>
-      <c r="Q4" s="37">
+      <c r="Q4" s="27">
         <v>9.44</v>
       </c>
-      <c r="R4" s="38">
+      <c r="R4" s="32">
         <v>11.38</v>
       </c>
-      <c r="S4" s="34">
+      <c r="S4" s="28">
         <v>11.1</v>
       </c>
-      <c r="T4" s="28">
-        <v>2.67</v>
+      <c r="T4" s="33">
+        <v>2.88</v>
       </c>
     </row>
     <row r="5">
@@ -8868,7 +8900,7 @@
       <c r="C5" t="str">
         <v>002639</v>
       </c>
-      <c r="D5" s="41" t="str">
+      <c r="D5" s="45" t="str">
         <v>净买: 6286.22万</v>
       </c>
       <c r="E5">
@@ -8883,25 +8915,25 @@
       <c r="H5">
         <v>-1.66</v>
       </c>
-      <c r="I5" s="42">
+      <c r="I5" s="51">
         <v>11.82</v>
       </c>
-      <c r="J5" s="45">
+      <c r="J5" s="52">
         <v>12.21</v>
       </c>
-      <c r="K5" s="43">
+      <c r="K5" s="40">
         <v>5.32</v>
       </c>
-      <c r="L5" s="48">
+      <c r="L5" s="46">
         <v>15.84</v>
       </c>
-      <c r="M5" s="46">
+      <c r="M5" s="47">
         <v>10.91</v>
       </c>
-      <c r="N5" s="51">
+      <c r="N5" s="48">
         <v>18.96</v>
       </c>
-      <c r="O5" s="52">
+      <c r="O5" s="41">
         <v>22.6</v>
       </c>
       <c r="P5" s="49">
@@ -8910,14 +8942,14 @@
       <c r="Q5" s="50">
         <v>4.16</v>
       </c>
-      <c r="R5" s="44">
+      <c r="R5" s="42">
         <v>-6.23</v>
       </c>
-      <c r="S5" s="47">
+      <c r="S5" s="43">
         <v>-8.18</v>
       </c>
-      <c r="T5" s="40">
-        <v>160.65</v>
+      <c r="T5" s="44">
+        <v>156.62</v>
       </c>
     </row>
     <row r="6">
@@ -8930,7 +8962,7 @@
       <c r="C6" t="str">
         <v>603226</v>
       </c>
-      <c r="D6" s="57" t="str">
+      <c r="D6" s="59" t="str">
         <v>净卖: -590.66万</v>
       </c>
       <c r="E6">
@@ -8945,41 +8977,41 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="58">
+      <c r="I6" s="61">
         <v>10.05</v>
       </c>
-      <c r="J6" s="61">
+      <c r="J6" s="60">
         <v>4.08</v>
       </c>
-      <c r="K6" s="53">
+      <c r="K6" s="62">
         <v>4.08</v>
       </c>
-      <c r="L6" s="59">
+      <c r="L6" s="54">
         <v>4.08</v>
       </c>
-      <c r="M6" s="62">
+      <c r="M6" s="55">
         <v>7.06</v>
       </c>
-      <c r="N6" s="54">
+      <c r="N6" s="56">
         <v>5.02</v>
       </c>
-      <c r="O6" s="64">
+      <c r="O6" s="63">
         <v>-5.49</v>
       </c>
-      <c r="P6" s="60">
+      <c r="P6" s="57">
         <v>-14.6</v>
       </c>
-      <c r="Q6" s="55">
+      <c r="Q6" s="58">
         <v>-9.26</v>
       </c>
-      <c r="R6" s="56">
+      <c r="R6" s="64">
         <v>-5.81</v>
       </c>
-      <c r="S6" s="63">
+      <c r="S6" s="65">
         <v>3.61</v>
       </c>
-      <c r="T6" s="65">
-        <v>507.85</v>
+      <c r="T6" s="53">
+        <v>504.71</v>
       </c>
     </row>
     <row r="7">
@@ -8992,7 +9024,7 @@
       <c r="C7" t="str">
         <v>603011</v>
       </c>
-      <c r="D7" s="78" t="str">
+      <c r="D7" s="77" t="str">
         <v>净卖: -2450.00万</v>
       </c>
       <c r="E7">
@@ -9007,41 +9039,41 @@
       <c r="H7">
         <v>-0.78</v>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="70">
         <v>10.9</v>
       </c>
-      <c r="J7" s="74">
+      <c r="J7" s="78">
         <v>5.29</v>
       </c>
-      <c r="K7" s="67">
+      <c r="K7" s="75">
         <v>-1.74</v>
       </c>
-      <c r="L7" s="68">
+      <c r="L7" s="71">
         <v>-11.53</v>
       </c>
-      <c r="M7" s="69">
+      <c r="M7" s="76">
         <v>-20.38</v>
       </c>
-      <c r="N7" s="75">
+      <c r="N7" s="66">
         <v>-24.17</v>
       </c>
-      <c r="O7" s="70">
+      <c r="O7" s="67">
         <v>-21.8</v>
       </c>
-      <c r="P7" s="71">
+      <c r="P7" s="68">
         <v>-20.46</v>
       </c>
-      <c r="Q7" s="76">
+      <c r="Q7" s="72">
         <v>-12.48</v>
       </c>
-      <c r="R7" s="72">
+      <c r="R7" s="73">
         <v>-15.24</v>
       </c>
-      <c r="S7" s="73">
+      <c r="S7" s="74">
         <v>-22.12</v>
       </c>
-      <c r="T7" s="77">
-        <v>75.75</v>
+      <c r="T7" s="69">
+        <v>73.3</v>
       </c>
     </row>
     <row r="8">
@@ -9054,7 +9086,7 @@
       <c r="C8" t="str">
         <v>000989</v>
       </c>
-      <c r="D8" s="90" t="str">
+      <c r="D8" s="79" t="str">
         <v>净卖: -4522.23万</v>
       </c>
       <c r="E8">
@@ -9069,41 +9101,41 @@
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="81">
+      <c r="I8" s="86">
         <v>-6.8</v>
       </c>
-      <c r="J8" s="85">
+      <c r="J8" s="91">
         <v>-8.95</v>
       </c>
-      <c r="K8" s="82">
+      <c r="K8" s="80">
         <v>-12.73</v>
       </c>
-      <c r="L8" s="79">
+      <c r="L8" s="87">
         <v>-12.41</v>
       </c>
-      <c r="M8" s="86">
+      <c r="M8" s="88">
         <v>-9.82</v>
       </c>
-      <c r="N8" s="83">
+      <c r="N8" s="90">
         <v>-6.8</v>
       </c>
-      <c r="O8" s="84">
+      <c r="O8" s="81">
         <v>-1.29</v>
       </c>
-      <c r="P8" s="80">
+      <c r="P8" s="89">
         <v>-3.78</v>
       </c>
-      <c r="Q8" s="87">
+      <c r="Q8" s="82">
         <v>-6.36</v>
       </c>
-      <c r="R8" s="88">
+      <c r="R8" s="83">
         <v>-5.83</v>
       </c>
-      <c r="S8" s="91">
+      <c r="S8" s="84">
         <v>-8.2</v>
       </c>
-      <c r="T8" s="89">
-        <v>2.16</v>
+      <c r="T8" s="85">
+        <v>1.08</v>
       </c>
     </row>
     <row r="9">
@@ -9116,7 +9148,7 @@
       <c r="C9" t="str">
         <v>603488</v>
       </c>
-      <c r="D9" s="96" t="str">
+      <c r="D9" s="104" t="str">
         <v>净卖: -414.45万</v>
       </c>
       <c r="E9">
@@ -9131,41 +9163,41 @@
       <c r="H9">
         <v>-0.82</v>
       </c>
-      <c r="I9" s="100">
+      <c r="I9" s="96">
         <v>10.89</v>
       </c>
-      <c r="J9" s="92">
+      <c r="J9" s="97">
         <v>2.01</v>
       </c>
-      <c r="K9" s="97">
+      <c r="K9" s="92">
         <v>-0.12</v>
       </c>
-      <c r="L9" s="102">
+      <c r="L9" s="93">
         <v>-4.5</v>
       </c>
-      <c r="M9" s="101">
+      <c r="M9" s="98">
         <v>-4.73</v>
       </c>
-      <c r="N9" s="103">
+      <c r="N9" s="99">
         <v>-6.27</v>
       </c>
-      <c r="O9" s="104">
+      <c r="O9" s="100">
         <v>-5.56</v>
       </c>
-      <c r="P9" s="93">
+      <c r="P9" s="101">
         <v>-9.11</v>
       </c>
-      <c r="Q9" s="94">
+      <c r="Q9" s="102">
         <v>-8.52</v>
       </c>
-      <c r="R9" s="98">
+      <c r="R9" s="103">
         <v>-7.1</v>
       </c>
-      <c r="S9" s="99">
+      <c r="S9" s="94">
         <v>-7.81</v>
       </c>
       <c r="T9" s="95">
-        <v>33.25</v>
+        <v>33.61</v>
       </c>
     </row>
     <row r="10">
@@ -9178,7 +9210,7 @@
       <c r="C10" t="str">
         <v>603429</v>
       </c>
-      <c r="D10" s="112" t="str">
+      <c r="D10" s="113" t="str">
         <v>净卖: -775.14万</v>
       </c>
       <c r="E10">
@@ -9193,41 +9225,41 @@
       <c r="H10">
         <v>-0.46</v>
       </c>
-      <c r="I10" s="113">
+      <c r="I10" s="114">
         <v>-9.58</v>
       </c>
-      <c r="J10" s="108">
+      <c r="J10" s="107">
         <v>-17.02</v>
       </c>
-      <c r="K10" s="114">
+      <c r="K10" s="115">
         <v>-15.53</v>
       </c>
-      <c r="L10" s="109">
+      <c r="L10" s="117">
         <v>-17.02</v>
       </c>
-      <c r="M10" s="115">
+      <c r="M10" s="108">
         <v>-25.3</v>
       </c>
-      <c r="N10" s="110">
+      <c r="N10" s="109">
         <v>-26.33</v>
       </c>
-      <c r="O10" s="105">
+      <c r="O10" s="110">
         <v>-22.79</v>
       </c>
-      <c r="P10" s="106">
+      <c r="P10" s="111">
         <v>-22.7</v>
       </c>
-      <c r="Q10" s="111">
+      <c r="Q10" s="105">
         <v>-24.47</v>
       </c>
       <c r="R10" s="116">
         <v>-23.91</v>
       </c>
-      <c r="S10" s="107">
+      <c r="S10" s="106">
         <v>-24.74</v>
       </c>
-      <c r="T10" s="117">
-        <v>-5.67</v>
+      <c r="T10" s="112">
+        <v>-7.16</v>
       </c>
     </row>
     <row r="11">
@@ -9240,7 +9272,7 @@
       <c r="C11" t="str">
         <v>600735</v>
       </c>
-      <c r="D11" s="130" t="str">
+      <c r="D11" s="126" t="str">
         <v>净买: 1079.52万</v>
       </c>
       <c r="E11">
@@ -9255,31 +9287,31 @@
       <c r="H11">
         <v>-5.01</v>
       </c>
-      <c r="I11" s="118">
+      <c r="I11" s="127">
         <v>5.4</v>
       </c>
       <c r="J11" s="128">
         <v>4.08</v>
       </c>
-      <c r="K11" s="119">
+      <c r="K11" s="129">
         <v>1.32</v>
       </c>
-      <c r="L11" s="129">
+      <c r="L11" s="130">
         <v>2.37</v>
       </c>
-      <c r="M11" s="125">
+      <c r="M11" s="124">
         <v>7.64</v>
       </c>
-      <c r="N11" s="123">
+      <c r="N11" s="118">
         <v>6.19</v>
       </c>
-      <c r="O11" s="126">
+      <c r="O11" s="125">
         <v>3.43</v>
       </c>
-      <c r="P11" s="120">
+      <c r="P11" s="119">
         <v>8.7</v>
       </c>
-      <c r="Q11" s="127">
+      <c r="Q11" s="120">
         <v>10.28</v>
       </c>
       <c r="R11" s="121">
@@ -9288,7 +9320,7 @@
       <c r="S11" s="122">
         <v>3.43</v>
       </c>
-      <c r="T11" s="124">
+      <c r="T11" s="123">
         <v>-11.33</v>
       </c>
     </row>
@@ -9302,7 +9334,7 @@
       <c r="C12" t="str">
         <v>603429</v>
       </c>
-      <c r="D12" s="138" t="str">
+      <c r="D12" s="139" t="str">
         <v>净买: 2015.22万</v>
       </c>
       <c r="E12">
@@ -9317,41 +9349,41 @@
       <c r="H12">
         <v>-4.22</v>
       </c>
-      <c r="I12" s="136">
+      <c r="I12" s="132">
         <v>-4.19</v>
       </c>
-      <c r="J12" s="139">
+      <c r="J12" s="136">
         <v>-2.47</v>
       </c>
-      <c r="K12" s="132">
+      <c r="K12" s="133">
         <v>-4.19</v>
       </c>
-      <c r="L12" s="133">
+      <c r="L12" s="134">
         <v>-13.75</v>
       </c>
-      <c r="M12" s="140">
+      <c r="M12" s="137">
         <v>-14.93</v>
       </c>
-      <c r="N12" s="143">
+      <c r="N12" s="135">
         <v>-10.85</v>
       </c>
-      <c r="O12" s="131">
+      <c r="O12" s="140">
         <v>-10.74</v>
       </c>
-      <c r="P12" s="134">
+      <c r="P12" s="138">
         <v>-12.78</v>
       </c>
-      <c r="Q12" s="135">
+      <c r="Q12" s="141">
         <v>-12.14</v>
       </c>
-      <c r="R12" s="141">
+      <c r="R12" s="142">
         <v>-13.1</v>
       </c>
-      <c r="S12" s="137">
+      <c r="S12" s="143">
         <v>-14.18</v>
       </c>
-      <c r="T12" s="142">
-        <v>8.92</v>
+      <c r="T12" s="131">
+        <v>7.2</v>
       </c>
     </row>
     <row r="13">
@@ -9364,7 +9396,7 @@
       <c r="C13" t="str">
         <v>603429</v>
       </c>
-      <c r="D13" s="152" t="str">
+      <c r="D13" s="156" t="str">
         <v>净卖: -2033.97万</v>
       </c>
       <c r="E13">
@@ -9379,41 +9411,41 @@
       <c r="H13">
         <v>-0.45</v>
       </c>
-      <c r="I13" s="153">
+      <c r="I13" s="144">
         <v>-9.57</v>
       </c>
-      <c r="J13" s="148">
+      <c r="J13" s="146">
         <v>-10.81</v>
       </c>
-      <c r="K13" s="154">
+      <c r="K13" s="149">
         <v>-6.53</v>
       </c>
-      <c r="L13" s="155">
+      <c r="L13" s="154">
         <v>-6.42</v>
       </c>
-      <c r="M13" s="156">
+      <c r="M13" s="150">
         <v>-8.56</v>
       </c>
-      <c r="N13" s="144">
+      <c r="N13" s="151">
         <v>-7.88</v>
       </c>
-      <c r="O13" s="149">
+      <c r="O13" s="152">
         <v>-8.9</v>
       </c>
-      <c r="P13" s="145">
+      <c r="P13" s="147">
         <v>-10.02</v>
       </c>
-      <c r="Q13" s="150">
+      <c r="Q13" s="145">
         <v>-8.78</v>
       </c>
-      <c r="R13" s="151">
+      <c r="R13" s="153">
         <v>-8.78</v>
       </c>
-      <c r="S13" s="146">
+      <c r="S13" s="148">
         <v>-5.86</v>
       </c>
-      <c r="T13" s="147">
-        <v>14.19</v>
+      <c r="T13" s="155">
+        <v>12.39</v>
       </c>
     </row>
     <row r="14">
@@ -9426,7 +9458,7 @@
       <c r="C14" t="str">
         <v>600735</v>
       </c>
-      <c r="D14" s="167" t="str">
+      <c r="D14" s="161" t="str">
         <v>净买: 450.48万</v>
       </c>
       <c r="E14">
@@ -9441,40 +9473,40 @@
       <c r="H14">
         <v>-9.95</v>
       </c>
-      <c r="I14" s="160">
+      <c r="I14" s="162">
         <v>0</v>
       </c>
       <c r="J14" s="157">
         <v>-0.12</v>
       </c>
-      <c r="K14" s="158">
+      <c r="K14" s="166">
         <v>0.6</v>
       </c>
-      <c r="L14" s="168">
+      <c r="L14" s="167">
         <v>2.04</v>
       </c>
-      <c r="M14" s="161">
+      <c r="M14" s="163">
         <v>-0.96</v>
       </c>
       <c r="N14" s="164">
         <v>-3.72</v>
       </c>
-      <c r="O14" s="159">
+      <c r="O14" s="168">
         <v>2.4</v>
       </c>
-      <c r="P14" s="162">
+      <c r="P14" s="165">
         <v>2.88</v>
       </c>
-      <c r="Q14" s="165">
+      <c r="Q14" s="169">
         <v>3.48</v>
       </c>
-      <c r="R14" s="163">
+      <c r="R14" s="159">
         <v>2.76</v>
       </c>
-      <c r="S14" s="169">
+      <c r="S14" s="160">
         <v>4.32</v>
       </c>
-      <c r="T14" s="166">
+      <c r="T14" s="158">
         <v>-19.21</v>
       </c>
     </row>
@@ -9488,7 +9520,7 @@
       <c r="C15" t="str">
         <v>605198</v>
       </c>
-      <c r="D15" s="177" t="str">
+      <c r="D15" s="181" t="str">
         <v>净买: 424.10万</v>
       </c>
       <c r="E15">
@@ -9503,19 +9535,19 @@
       <c r="H15">
         <v>-3.44</v>
       </c>
-      <c r="I15" s="178">
+      <c r="I15" s="182">
         <v>-6.79</v>
       </c>
-      <c r="J15" s="179">
+      <c r="J15" s="178">
         <v>-11.34</v>
       </c>
-      <c r="K15" s="180">
+      <c r="K15" s="174">
         <v>-12.86</v>
       </c>
-      <c r="L15" s="181">
+      <c r="L15" s="179">
         <v>-11.52</v>
       </c>
-      <c r="M15" s="182">
+      <c r="M15" s="177">
         <v>-11.25</v>
       </c>
       <c r="N15" s="170">
@@ -9524,20 +9556,20 @@
       <c r="O15" s="171">
         <v>-11.43</v>
       </c>
-      <c r="P15" s="173">
+      <c r="P15" s="172">
         <v>-11.41</v>
       </c>
-      <c r="Q15" s="172">
+      <c r="Q15" s="180">
         <v>-9.78</v>
       </c>
-      <c r="R15" s="174">
+      <c r="R15" s="173">
         <v>-11.65</v>
       </c>
       <c r="S15" s="175">
         <v>-11.96</v>
       </c>
       <c r="T15" s="176">
-        <v>0.66</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="16">
@@ -9550,7 +9582,7 @@
       <c r="C16" t="str">
         <v>600208</v>
       </c>
-      <c r="D16" s="189" t="str">
+      <c r="D16" s="191" t="str">
         <v>净卖: -1100.93万</v>
       </c>
       <c r="E16">
@@ -9565,41 +9597,41 @@
       <c r="H16">
         <v>9.93</v>
       </c>
-      <c r="I16" s="190">
+      <c r="I16" s="185">
         <v>0</v>
       </c>
       <c r="J16" s="186">
         <v>10.04</v>
       </c>
-      <c r="K16" s="187">
+      <c r="K16" s="192">
         <v>7.23</v>
       </c>
-      <c r="L16" s="191">
+      <c r="L16" s="193">
         <v>11.24</v>
       </c>
-      <c r="M16" s="183">
+      <c r="M16" s="187">
         <v>0.2</v>
       </c>
-      <c r="N16" s="184">
+      <c r="N16" s="189">
         <v>-4.42</v>
       </c>
-      <c r="O16" s="185">
+      <c r="O16" s="194">
         <v>-2.81</v>
       </c>
-      <c r="P16" s="192">
+      <c r="P16" s="195">
         <v>3.41</v>
       </c>
-      <c r="Q16" s="193">
+      <c r="Q16" s="188">
         <v>0.4</v>
       </c>
-      <c r="R16" s="194">
+      <c r="R16" s="183">
         <v>-5.82</v>
       </c>
-      <c r="S16" s="195">
+      <c r="S16" s="190">
         <v>-3.21</v>
       </c>
-      <c r="T16" s="188">
-        <v>-25.5</v>
+      <c r="T16" s="184">
+        <v>-21.69</v>
       </c>
     </row>
     <row r="17">
@@ -9612,7 +9644,7 @@
       <c r="C17" t="str">
         <v>600590</v>
       </c>
-      <c r="D17" s="198" t="str">
+      <c r="D17" s="200" t="str">
         <v>净买: 1371.16万</v>
       </c>
       <c r="E17">
@@ -9627,41 +9659,41 @@
       <c r="H17">
         <v>9.98</v>
       </c>
-      <c r="I17" s="203">
+      <c r="I17" s="198">
         <v>0</v>
       </c>
-      <c r="J17" s="206">
+      <c r="J17" s="207">
         <v>-3.03</v>
       </c>
-      <c r="K17" s="207">
+      <c r="K17" s="201">
         <v>-5.43</v>
       </c>
-      <c r="L17" s="208">
+      <c r="L17" s="196">
         <v>-8.3</v>
       </c>
-      <c r="M17" s="199">
+      <c r="M17" s="202">
         <v>-9.54</v>
       </c>
-      <c r="N17" s="196">
+      <c r="N17" s="208">
         <v>-11.64</v>
       </c>
-      <c r="O17" s="201">
+      <c r="O17" s="203">
         <v>-10.4</v>
       </c>
-      <c r="P17" s="204">
+      <c r="P17" s="199">
         <v>-12.57</v>
       </c>
-      <c r="Q17" s="200">
+      <c r="Q17" s="197">
         <v>-13.03</v>
       </c>
-      <c r="R17" s="197">
+      <c r="R17" s="204">
         <v>-14.82</v>
       </c>
-      <c r="S17" s="202">
+      <c r="S17" s="205">
         <v>-21.26</v>
       </c>
-      <c r="T17" s="205">
-        <v>35.14</v>
+      <c r="T17" s="206">
+        <v>34.45</v>
       </c>
     </row>
     <row r="18">
@@ -9674,7 +9706,7 @@
       <c r="C18" t="str">
         <v>000063</v>
       </c>
-      <c r="D18" s="211" t="str">
+      <c r="D18" s="221" t="str">
         <v>净买: 5.93亿</v>
       </c>
       <c r="E18">
@@ -9689,41 +9721,41 @@
       <c r="H18">
         <v>2.21</v>
       </c>
-      <c r="I18" s="218">
+      <c r="I18" s="213">
         <v>7.01</v>
       </c>
-      <c r="J18" s="221">
+      <c r="J18" s="209">
         <v>5.38</v>
       </c>
-      <c r="K18" s="209">
+      <c r="K18" s="219">
         <v>3.49</v>
       </c>
-      <c r="L18" s="214">
+      <c r="L18" s="210">
         <v>1.38</v>
       </c>
-      <c r="M18" s="212">
+      <c r="M18" s="215">
         <v>9.01</v>
       </c>
-      <c r="N18" s="213">
+      <c r="N18" s="214">
         <v>4.46</v>
       </c>
-      <c r="O18" s="215">
+      <c r="O18" s="216">
         <v>10.34</v>
       </c>
-      <c r="P18" s="219">
+      <c r="P18" s="217">
         <v>3.06</v>
       </c>
-      <c r="Q18" s="210">
+      <c r="Q18" s="211">
         <v>1.01</v>
       </c>
       <c r="R18" s="220">
         <v>-6.11</v>
       </c>
-      <c r="S18" s="216">
+      <c r="S18" s="218">
         <v>-3.86</v>
       </c>
-      <c r="T18" s="217">
-        <v>-17.63</v>
+      <c r="T18" s="212">
+        <v>-19.08</v>
       </c>
     </row>
     <row r="19">
@@ -9736,7 +9768,7 @@
       <c r="C19" t="str">
         <v>000061</v>
       </c>
-      <c r="D19" s="230" t="str">
+      <c r="D19" s="224" t="str">
         <v>净买: 2178.30万</v>
       </c>
       <c r="E19">
@@ -9751,41 +9783,41 @@
       <c r="H19">
         <v>5.09</v>
       </c>
-      <c r="I19" s="228">
+      <c r="I19" s="226">
         <v>4.72</v>
       </c>
-      <c r="J19" s="222">
+      <c r="J19" s="234">
         <v>8.94</v>
       </c>
-      <c r="K19" s="231">
+      <c r="K19" s="227">
         <v>3.73</v>
       </c>
-      <c r="L19" s="225">
+      <c r="L19" s="228">
         <v>-1.99</v>
       </c>
-      <c r="M19" s="232">
+      <c r="M19" s="229">
         <v>-1.49</v>
       </c>
-      <c r="N19" s="229">
+      <c r="N19" s="222">
         <v>-0.25</v>
       </c>
-      <c r="O19" s="223">
+      <c r="O19" s="225">
         <v>-0.12</v>
       </c>
-      <c r="P19" s="233">
+      <c r="P19" s="223">
         <v>3.11</v>
       </c>
-      <c r="Q19" s="226">
+      <c r="Q19" s="230">
         <v>4.84</v>
       </c>
-      <c r="R19" s="234">
+      <c r="R19" s="231">
         <v>15.28</v>
       </c>
-      <c r="S19" s="227">
+      <c r="S19" s="232">
         <v>14.53</v>
       </c>
-      <c r="T19" s="224">
-        <v>-7.95</v>
+      <c r="T19" s="233">
+        <v>-6.34</v>
       </c>
     </row>
     <row r="20">
@@ -9798,7 +9830,7 @@
       <c r="C20" t="str">
         <v>837174</v>
       </c>
-      <c r="D20" s="243" t="str">
+      <c r="D20" s="247" t="str">
         <v>净买: 1878.87万</v>
       </c>
       <c r="E20">
@@ -9813,19 +9845,19 @@
       <c r="H20">
         <v>-0.85</v>
       </c>
-      <c r="I20" s="235">
+      <c r="I20" s="239">
         <v>31.1</v>
       </c>
-      <c r="J20" s="237">
+      <c r="J20" s="235">
         <v>25.62</v>
       </c>
-      <c r="K20" s="241">
+      <c r="K20" s="240">
         <v>0.1</v>
       </c>
-      <c r="L20" s="244">
+      <c r="L20" s="241">
         <v>-14.6</v>
       </c>
-      <c r="M20" s="236">
+      <c r="M20" s="237">
         <v>-15.25</v>
       </c>
       <c r="N20" s="242">
@@ -9837,16 +9869,16 @@
       <c r="P20" s="238">
         <v>-18.77</v>
       </c>
-      <c r="Q20" s="239">
+      <c r="Q20" s="243">
         <v>-23.13</v>
       </c>
-      <c r="R20" s="246">
+      <c r="R20" s="236">
         <v>-22.25</v>
       </c>
-      <c r="S20" s="240">
+      <c r="S20" s="244">
         <v>-22.58</v>
       </c>
-      <c r="T20" s="247">
+      <c r="T20" s="246">
         <v>-29.79</v>
       </c>
     </row>
@@ -9860,7 +9892,7 @@
       <c r="C21" t="str">
         <v>002050</v>
       </c>
-      <c r="D21" s="257" t="str">
+      <c r="D21" s="252" t="str">
         <v>净买: 2.36亿</v>
       </c>
       <c r="E21">
@@ -9875,41 +9907,41 @@
       <c r="H21">
         <v>2.54</v>
       </c>
-      <c r="I21" s="250">
+      <c r="I21" s="248">
         <v>7.27</v>
       </c>
-      <c r="J21" s="254">
+      <c r="J21" s="255">
         <v>8.13</v>
       </c>
-      <c r="K21" s="255">
+      <c r="K21" s="249">
         <v>6.42</v>
       </c>
-      <c r="L21" s="251">
+      <c r="L21" s="250">
         <v>10.42</v>
       </c>
-      <c r="M21" s="256">
+      <c r="M21" s="258">
         <v>9.59</v>
       </c>
-      <c r="N21" s="252">
+      <c r="N21" s="256">
         <v>13.28</v>
       </c>
-      <c r="O21" s="258">
+      <c r="O21" s="253">
         <v>24.62</v>
       </c>
-      <c r="P21" s="248">
+      <c r="P21" s="259">
         <v>33.1</v>
       </c>
-      <c r="Q21" s="249">
+      <c r="Q21" s="260">
         <v>44.7</v>
       </c>
-      <c r="R21" s="253">
+      <c r="R21" s="251">
         <v>32.31</v>
       </c>
-      <c r="S21" s="259">
+      <c r="S21" s="257">
         <v>36.5</v>
       </c>
-      <c r="T21" s="260">
-        <v>45.93</v>
+      <c r="T21" s="254">
+        <v>46.47</v>
       </c>
     </row>
     <row r="22">
@@ -9922,7 +9954,7 @@
       <c r="C22" t="str">
         <v>603429</v>
       </c>
-      <c r="D22" s="272" t="str">
+      <c r="D22" s="271" t="str">
         <v>净买: 1423.30万</v>
       </c>
       <c r="E22">
@@ -9937,10 +9969,10 @@
       <c r="H22">
         <v>-0.38</v>
       </c>
-      <c r="I22" s="269">
+      <c r="I22" s="272">
         <v>-6.68</v>
       </c>
-      <c r="J22" s="265">
+      <c r="J22" s="263">
         <v>-8.22</v>
       </c>
       <c r="K22" s="266">
@@ -9949,29 +9981,29 @@
       <c r="L22" s="273">
         <v>-8.76</v>
       </c>
-      <c r="M22" s="267">
+      <c r="M22" s="261">
         <v>-10.37</v>
       </c>
-      <c r="N22" s="264">
+      <c r="N22" s="262">
         <v>-10.68</v>
       </c>
-      <c r="O22" s="261">
+      <c r="O22" s="267">
         <v>-12.75</v>
       </c>
-      <c r="P22" s="270">
+      <c r="P22" s="269">
         <v>-9.75</v>
       </c>
-      <c r="Q22" s="262">
+      <c r="Q22" s="264">
         <v>-0.69</v>
       </c>
-      <c r="R22" s="263">
+      <c r="R22" s="265">
         <v>-0.92</v>
       </c>
       <c r="S22" s="268">
         <v>2</v>
       </c>
-      <c r="T22" s="271">
-        <v>-22.12</v>
+      <c r="T22" s="270">
+        <v>-23.35</v>
       </c>
     </row>
     <row r="23">
@@ -9984,7 +10016,7 @@
       <c r="C23" t="str">
         <v>002475</v>
       </c>
-      <c r="D23" s="285" t="str">
+      <c r="D23" s="280" t="str">
         <v>净买: 2.00亿</v>
       </c>
       <c r="E23">
@@ -9999,41 +10031,41 @@
       <c r="H23">
         <v>-1.85</v>
       </c>
-      <c r="I23" s="286">
+      <c r="I23" s="278">
         <v>12.08</v>
       </c>
-      <c r="J23" s="275">
+      <c r="J23" s="283">
         <v>11.67</v>
       </c>
-      <c r="K23" s="280">
+      <c r="K23" s="284">
         <v>11.74</v>
       </c>
-      <c r="L23" s="274">
+      <c r="L23" s="281">
         <v>11</v>
       </c>
-      <c r="M23" s="276">
+      <c r="M23" s="275">
         <v>10.19</v>
       </c>
-      <c r="N23" s="281">
+      <c r="N23" s="279">
         <v>12.52</v>
       </c>
-      <c r="O23" s="282">
+      <c r="O23" s="276">
         <v>17.39</v>
       </c>
-      <c r="P23" s="283">
+      <c r="P23" s="285">
         <v>29.13</v>
       </c>
       <c r="Q23" s="277">
         <v>39.19</v>
       </c>
-      <c r="R23" s="278">
+      <c r="R23" s="282">
         <v>48.73</v>
       </c>
-      <c r="S23" s="279">
+      <c r="S23" s="286">
         <v>45.64</v>
       </c>
-      <c r="T23" s="284">
-        <v>39.26</v>
+      <c r="T23" s="274">
+        <v>39.3</v>
       </c>
     </row>
     <row r="24">
@@ -10046,7 +10078,7 @@
       <c r="C24" t="str">
         <v>002146</v>
       </c>
-      <c r="D24" s="294" t="str">
+      <c r="D24" s="287" t="str">
         <v>净买: 2134.01万</v>
       </c>
       <c r="E24">
@@ -10061,41 +10093,41 @@
       <c r="H24">
         <v>0.5</v>
       </c>
-      <c r="I24" s="292">
+      <c r="I24" s="295">
         <v>-9</v>
       </c>
-      <c r="J24" s="298">
+      <c r="J24" s="288">
         <v>-11</v>
       </c>
-      <c r="K24" s="299">
+      <c r="K24" s="291">
         <v>-14.5</v>
       </c>
-      <c r="L24" s="287">
+      <c r="L24" s="296">
         <v>-17.5</v>
       </c>
-      <c r="M24" s="288">
+      <c r="M24" s="292">
         <v>-16.5</v>
       </c>
-      <c r="N24" s="289">
+      <c r="N24" s="297">
         <v>-19</v>
       </c>
-      <c r="O24" s="290">
+      <c r="O24" s="289">
         <v>-20</v>
       </c>
-      <c r="P24" s="293">
+      <c r="P24" s="290">
         <v>-19.5</v>
       </c>
-      <c r="Q24" s="295">
+      <c r="Q24" s="293">
         <v>-19.5</v>
       </c>
-      <c r="R24" s="291">
+      <c r="R24" s="298">
         <v>-19</v>
       </c>
-      <c r="S24" s="296">
+      <c r="S24" s="294">
         <v>-18.5</v>
       </c>
-      <c r="T24" s="297">
-        <v>-32.5</v>
+      <c r="T24" s="299">
+        <v>-33</v>
       </c>
     </row>
     <row r="25">
@@ -10108,7 +10140,7 @@
       <c r="C25" t="str">
         <v>002743</v>
       </c>
-      <c r="D25" s="303" t="str">
+      <c r="D25" s="312" t="str">
         <v>净卖: -133.27万</v>
       </c>
       <c r="E25">
@@ -10123,41 +10155,41 @@
       <c r="H25">
         <v>-9.98</v>
       </c>
-      <c r="I25" s="309">
+      <c r="I25" s="308">
         <v>0</v>
       </c>
       <c r="J25" s="310">
         <v>-5.83</v>
       </c>
-      <c r="K25" s="304">
+      <c r="K25" s="311">
         <v>-3.38</v>
       </c>
-      <c r="L25" s="305">
+      <c r="L25" s="300">
         <v>0.75</v>
       </c>
-      <c r="M25" s="311">
+      <c r="M25" s="301">
         <v>1.88</v>
       </c>
-      <c r="N25" s="312">
+      <c r="N25" s="302">
         <v>3.01</v>
       </c>
-      <c r="O25" s="306">
+      <c r="O25" s="303">
         <v>3.95</v>
       </c>
-      <c r="P25" s="300">
+      <c r="P25" s="306">
         <v>0.75</v>
       </c>
       <c r="Q25" s="307">
         <v>-0.19</v>
       </c>
-      <c r="R25" s="301">
+      <c r="R25" s="304">
         <v>1.5</v>
       </c>
-      <c r="S25" s="302">
+      <c r="S25" s="309">
         <v>5.83</v>
       </c>
-      <c r="T25" s="308">
-        <v>0.19</v>
+      <c r="T25" s="305">
+        <v>-0.56</v>
       </c>
     </row>
     <row r="26">
@@ -10170,7 +10202,7 @@
       <c r="C26" t="str">
         <v>601011</v>
       </c>
-      <c r="D26" s="324" t="str">
+      <c r="D26" s="319" t="str">
         <v>净卖: -479.33万</v>
       </c>
       <c r="E26">
@@ -10185,41 +10217,41 @@
       <c r="H26">
         <v>3.37</v>
       </c>
-      <c r="I26" s="314">
+      <c r="I26" s="325">
         <v>6.51</v>
       </c>
       <c r="J26" s="320">
         <v>17.26</v>
       </c>
-      <c r="K26" s="321">
+      <c r="K26" s="313">
         <v>28.99</v>
       </c>
-      <c r="L26" s="313">
+      <c r="L26" s="317">
         <v>16.94</v>
       </c>
-      <c r="M26" s="315">
+      <c r="M26" s="318">
         <v>28.66</v>
       </c>
-      <c r="N26" s="316">
+      <c r="N26" s="321">
         <v>30.29</v>
       </c>
-      <c r="O26" s="317">
+      <c r="O26" s="322">
         <v>43.32</v>
       </c>
-      <c r="P26" s="322">
+      <c r="P26" s="323">
         <v>33.55</v>
       </c>
-      <c r="Q26" s="318">
+      <c r="Q26" s="316">
         <v>25.08</v>
       </c>
-      <c r="R26" s="325">
+      <c r="R26" s="314">
         <v>29.97</v>
       </c>
-      <c r="S26" s="319">
+      <c r="S26" s="315">
         <v>21.5</v>
       </c>
-      <c r="T26" s="323">
-        <v>3.58</v>
+      <c r="T26" s="324">
+        <v>2.61</v>
       </c>
     </row>
     <row r="27">
@@ -10232,7 +10264,7 @@
       <c r="C27" t="str">
         <v>601011</v>
       </c>
-      <c r="D27" s="330" t="str">
+      <c r="D27" s="331" t="str">
         <v>净卖: -659.33万</v>
       </c>
       <c r="E27">
@@ -10247,10 +10279,10 @@
       <c r="H27">
         <v>10.09</v>
       </c>
-      <c r="I27" s="337">
+      <c r="I27" s="332">
         <v>0</v>
       </c>
-      <c r="J27" s="326">
+      <c r="J27" s="333">
         <v>10</v>
       </c>
       <c r="K27" s="334">
@@ -10259,29 +10291,29 @@
       <c r="L27" s="327">
         <v>9.72</v>
       </c>
-      <c r="M27" s="331">
+      <c r="M27" s="335">
         <v>11.11</v>
       </c>
-      <c r="N27" s="335">
+      <c r="N27" s="328">
         <v>22.22</v>
       </c>
-      <c r="O27" s="328">
+      <c r="O27" s="336">
         <v>13.89</v>
       </c>
-      <c r="P27" s="336">
+      <c r="P27" s="337">
         <v>6.67</v>
       </c>
       <c r="Q27" s="329">
         <v>10.83</v>
       </c>
-      <c r="R27" s="332">
+      <c r="R27" s="338">
         <v>3.61</v>
       </c>
-      <c r="S27" s="333">
+      <c r="S27" s="326">
         <v>4.17</v>
       </c>
-      <c r="T27" s="338">
-        <v>-11.67</v>
+      <c r="T27" s="330">
+        <v>-12.5</v>
       </c>
     </row>
     <row r="28">
@@ -10294,7 +10326,7 @@
       <c r="C28" t="str">
         <v>920765</v>
       </c>
-      <c r="D28" s="341" t="str">
+      <c r="D28" s="346" t="str">
         <v>净卖: -291.63万</v>
       </c>
       <c r="E28">
@@ -10309,41 +10341,41 @@
       <c r="H28">
         <v>-0.26</v>
       </c>
-      <c r="I28" s="345">
+      <c r="I28" s="349">
         <v>21.66</v>
       </c>
-      <c r="J28" s="350">
+      <c r="J28" s="339">
         <v>16.41</v>
       </c>
       <c r="K28" s="347">
         <v>26.65</v>
       </c>
-      <c r="L28" s="346">
+      <c r="L28" s="350">
         <v>21.66</v>
       </c>
-      <c r="M28" s="348">
+      <c r="M28" s="340">
         <v>16.11</v>
       </c>
-      <c r="N28" s="351">
+      <c r="N28" s="341">
         <v>14.53</v>
       </c>
-      <c r="O28" s="349">
+      <c r="O28" s="342">
         <v>11.07</v>
       </c>
-      <c r="P28" s="339">
+      <c r="P28" s="348">
         <v>10.15</v>
       </c>
-      <c r="Q28" s="342">
+      <c r="Q28" s="343">
         <v>9.63</v>
       </c>
-      <c r="R28" s="343">
+      <c r="R28" s="344">
         <v>8.67</v>
       </c>
-      <c r="S28" s="340">
+      <c r="S28" s="345">
         <v>9.1</v>
       </c>
-      <c r="T28" s="344">
-        <v>-32.91</v>
+      <c r="T28" s="351">
+        <v>-34.75</v>
       </c>
     </row>
     <row r="29">
@@ -10371,41 +10403,41 @@
       <c r="H29">
         <v>16.03</v>
       </c>
-      <c r="I29" s="359">
+      <c r="I29" s="353">
         <v>3.42</v>
       </c>
-      <c r="J29" s="353">
+      <c r="J29" s="361">
         <v>1.23</v>
       </c>
-      <c r="K29" s="354">
+      <c r="K29" s="358">
         <v>10.14</v>
       </c>
-      <c r="L29" s="355">
+      <c r="L29" s="354">
         <v>-0.87</v>
       </c>
-      <c r="M29" s="362">
+      <c r="M29" s="355">
         <v>5.63</v>
       </c>
-      <c r="N29" s="356">
+      <c r="N29" s="357">
         <v>-0.83</v>
       </c>
-      <c r="O29" s="360">
+      <c r="O29" s="362">
         <v>-0.62</v>
       </c>
-      <c r="P29" s="361">
+      <c r="P29" s="356">
         <v>-6.58</v>
       </c>
-      <c r="Q29" s="357">
+      <c r="Q29" s="359">
         <v>-16.49</v>
       </c>
-      <c r="R29" s="364">
+      <c r="R29" s="363">
         <v>-10.75</v>
       </c>
-      <c r="S29" s="363">
+      <c r="S29" s="360">
         <v>0.63</v>
       </c>
-      <c r="T29" s="358">
-        <v>7.75</v>
+      <c r="T29" s="364">
+        <v>11.73</v>
       </c>
     </row>
     <row r="30">
@@ -10418,7 +10450,7 @@
       <c r="C30" t="str">
         <v>603130</v>
       </c>
-      <c r="D30" s="368" t="str">
+      <c r="D30" s="372" t="str">
         <v>净买: 297.33万</v>
       </c>
       <c r="E30">
@@ -10433,41 +10465,41 @@
       <c r="H30">
         <v>-0.93</v>
       </c>
-      <c r="I30" s="369">
+      <c r="I30" s="373">
         <v>-8.65</v>
       </c>
-      <c r="J30" s="367">
+      <c r="J30" s="374">
         <v>-3.96</v>
       </c>
-      <c r="K30" s="366">
+      <c r="K30" s="375">
         <v>-6.7</v>
       </c>
-      <c r="L30" s="376">
+      <c r="L30" s="365">
         <v>-2.84</v>
       </c>
-      <c r="M30" s="370">
+      <c r="M30" s="376">
         <v>-5.33</v>
       </c>
-      <c r="N30" s="371">
+      <c r="N30" s="368">
         <v>-7.23</v>
       </c>
-      <c r="O30" s="372">
+      <c r="O30" s="369">
         <v>-9.19</v>
       </c>
-      <c r="P30" s="373">
+      <c r="P30" s="377">
         <v>-11.19</v>
       </c>
-      <c r="Q30" s="377">
+      <c r="Q30" s="366">
         <v>-10.76</v>
       </c>
-      <c r="R30" s="374">
+      <c r="R30" s="367">
         <v>-1.83</v>
       </c>
-      <c r="S30" s="365">
+      <c r="S30" s="370">
         <v>2.97</v>
       </c>
-      <c r="T30" s="375">
-        <v>12.89</v>
+      <c r="T30" s="371">
+        <v>15.23</v>
       </c>
     </row>
     <row r="31">
@@ -10480,7 +10512,7 @@
       <c r="C31" t="str">
         <v>000695</v>
       </c>
-      <c r="D31" s="382" t="str">
+      <c r="D31" s="384" t="str">
         <v>净买: 1731.47万</v>
       </c>
       <c r="E31">
@@ -10495,41 +10527,41 @@
       <c r="H31">
         <v>-2.44</v>
       </c>
-      <c r="I31" s="383">
+      <c r="I31" s="381">
         <v>-7.67</v>
       </c>
-      <c r="J31" s="384">
+      <c r="J31" s="389">
         <v>-10.54</v>
       </c>
-      <c r="K31" s="386">
+      <c r="K31" s="382">
         <v>-16.08</v>
       </c>
-      <c r="L31" s="385">
+      <c r="L31" s="390">
         <v>-21.88</v>
       </c>
-      <c r="M31" s="387">
+      <c r="M31" s="385">
         <v>-23.96</v>
       </c>
-      <c r="N31" s="388">
+      <c r="N31" s="386">
         <v>-24.6</v>
       </c>
-      <c r="O31" s="389">
+      <c r="O31" s="378">
         <v>-28.17</v>
       </c>
-      <c r="P31" s="390">
+      <c r="P31" s="379">
         <v>-28.81</v>
       </c>
-      <c r="Q31" s="378">
+      <c r="Q31" s="383">
         <v>-30.62</v>
       </c>
-      <c r="R31" s="380">
+      <c r="R31" s="387">
         <v>-32.37</v>
       </c>
-      <c r="S31" s="379">
+      <c r="S31" s="380">
         <v>-32.16</v>
       </c>
-      <c r="T31" s="381">
-        <v>-18.69</v>
+      <c r="T31" s="388">
+        <v>-19.76</v>
       </c>
     </row>
     <row r="32">
@@ -10542,7 +10574,7 @@
       <c r="C32" t="str">
         <v>920407</v>
       </c>
-      <c r="D32" s="399" t="str">
+      <c r="D32" s="401" t="str">
         <v>净买: 722.34万</v>
       </c>
       <c r="E32">
@@ -10560,38 +10592,38 @@
       <c r="I32" s="391">
         <v>28.31</v>
       </c>
-      <c r="J32" s="400">
+      <c r="J32" s="392">
         <v>29.11</v>
       </c>
-      <c r="K32" s="392">
+      <c r="K32" s="393">
         <v>15.45</v>
       </c>
-      <c r="L32" s="393">
+      <c r="L32" s="399">
         <v>17.04</v>
       </c>
       <c r="M32" s="396">
         <v>25.35</v>
       </c>
-      <c r="N32" s="401">
+      <c r="N32" s="400">
         <v>62.96</v>
       </c>
-      <c r="O32" s="394">
+      <c r="O32" s="402">
         <v>42.07</v>
       </c>
-      <c r="P32" s="395">
+      <c r="P32" s="397">
         <v>32.35</v>
       </c>
-      <c r="Q32" s="403">
+      <c r="Q32" s="398">
         <v>36.62</v>
       </c>
-      <c r="R32" s="402">
+      <c r="R32" s="403">
         <v>27.7</v>
       </c>
-      <c r="S32" s="397">
+      <c r="S32" s="394">
         <v>27.7</v>
       </c>
-      <c r="T32" s="398">
-        <v>-9.77</v>
+      <c r="T32" s="395">
+        <v>-12.11</v>
       </c>
     </row>
     <row r="33">
@@ -10604,7 +10636,7 @@
       <c r="C33" t="str">
         <v>920765</v>
       </c>
-      <c r="D33" s="405" t="str">
+      <c r="D33" s="407" t="str">
         <v>净卖: -3268.70万</v>
       </c>
       <c r="E33">
@@ -10619,41 +10651,41 @@
       <c r="H33">
         <v>-10.08</v>
       </c>
-      <c r="I33" s="406">
+      <c r="I33" s="408">
         <v>2.35</v>
       </c>
-      <c r="J33" s="407">
+      <c r="J33" s="413">
         <v>-1.45</v>
       </c>
-      <c r="K33" s="411">
+      <c r="K33" s="409">
         <v>-5.92</v>
       </c>
-      <c r="L33" s="413">
+      <c r="L33" s="414">
         <v>-10.71</v>
       </c>
-      <c r="M33" s="410">
+      <c r="M33" s="415">
         <v>-10.51</v>
       </c>
-      <c r="N33" s="414">
+      <c r="N33" s="410">
         <v>-12.16</v>
       </c>
-      <c r="O33" s="408">
+      <c r="O33" s="416">
         <v>-14.08</v>
       </c>
-      <c r="P33" s="415">
+      <c r="P33" s="411">
         <v>-16.59</v>
       </c>
-      <c r="Q33" s="416">
+      <c r="Q33" s="404">
         <v>-19.14</v>
       </c>
-      <c r="R33" s="404">
+      <c r="R33" s="405">
         <v>-18.63</v>
       </c>
-      <c r="S33" s="409">
+      <c r="S33" s="412">
         <v>-18.86</v>
       </c>
-      <c r="T33" s="412">
-        <v>-39.88</v>
+      <c r="T33" s="406">
+        <v>-41.53</v>
       </c>
     </row>
     <row r="34">
@@ -10666,7 +10698,7 @@
       <c r="C34" t="str">
         <v>603458</v>
       </c>
-      <c r="D34" s="427" t="str">
+      <c r="D34" s="429" t="str">
         <v>净买: 2084.50万</v>
       </c>
       <c r="E34">
@@ -10681,41 +10713,41 @@
       <c r="H34">
         <v>5.37</v>
       </c>
-      <c r="I34" s="428">
+      <c r="I34" s="417">
         <v>4.4</v>
       </c>
-      <c r="J34" s="429">
+      <c r="J34" s="425">
         <v>0.2</v>
       </c>
-      <c r="K34" s="423">
+      <c r="K34" s="418">
         <v>10.2</v>
       </c>
-      <c r="L34" s="424">
+      <c r="L34" s="423">
         <v>14</v>
       </c>
-      <c r="M34" s="421">
+      <c r="M34" s="427">
         <v>13.9</v>
       </c>
-      <c r="N34" s="425">
+      <c r="N34" s="426">
         <v>20.5</v>
       </c>
-      <c r="O34" s="417">
+      <c r="O34" s="428">
         <v>20.4</v>
       </c>
-      <c r="P34" s="422">
+      <c r="P34" s="419">
         <v>21.7</v>
       </c>
-      <c r="Q34" s="426">
+      <c r="Q34" s="424">
         <v>19.2</v>
       </c>
-      <c r="R34" s="418">
+      <c r="R34" s="420">
         <v>31.1</v>
       </c>
-      <c r="S34" s="419">
+      <c r="S34" s="421">
         <v>27.9</v>
       </c>
-      <c r="T34" s="420">
-        <v>24</v>
+      <c r="T34" s="422">
+        <v>20.6</v>
       </c>
     </row>
     <row r="35">
@@ -10728,7 +10760,7 @@
       <c r="C35" t="str">
         <v>920179</v>
       </c>
-      <c r="D35" s="441" t="str">
+      <c r="D35" s="435" t="str">
         <v>净买: 1651.86万</v>
       </c>
       <c r="E35">
@@ -10743,41 +10775,41 @@
       <c r="H35">
         <v>5.59</v>
       </c>
-      <c r="I35" s="434">
+      <c r="I35" s="436">
         <v>15.88</v>
       </c>
-      <c r="J35" s="435">
+      <c r="J35" s="433">
         <v>19.24</v>
       </c>
-      <c r="K35" s="438">
+      <c r="K35" s="437">
         <v>13.24</v>
       </c>
-      <c r="L35" s="436">
+      <c r="L35" s="438">
         <v>17.03</v>
       </c>
-      <c r="M35" s="431">
+      <c r="M35" s="439">
         <v>8.58</v>
       </c>
-      <c r="N35" s="442">
+      <c r="N35" s="434">
         <v>8.97</v>
       </c>
-      <c r="O35" s="437">
+      <c r="O35" s="440">
         <v>10.54</v>
       </c>
-      <c r="P35" s="432">
+      <c r="P35" s="431">
         <v>7.38</v>
       </c>
-      <c r="Q35" s="433">
+      <c r="Q35" s="441">
         <v>13.87</v>
       </c>
-      <c r="R35" s="439">
+      <c r="R35" s="442">
         <v>36.96</v>
       </c>
       <c r="S35" s="430">
         <v>37.84</v>
       </c>
-      <c r="T35" s="440">
-        <v>29.14</v>
+      <c r="T35" s="432">
+        <v>27.6</v>
       </c>
     </row>
     <row r="36">
@@ -10790,7 +10822,7 @@
       <c r="C36" t="str">
         <v>603488</v>
       </c>
-      <c r="D36" s="451" t="str">
+      <c r="D36" s="453" t="str">
         <v>净买: 3230.20万</v>
       </c>
       <c r="E36">
@@ -10805,41 +10837,41 @@
       <c r="H36">
         <v>-0.94</v>
       </c>
-      <c r="I36" s="448">
+      <c r="I36" s="451">
         <v>11.07</v>
       </c>
-      <c r="J36" s="452">
+      <c r="J36" s="444">
         <v>9.74</v>
       </c>
-      <c r="K36" s="445">
+      <c r="K36" s="449">
         <v>7.38</v>
       </c>
-      <c r="L36" s="454">
+      <c r="L36" s="445">
         <v>2.93</v>
       </c>
-      <c r="M36" s="455">
+      <c r="M36" s="454">
         <v>-3.12</v>
       </c>
-      <c r="N36" s="449">
+      <c r="N36" s="455">
         <v>-5.01</v>
       </c>
-      <c r="O36" s="450">
+      <c r="O36" s="446">
         <v>-4.92</v>
       </c>
-      <c r="P36" s="446">
+      <c r="P36" s="447">
         <v>-5.11</v>
       </c>
-      <c r="Q36" s="453">
+      <c r="Q36" s="450">
         <v>-5.3</v>
       </c>
-      <c r="R36" s="443">
+      <c r="R36" s="452">
         <v>-8.89</v>
       </c>
-      <c r="S36" s="447">
+      <c r="S36" s="448">
         <v>0.19</v>
       </c>
-      <c r="T36" s="444">
-        <v>6.53</v>
+      <c r="T36" s="443">
+        <v>6.81</v>
       </c>
     </row>
     <row r="37">
@@ -10852,7 +10884,7 @@
       <c r="C37" t="str">
         <v>688115</v>
       </c>
-      <c r="D37" s="465" t="str">
+      <c r="D37" s="463" t="str">
         <v>净买: 534.48万</v>
       </c>
       <c r="E37">
@@ -10867,41 +10899,41 @@
       <c r="H37">
         <v>-0.49</v>
       </c>
-      <c r="I37" s="458">
+      <c r="I37" s="465">
         <v>-15.96</v>
       </c>
-      <c r="J37" s="466">
+      <c r="J37" s="464">
         <v>-24.38</v>
       </c>
-      <c r="K37" s="467">
+      <c r="K37" s="456">
         <v>-27.28</v>
       </c>
-      <c r="L37" s="462">
+      <c r="L37" s="466">
         <v>-26.26</v>
       </c>
-      <c r="M37" s="461">
+      <c r="M37" s="457">
         <v>-29.33</v>
       </c>
-      <c r="N37" s="463">
+      <c r="N37" s="467">
         <v>-33.51</v>
       </c>
-      <c r="O37" s="468">
+      <c r="O37" s="458">
         <v>-34.12</v>
       </c>
-      <c r="P37" s="464">
+      <c r="P37" s="459">
         <v>-35.51</v>
       </c>
-      <c r="Q37" s="459">
+      <c r="Q37" s="460">
         <v>-35.8</v>
       </c>
-      <c r="R37" s="460">
+      <c r="R37" s="461">
         <v>-33.88</v>
       </c>
-      <c r="S37" s="456">
+      <c r="S37" s="462">
         <v>-35.38</v>
       </c>
-      <c r="T37" s="457">
-        <v>-36.68</v>
+      <c r="T37" s="468">
+        <v>-36.14</v>
       </c>
     </row>
     <row r="38">
@@ -10932,38 +10964,38 @@
       <c r="I38" s="471">
         <v>-8.5</v>
       </c>
-      <c r="J38" s="472">
+      <c r="J38" s="479">
         <v>-11.05</v>
       </c>
-      <c r="K38" s="479">
+      <c r="K38" s="472">
         <v>-13.41</v>
       </c>
-      <c r="L38" s="480">
+      <c r="L38" s="475">
         <v>-13.14</v>
       </c>
-      <c r="M38" s="481">
+      <c r="M38" s="480">
         <v>-15.18</v>
       </c>
       <c r="N38" s="473">
         <v>-15.68</v>
       </c>
-      <c r="O38" s="474">
+      <c r="O38" s="476">
         <v>-13.05</v>
       </c>
-      <c r="P38" s="469">
+      <c r="P38" s="474">
         <v>-15.68</v>
       </c>
-      <c r="Q38" s="477">
+      <c r="Q38" s="481">
         <v>-14.45</v>
       </c>
-      <c r="R38" s="475">
+      <c r="R38" s="477">
         <v>-13.27</v>
       </c>
-      <c r="S38" s="478">
+      <c r="S38" s="469">
         <v>-11.23</v>
       </c>
-      <c r="T38" s="476">
-        <v>-10.09</v>
+      <c r="T38" s="478">
+        <v>-12.14</v>
       </c>
     </row>
     <row r="39">
@@ -10976,7 +11008,7 @@
       <c r="C39" t="str">
         <v>300017</v>
       </c>
-      <c r="D39" s="493" t="str">
+      <c r="D39" s="483" t="str">
         <v>净买: 3.37亿</v>
       </c>
       <c r="E39">
@@ -10991,94 +11023,86 @@
       <c r="H39">
         <v>15.07</v>
       </c>
-      <c r="I39" s="494">
+      <c r="I39" s="484">
         <v>0.06</v>
       </c>
-      <c r="J39" s="490">
+      <c r="J39" s="485">
         <v>7.83</v>
       </c>
       <c r="K39" s="492">
         <v>6.29</v>
       </c>
-      <c r="L39" s="482">
+      <c r="L39" s="486">
         <v>8.34</v>
       </c>
-      <c r="M39" s="487">
+      <c r="M39" s="493">
         <v>23.94</v>
       </c>
-      <c r="N39" s="483">
+      <c r="N39" s="489">
         <v>7.32</v>
       </c>
-      <c r="O39" s="484">
+      <c r="O39" s="487">
         <v>15.34</v>
       </c>
-      <c r="P39" s="485">
+      <c r="P39" s="490">
         <v>15.08</v>
       </c>
-      <c r="Q39" s="486">
+      <c r="Q39" s="488">
         <v>21.31</v>
       </c>
-      <c r="R39" s="491">
+      <c r="R39" s="482">
         <v>19.9</v>
       </c>
-      <c r="S39" s="488">
+      <c r="S39" s="494">
         <v>31.26</v>
       </c>
-      <c r="T39" s="489">
-        <v>19.77</v>
+      <c r="T39" s="491">
+        <v>15.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>纪录总数</v>
-      </c>
-      <c r="B40" t="str"/>
-      <c r="C40" t="str"/>
-      <c r="D40" t="str"/>
-      <c r="E40" t="str"/>
-      <c r="F40" t="str"/>
-      <c r="G40" t="str"/>
-      <c r="H40" t="str"/>
-      <c r="I40">
-        <v>38</v>
-      </c>
-      <c r="J40">
-        <v>38</v>
-      </c>
-      <c r="K40">
-        <v>38</v>
-      </c>
-      <c r="L40">
-        <v>38</v>
-      </c>
-      <c r="M40">
-        <v>38</v>
-      </c>
-      <c r="N40">
-        <v>38</v>
-      </c>
-      <c r="O40">
-        <v>38</v>
-      </c>
-      <c r="P40">
-        <v>38</v>
-      </c>
-      <c r="Q40">
-        <v>38</v>
-      </c>
-      <c r="R40">
-        <v>38</v>
-      </c>
-      <c r="S40">
-        <v>38</v>
-      </c>
-      <c r="T40">
-        <v>38</v>
-      </c>
+        <v>2026-04-21</v>
+      </c>
+      <c r="B40" t="str">
+        <v>致尚科技</v>
+      </c>
+      <c r="C40" t="str">
+        <v>301486</v>
+      </c>
+      <c r="D40" s="496" t="str">
+        <v>净买: 6753.30万</v>
+      </c>
+      <c r="E40">
+        <v>167.6</v>
+      </c>
+      <c r="F40">
+        <v>209.06</v>
+      </c>
+      <c r="G40">
+        <v>167.6</v>
+      </c>
+      <c r="H40">
+        <v>-3.8</v>
+      </c>
+      <c r="I40" s="495">
+        <v>24.74</v>
+      </c>
+      <c r="J40" t="str"/>
+      <c r="K40" t="str"/>
+      <c r="L40" t="str"/>
+      <c r="M40" t="str"/>
+      <c r="N40" t="str"/>
+      <c r="O40" t="str"/>
+      <c r="P40" t="str"/>
+      <c r="Q40" t="str"/>
+      <c r="R40" t="str"/>
+      <c r="S40" t="str"/>
+      <c r="T40" t="str"/>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>上涨比例</v>
+        <v>纪录总数</v>
       </c>
       <c r="B41" t="str"/>
       <c r="C41" t="str"/>
@@ -11087,46 +11111,46 @@
       <c r="F41" t="str"/>
       <c r="G41" t="str"/>
       <c r="H41" t="str"/>
-      <c r="I41" s="502">
-        <v>55.26</v>
-      </c>
-      <c r="J41" s="500">
-        <v>60.53</v>
-      </c>
-      <c r="K41" s="504">
-        <v>55.26</v>
-      </c>
-      <c r="L41" s="495">
-        <v>52.63</v>
-      </c>
-      <c r="M41" s="505">
-        <v>50</v>
-      </c>
-      <c r="N41" s="501">
-        <v>44.74</v>
-      </c>
-      <c r="O41" s="496">
-        <v>44.74</v>
-      </c>
-      <c r="P41" s="503">
-        <v>50</v>
-      </c>
-      <c r="Q41" s="497">
-        <v>44.74</v>
-      </c>
-      <c r="R41" s="506">
-        <v>39.47</v>
-      </c>
-      <c r="S41" s="498">
-        <v>50</v>
-      </c>
-      <c r="T41" s="499">
-        <v>57.89</v>
+      <c r="I41">
+        <v>39</v>
+      </c>
+      <c r="J41">
+        <v>38</v>
+      </c>
+      <c r="K41">
+        <v>38</v>
+      </c>
+      <c r="L41">
+        <v>38</v>
+      </c>
+      <c r="M41">
+        <v>38</v>
+      </c>
+      <c r="N41">
+        <v>38</v>
+      </c>
+      <c r="O41">
+        <v>38</v>
+      </c>
+      <c r="P41">
+        <v>38</v>
+      </c>
+      <c r="Q41">
+        <v>38</v>
+      </c>
+      <c r="R41">
+        <v>38</v>
+      </c>
+      <c r="S41">
+        <v>38</v>
+      </c>
+      <c r="T41">
+        <v>38</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>平均涨幅</v>
+        <v>上涨比例</v>
       </c>
       <c r="B42" t="str"/>
       <c r="C42" t="str"/>
@@ -11135,41 +11159,89 @@
       <c r="F42" t="str"/>
       <c r="G42" t="str"/>
       <c r="H42" t="str"/>
-      <c r="I42" s="512">
-        <v>3.07</v>
-      </c>
-      <c r="J42" s="507">
+      <c r="I42" s="506">
+        <v>56.41</v>
+      </c>
+      <c r="J42" s="500">
+        <v>60.53</v>
+      </c>
+      <c r="K42" s="503">
+        <v>55.26</v>
+      </c>
+      <c r="L42" s="497">
+        <v>52.63</v>
+      </c>
+      <c r="M42" s="504">
+        <v>50</v>
+      </c>
+      <c r="N42" s="501">
+        <v>44.74</v>
+      </c>
+      <c r="O42" s="507">
+        <v>44.74</v>
+      </c>
+      <c r="P42" s="505">
+        <v>50</v>
+      </c>
+      <c r="Q42" s="498">
+        <v>44.74</v>
+      </c>
+      <c r="R42" s="499">
+        <v>39.47</v>
+      </c>
+      <c r="S42" s="502">
+        <v>50</v>
+      </c>
+      <c r="T42" s="508">
+        <v>52.63</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>平均涨幅</v>
+      </c>
+      <c r="B43" t="str"/>
+      <c r="C43" t="str"/>
+      <c r="D43" t="str"/>
+      <c r="E43" t="str"/>
+      <c r="F43" t="str"/>
+      <c r="G43" t="str"/>
+      <c r="H43" t="str"/>
+      <c r="I43" s="511">
+        <v>3.63</v>
+      </c>
+      <c r="J43" s="517">
         <v>2.73</v>
       </c>
-      <c r="K42" s="508">
+      <c r="K43" s="519">
         <v>0.67</v>
       </c>
-      <c r="L42" s="513">
+      <c r="L43" s="512">
         <v>-0.15</v>
       </c>
-      <c r="M42" s="509">
+      <c r="M43" s="520">
         <v>-0.18</v>
       </c>
-      <c r="N42" s="510">
+      <c r="N43" s="513">
         <v>0.5</v>
       </c>
-      <c r="O42" s="511">
+      <c r="O43" s="514">
         <v>0.7</v>
       </c>
-      <c r="P42" s="516">
+      <c r="P43" s="509">
         <v>-0.65</v>
       </c>
-      <c r="Q42" s="514">
+      <c r="Q43" s="515">
         <v>-0.47</v>
       </c>
-      <c r="R42" s="517">
+      <c r="R43" s="518">
         <v>-0.13</v>
       </c>
-      <c r="S42" s="515">
+      <c r="S43" s="516">
         <v>0.43</v>
       </c>
-      <c r="T42" s="518">
-        <v>19.11</v>
+      <c r="T43" s="510">
+        <v>18.16</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/小鳄鱼/index.xlsx
+++ b/youzi/小鳄鱼/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="522">
+  <fills count="536">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,79 +39,499 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA91D2B"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDFF1E3"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FA94B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C788"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15664"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4E0BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,13 +543,889 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF76C788"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A712F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A143"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9818B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBEE4C7"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -147,31 +1443,433 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2FA94B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1E2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F2E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -183,19 +1881,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6707C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2D"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9858F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CE"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -213,6 +1971,996 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CDD1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B96B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8790"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CD95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04D5B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BABF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -231,157 +2979,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15664"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -393,103 +3045,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB4E0BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -501,313 +3099,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15260"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F2"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -819,1279 +3201,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A712F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF2E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A143"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9818B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBEE4C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1E2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F2E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9858F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2103,985 +3213,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CDD1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CD95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8790"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF54B96B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04D5B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC32938"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87D87"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CE"/>
+        <fgColor rgb="FFEBF7EE"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3093,25 +3231,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
+        <fgColor rgb="FFCCEAD3"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3121,44 +3241,106 @@
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="521">
+  <borders count="535">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -6810,7 +6992,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="521">
+  <cellXfs count="535">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -8370,6 +8552,48 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="520" fillId="521" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="521" fillId="522" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="522" fillId="523" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="523" fillId="524" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="524" fillId="525" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="525" fillId="526" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="526" fillId="527" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="527" fillId="528" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="528" fillId="529" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="529" fillId="530" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="530" fillId="531" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="531" fillId="532" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="532" fillId="533" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="533" fillId="534" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="534" fillId="535" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -8714,7 +8938,7 @@
       <c r="C2" t="str">
         <v>603881</v>
       </c>
-      <c r="D2" s="3" t="str">
+      <c r="D2" s="6" t="str">
         <v>净买: 1.27亿</v>
       </c>
       <c r="E2">
@@ -8729,41 +8953,41 @@
       <c r="H2">
         <v>8.87</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="1">
         <v>1.04</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="2">
         <v>11.14</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="3">
         <v>0.03</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="4">
         <v>7.5</v>
       </c>
-      <c r="M2" s="11">
+      <c r="M2" s="10">
         <v>8.74</v>
       </c>
-      <c r="N2" s="6">
+      <c r="N2" s="7">
         <v>19.61</v>
       </c>
-      <c r="O2" s="12">
+      <c r="O2" s="5">
         <v>25.9</v>
       </c>
-      <c r="P2" s="8">
+      <c r="P2" s="11">
         <v>21.45</v>
       </c>
-      <c r="Q2" s="13">
+      <c r="Q2" s="12">
         <v>15.56</v>
       </c>
-      <c r="R2" s="1">
+      <c r="R2" s="8">
         <v>9.81</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S2" s="13">
         <v>-0.74</v>
       </c>
       <c r="T2" s="9">
-        <v>12.83</v>
+        <v>12.36</v>
       </c>
     </row>
     <row r="3">
@@ -8776,7 +9000,7 @@
       <c r="C3" t="str">
         <v>603881</v>
       </c>
-      <c r="D3" s="24" t="str">
+      <c r="D3" s="22" t="str">
         <v>净卖: -9150.08万</v>
       </c>
       <c r="E3">
@@ -8791,41 +9015,41 @@
       <c r="H3">
         <v>-4.56</v>
       </c>
-      <c r="I3" s="20">
+      <c r="I3" s="23">
         <v>-5.7</v>
       </c>
-      <c r="J3" s="21">
+      <c r="J3" s="14">
         <v>1.34</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="19">
         <v>2.51</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="20">
         <v>12.77</v>
       </c>
-      <c r="M3" s="25">
+      <c r="M3" s="15">
         <v>18.69</v>
       </c>
-      <c r="N3" s="17">
+      <c r="N3" s="24">
         <v>14.5</v>
       </c>
-      <c r="O3" s="18">
+      <c r="O3" s="17">
         <v>8.94</v>
       </c>
-      <c r="P3" s="26">
+      <c r="P3" s="21">
         <v>3.52</v>
       </c>
-      <c r="Q3" s="14">
+      <c r="Q3" s="25">
         <v>-6.42</v>
       </c>
-      <c r="R3" s="19">
+      <c r="R3" s="18">
         <v>-4.83</v>
       </c>
-      <c r="S3" s="15">
+      <c r="S3" s="26">
         <v>-3.18</v>
       </c>
-      <c r="T3" s="22">
-        <v>6.37</v>
+      <c r="T3" s="16">
+        <v>5.92</v>
       </c>
     </row>
     <row r="4">
@@ -8838,7 +9062,7 @@
       <c r="C4" t="str">
         <v>603511</v>
       </c>
-      <c r="D4" s="29" t="str">
+      <c r="D4" s="35" t="str">
         <v>净卖: -457.10万</v>
       </c>
       <c r="E4">
@@ -8853,41 +9077,41 @@
       <c r="H4">
         <v>0.22</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I4" s="36">
         <v>9.8</v>
       </c>
       <c r="J4" s="37">
         <v>13.04</v>
       </c>
-      <c r="K4" s="30">
+      <c r="K4" s="27">
         <v>17.87</v>
       </c>
       <c r="L4" s="38">
         <v>11.31</v>
       </c>
-      <c r="M4" s="35">
+      <c r="M4" s="28">
         <v>12.39</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="29">
         <v>15.13</v>
       </c>
-      <c r="O4" s="39">
+      <c r="O4" s="30">
         <v>7.93</v>
       </c>
-      <c r="P4" s="31">
+      <c r="P4" s="32">
         <v>8.36</v>
       </c>
-      <c r="Q4" s="27">
+      <c r="Q4" s="33">
         <v>9.44</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="34">
         <v>11.38</v>
       </c>
-      <c r="S4" s="28">
+      <c r="S4" s="31">
         <v>11.1</v>
       </c>
-      <c r="T4" s="33">
-        <v>2.88</v>
+      <c r="T4" s="39">
+        <v>3.24</v>
       </c>
     </row>
     <row r="5">
@@ -8900,7 +9124,7 @@
       <c r="C5" t="str">
         <v>002639</v>
       </c>
-      <c r="D5" s="45" t="str">
+      <c r="D5" s="43" t="str">
         <v>净买: 6286.22万</v>
       </c>
       <c r="E5">
@@ -8915,13 +9139,13 @@
       <c r="H5">
         <v>-1.66</v>
       </c>
-      <c r="I5" s="51">
+      <c r="I5" s="44">
         <v>11.82</v>
       </c>
-      <c r="J5" s="52">
+      <c r="J5" s="48">
         <v>12.21</v>
       </c>
-      <c r="K5" s="40">
+      <c r="K5" s="45">
         <v>5.32</v>
       </c>
       <c r="L5" s="46">
@@ -8930,26 +9154,26 @@
       <c r="M5" s="47">
         <v>10.91</v>
       </c>
-      <c r="N5" s="48">
+      <c r="N5" s="52">
         <v>18.96</v>
       </c>
-      <c r="O5" s="41">
+      <c r="O5" s="40">
         <v>22.6</v>
       </c>
-      <c r="P5" s="49">
+      <c r="P5" s="41">
         <v>15.71</v>
       </c>
-      <c r="Q5" s="50">
+      <c r="Q5" s="49">
         <v>4.16</v>
       </c>
       <c r="R5" s="42">
         <v>-6.23</v>
       </c>
-      <c r="S5" s="43">
+      <c r="S5" s="50">
         <v>-8.18</v>
       </c>
-      <c r="T5" s="44">
-        <v>156.62</v>
+      <c r="T5" s="51">
+        <v>134.29</v>
       </c>
     </row>
     <row r="6">
@@ -8962,7 +9186,7 @@
       <c r="C6" t="str">
         <v>603226</v>
       </c>
-      <c r="D6" s="59" t="str">
+      <c r="D6" s="61" t="str">
         <v>净卖: -590.66万</v>
       </c>
       <c r="E6">
@@ -8977,7 +9201,7 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="61">
+      <c r="I6" s="54">
         <v>10.05</v>
       </c>
       <c r="J6" s="60">
@@ -8986,32 +9210,32 @@
       <c r="K6" s="62">
         <v>4.08</v>
       </c>
-      <c r="L6" s="54">
+      <c r="L6" s="58">
         <v>4.08</v>
       </c>
-      <c r="M6" s="55">
+      <c r="M6" s="63">
         <v>7.06</v>
       </c>
-      <c r="N6" s="56">
+      <c r="N6" s="64">
         <v>5.02</v>
       </c>
-      <c r="O6" s="63">
+      <c r="O6" s="65">
         <v>-5.49</v>
       </c>
-      <c r="P6" s="57">
+      <c r="P6" s="55">
         <v>-14.6</v>
       </c>
-      <c r="Q6" s="58">
+      <c r="Q6" s="59">
         <v>-9.26</v>
       </c>
-      <c r="R6" s="64">
+      <c r="R6" s="56">
         <v>-5.81</v>
       </c>
-      <c r="S6" s="65">
+      <c r="S6" s="57">
         <v>3.61</v>
       </c>
       <c r="T6" s="53">
-        <v>504.71</v>
+        <v>502.83</v>
       </c>
     </row>
     <row r="7">
@@ -9024,7 +9248,7 @@
       <c r="C7" t="str">
         <v>603011</v>
       </c>
-      <c r="D7" s="77" t="str">
+      <c r="D7" s="70" t="str">
         <v>净卖: -2450.00万</v>
       </c>
       <c r="E7">
@@ -9039,41 +9263,41 @@
       <c r="H7">
         <v>-0.78</v>
       </c>
-      <c r="I7" s="70">
+      <c r="I7" s="71">
         <v>10.9</v>
       </c>
-      <c r="J7" s="78">
+      <c r="J7" s="72">
         <v>5.29</v>
       </c>
-      <c r="K7" s="75">
+      <c r="K7" s="78">
         <v>-1.74</v>
       </c>
-      <c r="L7" s="71">
+      <c r="L7" s="73">
         <v>-11.53</v>
       </c>
-      <c r="M7" s="76">
+      <c r="M7" s="74">
         <v>-20.38</v>
       </c>
-      <c r="N7" s="66">
+      <c r="N7" s="75">
         <v>-24.17</v>
       </c>
-      <c r="O7" s="67">
+      <c r="O7" s="66">
         <v>-21.8</v>
       </c>
-      <c r="P7" s="68">
+      <c r="P7" s="67">
         <v>-20.46</v>
       </c>
-      <c r="Q7" s="72">
+      <c r="Q7" s="76">
         <v>-12.48</v>
       </c>
-      <c r="R7" s="73">
+      <c r="R7" s="77">
         <v>-15.24</v>
       </c>
-      <c r="S7" s="74">
+      <c r="S7" s="68">
         <v>-22.12</v>
       </c>
       <c r="T7" s="69">
-        <v>73.3</v>
+        <v>66.11</v>
       </c>
     </row>
     <row r="8">
@@ -9086,7 +9310,7 @@
       <c r="C8" t="str">
         <v>000989</v>
       </c>
-      <c r="D8" s="79" t="str">
+      <c r="D8" s="87" t="str">
         <v>净卖: -4522.23万</v>
       </c>
       <c r="E8">
@@ -9101,41 +9325,41 @@
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="86">
+      <c r="I8" s="79">
         <v>-6.8</v>
       </c>
-      <c r="J8" s="91">
+      <c r="J8" s="80">
         <v>-8.95</v>
       </c>
-      <c r="K8" s="80">
+      <c r="K8" s="81">
         <v>-12.73</v>
       </c>
-      <c r="L8" s="87">
+      <c r="L8" s="88">
         <v>-12.41</v>
       </c>
-      <c r="M8" s="88">
+      <c r="M8" s="82">
         <v>-9.82</v>
       </c>
-      <c r="N8" s="90">
+      <c r="N8" s="89">
         <v>-6.8</v>
       </c>
-      <c r="O8" s="81">
+      <c r="O8" s="90">
         <v>-1.29</v>
       </c>
-      <c r="P8" s="89">
+      <c r="P8" s="83">
         <v>-3.78</v>
       </c>
-      <c r="Q8" s="82">
+      <c r="Q8" s="84">
         <v>-6.36</v>
       </c>
-      <c r="R8" s="83">
+      <c r="R8" s="91">
         <v>-5.83</v>
       </c>
-      <c r="S8" s="84">
+      <c r="S8" s="85">
         <v>-8.2</v>
       </c>
-      <c r="T8" s="85">
-        <v>1.08</v>
+      <c r="T8" s="86">
+        <v>6.15</v>
       </c>
     </row>
     <row r="9">
@@ -9148,7 +9372,7 @@
       <c r="C9" t="str">
         <v>603488</v>
       </c>
-      <c r="D9" s="104" t="str">
+      <c r="D9" s="97" t="str">
         <v>净卖: -414.45万</v>
       </c>
       <c r="E9">
@@ -9163,41 +9387,41 @@
       <c r="H9">
         <v>-0.82</v>
       </c>
-      <c r="I9" s="96">
+      <c r="I9" s="98">
         <v>10.89</v>
       </c>
-      <c r="J9" s="97">
+      <c r="J9" s="102">
         <v>2.01</v>
       </c>
       <c r="K9" s="92">
         <v>-0.12</v>
       </c>
-      <c r="L9" s="93">
+      <c r="L9" s="95">
         <v>-4.5</v>
       </c>
-      <c r="M9" s="98">
+      <c r="M9" s="103">
         <v>-4.73</v>
       </c>
-      <c r="N9" s="99">
+      <c r="N9" s="96">
         <v>-6.27</v>
       </c>
-      <c r="O9" s="100">
+      <c r="O9" s="99">
         <v>-5.56</v>
       </c>
-      <c r="P9" s="101">
+      <c r="P9" s="104">
         <v>-9.11</v>
       </c>
-      <c r="Q9" s="102">
+      <c r="Q9" s="93">
         <v>-8.52</v>
       </c>
-      <c r="R9" s="103">
+      <c r="R9" s="100">
         <v>-7.1</v>
       </c>
       <c r="S9" s="94">
         <v>-7.81</v>
       </c>
-      <c r="T9" s="95">
-        <v>33.61</v>
+      <c r="T9" s="101">
+        <v>27.22</v>
       </c>
     </row>
     <row r="10">
@@ -9210,7 +9434,7 @@
       <c r="C10" t="str">
         <v>603429</v>
       </c>
-      <c r="D10" s="113" t="str">
+      <c r="D10" s="114" t="str">
         <v>净卖: -775.14万</v>
       </c>
       <c r="E10">
@@ -9225,41 +9449,41 @@
       <c r="H10">
         <v>-0.46</v>
       </c>
-      <c r="I10" s="114">
+      <c r="I10" s="115">
         <v>-9.58</v>
       </c>
       <c r="J10" s="107">
         <v>-17.02</v>
       </c>
-      <c r="K10" s="115">
+      <c r="K10" s="116">
         <v>-15.53</v>
       </c>
-      <c r="L10" s="117">
+      <c r="L10" s="108">
         <v>-17.02</v>
       </c>
-      <c r="M10" s="108">
+      <c r="M10" s="117">
         <v>-25.3</v>
       </c>
       <c r="N10" s="109">
         <v>-26.33</v>
       </c>
-      <c r="O10" s="110">
+      <c r="O10" s="111">
         <v>-22.79</v>
       </c>
-      <c r="P10" s="111">
+      <c r="P10" s="112">
         <v>-22.7</v>
       </c>
-      <c r="Q10" s="105">
+      <c r="Q10" s="113">
         <v>-24.47</v>
       </c>
-      <c r="R10" s="116">
+      <c r="R10" s="105">
         <v>-23.91</v>
       </c>
       <c r="S10" s="106">
         <v>-24.74</v>
       </c>
-      <c r="T10" s="112">
-        <v>-7.16</v>
+      <c r="T10" s="110">
+        <v>-7.44</v>
       </c>
     </row>
     <row r="11">
@@ -9272,7 +9496,7 @@
       <c r="C11" t="str">
         <v>600735</v>
       </c>
-      <c r="D11" s="126" t="str">
+      <c r="D11" s="130" t="str">
         <v>净买: 1079.52万</v>
       </c>
       <c r="E11">
@@ -9287,34 +9511,34 @@
       <c r="H11">
         <v>-5.01</v>
       </c>
-      <c r="I11" s="127">
+      <c r="I11" s="124">
         <v>5.4</v>
       </c>
-      <c r="J11" s="128">
+      <c r="J11" s="121">
         <v>4.08</v>
       </c>
-      <c r="K11" s="129">
+      <c r="K11" s="118">
         <v>1.32</v>
       </c>
-      <c r="L11" s="130">
+      <c r="L11" s="125">
         <v>2.37</v>
       </c>
-      <c r="M11" s="124">
+      <c r="M11" s="129">
         <v>7.64</v>
       </c>
-      <c r="N11" s="118">
+      <c r="N11" s="126">
         <v>6.19</v>
       </c>
-      <c r="O11" s="125">
+      <c r="O11" s="127">
         <v>3.43</v>
       </c>
       <c r="P11" s="119">
         <v>8.7</v>
       </c>
-      <c r="Q11" s="120">
+      <c r="Q11" s="128">
         <v>10.28</v>
       </c>
-      <c r="R11" s="121">
+      <c r="R11" s="120">
         <v>6.59</v>
       </c>
       <c r="S11" s="122">
@@ -9334,7 +9558,7 @@
       <c r="C12" t="str">
         <v>603429</v>
       </c>
-      <c r="D12" s="139" t="str">
+      <c r="D12" s="143" t="str">
         <v>净买: 2015.22万</v>
       </c>
       <c r="E12">
@@ -9349,41 +9573,41 @@
       <c r="H12">
         <v>-4.22</v>
       </c>
-      <c r="I12" s="132">
+      <c r="I12" s="131">
         <v>-4.19</v>
       </c>
-      <c r="J12" s="136">
+      <c r="J12" s="132">
         <v>-2.47</v>
       </c>
-      <c r="K12" s="133">
+      <c r="K12" s="137">
         <v>-4.19</v>
       </c>
-      <c r="L12" s="134">
+      <c r="L12" s="133">
         <v>-13.75</v>
       </c>
-      <c r="M12" s="137">
+      <c r="M12" s="135">
         <v>-14.93</v>
       </c>
-      <c r="N12" s="135">
+      <c r="N12" s="138">
         <v>-10.85</v>
       </c>
-      <c r="O12" s="140">
+      <c r="O12" s="139">
         <v>-10.74</v>
       </c>
-      <c r="P12" s="138">
+      <c r="P12" s="134">
         <v>-12.78</v>
       </c>
-      <c r="Q12" s="141">
+      <c r="Q12" s="140">
         <v>-12.14</v>
       </c>
-      <c r="R12" s="142">
+      <c r="R12" s="141">
         <v>-13.1</v>
       </c>
-      <c r="S12" s="143">
+      <c r="S12" s="136">
         <v>-14.18</v>
       </c>
-      <c r="T12" s="131">
-        <v>7.2</v>
+      <c r="T12" s="142">
+        <v>6.87</v>
       </c>
     </row>
     <row r="13">
@@ -9396,7 +9620,7 @@
       <c r="C13" t="str">
         <v>603429</v>
       </c>
-      <c r="D13" s="156" t="str">
+      <c r="D13" s="146" t="str">
         <v>净卖: -2033.97万</v>
       </c>
       <c r="E13">
@@ -9411,41 +9635,41 @@
       <c r="H13">
         <v>-0.45</v>
       </c>
-      <c r="I13" s="144">
+      <c r="I13" s="150">
         <v>-9.57</v>
       </c>
-      <c r="J13" s="146">
+      <c r="J13" s="153">
         <v>-10.81</v>
       </c>
-      <c r="K13" s="149">
+      <c r="K13" s="154">
         <v>-6.53</v>
       </c>
-      <c r="L13" s="154">
+      <c r="L13" s="151">
         <v>-6.42</v>
       </c>
-      <c r="M13" s="150">
+      <c r="M13" s="145">
         <v>-8.56</v>
       </c>
-      <c r="N13" s="151">
+      <c r="N13" s="155">
         <v>-7.88</v>
       </c>
-      <c r="O13" s="152">
+      <c r="O13" s="156">
         <v>-8.9</v>
       </c>
       <c r="P13" s="147">
         <v>-10.02</v>
       </c>
-      <c r="Q13" s="145">
+      <c r="Q13" s="148">
         <v>-8.78</v>
       </c>
-      <c r="R13" s="153">
+      <c r="R13" s="149">
         <v>-8.78</v>
       </c>
-      <c r="S13" s="148">
+      <c r="S13" s="144">
         <v>-5.86</v>
       </c>
-      <c r="T13" s="155">
-        <v>12.39</v>
+      <c r="T13" s="152">
+        <v>12.05</v>
       </c>
     </row>
     <row r="14">
@@ -9458,7 +9682,7 @@
       <c r="C14" t="str">
         <v>600735</v>
       </c>
-      <c r="D14" s="161" t="str">
+      <c r="D14" s="168" t="str">
         <v>净买: 450.48万</v>
       </c>
       <c r="E14">
@@ -9473,40 +9697,40 @@
       <c r="H14">
         <v>-9.95</v>
       </c>
-      <c r="I14" s="162">
+      <c r="I14" s="169">
         <v>0</v>
       </c>
-      <c r="J14" s="157">
+      <c r="J14" s="164">
         <v>-0.12</v>
       </c>
-      <c r="K14" s="166">
+      <c r="K14" s="157">
         <v>0.6</v>
       </c>
-      <c r="L14" s="167">
+      <c r="L14" s="165">
         <v>2.04</v>
       </c>
-      <c r="M14" s="163">
+      <c r="M14" s="166">
         <v>-0.96</v>
       </c>
-      <c r="N14" s="164">
+      <c r="N14" s="161">
         <v>-3.72</v>
       </c>
-      <c r="O14" s="168">
+      <c r="O14" s="158">
         <v>2.4</v>
       </c>
-      <c r="P14" s="165">
+      <c r="P14" s="162">
         <v>2.88</v>
       </c>
-      <c r="Q14" s="169">
+      <c r="Q14" s="159">
         <v>3.48</v>
       </c>
-      <c r="R14" s="159">
+      <c r="R14" s="163">
         <v>2.76</v>
       </c>
-      <c r="S14" s="160">
+      <c r="S14" s="167">
         <v>4.32</v>
       </c>
-      <c r="T14" s="158">
+      <c r="T14" s="160">
         <v>-19.21</v>
       </c>
     </row>
@@ -9520,7 +9744,7 @@
       <c r="C15" t="str">
         <v>605198</v>
       </c>
-      <c r="D15" s="181" t="str">
+      <c r="D15" s="170" t="str">
         <v>净买: 424.10万</v>
       </c>
       <c r="E15">
@@ -9535,41 +9759,41 @@
       <c r="H15">
         <v>-3.44</v>
       </c>
-      <c r="I15" s="182">
+      <c r="I15" s="171">
         <v>-6.79</v>
       </c>
       <c r="J15" s="178">
         <v>-11.34</v>
       </c>
-      <c r="K15" s="174">
+      <c r="K15" s="179">
         <v>-12.86</v>
       </c>
-      <c r="L15" s="179">
+      <c r="L15" s="181">
         <v>-11.52</v>
       </c>
-      <c r="M15" s="177">
+      <c r="M15" s="175">
         <v>-11.25</v>
       </c>
-      <c r="N15" s="170">
+      <c r="N15" s="172">
         <v>-11.47</v>
       </c>
-      <c r="O15" s="171">
+      <c r="O15" s="182">
         <v>-11.43</v>
       </c>
-      <c r="P15" s="172">
+      <c r="P15" s="173">
         <v>-11.41</v>
       </c>
-      <c r="Q15" s="180">
+      <c r="Q15" s="176">
         <v>-9.78</v>
       </c>
-      <c r="R15" s="173">
+      <c r="R15" s="177">
         <v>-11.65</v>
       </c>
-      <c r="S15" s="175">
+      <c r="S15" s="180">
         <v>-11.96</v>
       </c>
-      <c r="T15" s="176">
-        <v>-0.73</v>
+      <c r="T15" s="174">
+        <v>1.74</v>
       </c>
     </row>
     <row r="16">
@@ -9582,7 +9806,7 @@
       <c r="C16" t="str">
         <v>600208</v>
       </c>
-      <c r="D16" s="191" t="str">
+      <c r="D16" s="190" t="str">
         <v>净卖: -1100.93万</v>
       </c>
       <c r="E16">
@@ -9597,41 +9821,41 @@
       <c r="H16">
         <v>9.93</v>
       </c>
-      <c r="I16" s="185">
+      <c r="I16" s="191">
         <v>0</v>
       </c>
-      <c r="J16" s="186">
+      <c r="J16" s="185">
         <v>10.04</v>
       </c>
-      <c r="K16" s="192">
+      <c r="K16" s="184">
         <v>7.23</v>
       </c>
-      <c r="L16" s="193">
+      <c r="L16" s="187">
         <v>11.24</v>
       </c>
-      <c r="M16" s="187">
+      <c r="M16" s="192">
         <v>0.2</v>
       </c>
-      <c r="N16" s="189">
+      <c r="N16" s="193">
         <v>-4.42</v>
       </c>
       <c r="O16" s="194">
         <v>-2.81</v>
       </c>
-      <c r="P16" s="195">
+      <c r="P16" s="188">
         <v>3.41</v>
       </c>
-      <c r="Q16" s="188">
+      <c r="Q16" s="195">
         <v>0.4</v>
       </c>
-      <c r="R16" s="183">
+      <c r="R16" s="186">
         <v>-5.82</v>
       </c>
-      <c r="S16" s="190">
+      <c r="S16" s="189">
         <v>-3.21</v>
       </c>
-      <c r="T16" s="184">
-        <v>-21.69</v>
+      <c r="T16" s="183">
+        <v>-5.02</v>
       </c>
     </row>
     <row r="17">
@@ -9644,7 +9868,7 @@
       <c r="C17" t="str">
         <v>600590</v>
       </c>
-      <c r="D17" s="200" t="str">
+      <c r="D17" s="208" t="str">
         <v>净买: 1371.16万</v>
       </c>
       <c r="E17">
@@ -9659,41 +9883,41 @@
       <c r="H17">
         <v>9.98</v>
       </c>
-      <c r="I17" s="198">
+      <c r="I17" s="196">
         <v>0</v>
       </c>
-      <c r="J17" s="207">
+      <c r="J17" s="205">
         <v>-3.03</v>
       </c>
-      <c r="K17" s="201">
+      <c r="K17" s="204">
         <v>-5.43</v>
       </c>
-      <c r="L17" s="196">
+      <c r="L17" s="197">
         <v>-8.3</v>
       </c>
-      <c r="M17" s="202">
+      <c r="M17" s="198">
         <v>-9.54</v>
       </c>
-      <c r="N17" s="208">
+      <c r="N17" s="199">
         <v>-11.64</v>
       </c>
-      <c r="O17" s="203">
+      <c r="O17" s="200">
         <v>-10.4</v>
       </c>
-      <c r="P17" s="199">
+      <c r="P17" s="206">
         <v>-12.57</v>
       </c>
-      <c r="Q17" s="197">
+      <c r="Q17" s="202">
         <v>-13.03</v>
       </c>
-      <c r="R17" s="204">
+      <c r="R17" s="201">
         <v>-14.82</v>
       </c>
-      <c r="S17" s="205">
+      <c r="S17" s="207">
         <v>-21.26</v>
       </c>
-      <c r="T17" s="206">
-        <v>34.45</v>
+      <c r="T17" s="203">
+        <v>32.35</v>
       </c>
     </row>
     <row r="18">
@@ -9706,7 +9930,7 @@
       <c r="C18" t="str">
         <v>000063</v>
       </c>
-      <c r="D18" s="221" t="str">
+      <c r="D18" s="214" t="str">
         <v>净买: 5.93亿</v>
       </c>
       <c r="E18">
@@ -9721,41 +9945,41 @@
       <c r="H18">
         <v>2.21</v>
       </c>
-      <c r="I18" s="213">
+      <c r="I18" s="215">
         <v>7.01</v>
       </c>
-      <c r="J18" s="209">
+      <c r="J18" s="219">
         <v>5.38</v>
       </c>
-      <c r="K18" s="219">
+      <c r="K18" s="220">
         <v>3.49</v>
       </c>
-      <c r="L18" s="210">
+      <c r="L18" s="221">
         <v>1.38</v>
       </c>
-      <c r="M18" s="215">
+      <c r="M18" s="217">
         <v>9.01</v>
       </c>
-      <c r="N18" s="214">
+      <c r="N18" s="211">
         <v>4.46</v>
       </c>
       <c r="O18" s="216">
         <v>10.34</v>
       </c>
-      <c r="P18" s="217">
+      <c r="P18" s="209">
         <v>3.06</v>
       </c>
-      <c r="Q18" s="211">
+      <c r="Q18" s="212">
         <v>1.01</v>
       </c>
-      <c r="R18" s="220">
+      <c r="R18" s="210">
         <v>-6.11</v>
       </c>
-      <c r="S18" s="218">
+      <c r="S18" s="213">
         <v>-3.86</v>
       </c>
-      <c r="T18" s="212">
-        <v>-19.08</v>
+      <c r="T18" s="218">
+        <v>-16.37</v>
       </c>
     </row>
     <row r="19">
@@ -9768,7 +9992,7 @@
       <c r="C19" t="str">
         <v>000061</v>
       </c>
-      <c r="D19" s="224" t="str">
+      <c r="D19" s="231" t="str">
         <v>净买: 2178.30万</v>
       </c>
       <c r="E19">
@@ -9783,41 +10007,41 @@
       <c r="H19">
         <v>5.09</v>
       </c>
-      <c r="I19" s="226">
+      <c r="I19" s="224">
         <v>4.72</v>
       </c>
       <c r="J19" s="234">
         <v>8.94</v>
       </c>
-      <c r="K19" s="227">
+      <c r="K19" s="230">
         <v>3.73</v>
       </c>
-      <c r="L19" s="228">
+      <c r="L19" s="222">
         <v>-1.99</v>
       </c>
-      <c r="M19" s="229">
+      <c r="M19" s="232">
         <v>-1.49</v>
       </c>
-      <c r="N19" s="222">
+      <c r="N19" s="223">
         <v>-0.25</v>
       </c>
       <c r="O19" s="225">
         <v>-0.12</v>
       </c>
-      <c r="P19" s="223">
+      <c r="P19" s="226">
         <v>3.11</v>
       </c>
-      <c r="Q19" s="230">
+      <c r="Q19" s="227">
         <v>4.84</v>
       </c>
-      <c r="R19" s="231">
+      <c r="R19" s="233">
         <v>15.28</v>
       </c>
-      <c r="S19" s="232">
+      <c r="S19" s="228">
         <v>14.53</v>
       </c>
-      <c r="T19" s="233">
-        <v>-6.34</v>
+      <c r="T19" s="229">
+        <v>-7.7</v>
       </c>
     </row>
     <row r="20">
@@ -9830,7 +10054,7 @@
       <c r="C20" t="str">
         <v>837174</v>
       </c>
-      <c r="D20" s="247" t="str">
+      <c r="D20" s="239" t="str">
         <v>净买: 1878.87万</v>
       </c>
       <c r="E20">
@@ -9845,40 +10069,40 @@
       <c r="H20">
         <v>-0.85</v>
       </c>
-      <c r="I20" s="239">
+      <c r="I20" s="240">
         <v>31.1</v>
       </c>
-      <c r="J20" s="235">
+      <c r="J20" s="246">
         <v>25.62</v>
       </c>
-      <c r="K20" s="240">
+      <c r="K20" s="236">
         <v>0.1</v>
       </c>
-      <c r="L20" s="241">
+      <c r="L20" s="237">
         <v>-14.6</v>
       </c>
-      <c r="M20" s="237">
+      <c r="M20" s="241">
         <v>-15.25</v>
       </c>
-      <c r="N20" s="242">
+      <c r="N20" s="247">
         <v>-17.98</v>
       </c>
-      <c r="O20" s="245">
+      <c r="O20" s="244">
         <v>-19.46</v>
       </c>
       <c r="P20" s="238">
         <v>-18.77</v>
       </c>
-      <c r="Q20" s="243">
+      <c r="Q20" s="245">
         <v>-23.13</v>
       </c>
-      <c r="R20" s="236">
+      <c r="R20" s="242">
         <v>-22.25</v>
       </c>
-      <c r="S20" s="244">
+      <c r="S20" s="243">
         <v>-22.58</v>
       </c>
-      <c r="T20" s="246">
+      <c r="T20" s="235">
         <v>-29.79</v>
       </c>
     </row>
@@ -9892,7 +10116,7 @@
       <c r="C21" t="str">
         <v>002050</v>
       </c>
-      <c r="D21" s="252" t="str">
+      <c r="D21" s="253" t="str">
         <v>净买: 2.36亿</v>
       </c>
       <c r="E21">
@@ -9907,41 +10131,41 @@
       <c r="H21">
         <v>2.54</v>
       </c>
-      <c r="I21" s="248">
+      <c r="I21" s="259">
         <v>7.27</v>
       </c>
-      <c r="J21" s="255">
+      <c r="J21" s="257">
         <v>8.13</v>
       </c>
-      <c r="K21" s="249">
+      <c r="K21" s="251">
         <v>6.42</v>
       </c>
-      <c r="L21" s="250">
+      <c r="L21" s="254">
         <v>10.42</v>
       </c>
-      <c r="M21" s="258">
+      <c r="M21" s="255">
         <v>9.59</v>
       </c>
-      <c r="N21" s="256">
+      <c r="N21" s="260">
         <v>13.28</v>
       </c>
-      <c r="O21" s="253">
+      <c r="O21" s="258">
         <v>24.62</v>
       </c>
-      <c r="P21" s="259">
+      <c r="P21" s="248">
         <v>33.1</v>
       </c>
-      <c r="Q21" s="260">
+      <c r="Q21" s="252">
         <v>44.7</v>
       </c>
-      <c r="R21" s="251">
+      <c r="R21" s="249">
         <v>32.31</v>
       </c>
-      <c r="S21" s="257">
+      <c r="S21" s="250">
         <v>36.5</v>
       </c>
-      <c r="T21" s="254">
-        <v>46.47</v>
+      <c r="T21" s="256">
+        <v>42.76</v>
       </c>
     </row>
     <row r="22">
@@ -9954,7 +10178,7 @@
       <c r="C22" t="str">
         <v>603429</v>
       </c>
-      <c r="D22" s="271" t="str">
+      <c r="D22" s="264" t="str">
         <v>净买: 1423.30万</v>
       </c>
       <c r="E22">
@@ -9969,41 +10193,41 @@
       <c r="H22">
         <v>-0.38</v>
       </c>
-      <c r="I22" s="272">
+      <c r="I22" s="271">
         <v>-6.68</v>
       </c>
-      <c r="J22" s="263">
+      <c r="J22" s="268">
         <v>-8.22</v>
       </c>
-      <c r="K22" s="266">
+      <c r="K22" s="272">
         <v>-10.52</v>
       </c>
-      <c r="L22" s="273">
+      <c r="L22" s="269">
         <v>-8.76</v>
       </c>
-      <c r="M22" s="261">
+      <c r="M22" s="273">
         <v>-10.37</v>
       </c>
-      <c r="N22" s="262">
+      <c r="N22" s="270">
         <v>-10.68</v>
       </c>
-      <c r="O22" s="267">
+      <c r="O22" s="262">
         <v>-12.75</v>
       </c>
-      <c r="P22" s="269">
+      <c r="P22" s="265">
         <v>-9.75</v>
       </c>
-      <c r="Q22" s="264">
+      <c r="Q22" s="261">
         <v>-0.69</v>
       </c>
-      <c r="R22" s="265">
+      <c r="R22" s="266">
         <v>-0.92</v>
       </c>
-      <c r="S22" s="268">
+      <c r="S22" s="263">
         <v>2</v>
       </c>
-      <c r="T22" s="270">
-        <v>-23.35</v>
+      <c r="T22" s="267">
+        <v>-23.58</v>
       </c>
     </row>
     <row r="23">
@@ -10016,7 +10240,7 @@
       <c r="C23" t="str">
         <v>002475</v>
       </c>
-      <c r="D23" s="280" t="str">
+      <c r="D23" s="286" t="str">
         <v>净买: 2.00亿</v>
       </c>
       <c r="E23">
@@ -10031,41 +10255,41 @@
       <c r="H23">
         <v>-1.85</v>
       </c>
-      <c r="I23" s="278">
+      <c r="I23" s="280">
         <v>12.08</v>
       </c>
-      <c r="J23" s="283">
+      <c r="J23" s="274">
         <v>11.67</v>
       </c>
-      <c r="K23" s="284">
+      <c r="K23" s="275">
         <v>11.74</v>
       </c>
-      <c r="L23" s="281">
+      <c r="L23" s="283">
         <v>11</v>
       </c>
-      <c r="M23" s="275">
+      <c r="M23" s="276">
         <v>10.19</v>
       </c>
-      <c r="N23" s="279">
+      <c r="N23" s="281">
         <v>12.52</v>
       </c>
-      <c r="O23" s="276">
+      <c r="O23" s="277">
         <v>17.39</v>
       </c>
-      <c r="P23" s="285">
+      <c r="P23" s="282">
         <v>29.13</v>
       </c>
-      <c r="Q23" s="277">
+      <c r="Q23" s="278">
         <v>39.19</v>
       </c>
-      <c r="R23" s="282">
+      <c r="R23" s="279">
         <v>48.73</v>
       </c>
-      <c r="S23" s="286">
+      <c r="S23" s="284">
         <v>45.64</v>
       </c>
-      <c r="T23" s="274">
-        <v>39.3</v>
+      <c r="T23" s="285">
+        <v>39.83</v>
       </c>
     </row>
     <row r="24">
@@ -10093,41 +10317,41 @@
       <c r="H24">
         <v>0.5</v>
       </c>
-      <c r="I24" s="295">
+      <c r="I24" s="294">
         <v>-9</v>
       </c>
       <c r="J24" s="288">
         <v>-11</v>
       </c>
-      <c r="K24" s="291">
+      <c r="K24" s="289">
         <v>-14.5</v>
       </c>
-      <c r="L24" s="296">
+      <c r="L24" s="290">
         <v>-17.5</v>
       </c>
-      <c r="M24" s="292">
+      <c r="M24" s="291">
         <v>-16.5</v>
       </c>
       <c r="N24" s="297">
         <v>-19</v>
       </c>
-      <c r="O24" s="289">
+      <c r="O24" s="292">
         <v>-20</v>
       </c>
-      <c r="P24" s="290">
+      <c r="P24" s="298">
         <v>-19.5</v>
       </c>
       <c r="Q24" s="293">
         <v>-19.5</v>
       </c>
-      <c r="R24" s="298">
+      <c r="R24" s="295">
         <v>-19</v>
       </c>
-      <c r="S24" s="294">
+      <c r="S24" s="296">
         <v>-18.5</v>
       </c>
       <c r="T24" s="299">
-        <v>-33</v>
+        <v>-37.5</v>
       </c>
     </row>
     <row r="25">
@@ -10140,7 +10364,7 @@
       <c r="C25" t="str">
         <v>002743</v>
       </c>
-      <c r="D25" s="312" t="str">
+      <c r="D25" s="307" t="str">
         <v>净卖: -133.27万</v>
       </c>
       <c r="E25">
@@ -10158,38 +10382,38 @@
       <c r="I25" s="308">
         <v>0</v>
       </c>
-      <c r="J25" s="310">
+      <c r="J25" s="311">
         <v>-5.83</v>
       </c>
-      <c r="K25" s="311">
+      <c r="K25" s="312">
         <v>-3.38</v>
       </c>
-      <c r="L25" s="300">
+      <c r="L25" s="309">
         <v>0.75</v>
       </c>
-      <c r="M25" s="301">
+      <c r="M25" s="300">
         <v>1.88</v>
       </c>
-      <c r="N25" s="302">
+      <c r="N25" s="310">
         <v>3.01</v>
       </c>
-      <c r="O25" s="303">
+      <c r="O25" s="301">
         <v>3.95</v>
       </c>
-      <c r="P25" s="306">
+      <c r="P25" s="305">
         <v>0.75</v>
       </c>
-      <c r="Q25" s="307">
+      <c r="Q25" s="303">
         <v>-0.19</v>
       </c>
-      <c r="R25" s="304">
+      <c r="R25" s="302">
         <v>1.5</v>
       </c>
-      <c r="S25" s="309">
+      <c r="S25" s="306">
         <v>5.83</v>
       </c>
-      <c r="T25" s="305">
-        <v>-0.56</v>
+      <c r="T25" s="304">
+        <v>-2.44</v>
       </c>
     </row>
     <row r="26">
@@ -10202,7 +10426,7 @@
       <c r="C26" t="str">
         <v>601011</v>
       </c>
-      <c r="D26" s="319" t="str">
+      <c r="D26" s="322" t="str">
         <v>净卖: -479.33万</v>
       </c>
       <c r="E26">
@@ -10217,41 +10441,41 @@
       <c r="H26">
         <v>3.37</v>
       </c>
-      <c r="I26" s="325">
+      <c r="I26" s="323">
         <v>6.51</v>
       </c>
-      <c r="J26" s="320">
+      <c r="J26" s="313">
         <v>17.26</v>
       </c>
-      <c r="K26" s="313">
+      <c r="K26" s="321">
         <v>28.99</v>
       </c>
-      <c r="L26" s="317">
+      <c r="L26" s="318">
         <v>16.94</v>
       </c>
-      <c r="M26" s="318">
+      <c r="M26" s="314">
         <v>28.66</v>
       </c>
-      <c r="N26" s="321">
+      <c r="N26" s="319">
         <v>30.29</v>
       </c>
-      <c r="O26" s="322">
+      <c r="O26" s="315">
         <v>43.32</v>
       </c>
-      <c r="P26" s="323">
+      <c r="P26" s="324">
         <v>33.55</v>
       </c>
       <c r="Q26" s="316">
         <v>25.08</v>
       </c>
-      <c r="R26" s="314">
+      <c r="R26" s="325">
         <v>29.97</v>
       </c>
-      <c r="S26" s="315">
+      <c r="S26" s="317">
         <v>21.5</v>
       </c>
-      <c r="T26" s="324">
-        <v>2.61</v>
+      <c r="T26" s="320">
+        <v>-1.3</v>
       </c>
     </row>
     <row r="27">
@@ -10264,7 +10488,7 @@
       <c r="C27" t="str">
         <v>601011</v>
       </c>
-      <c r="D27" s="331" t="str">
+      <c r="D27" s="333" t="str">
         <v>净卖: -659.33万</v>
       </c>
       <c r="E27">
@@ -10279,41 +10503,41 @@
       <c r="H27">
         <v>10.09</v>
       </c>
-      <c r="I27" s="332">
+      <c r="I27" s="334">
         <v>0</v>
       </c>
-      <c r="J27" s="333">
+      <c r="J27" s="326">
         <v>10</v>
       </c>
-      <c r="K27" s="334">
+      <c r="K27" s="327">
         <v>-0.28</v>
       </c>
-      <c r="L27" s="327">
+      <c r="L27" s="335">
         <v>9.72</v>
       </c>
-      <c r="M27" s="335">
+      <c r="M27" s="330">
         <v>11.11</v>
       </c>
-      <c r="N27" s="328">
+      <c r="N27" s="336">
         <v>22.22</v>
       </c>
-      <c r="O27" s="336">
+      <c r="O27" s="331">
         <v>13.89</v>
       </c>
-      <c r="P27" s="337">
+      <c r="P27" s="338">
         <v>6.67</v>
       </c>
-      <c r="Q27" s="329">
+      <c r="Q27" s="337">
         <v>10.83</v>
       </c>
-      <c r="R27" s="338">
+      <c r="R27" s="328">
         <v>3.61</v>
       </c>
-      <c r="S27" s="326">
+      <c r="S27" s="329">
         <v>4.17</v>
       </c>
-      <c r="T27" s="330">
-        <v>-12.5</v>
+      <c r="T27" s="332">
+        <v>-15.83</v>
       </c>
     </row>
     <row r="28">
@@ -10341,41 +10565,41 @@
       <c r="H28">
         <v>-0.26</v>
       </c>
-      <c r="I28" s="349">
+      <c r="I28" s="348">
         <v>21.66</v>
       </c>
-      <c r="J28" s="339">
+      <c r="J28" s="350">
         <v>16.41</v>
       </c>
-      <c r="K28" s="347">
+      <c r="K28" s="342">
         <v>26.65</v>
       </c>
-      <c r="L28" s="350">
+      <c r="L28" s="351">
         <v>21.66</v>
       </c>
-      <c r="M28" s="340">
+      <c r="M28" s="349">
         <v>16.11</v>
       </c>
-      <c r="N28" s="341">
+      <c r="N28" s="339">
         <v>14.53</v>
       </c>
-      <c r="O28" s="342">
+      <c r="O28" s="340">
         <v>11.07</v>
       </c>
-      <c r="P28" s="348">
+      <c r="P28" s="343">
         <v>10.15</v>
       </c>
-      <c r="Q28" s="343">
+      <c r="Q28" s="344">
         <v>9.63</v>
       </c>
-      <c r="R28" s="344">
+      <c r="R28" s="341">
         <v>8.67</v>
       </c>
       <c r="S28" s="345">
         <v>9.1</v>
       </c>
-      <c r="T28" s="351">
-        <v>-34.75</v>
+      <c r="T28" s="347">
+        <v>-37.55</v>
       </c>
     </row>
     <row r="29">
@@ -10388,7 +10612,7 @@
       <c r="C29" t="str">
         <v>688233</v>
       </c>
-      <c r="D29" s="352" t="str">
+      <c r="D29" s="359" t="str">
         <v>净买: 4489.13万</v>
       </c>
       <c r="E29">
@@ -10403,41 +10627,41 @@
       <c r="H29">
         <v>16.03</v>
       </c>
-      <c r="I29" s="353">
+      <c r="I29" s="361">
         <v>3.42</v>
       </c>
-      <c r="J29" s="361">
+      <c r="J29" s="363">
         <v>1.23</v>
       </c>
-      <c r="K29" s="358">
+      <c r="K29" s="364">
         <v>10.14</v>
       </c>
-      <c r="L29" s="354">
+      <c r="L29" s="360">
         <v>-0.87</v>
       </c>
-      <c r="M29" s="355">
+      <c r="M29" s="352">
         <v>5.63</v>
       </c>
-      <c r="N29" s="357">
+      <c r="N29" s="353">
         <v>-0.83</v>
       </c>
-      <c r="O29" s="362">
+      <c r="O29" s="355">
         <v>-0.62</v>
       </c>
-      <c r="P29" s="356">
+      <c r="P29" s="362">
         <v>-6.58</v>
       </c>
-      <c r="Q29" s="359">
+      <c r="Q29" s="356">
         <v>-16.49</v>
       </c>
-      <c r="R29" s="363">
+      <c r="R29" s="357">
         <v>-10.75</v>
       </c>
-      <c r="S29" s="360">
+      <c r="S29" s="354">
         <v>0.63</v>
       </c>
-      <c r="T29" s="364">
-        <v>11.73</v>
+      <c r="T29" s="358">
+        <v>16.49</v>
       </c>
     </row>
     <row r="30">
@@ -10450,7 +10674,7 @@
       <c r="C30" t="str">
         <v>603130</v>
       </c>
-      <c r="D30" s="372" t="str">
+      <c r="D30" s="366" t="str">
         <v>净买: 297.33万</v>
       </c>
       <c r="E30">
@@ -10465,41 +10689,41 @@
       <c r="H30">
         <v>-0.93</v>
       </c>
-      <c r="I30" s="373">
+      <c r="I30" s="372">
         <v>-8.65</v>
       </c>
-      <c r="J30" s="374">
+      <c r="J30" s="367">
         <v>-3.96</v>
       </c>
-      <c r="K30" s="375">
+      <c r="K30" s="373">
         <v>-6.7</v>
       </c>
-      <c r="L30" s="365">
+      <c r="L30" s="377">
         <v>-2.84</v>
       </c>
-      <c r="M30" s="376">
+      <c r="M30" s="374">
         <v>-5.33</v>
       </c>
       <c r="N30" s="368">
         <v>-7.23</v>
       </c>
-      <c r="O30" s="369">
+      <c r="O30" s="365">
         <v>-9.19</v>
       </c>
-      <c r="P30" s="377">
+      <c r="P30" s="369">
         <v>-11.19</v>
       </c>
-      <c r="Q30" s="366">
+      <c r="Q30" s="370">
         <v>-10.76</v>
       </c>
-      <c r="R30" s="367">
+      <c r="R30" s="371">
         <v>-1.83</v>
       </c>
-      <c r="S30" s="370">
+      <c r="S30" s="375">
         <v>2.97</v>
       </c>
-      <c r="T30" s="371">
-        <v>15.23</v>
+      <c r="T30" s="376">
+        <v>23.55</v>
       </c>
     </row>
     <row r="31">
@@ -10512,7 +10736,7 @@
       <c r="C31" t="str">
         <v>000695</v>
       </c>
-      <c r="D31" s="384" t="str">
+      <c r="D31" s="383" t="str">
         <v>净买: 1731.47万</v>
       </c>
       <c r="E31">
@@ -10527,41 +10751,41 @@
       <c r="H31">
         <v>-2.44</v>
       </c>
-      <c r="I31" s="381">
+      <c r="I31" s="384">
         <v>-7.67</v>
       </c>
-      <c r="J31" s="389">
+      <c r="J31" s="378">
         <v>-10.54</v>
       </c>
-      <c r="K31" s="382">
+      <c r="K31" s="379">
         <v>-16.08</v>
       </c>
-      <c r="L31" s="390">
+      <c r="L31" s="380">
         <v>-21.88</v>
       </c>
-      <c r="M31" s="385">
+      <c r="M31" s="382">
         <v>-23.96</v>
       </c>
-      <c r="N31" s="386">
+      <c r="N31" s="385">
         <v>-24.6</v>
       </c>
-      <c r="O31" s="378">
+      <c r="O31" s="388">
         <v>-28.17</v>
       </c>
-      <c r="P31" s="379">
+      <c r="P31" s="386">
         <v>-28.81</v>
       </c>
-      <c r="Q31" s="383">
+      <c r="Q31" s="381">
         <v>-30.62</v>
       </c>
-      <c r="R31" s="387">
+      <c r="R31" s="389">
         <v>-32.37</v>
       </c>
-      <c r="S31" s="380">
+      <c r="S31" s="390">
         <v>-32.16</v>
       </c>
-      <c r="T31" s="388">
-        <v>-19.76</v>
+      <c r="T31" s="387">
+        <v>-21.88</v>
       </c>
     </row>
     <row r="32">
@@ -10574,7 +10798,7 @@
       <c r="C32" t="str">
         <v>920407</v>
       </c>
-      <c r="D32" s="401" t="str">
+      <c r="D32" s="398" t="str">
         <v>净买: 722.34万</v>
       </c>
       <c r="E32">
@@ -10589,41 +10813,41 @@
       <c r="H32">
         <v>1.28</v>
       </c>
-      <c r="I32" s="391">
+      <c r="I32" s="399">
         <v>28.31</v>
       </c>
-      <c r="J32" s="392">
+      <c r="J32" s="403">
         <v>29.11</v>
       </c>
-      <c r="K32" s="393">
+      <c r="K32" s="400">
         <v>15.45</v>
       </c>
-      <c r="L32" s="399">
+      <c r="L32" s="394">
         <v>17.04</v>
       </c>
-      <c r="M32" s="396">
+      <c r="M32" s="401">
         <v>25.35</v>
       </c>
-      <c r="N32" s="400">
+      <c r="N32" s="395">
         <v>62.96</v>
       </c>
-      <c r="O32" s="402">
+      <c r="O32" s="391">
         <v>42.07</v>
       </c>
-      <c r="P32" s="397">
+      <c r="P32" s="402">
         <v>32.35</v>
       </c>
-      <c r="Q32" s="398">
+      <c r="Q32" s="392">
         <v>36.62</v>
       </c>
-      <c r="R32" s="403">
+      <c r="R32" s="393">
         <v>27.7</v>
       </c>
-      <c r="S32" s="394">
+      <c r="S32" s="396">
         <v>27.7</v>
       </c>
-      <c r="T32" s="395">
-        <v>-12.11</v>
+      <c r="T32" s="397">
+        <v>-16.62</v>
       </c>
     </row>
     <row r="33">
@@ -10636,7 +10860,7 @@
       <c r="C33" t="str">
         <v>920765</v>
       </c>
-      <c r="D33" s="407" t="str">
+      <c r="D33" s="408" t="str">
         <v>净卖: -3268.70万</v>
       </c>
       <c r="E33">
@@ -10651,41 +10875,41 @@
       <c r="H33">
         <v>-10.08</v>
       </c>
-      <c r="I33" s="408">
+      <c r="I33" s="415">
         <v>2.35</v>
       </c>
-      <c r="J33" s="413">
+      <c r="J33" s="409">
         <v>-1.45</v>
       </c>
-      <c r="K33" s="409">
+      <c r="K33" s="413">
         <v>-5.92</v>
       </c>
-      <c r="L33" s="414">
+      <c r="L33" s="410">
         <v>-10.71</v>
       </c>
-      <c r="M33" s="415">
+      <c r="M33" s="411">
         <v>-10.51</v>
       </c>
-      <c r="N33" s="410">
+      <c r="N33" s="416">
         <v>-12.16</v>
       </c>
-      <c r="O33" s="416">
+      <c r="O33" s="406">
         <v>-14.08</v>
       </c>
-      <c r="P33" s="411">
+      <c r="P33" s="412">
         <v>-16.59</v>
       </c>
       <c r="Q33" s="404">
         <v>-19.14</v>
       </c>
-      <c r="R33" s="405">
+      <c r="R33" s="407">
         <v>-18.63</v>
       </c>
-      <c r="S33" s="412">
+      <c r="S33" s="405">
         <v>-18.86</v>
       </c>
-      <c r="T33" s="406">
-        <v>-41.53</v>
+      <c r="T33" s="414">
+        <v>-44.04</v>
       </c>
     </row>
     <row r="34">
@@ -10698,7 +10922,7 @@
       <c r="C34" t="str">
         <v>603458</v>
       </c>
-      <c r="D34" s="429" t="str">
+      <c r="D34" s="427" t="str">
         <v>净买: 2084.50万</v>
       </c>
       <c r="E34">
@@ -10713,41 +10937,41 @@
       <c r="H34">
         <v>5.37</v>
       </c>
-      <c r="I34" s="417">
+      <c r="I34" s="423">
         <v>4.4</v>
       </c>
-      <c r="J34" s="425">
+      <c r="J34" s="428">
         <v>0.2</v>
       </c>
-      <c r="K34" s="418">
+      <c r="K34" s="429">
         <v>10.2</v>
       </c>
-      <c r="L34" s="423">
+      <c r="L34" s="426">
         <v>14</v>
       </c>
-      <c r="M34" s="427">
+      <c r="M34" s="420">
         <v>13.9</v>
       </c>
-      <c r="N34" s="426">
+      <c r="N34" s="424">
         <v>20.5</v>
       </c>
-      <c r="O34" s="428">
+      <c r="O34" s="417">
         <v>20.4</v>
       </c>
-      <c r="P34" s="419">
+      <c r="P34" s="418">
         <v>21.7</v>
       </c>
-      <c r="Q34" s="424">
+      <c r="Q34" s="425">
         <v>19.2</v>
       </c>
-      <c r="R34" s="420">
+      <c r="R34" s="419">
         <v>31.1</v>
       </c>
       <c r="S34" s="421">
         <v>27.9</v>
       </c>
       <c r="T34" s="422">
-        <v>20.6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35">
@@ -10760,7 +10984,7 @@
       <c r="C35" t="str">
         <v>920179</v>
       </c>
-      <c r="D35" s="435" t="str">
+      <c r="D35" s="438" t="str">
         <v>净买: 1651.86万</v>
       </c>
       <c r="E35">
@@ -10775,41 +10999,41 @@
       <c r="H35">
         <v>5.59</v>
       </c>
-      <c r="I35" s="436">
+      <c r="I35" s="439">
         <v>15.88</v>
       </c>
-      <c r="J35" s="433">
+      <c r="J35" s="440">
         <v>19.24</v>
       </c>
-      <c r="K35" s="437">
+      <c r="K35" s="442">
         <v>13.24</v>
       </c>
-      <c r="L35" s="438">
+      <c r="L35" s="432">
         <v>17.03</v>
       </c>
-      <c r="M35" s="439">
+      <c r="M35" s="433">
         <v>8.58</v>
       </c>
-      <c r="N35" s="434">
+      <c r="N35" s="430">
         <v>8.97</v>
       </c>
-      <c r="O35" s="440">
+      <c r="O35" s="434">
         <v>10.54</v>
       </c>
-      <c r="P35" s="431">
+      <c r="P35" s="435">
         <v>7.38</v>
       </c>
-      <c r="Q35" s="441">
+      <c r="Q35" s="431">
         <v>13.87</v>
       </c>
-      <c r="R35" s="442">
+      <c r="R35" s="436">
         <v>36.96</v>
       </c>
-      <c r="S35" s="430">
+      <c r="S35" s="437">
         <v>37.84</v>
       </c>
-      <c r="T35" s="432">
-        <v>27.6</v>
+      <c r="T35" s="441">
+        <v>22.4</v>
       </c>
     </row>
     <row r="36">
@@ -10822,7 +11046,7 @@
       <c r="C36" t="str">
         <v>603488</v>
       </c>
-      <c r="D36" s="453" t="str">
+      <c r="D36" s="455" t="str">
         <v>净买: 3230.20万</v>
       </c>
       <c r="E36">
@@ -10837,41 +11061,41 @@
       <c r="H36">
         <v>-0.94</v>
       </c>
-      <c r="I36" s="451">
+      <c r="I36" s="449">
         <v>11.07</v>
       </c>
-      <c r="J36" s="444">
+      <c r="J36" s="443">
         <v>9.74</v>
       </c>
-      <c r="K36" s="449">
+      <c r="K36" s="444">
         <v>7.38</v>
       </c>
       <c r="L36" s="445">
         <v>2.93</v>
       </c>
-      <c r="M36" s="454">
+      <c r="M36" s="446">
         <v>-3.12</v>
       </c>
-      <c r="N36" s="455">
+      <c r="N36" s="450">
         <v>-5.01</v>
       </c>
-      <c r="O36" s="446">
+      <c r="O36" s="451">
         <v>-4.92</v>
       </c>
-      <c r="P36" s="447">
+      <c r="P36" s="452">
         <v>-5.11</v>
       </c>
-      <c r="Q36" s="450">
+      <c r="Q36" s="447">
         <v>-5.3</v>
       </c>
-      <c r="R36" s="452">
+      <c r="R36" s="453">
         <v>-8.89</v>
       </c>
       <c r="S36" s="448">
         <v>0.19</v>
       </c>
-      <c r="T36" s="443">
-        <v>6.81</v>
+      <c r="T36" s="454">
+        <v>1.7</v>
       </c>
     </row>
     <row r="37">
@@ -10884,7 +11108,7 @@
       <c r="C37" t="str">
         <v>688115</v>
       </c>
-      <c r="D37" s="463" t="str">
+      <c r="D37" s="466" t="str">
         <v>净买: 534.48万</v>
       </c>
       <c r="E37">
@@ -10899,41 +11123,41 @@
       <c r="H37">
         <v>-0.49</v>
       </c>
-      <c r="I37" s="465">
+      <c r="I37" s="467">
         <v>-15.96</v>
       </c>
-      <c r="J37" s="464">
+      <c r="J37" s="459">
         <v>-24.38</v>
       </c>
-      <c r="K37" s="456">
+      <c r="K37" s="460">
         <v>-27.28</v>
       </c>
-      <c r="L37" s="466">
+      <c r="L37" s="461">
         <v>-26.26</v>
       </c>
-      <c r="M37" s="457">
+      <c r="M37" s="468">
         <v>-29.33</v>
       </c>
-      <c r="N37" s="467">
+      <c r="N37" s="456">
         <v>-33.51</v>
       </c>
-      <c r="O37" s="458">
+      <c r="O37" s="463">
         <v>-34.12</v>
       </c>
-      <c r="P37" s="459">
+      <c r="P37" s="464">
         <v>-35.51</v>
       </c>
-      <c r="Q37" s="460">
+      <c r="Q37" s="457">
         <v>-35.8</v>
       </c>
-      <c r="R37" s="461">
+      <c r="R37" s="458">
         <v>-33.88</v>
       </c>
       <c r="S37" s="462">
         <v>-35.38</v>
       </c>
-      <c r="T37" s="468">
-        <v>-36.14</v>
+      <c r="T37" s="465">
+        <v>-30.88</v>
       </c>
     </row>
     <row r="38">
@@ -10946,7 +11170,7 @@
       <c r="C38" t="str">
         <v>600671</v>
       </c>
-      <c r="D38" s="470" t="str">
+      <c r="D38" s="473" t="str">
         <v>净卖: -271.42万</v>
       </c>
       <c r="E38">
@@ -10961,41 +11185,41 @@
       <c r="H38">
         <v>-1.3</v>
       </c>
-      <c r="I38" s="471">
+      <c r="I38" s="477">
         <v>-8.5</v>
       </c>
-      <c r="J38" s="479">
+      <c r="J38" s="481">
         <v>-11.05</v>
       </c>
-      <c r="K38" s="472">
+      <c r="K38" s="469">
         <v>-13.41</v>
       </c>
-      <c r="L38" s="475">
+      <c r="L38" s="474">
         <v>-13.14</v>
       </c>
-      <c r="M38" s="480">
+      <c r="M38" s="475">
         <v>-15.18</v>
       </c>
-      <c r="N38" s="473">
+      <c r="N38" s="478">
         <v>-15.68</v>
       </c>
-      <c r="O38" s="476">
+      <c r="O38" s="470">
         <v>-13.05</v>
       </c>
-      <c r="P38" s="474">
+      <c r="P38" s="471">
         <v>-15.68</v>
       </c>
-      <c r="Q38" s="481">
+      <c r="Q38" s="479">
         <v>-14.45</v>
       </c>
-      <c r="R38" s="477">
+      <c r="R38" s="476">
         <v>-13.27</v>
       </c>
-      <c r="S38" s="469">
+      <c r="S38" s="472">
         <v>-11.23</v>
       </c>
-      <c r="T38" s="478">
-        <v>-12.14</v>
+      <c r="T38" s="480">
+        <v>-12.91</v>
       </c>
     </row>
     <row r="39">
@@ -11008,7 +11232,7 @@
       <c r="C39" t="str">
         <v>300017</v>
       </c>
-      <c r="D39" s="483" t="str">
+      <c r="D39" s="491" t="str">
         <v>净买: 3.37亿</v>
       </c>
       <c r="E39">
@@ -11023,41 +11247,41 @@
       <c r="H39">
         <v>15.07</v>
       </c>
-      <c r="I39" s="484">
+      <c r="I39" s="492">
         <v>0.06</v>
       </c>
-      <c r="J39" s="485">
+      <c r="J39" s="487">
         <v>7.83</v>
       </c>
-      <c r="K39" s="492">
+      <c r="K39" s="493">
         <v>6.29</v>
       </c>
-      <c r="L39" s="486">
+      <c r="L39" s="489">
         <v>8.34</v>
       </c>
-      <c r="M39" s="493">
+      <c r="M39" s="482">
         <v>23.94</v>
       </c>
-      <c r="N39" s="489">
+      <c r="N39" s="483">
         <v>7.32</v>
       </c>
-      <c r="O39" s="487">
+      <c r="O39" s="484">
         <v>15.34</v>
       </c>
-      <c r="P39" s="490">
+      <c r="P39" s="494">
         <v>15.08</v>
       </c>
       <c r="Q39" s="488">
         <v>21.31</v>
       </c>
-      <c r="R39" s="482">
+      <c r="R39" s="485">
         <v>19.9</v>
       </c>
-      <c r="S39" s="494">
+      <c r="S39" s="486">
         <v>31.26</v>
       </c>
-      <c r="T39" s="491">
-        <v>15.4</v>
+      <c r="T39" s="490">
+        <v>14.25</v>
       </c>
     </row>
     <row r="40">
@@ -11085,12 +11309,18 @@
       <c r="H40">
         <v>-3.8</v>
       </c>
-      <c r="I40" s="495">
+      <c r="I40" s="497">
         <v>24.74</v>
       </c>
-      <c r="J40" t="str"/>
-      <c r="K40" t="str"/>
-      <c r="L40" t="str"/>
+      <c r="J40" s="498">
+        <v>27.42</v>
+      </c>
+      <c r="K40" s="499">
+        <v>22.58</v>
+      </c>
+      <c r="L40" s="500">
+        <v>17.3</v>
+      </c>
       <c r="M40" t="str"/>
       <c r="N40" t="str"/>
       <c r="O40" t="str"/>
@@ -11098,107 +11328,105 @@
       <c r="Q40" t="str"/>
       <c r="R40" t="str"/>
       <c r="S40" t="str"/>
-      <c r="T40" t="str"/>
+      <c r="T40" s="495">
+        <v>17.3</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>纪录总数</v>
-      </c>
-      <c r="B41" t="str"/>
-      <c r="C41" t="str"/>
-      <c r="D41" t="str"/>
-      <c r="E41" t="str"/>
-      <c r="F41" t="str"/>
-      <c r="G41" t="str"/>
-      <c r="H41" t="str"/>
-      <c r="I41">
-        <v>39</v>
-      </c>
-      <c r="J41">
-        <v>38</v>
-      </c>
-      <c r="K41">
-        <v>38</v>
-      </c>
-      <c r="L41">
-        <v>38</v>
-      </c>
-      <c r="M41">
-        <v>38</v>
-      </c>
-      <c r="N41">
-        <v>38</v>
-      </c>
-      <c r="O41">
-        <v>38</v>
-      </c>
-      <c r="P41">
-        <v>38</v>
-      </c>
-      <c r="Q41">
-        <v>38</v>
-      </c>
-      <c r="R41">
-        <v>38</v>
-      </c>
-      <c r="S41">
-        <v>38</v>
-      </c>
-      <c r="T41">
-        <v>38</v>
+        <v>2026-04-21</v>
+      </c>
+      <c r="B41" t="str">
+        <v>实达集团</v>
+      </c>
+      <c r="C41" t="str">
+        <v>600734</v>
+      </c>
+      <c r="D41" s="501" t="str">
+        <v>净卖: -404.86万</v>
+      </c>
+      <c r="E41">
+        <v>2.76</v>
+      </c>
+      <c r="F41">
+        <v>2.76</v>
+      </c>
+      <c r="G41">
+        <v>2.76</v>
+      </c>
+      <c r="H41">
+        <v>-10.1</v>
+      </c>
+      <c r="I41" s="502">
+        <v>0</v>
+      </c>
+      <c r="J41" s="503">
+        <v>-4.35</v>
+      </c>
+      <c r="K41" s="504">
+        <v>-10.14</v>
+      </c>
+      <c r="L41" s="505">
+        <v>-13.41</v>
+      </c>
+      <c r="M41" t="str"/>
+      <c r="N41" t="str"/>
+      <c r="O41" t="str"/>
+      <c r="P41" t="str"/>
+      <c r="Q41" t="str"/>
+      <c r="R41" t="str"/>
+      <c r="S41" t="str"/>
+      <c r="T41" s="506">
+        <v>-13.41</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>上涨比例</v>
-      </c>
-      <c r="B42" t="str"/>
-      <c r="C42" t="str"/>
-      <c r="D42" t="str"/>
-      <c r="E42" t="str"/>
-      <c r="F42" t="str"/>
-      <c r="G42" t="str"/>
-      <c r="H42" t="str"/>
-      <c r="I42" s="506">
-        <v>56.41</v>
-      </c>
-      <c r="J42" s="500">
-        <v>60.53</v>
-      </c>
-      <c r="K42" s="503">
-        <v>55.26</v>
-      </c>
-      <c r="L42" s="497">
-        <v>52.63</v>
-      </c>
-      <c r="M42" s="504">
-        <v>50</v>
-      </c>
-      <c r="N42" s="501">
-        <v>44.74</v>
-      </c>
-      <c r="O42" s="507">
-        <v>44.74</v>
-      </c>
-      <c r="P42" s="505">
-        <v>50</v>
-      </c>
-      <c r="Q42" s="498">
-        <v>44.74</v>
-      </c>
-      <c r="R42" s="499">
-        <v>39.47</v>
-      </c>
-      <c r="S42" s="502">
-        <v>50</v>
-      </c>
-      <c r="T42" s="508">
-        <v>52.63</v>
+        <v>2026-04-23</v>
+      </c>
+      <c r="B42" t="str">
+        <v>兰石重装</v>
+      </c>
+      <c r="C42" t="str">
+        <v>603169</v>
+      </c>
+      <c r="D42" s="510" t="str">
+        <v>净卖: -374.20万</v>
+      </c>
+      <c r="E42">
+        <v>8.82</v>
+      </c>
+      <c r="F42">
+        <v>8.82</v>
+      </c>
+      <c r="G42">
+        <v>8.82</v>
+      </c>
+      <c r="H42">
+        <v>-10</v>
+      </c>
+      <c r="I42" s="507">
+        <v>0</v>
+      </c>
+      <c r="J42" s="508">
+        <v>-6.69</v>
+      </c>
+      <c r="K42" t="str"/>
+      <c r="L42" t="str"/>
+      <c r="M42" t="str"/>
+      <c r="N42" t="str"/>
+      <c r="O42" t="str"/>
+      <c r="P42" t="str"/>
+      <c r="Q42" t="str"/>
+      <c r="R42" t="str"/>
+      <c r="S42" t="str"/>
+      <c r="T42" s="509">
+        <v>-6.69</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>平均涨幅</v>
+        <v>纪录总数</v>
       </c>
       <c r="B43" t="str"/>
       <c r="C43" t="str"/>
@@ -11207,41 +11435,137 @@
       <c r="F43" t="str"/>
       <c r="G43" t="str"/>
       <c r="H43" t="str"/>
-      <c r="I43" s="511">
-        <v>3.63</v>
-      </c>
-      <c r="J43" s="517">
-        <v>2.73</v>
-      </c>
-      <c r="K43" s="519">
-        <v>0.67</v>
-      </c>
-      <c r="L43" s="512">
-        <v>-0.15</v>
-      </c>
-      <c r="M43" s="520">
+      <c r="I43">
+        <v>41</v>
+      </c>
+      <c r="J43">
+        <v>41</v>
+      </c>
+      <c r="K43">
+        <v>40</v>
+      </c>
+      <c r="L43">
+        <v>40</v>
+      </c>
+      <c r="M43">
+        <v>38</v>
+      </c>
+      <c r="N43">
+        <v>38</v>
+      </c>
+      <c r="O43">
+        <v>38</v>
+      </c>
+      <c r="P43">
+        <v>38</v>
+      </c>
+      <c r="Q43">
+        <v>38</v>
+      </c>
+      <c r="R43">
+        <v>38</v>
+      </c>
+      <c r="S43">
+        <v>38</v>
+      </c>
+      <c r="T43">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>上涨比例</v>
+      </c>
+      <c r="B44" t="str"/>
+      <c r="C44" t="str"/>
+      <c r="D44" t="str"/>
+      <c r="E44" t="str"/>
+      <c r="F44" t="str"/>
+      <c r="G44" t="str"/>
+      <c r="H44" t="str"/>
+      <c r="I44" s="513">
+        <v>53.66</v>
+      </c>
+      <c r="J44" s="522">
+        <v>58.54</v>
+      </c>
+      <c r="K44" s="511">
+        <v>55</v>
+      </c>
+      <c r="L44" s="514">
+        <v>52.5</v>
+      </c>
+      <c r="M44" s="515">
+        <v>50</v>
+      </c>
+      <c r="N44" s="519">
+        <v>44.74</v>
+      </c>
+      <c r="O44" s="516">
+        <v>44.74</v>
+      </c>
+      <c r="P44" s="517">
+        <v>50</v>
+      </c>
+      <c r="Q44" s="520">
+        <v>44.74</v>
+      </c>
+      <c r="R44" s="512">
+        <v>39.47</v>
+      </c>
+      <c r="S44" s="521">
+        <v>50</v>
+      </c>
+      <c r="T44" s="518">
+        <v>51.22</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>平均涨幅</v>
+      </c>
+      <c r="B45" t="str"/>
+      <c r="C45" t="str"/>
+      <c r="D45" t="str"/>
+      <c r="E45" t="str"/>
+      <c r="F45" t="str"/>
+      <c r="G45" t="str"/>
+      <c r="H45" t="str"/>
+      <c r="I45" s="529">
+        <v>3.45</v>
+      </c>
+      <c r="J45" s="530">
+        <v>2.93</v>
+      </c>
+      <c r="K45" s="527">
+        <v>0.95</v>
+      </c>
+      <c r="L45" s="524">
+        <v>-0.04</v>
+      </c>
+      <c r="M45" s="531">
         <v>-0.18</v>
       </c>
-      <c r="N43" s="513">
+      <c r="N45" s="525">
         <v>0.5</v>
       </c>
-      <c r="O43" s="514">
+      <c r="O45" s="534">
         <v>0.7</v>
       </c>
-      <c r="P43" s="509">
+      <c r="P45" s="532">
         <v>-0.65</v>
       </c>
-      <c r="Q43" s="515">
+      <c r="Q45" s="533">
         <v>-0.47</v>
       </c>
-      <c r="R43" s="518">
+      <c r="R45" s="526">
         <v>-0.13</v>
       </c>
-      <c r="S43" s="516">
+      <c r="S45" s="523">
         <v>0.43</v>
       </c>
-      <c r="T43" s="510">
-        <v>18.16</v>
+      <c r="T45" s="528">
+        <v>15.68</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/小鳄鱼/index.xlsx
+++ b/youzi/小鳄鱼/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="536">
+  <fills count="539">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,6 +39,54 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF7D4D8"/>
         <bgColor/>
       </patternFill>
@@ -51,12 +99,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC12937"/>
         <bgColor/>
       </patternFill>
@@ -69,6 +111,174 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C788"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FA94B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
@@ -81,55 +291,1123 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15664"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4E0BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3747"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A712F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A143"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBEE4C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9818B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,25 +1419,463 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2FA94B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6707C"/>
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1E2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F2E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9858F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF8F0"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -171,55 +1887,1105 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF76C788"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAEFDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CDD1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CD95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8790"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B96B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04D5B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -231,13 +2997,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -249,151 +3063,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15664"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -405,571 +3117,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB4E0BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A712F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
+        <fgColor rgb="FFE15260"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -981,631 +3189,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFDF6F7"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A143"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9818B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBEE4C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1E2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F2E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F2"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1617,462 +3225,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9858F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -2085,847 +3237,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CDD1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF54B96B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8790"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CD95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04D5B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BABF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFFAFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2937,312 +3255,33 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15260"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF7D3D7"/>
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="535">
+  <borders count="538">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -6992,7 +7031,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="535">
+  <cellXfs count="538">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -8594,6 +8633,15 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="534" fillId="535" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="535" fillId="536" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="536" fillId="537" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="537" fillId="538" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -8938,7 +8986,7 @@
       <c r="C2" t="str">
         <v>603881</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="1" t="str">
         <v>净买: 1.27亿</v>
       </c>
       <c r="E2">
@@ -8953,41 +9001,41 @@
       <c r="H2">
         <v>8.87</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="9">
         <v>1.04</v>
       </c>
       <c r="J2" s="2">
         <v>11.14</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="5">
         <v>0.03</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="11">
         <v>7.5</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="3">
         <v>8.74</v>
       </c>
-      <c r="N2" s="7">
+      <c r="N2" s="6">
         <v>19.61</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="7">
         <v>25.9</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="12">
         <v>21.45</v>
       </c>
-      <c r="Q2" s="12">
+      <c r="Q2" s="10">
         <v>15.56</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="13">
         <v>9.81</v>
       </c>
-      <c r="S2" s="13">
+      <c r="S2" s="8">
         <v>-0.74</v>
       </c>
-      <c r="T2" s="9">
-        <v>12.36</v>
+      <c r="T2" s="4">
+        <v>10.52</v>
       </c>
     </row>
     <row r="3">
@@ -9000,7 +9048,7 @@
       <c r="C3" t="str">
         <v>603881</v>
       </c>
-      <c r="D3" s="22" t="str">
+      <c r="D3" s="21" t="str">
         <v>净卖: -9150.08万</v>
       </c>
       <c r="E3">
@@ -9018,38 +9066,38 @@
       <c r="I3" s="23">
         <v>-5.7</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="24">
         <v>1.34</v>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="25">
         <v>2.51</v>
       </c>
-      <c r="L3" s="20">
+      <c r="L3" s="19">
         <v>12.77</v>
       </c>
-      <c r="M3" s="15">
+      <c r="M3" s="22">
         <v>18.69</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="26">
         <v>14.5</v>
       </c>
-      <c r="O3" s="17">
+      <c r="O3" s="15">
         <v>8.94</v>
       </c>
-      <c r="P3" s="21">
+      <c r="P3" s="20">
         <v>3.52</v>
       </c>
-      <c r="Q3" s="25">
+      <c r="Q3" s="16">
         <v>-6.42</v>
       </c>
-      <c r="R3" s="18">
+      <c r="R3" s="17">
         <v>-4.83</v>
       </c>
-      <c r="S3" s="26">
+      <c r="S3" s="14">
         <v>-3.18</v>
       </c>
-      <c r="T3" s="16">
-        <v>5.92</v>
+      <c r="T3" s="18">
+        <v>4.19</v>
       </c>
     </row>
     <row r="4">
@@ -9062,7 +9110,7 @@
       <c r="C4" t="str">
         <v>603511</v>
       </c>
-      <c r="D4" s="35" t="str">
+      <c r="D4" s="30" t="str">
         <v>净卖: -457.10万</v>
       </c>
       <c r="E4">
@@ -9077,41 +9125,41 @@
       <c r="H4">
         <v>0.22</v>
       </c>
-      <c r="I4" s="36">
+      <c r="I4" s="28">
         <v>9.8</v>
       </c>
-      <c r="J4" s="37">
+      <c r="J4" s="35">
         <v>13.04</v>
       </c>
-      <c r="K4" s="27">
+      <c r="K4" s="38">
         <v>17.87</v>
       </c>
-      <c r="L4" s="38">
+      <c r="L4" s="39">
         <v>11.31</v>
       </c>
-      <c r="M4" s="28">
+      <c r="M4" s="27">
         <v>12.39</v>
       </c>
-      <c r="N4" s="29">
+      <c r="N4" s="36">
         <v>15.13</v>
       </c>
-      <c r="O4" s="30">
+      <c r="O4" s="31">
         <v>7.93</v>
       </c>
       <c r="P4" s="32">
         <v>8.36</v>
       </c>
-      <c r="Q4" s="33">
+      <c r="Q4" s="29">
         <v>9.44</v>
       </c>
-      <c r="R4" s="34">
+      <c r="R4" s="33">
         <v>11.38</v>
       </c>
-      <c r="S4" s="31">
+      <c r="S4" s="34">
         <v>11.1</v>
       </c>
-      <c r="T4" s="39">
-        <v>3.24</v>
+      <c r="T4" s="37">
+        <v>5.91</v>
       </c>
     </row>
     <row r="5">
@@ -9124,7 +9172,7 @@
       <c r="C5" t="str">
         <v>002639</v>
       </c>
-      <c r="D5" s="43" t="str">
+      <c r="D5" s="41" t="str">
         <v>净买: 6286.22万</v>
       </c>
       <c r="E5">
@@ -9139,41 +9187,41 @@
       <c r="H5">
         <v>-1.66</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="42">
         <v>11.82</v>
       </c>
-      <c r="J5" s="48">
+      <c r="J5" s="43">
         <v>12.21</v>
       </c>
-      <c r="K5" s="45">
+      <c r="K5" s="49">
         <v>5.32</v>
       </c>
-      <c r="L5" s="46">
+      <c r="L5" s="52">
         <v>15.84</v>
       </c>
-      <c r="M5" s="47">
+      <c r="M5" s="44">
         <v>10.91</v>
       </c>
-      <c r="N5" s="52">
+      <c r="N5" s="40">
         <v>18.96</v>
       </c>
-      <c r="O5" s="40">
+      <c r="O5" s="45">
         <v>22.6</v>
       </c>
-      <c r="P5" s="41">
+      <c r="P5" s="46">
         <v>15.71</v>
       </c>
-      <c r="Q5" s="49">
+      <c r="Q5" s="47">
         <v>4.16</v>
       </c>
-      <c r="R5" s="42">
+      <c r="R5" s="50">
         <v>-6.23</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="48">
         <v>-8.18</v>
       </c>
       <c r="T5" s="51">
-        <v>134.29</v>
+        <v>134.68</v>
       </c>
     </row>
     <row r="6">
@@ -9186,7 +9234,7 @@
       <c r="C6" t="str">
         <v>603226</v>
       </c>
-      <c r="D6" s="61" t="str">
+      <c r="D6" s="63" t="str">
         <v>净卖: -590.66万</v>
       </c>
       <c r="E6">
@@ -9201,41 +9249,41 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="54">
+      <c r="I6" s="64">
         <v>10.05</v>
       </c>
-      <c r="J6" s="60">
+      <c r="J6" s="65">
         <v>4.08</v>
       </c>
-      <c r="K6" s="62">
+      <c r="K6" s="53">
         <v>4.08</v>
       </c>
-      <c r="L6" s="58">
+      <c r="L6" s="55">
         <v>4.08</v>
       </c>
-      <c r="M6" s="63">
+      <c r="M6" s="56">
         <v>7.06</v>
       </c>
-      <c r="N6" s="64">
+      <c r="N6" s="60">
         <v>5.02</v>
       </c>
-      <c r="O6" s="65">
+      <c r="O6" s="54">
         <v>-5.49</v>
       </c>
-      <c r="P6" s="55">
+      <c r="P6" s="57">
         <v>-14.6</v>
       </c>
-      <c r="Q6" s="59">
+      <c r="Q6" s="58">
         <v>-9.26</v>
       </c>
-      <c r="R6" s="56">
+      <c r="R6" s="61">
         <v>-5.81</v>
       </c>
-      <c r="S6" s="57">
+      <c r="S6" s="59">
         <v>3.61</v>
       </c>
-      <c r="T6" s="53">
-        <v>502.83</v>
+      <c r="T6" s="62">
+        <v>513.66</v>
       </c>
     </row>
     <row r="7">
@@ -9248,7 +9296,7 @@
       <c r="C7" t="str">
         <v>603011</v>
       </c>
-      <c r="D7" s="70" t="str">
+      <c r="D7" s="76" t="str">
         <v>净卖: -2450.00万</v>
       </c>
       <c r="E7">
@@ -9263,41 +9311,41 @@
       <c r="H7">
         <v>-0.78</v>
       </c>
-      <c r="I7" s="71">
+      <c r="I7" s="77">
         <v>10.9</v>
       </c>
-      <c r="J7" s="72">
+      <c r="J7" s="69">
         <v>5.29</v>
       </c>
-      <c r="K7" s="78">
+      <c r="K7" s="66">
         <v>-1.74</v>
       </c>
       <c r="L7" s="73">
         <v>-11.53</v>
       </c>
-      <c r="M7" s="74">
+      <c r="M7" s="70">
         <v>-20.38</v>
       </c>
-      <c r="N7" s="75">
+      <c r="N7" s="74">
         <v>-24.17</v>
       </c>
-      <c r="O7" s="66">
+      <c r="O7" s="71">
         <v>-21.8</v>
       </c>
-      <c r="P7" s="67">
+      <c r="P7" s="78">
         <v>-20.46</v>
       </c>
-      <c r="Q7" s="76">
+      <c r="Q7" s="67">
         <v>-12.48</v>
       </c>
-      <c r="R7" s="77">
+      <c r="R7" s="75">
         <v>-15.24</v>
       </c>
-      <c r="S7" s="68">
+      <c r="S7" s="72">
         <v>-22.12</v>
       </c>
-      <c r="T7" s="69">
-        <v>66.11</v>
+      <c r="T7" s="68">
+        <v>67.22</v>
       </c>
     </row>
     <row r="8">
@@ -9325,41 +9373,41 @@
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="79">
+      <c r="I8" s="88">
         <v>-6.8</v>
       </c>
-      <c r="J8" s="80">
+      <c r="J8" s="81">
         <v>-8.95</v>
       </c>
-      <c r="K8" s="81">
+      <c r="K8" s="89">
         <v>-12.73</v>
       </c>
-      <c r="L8" s="88">
+      <c r="L8" s="82">
         <v>-12.41</v>
       </c>
-      <c r="M8" s="82">
+      <c r="M8" s="83">
         <v>-9.82</v>
       </c>
-      <c r="N8" s="89">
+      <c r="N8" s="90">
         <v>-6.8</v>
       </c>
-      <c r="O8" s="90">
+      <c r="O8" s="91">
         <v>-1.29</v>
       </c>
-      <c r="P8" s="83">
+      <c r="P8" s="84">
         <v>-3.78</v>
       </c>
-      <c r="Q8" s="84">
+      <c r="Q8" s="85">
         <v>-6.36</v>
       </c>
-      <c r="R8" s="91">
+      <c r="R8" s="79">
         <v>-5.83</v>
       </c>
-      <c r="S8" s="85">
+      <c r="S8" s="86">
         <v>-8.2</v>
       </c>
-      <c r="T8" s="86">
-        <v>6.15</v>
+      <c r="T8" s="80">
+        <v>7.12</v>
       </c>
     </row>
     <row r="9">
@@ -9372,7 +9420,7 @@
       <c r="C9" t="str">
         <v>603488</v>
       </c>
-      <c r="D9" s="97" t="str">
+      <c r="D9" s="94" t="str">
         <v>净卖: -414.45万</v>
       </c>
       <c r="E9">
@@ -9387,41 +9435,41 @@
       <c r="H9">
         <v>-0.82</v>
       </c>
-      <c r="I9" s="98">
+      <c r="I9" s="103">
         <v>10.89</v>
       </c>
-      <c r="J9" s="102">
+      <c r="J9" s="98">
         <v>2.01</v>
       </c>
-      <c r="K9" s="92">
+      <c r="K9" s="104">
         <v>-0.12</v>
       </c>
-      <c r="L9" s="95">
+      <c r="L9" s="93">
         <v>-4.5</v>
       </c>
-      <c r="M9" s="103">
+      <c r="M9" s="99">
         <v>-4.73</v>
       </c>
-      <c r="N9" s="96">
+      <c r="N9" s="100">
         <v>-6.27</v>
       </c>
-      <c r="O9" s="99">
+      <c r="O9" s="95">
         <v>-5.56</v>
       </c>
-      <c r="P9" s="104">
+      <c r="P9" s="101">
         <v>-9.11</v>
       </c>
-      <c r="Q9" s="93">
+      <c r="Q9" s="92">
         <v>-8.52</v>
       </c>
-      <c r="R9" s="100">
+      <c r="R9" s="102">
         <v>-7.1</v>
       </c>
-      <c r="S9" s="94">
+      <c r="S9" s="96">
         <v>-7.81</v>
       </c>
-      <c r="T9" s="101">
-        <v>27.22</v>
+      <c r="T9" s="97">
+        <v>35.86</v>
       </c>
     </row>
     <row r="10">
@@ -9434,7 +9482,7 @@
       <c r="C10" t="str">
         <v>603429</v>
       </c>
-      <c r="D10" s="114" t="str">
+      <c r="D10" s="108" t="str">
         <v>净卖: -775.14万</v>
       </c>
       <c r="E10">
@@ -9449,41 +9497,41 @@
       <c r="H10">
         <v>-0.46</v>
       </c>
-      <c r="I10" s="115">
+      <c r="I10" s="109">
         <v>-9.58</v>
       </c>
-      <c r="J10" s="107">
+      <c r="J10" s="117">
         <v>-17.02</v>
       </c>
-      <c r="K10" s="116">
+      <c r="K10" s="110">
         <v>-15.53</v>
       </c>
-      <c r="L10" s="108">
+      <c r="L10" s="113">
         <v>-17.02</v>
       </c>
-      <c r="M10" s="117">
+      <c r="M10" s="105">
         <v>-25.3</v>
       </c>
-      <c r="N10" s="109">
+      <c r="N10" s="111">
         <v>-26.33</v>
       </c>
-      <c r="O10" s="111">
+      <c r="O10" s="115">
         <v>-22.79</v>
       </c>
-      <c r="P10" s="112">
+      <c r="P10" s="106">
         <v>-22.7</v>
       </c>
-      <c r="Q10" s="113">
+      <c r="Q10" s="112">
         <v>-24.47</v>
       </c>
-      <c r="R10" s="105">
+      <c r="R10" s="114">
         <v>-23.91</v>
       </c>
-      <c r="S10" s="106">
+      <c r="S10" s="107">
         <v>-24.74</v>
       </c>
-      <c r="T10" s="110">
-        <v>-7.44</v>
+      <c r="T10" s="116">
+        <v>-9.12</v>
       </c>
     </row>
     <row r="11">
@@ -9496,7 +9544,7 @@
       <c r="C11" t="str">
         <v>600735</v>
       </c>
-      <c r="D11" s="130" t="str">
+      <c r="D11" s="127" t="str">
         <v>净买: 1079.52万</v>
       </c>
       <c r="E11">
@@ -9511,41 +9559,41 @@
       <c r="H11">
         <v>-5.01</v>
       </c>
-      <c r="I11" s="124">
+      <c r="I11" s="122">
         <v>5.4</v>
       </c>
-      <c r="J11" s="121">
+      <c r="J11" s="128">
         <v>4.08</v>
       </c>
-      <c r="K11" s="118">
+      <c r="K11" s="129">
         <v>1.32</v>
       </c>
-      <c r="L11" s="125">
+      <c r="L11" s="130">
         <v>2.37</v>
       </c>
-      <c r="M11" s="129">
+      <c r="M11" s="123">
         <v>7.64</v>
       </c>
-      <c r="N11" s="126">
+      <c r="N11" s="125">
         <v>6.19</v>
       </c>
-      <c r="O11" s="127">
+      <c r="O11" s="118">
         <v>3.43</v>
       </c>
-      <c r="P11" s="119">
+      <c r="P11" s="124">
         <v>8.7</v>
       </c>
-      <c r="Q11" s="128">
+      <c r="Q11" s="119">
         <v>10.28</v>
       </c>
-      <c r="R11" s="120">
+      <c r="R11" s="126">
         <v>6.59</v>
       </c>
-      <c r="S11" s="122">
+      <c r="S11" s="120">
         <v>3.43</v>
       </c>
-      <c r="T11" s="123">
-        <v>-11.33</v>
+      <c r="T11" s="121">
+        <v>-6.85</v>
       </c>
     </row>
     <row r="12">
@@ -9558,7 +9606,7 @@
       <c r="C12" t="str">
         <v>603429</v>
       </c>
-      <c r="D12" s="143" t="str">
+      <c r="D12" s="138" t="str">
         <v>净买: 2015.22万</v>
       </c>
       <c r="E12">
@@ -9573,41 +9621,41 @@
       <c r="H12">
         <v>-4.22</v>
       </c>
-      <c r="I12" s="131">
+      <c r="I12" s="133">
         <v>-4.19</v>
       </c>
-      <c r="J12" s="132">
+      <c r="J12" s="141">
         <v>-2.47</v>
       </c>
-      <c r="K12" s="137">
+      <c r="K12" s="134">
         <v>-4.19</v>
       </c>
-      <c r="L12" s="133">
+      <c r="L12" s="142">
         <v>-13.75</v>
       </c>
-      <c r="M12" s="135">
+      <c r="M12" s="136">
         <v>-14.93</v>
       </c>
-      <c r="N12" s="138">
+      <c r="N12" s="137">
         <v>-10.85</v>
       </c>
-      <c r="O12" s="139">
+      <c r="O12" s="135">
         <v>-10.74</v>
       </c>
-      <c r="P12" s="134">
+      <c r="P12" s="139">
         <v>-12.78</v>
       </c>
-      <c r="Q12" s="140">
+      <c r="Q12" s="143">
         <v>-12.14</v>
       </c>
-      <c r="R12" s="141">
+      <c r="R12" s="140">
         <v>-13.1</v>
       </c>
-      <c r="S12" s="136">
+      <c r="S12" s="131">
         <v>-14.18</v>
       </c>
-      <c r="T12" s="142">
-        <v>6.87</v>
+      <c r="T12" s="132">
+        <v>4.94</v>
       </c>
     </row>
     <row r="13">
@@ -9635,41 +9683,41 @@
       <c r="H13">
         <v>-0.45</v>
       </c>
-      <c r="I13" s="150">
+      <c r="I13" s="151">
         <v>-9.57</v>
       </c>
-      <c r="J13" s="153">
+      <c r="J13" s="155">
         <v>-10.81</v>
       </c>
-      <c r="K13" s="154">
+      <c r="K13" s="149">
         <v>-6.53</v>
       </c>
-      <c r="L13" s="151">
+      <c r="L13" s="147">
         <v>-6.42</v>
       </c>
-      <c r="M13" s="145">
+      <c r="M13" s="148">
         <v>-8.56</v>
       </c>
-      <c r="N13" s="155">
+      <c r="N13" s="156">
         <v>-7.88</v>
       </c>
-      <c r="O13" s="156">
+      <c r="O13" s="144">
         <v>-8.9</v>
       </c>
-      <c r="P13" s="147">
+      <c r="P13" s="145">
         <v>-10.02</v>
       </c>
-      <c r="Q13" s="148">
+      <c r="Q13" s="152">
         <v>-8.78</v>
       </c>
-      <c r="R13" s="149">
+      <c r="R13" s="153">
         <v>-8.78</v>
       </c>
-      <c r="S13" s="144">
+      <c r="S13" s="154">
         <v>-5.86</v>
       </c>
-      <c r="T13" s="152">
-        <v>12.05</v>
+      <c r="T13" s="150">
+        <v>10.02</v>
       </c>
     </row>
     <row r="14">
@@ -9682,7 +9730,7 @@
       <c r="C14" t="str">
         <v>600735</v>
       </c>
-      <c r="D14" s="168" t="str">
+      <c r="D14" s="158" t="str">
         <v>净买: 450.48万</v>
       </c>
       <c r="E14">
@@ -9700,38 +9748,38 @@
       <c r="I14" s="169">
         <v>0</v>
       </c>
-      <c r="J14" s="164">
+      <c r="J14" s="162">
         <v>-0.12</v>
       </c>
-      <c r="K14" s="157">
+      <c r="K14" s="159">
         <v>0.6</v>
       </c>
-      <c r="L14" s="165">
+      <c r="L14" s="160">
         <v>2.04</v>
       </c>
-      <c r="M14" s="166">
+      <c r="M14" s="164">
         <v>-0.96</v>
       </c>
-      <c r="N14" s="161">
+      <c r="N14" s="165">
         <v>-3.72</v>
       </c>
-      <c r="O14" s="158">
+      <c r="O14" s="163">
         <v>2.4</v>
       </c>
-      <c r="P14" s="162">
+      <c r="P14" s="166">
         <v>2.88</v>
       </c>
-      <c r="Q14" s="159">
+      <c r="Q14" s="167">
         <v>3.48</v>
       </c>
-      <c r="R14" s="163">
+      <c r="R14" s="157">
         <v>2.76</v>
       </c>
-      <c r="S14" s="167">
+      <c r="S14" s="168">
         <v>4.32</v>
       </c>
-      <c r="T14" s="160">
-        <v>-19.21</v>
+      <c r="T14" s="161">
+        <v>-15.13</v>
       </c>
     </row>
     <row r="15">
@@ -9744,7 +9792,7 @@
       <c r="C15" t="str">
         <v>605198</v>
       </c>
-      <c r="D15" s="170" t="str">
+      <c r="D15" s="181" t="str">
         <v>净买: 424.10万</v>
       </c>
       <c r="E15">
@@ -9759,28 +9807,28 @@
       <c r="H15">
         <v>-3.44</v>
       </c>
-      <c r="I15" s="171">
+      <c r="I15" s="172">
         <v>-6.79</v>
       </c>
-      <c r="J15" s="178">
+      <c r="J15" s="182">
         <v>-11.34</v>
       </c>
-      <c r="K15" s="179">
+      <c r="K15" s="170">
         <v>-12.86</v>
       </c>
-      <c r="L15" s="181">
+      <c r="L15" s="173">
         <v>-11.52</v>
       </c>
-      <c r="M15" s="175">
+      <c r="M15" s="179">
         <v>-11.25</v>
       </c>
-      <c r="N15" s="172">
+      <c r="N15" s="175">
         <v>-11.47</v>
       </c>
-      <c r="O15" s="182">
+      <c r="O15" s="174">
         <v>-11.43</v>
       </c>
-      <c r="P15" s="173">
+      <c r="P15" s="180">
         <v>-11.41</v>
       </c>
       <c r="Q15" s="176">
@@ -9789,11 +9837,11 @@
       <c r="R15" s="177">
         <v>-11.65</v>
       </c>
-      <c r="S15" s="180">
+      <c r="S15" s="178">
         <v>-11.96</v>
       </c>
-      <c r="T15" s="174">
-        <v>1.74</v>
+      <c r="T15" s="171">
+        <v>1.32</v>
       </c>
     </row>
     <row r="16">
@@ -9806,7 +9854,7 @@
       <c r="C16" t="str">
         <v>600208</v>
       </c>
-      <c r="D16" s="190" t="str">
+      <c r="D16" s="192" t="str">
         <v>净卖: -1100.93万</v>
       </c>
       <c r="E16">
@@ -9821,28 +9869,28 @@
       <c r="H16">
         <v>9.93</v>
       </c>
-      <c r="I16" s="191">
+      <c r="I16" s="187">
         <v>0</v>
       </c>
-      <c r="J16" s="185">
+      <c r="J16" s="189">
         <v>10.04</v>
       </c>
-      <c r="K16" s="184">
+      <c r="K16" s="183">
         <v>7.23</v>
       </c>
-      <c r="L16" s="187">
+      <c r="L16" s="184">
         <v>11.24</v>
       </c>
-      <c r="M16" s="192">
+      <c r="M16" s="193">
         <v>0.2</v>
       </c>
-      <c r="N16" s="193">
+      <c r="N16" s="190">
         <v>-4.42</v>
       </c>
-      <c r="O16" s="194">
+      <c r="O16" s="185">
         <v>-2.81</v>
       </c>
-      <c r="P16" s="188">
+      <c r="P16" s="194">
         <v>3.41</v>
       </c>
       <c r="Q16" s="195">
@@ -9851,11 +9899,11 @@
       <c r="R16" s="186">
         <v>-5.82</v>
       </c>
-      <c r="S16" s="189">
+      <c r="S16" s="191">
         <v>-3.21</v>
       </c>
-      <c r="T16" s="183">
-        <v>-5.02</v>
+      <c r="T16" s="188">
+        <v>-14.46</v>
       </c>
     </row>
     <row r="17">
@@ -9868,7 +9916,7 @@
       <c r="C17" t="str">
         <v>600590</v>
       </c>
-      <c r="D17" s="208" t="str">
+      <c r="D17" s="204" t="str">
         <v>净买: 1371.16万</v>
       </c>
       <c r="E17">
@@ -9883,41 +9931,41 @@
       <c r="H17">
         <v>9.98</v>
       </c>
-      <c r="I17" s="196">
+      <c r="I17" s="205">
         <v>0</v>
       </c>
-      <c r="J17" s="205">
+      <c r="J17" s="207">
         <v>-3.03</v>
       </c>
-      <c r="K17" s="204">
+      <c r="K17" s="208">
         <v>-5.43</v>
       </c>
-      <c r="L17" s="197">
+      <c r="L17" s="206">
         <v>-8.3</v>
       </c>
-      <c r="M17" s="198">
+      <c r="M17" s="200">
         <v>-9.54</v>
       </c>
-      <c r="N17" s="199">
+      <c r="N17" s="197">
         <v>-11.64</v>
       </c>
-      <c r="O17" s="200">
+      <c r="O17" s="198">
         <v>-10.4</v>
       </c>
-      <c r="P17" s="206">
+      <c r="P17" s="201">
         <v>-12.57</v>
       </c>
       <c r="Q17" s="202">
         <v>-13.03</v>
       </c>
-      <c r="R17" s="201">
+      <c r="R17" s="199">
         <v>-14.82</v>
       </c>
-      <c r="S17" s="207">
+      <c r="S17" s="203">
         <v>-21.26</v>
       </c>
-      <c r="T17" s="203">
-        <v>32.35</v>
+      <c r="T17" s="196">
+        <v>27.08</v>
       </c>
     </row>
     <row r="18">
@@ -9930,7 +9978,7 @@
       <c r="C18" t="str">
         <v>000063</v>
       </c>
-      <c r="D18" s="214" t="str">
+      <c r="D18" s="217" t="str">
         <v>净买: 5.93亿</v>
       </c>
       <c r="E18">
@@ -9945,41 +9993,41 @@
       <c r="H18">
         <v>2.21</v>
       </c>
-      <c r="I18" s="215">
+      <c r="I18" s="218">
         <v>7.01</v>
       </c>
-      <c r="J18" s="219">
+      <c r="J18" s="209">
         <v>5.38</v>
       </c>
-      <c r="K18" s="220">
+      <c r="K18" s="213">
         <v>3.49</v>
       </c>
-      <c r="L18" s="221">
+      <c r="L18" s="210">
         <v>1.38</v>
       </c>
-      <c r="M18" s="217">
+      <c r="M18" s="214">
         <v>9.01</v>
       </c>
-      <c r="N18" s="211">
+      <c r="N18" s="221">
         <v>4.46</v>
       </c>
-      <c r="O18" s="216">
+      <c r="O18" s="211">
         <v>10.34</v>
       </c>
-      <c r="P18" s="209">
+      <c r="P18" s="215">
         <v>3.06</v>
       </c>
       <c r="Q18" s="212">
         <v>1.01</v>
       </c>
-      <c r="R18" s="210">
+      <c r="R18" s="219">
         <v>-6.11</v>
       </c>
-      <c r="S18" s="213">
+      <c r="S18" s="216">
         <v>-3.86</v>
       </c>
-      <c r="T18" s="218">
-        <v>-16.37</v>
+      <c r="T18" s="220">
+        <v>-14.34</v>
       </c>
     </row>
     <row r="19">
@@ -9992,7 +10040,7 @@
       <c r="C19" t="str">
         <v>000061</v>
       </c>
-      <c r="D19" s="231" t="str">
+      <c r="D19" s="224" t="str">
         <v>净买: 2178.30万</v>
       </c>
       <c r="E19">
@@ -10007,41 +10055,41 @@
       <c r="H19">
         <v>5.09</v>
       </c>
-      <c r="I19" s="224">
+      <c r="I19" s="229">
         <v>4.72</v>
       </c>
-      <c r="J19" s="234">
+      <c r="J19" s="230">
         <v>8.94</v>
       </c>
-      <c r="K19" s="230">
+      <c r="K19" s="231">
         <v>3.73</v>
       </c>
-      <c r="L19" s="222">
+      <c r="L19" s="234">
         <v>-1.99</v>
       </c>
-      <c r="M19" s="232">
+      <c r="M19" s="222">
         <v>-1.49</v>
       </c>
-      <c r="N19" s="223">
+      <c r="N19" s="232">
         <v>-0.25</v>
       </c>
-      <c r="O19" s="225">
+      <c r="O19" s="233">
         <v>-0.12</v>
       </c>
-      <c r="P19" s="226">
+      <c r="P19" s="225">
         <v>3.11</v>
       </c>
-      <c r="Q19" s="227">
+      <c r="Q19" s="223">
         <v>4.84</v>
       </c>
-      <c r="R19" s="233">
+      <c r="R19" s="226">
         <v>15.28</v>
       </c>
-      <c r="S19" s="228">
+      <c r="S19" s="227">
         <v>14.53</v>
       </c>
-      <c r="T19" s="229">
-        <v>-7.7</v>
+      <c r="T19" s="228">
+        <v>-8.07</v>
       </c>
     </row>
     <row r="20">
@@ -10054,7 +10102,7 @@
       <c r="C20" t="str">
         <v>837174</v>
       </c>
-      <c r="D20" s="239" t="str">
+      <c r="D20" s="237" t="str">
         <v>净买: 1878.87万</v>
       </c>
       <c r="E20">
@@ -10069,40 +10117,40 @@
       <c r="H20">
         <v>-0.85</v>
       </c>
-      <c r="I20" s="240">
+      <c r="I20" s="246">
         <v>31.1</v>
       </c>
-      <c r="J20" s="246">
+      <c r="J20" s="245">
         <v>25.62</v>
       </c>
-      <c r="K20" s="236">
+      <c r="K20" s="247">
         <v>0.1</v>
       </c>
-      <c r="L20" s="237">
+      <c r="L20" s="238">
         <v>-14.6</v>
       </c>
-      <c r="M20" s="241">
+      <c r="M20" s="235">
         <v>-15.25</v>
       </c>
-      <c r="N20" s="247">
+      <c r="N20" s="239">
         <v>-17.98</v>
       </c>
-      <c r="O20" s="244">
+      <c r="O20" s="240">
         <v>-19.46</v>
       </c>
-      <c r="P20" s="238">
+      <c r="P20" s="243">
         <v>-18.77</v>
       </c>
-      <c r="Q20" s="245">
+      <c r="Q20" s="241">
         <v>-23.13</v>
       </c>
-      <c r="R20" s="242">
+      <c r="R20" s="236">
         <v>-22.25</v>
       </c>
-      <c r="S20" s="243">
+      <c r="S20" s="244">
         <v>-22.58</v>
       </c>
-      <c r="T20" s="235">
+      <c r="T20" s="242">
         <v>-29.79</v>
       </c>
     </row>
@@ -10116,7 +10164,7 @@
       <c r="C21" t="str">
         <v>002050</v>
       </c>
-      <c r="D21" s="253" t="str">
+      <c r="D21" s="251" t="str">
         <v>净买: 2.36亿</v>
       </c>
       <c r="E21">
@@ -10131,41 +10179,41 @@
       <c r="H21">
         <v>2.54</v>
       </c>
-      <c r="I21" s="259">
+      <c r="I21" s="252">
         <v>7.27</v>
       </c>
-      <c r="J21" s="257">
+      <c r="J21" s="253">
         <v>8.13</v>
       </c>
-      <c r="K21" s="251">
+      <c r="K21" s="256">
         <v>6.42</v>
       </c>
       <c r="L21" s="254">
         <v>10.42</v>
       </c>
-      <c r="M21" s="255">
+      <c r="M21" s="248">
         <v>9.59</v>
       </c>
-      <c r="N21" s="260">
+      <c r="N21" s="255">
         <v>13.28</v>
       </c>
-      <c r="O21" s="258">
+      <c r="O21" s="249">
         <v>24.62</v>
       </c>
-      <c r="P21" s="248">
+      <c r="P21" s="257">
         <v>33.1</v>
       </c>
-      <c r="Q21" s="252">
+      <c r="Q21" s="258">
         <v>44.7</v>
       </c>
-      <c r="R21" s="249">
+      <c r="R21" s="250">
         <v>32.31</v>
       </c>
-      <c r="S21" s="250">
+      <c r="S21" s="259">
         <v>36.5</v>
       </c>
-      <c r="T21" s="256">
-        <v>42.76</v>
+      <c r="T21" s="260">
+        <v>45.84</v>
       </c>
     </row>
     <row r="22">
@@ -10178,7 +10226,7 @@
       <c r="C22" t="str">
         <v>603429</v>
       </c>
-      <c r="D22" s="264" t="str">
+      <c r="D22" s="263" t="str">
         <v>净买: 1423.30万</v>
       </c>
       <c r="E22">
@@ -10193,41 +10241,41 @@
       <c r="H22">
         <v>-0.38</v>
       </c>
-      <c r="I22" s="271">
+      <c r="I22" s="269">
         <v>-6.68</v>
       </c>
-      <c r="J22" s="268">
+      <c r="J22" s="266">
         <v>-8.22</v>
       </c>
       <c r="K22" s="272">
         <v>-10.52</v>
       </c>
-      <c r="L22" s="269">
+      <c r="L22" s="270">
         <v>-8.76</v>
       </c>
       <c r="M22" s="273">
         <v>-10.37</v>
       </c>
-      <c r="N22" s="270">
+      <c r="N22" s="261">
         <v>-10.68</v>
       </c>
-      <c r="O22" s="262">
+      <c r="O22" s="267">
         <v>-12.75</v>
       </c>
-      <c r="P22" s="265">
+      <c r="P22" s="262">
         <v>-9.75</v>
       </c>
-      <c r="Q22" s="261">
+      <c r="Q22" s="264">
         <v>-0.69</v>
       </c>
-      <c r="R22" s="266">
+      <c r="R22" s="271">
         <v>-0.92</v>
       </c>
-      <c r="S22" s="263">
+      <c r="S22" s="268">
         <v>2</v>
       </c>
-      <c r="T22" s="267">
-        <v>-23.58</v>
+      <c r="T22" s="265">
+        <v>-24.96</v>
       </c>
     </row>
     <row r="23">
@@ -10240,7 +10288,7 @@
       <c r="C23" t="str">
         <v>002475</v>
       </c>
-      <c r="D23" s="286" t="str">
+      <c r="D23" s="278" t="str">
         <v>净买: 2.00亿</v>
       </c>
       <c r="E23">
@@ -10255,41 +10303,41 @@
       <c r="H23">
         <v>-1.85</v>
       </c>
-      <c r="I23" s="280">
+      <c r="I23" s="279">
         <v>12.08</v>
       </c>
-      <c r="J23" s="274">
+      <c r="J23" s="285">
         <v>11.67</v>
       </c>
-      <c r="K23" s="275">
+      <c r="K23" s="280">
         <v>11.74</v>
       </c>
-      <c r="L23" s="283">
+      <c r="L23" s="282">
         <v>11</v>
       </c>
-      <c r="M23" s="276">
+      <c r="M23" s="286">
         <v>10.19</v>
       </c>
-      <c r="N23" s="281">
+      <c r="N23" s="283">
         <v>12.52</v>
       </c>
-      <c r="O23" s="277">
+      <c r="O23" s="284">
         <v>17.39</v>
       </c>
-      <c r="P23" s="282">
+      <c r="P23" s="274">
         <v>29.13</v>
       </c>
-      <c r="Q23" s="278">
+      <c r="Q23" s="275">
         <v>39.19</v>
       </c>
-      <c r="R23" s="279">
+      <c r="R23" s="276">
         <v>48.73</v>
       </c>
-      <c r="S23" s="284">
+      <c r="S23" s="281">
         <v>45.64</v>
       </c>
-      <c r="T23" s="285">
-        <v>39.83</v>
+      <c r="T23" s="277">
+        <v>52.48</v>
       </c>
     </row>
     <row r="24">
@@ -10302,7 +10350,7 @@
       <c r="C24" t="str">
         <v>002146</v>
       </c>
-      <c r="D24" s="287" t="str">
+      <c r="D24" s="299" t="str">
         <v>净买: 2134.01万</v>
       </c>
       <c r="E24">
@@ -10317,41 +10365,41 @@
       <c r="H24">
         <v>0.5</v>
       </c>
-      <c r="I24" s="294">
+      <c r="I24" s="296">
         <v>-9</v>
       </c>
-      <c r="J24" s="288">
+      <c r="J24" s="287">
         <v>-11</v>
       </c>
-      <c r="K24" s="289">
+      <c r="K24" s="297">
         <v>-14.5</v>
       </c>
-      <c r="L24" s="290">
+      <c r="L24" s="291">
         <v>-17.5</v>
       </c>
-      <c r="M24" s="291">
+      <c r="M24" s="294">
         <v>-16.5</v>
       </c>
-      <c r="N24" s="297">
+      <c r="N24" s="298">
         <v>-19</v>
       </c>
       <c r="O24" s="292">
         <v>-20</v>
       </c>
-      <c r="P24" s="298">
+      <c r="P24" s="293">
         <v>-19.5</v>
       </c>
-      <c r="Q24" s="293">
+      <c r="Q24" s="288">
         <v>-19.5</v>
       </c>
-      <c r="R24" s="295">
+      <c r="R24" s="289">
         <v>-19</v>
       </c>
-      <c r="S24" s="296">
+      <c r="S24" s="290">
         <v>-18.5</v>
       </c>
-      <c r="T24" s="299">
-        <v>-37.5</v>
+      <c r="T24" s="295">
+        <v>-36.5</v>
       </c>
     </row>
     <row r="25">
@@ -10364,7 +10412,7 @@
       <c r="C25" t="str">
         <v>002743</v>
       </c>
-      <c r="D25" s="307" t="str">
+      <c r="D25" s="308" t="str">
         <v>净卖: -133.27万</v>
       </c>
       <c r="E25">
@@ -10379,41 +10427,41 @@
       <c r="H25">
         <v>-9.98</v>
       </c>
-      <c r="I25" s="308">
+      <c r="I25" s="309">
         <v>0</v>
       </c>
-      <c r="J25" s="311">
+      <c r="J25" s="305">
         <v>-5.83</v>
       </c>
-      <c r="K25" s="312">
+      <c r="K25" s="301">
         <v>-3.38</v>
       </c>
-      <c r="L25" s="309">
+      <c r="L25" s="302">
         <v>0.75</v>
       </c>
-      <c r="M25" s="300">
+      <c r="M25" s="310">
         <v>1.88</v>
       </c>
-      <c r="N25" s="310">
+      <c r="N25" s="303">
         <v>3.01</v>
       </c>
-      <c r="O25" s="301">
+      <c r="O25" s="304">
         <v>3.95</v>
       </c>
-      <c r="P25" s="305">
+      <c r="P25" s="306">
         <v>0.75</v>
       </c>
-      <c r="Q25" s="303">
+      <c r="Q25" s="311">
         <v>-0.19</v>
       </c>
-      <c r="R25" s="302">
+      <c r="R25" s="300">
         <v>1.5</v>
       </c>
-      <c r="S25" s="306">
+      <c r="S25" s="312">
         <v>5.83</v>
       </c>
-      <c r="T25" s="304">
-        <v>-2.44</v>
+      <c r="T25" s="307">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="26">
@@ -10426,7 +10474,7 @@
       <c r="C26" t="str">
         <v>601011</v>
       </c>
-      <c r="D26" s="322" t="str">
+      <c r="D26" s="320" t="str">
         <v>净卖: -479.33万</v>
       </c>
       <c r="E26">
@@ -10441,41 +10489,41 @@
       <c r="H26">
         <v>3.37</v>
       </c>
-      <c r="I26" s="323">
+      <c r="I26" s="316">
         <v>6.51</v>
       </c>
-      <c r="J26" s="313">
+      <c r="J26" s="321">
         <v>17.26</v>
       </c>
-      <c r="K26" s="321">
+      <c r="K26" s="322">
         <v>28.99</v>
       </c>
-      <c r="L26" s="318">
+      <c r="L26" s="325">
         <v>16.94</v>
       </c>
-      <c r="M26" s="314">
+      <c r="M26" s="313">
         <v>28.66</v>
       </c>
-      <c r="N26" s="319">
+      <c r="N26" s="323">
         <v>30.29</v>
       </c>
-      <c r="O26" s="315">
+      <c r="O26" s="317">
         <v>43.32</v>
       </c>
-      <c r="P26" s="324">
+      <c r="P26" s="314">
         <v>33.55</v>
       </c>
-      <c r="Q26" s="316">
+      <c r="Q26" s="318">
         <v>25.08</v>
       </c>
-      <c r="R26" s="325">
+      <c r="R26" s="324">
         <v>29.97</v>
       </c>
-      <c r="S26" s="317">
+      <c r="S26" s="315">
         <v>21.5</v>
       </c>
-      <c r="T26" s="320">
-        <v>-1.3</v>
+      <c r="T26" s="319">
+        <v>0.98</v>
       </c>
     </row>
     <row r="27">
@@ -10488,7 +10536,7 @@
       <c r="C27" t="str">
         <v>601011</v>
       </c>
-      <c r="D27" s="333" t="str">
+      <c r="D27" s="331" t="str">
         <v>净卖: -659.33万</v>
       </c>
       <c r="E27">
@@ -10503,41 +10551,41 @@
       <c r="H27">
         <v>10.09</v>
       </c>
-      <c r="I27" s="334">
+      <c r="I27" s="336">
         <v>0</v>
       </c>
-      <c r="J27" s="326">
+      <c r="J27" s="337">
         <v>10</v>
       </c>
-      <c r="K27" s="327">
+      <c r="K27" s="332">
         <v>-0.28</v>
       </c>
-      <c r="L27" s="335">
+      <c r="L27" s="327">
         <v>9.72</v>
       </c>
-      <c r="M27" s="330">
+      <c r="M27" s="334">
         <v>11.11</v>
       </c>
-      <c r="N27" s="336">
+      <c r="N27" s="328">
         <v>22.22</v>
       </c>
-      <c r="O27" s="331">
+      <c r="O27" s="338">
         <v>13.89</v>
       </c>
-      <c r="P27" s="338">
+      <c r="P27" s="329">
         <v>6.67</v>
       </c>
-      <c r="Q27" s="337">
+      <c r="Q27" s="326">
         <v>10.83</v>
       </c>
-      <c r="R27" s="328">
+      <c r="R27" s="330">
         <v>3.61</v>
       </c>
-      <c r="S27" s="329">
+      <c r="S27" s="335">
         <v>4.17</v>
       </c>
-      <c r="T27" s="332">
-        <v>-15.83</v>
+      <c r="T27" s="333">
+        <v>-13.89</v>
       </c>
     </row>
     <row r="28">
@@ -10550,7 +10598,7 @@
       <c r="C28" t="str">
         <v>920765</v>
       </c>
-      <c r="D28" s="346" t="str">
+      <c r="D28" s="345" t="str">
         <v>净卖: -291.63万</v>
       </c>
       <c r="E28">
@@ -10565,41 +10613,41 @@
       <c r="H28">
         <v>-0.26</v>
       </c>
-      <c r="I28" s="348">
+      <c r="I28" s="346">
         <v>21.66</v>
       </c>
-      <c r="J28" s="350">
+      <c r="J28" s="342">
         <v>16.41</v>
       </c>
-      <c r="K28" s="342">
+      <c r="K28" s="339">
         <v>26.65</v>
       </c>
-      <c r="L28" s="351">
+      <c r="L28" s="340">
         <v>21.66</v>
       </c>
-      <c r="M28" s="349">
+      <c r="M28" s="343">
         <v>16.11</v>
       </c>
-      <c r="N28" s="339">
+      <c r="N28" s="349">
         <v>14.53</v>
       </c>
-      <c r="O28" s="340">
+      <c r="O28" s="347">
         <v>11.07</v>
       </c>
-      <c r="P28" s="343">
+      <c r="P28" s="344">
         <v>10.15</v>
       </c>
-      <c r="Q28" s="344">
+      <c r="Q28" s="350">
         <v>9.63</v>
       </c>
-      <c r="R28" s="341">
+      <c r="R28" s="351">
         <v>8.67</v>
       </c>
-      <c r="S28" s="345">
+      <c r="S28" s="348">
         <v>9.1</v>
       </c>
-      <c r="T28" s="347">
-        <v>-37.55</v>
+      <c r="T28" s="341">
+        <v>-40.39</v>
       </c>
     </row>
     <row r="29">
@@ -10612,7 +10660,7 @@
       <c r="C29" t="str">
         <v>688233</v>
       </c>
-      <c r="D29" s="359" t="str">
+      <c r="D29" s="356" t="str">
         <v>净买: 4489.13万</v>
       </c>
       <c r="E29">
@@ -10627,41 +10675,41 @@
       <c r="H29">
         <v>16.03</v>
       </c>
-      <c r="I29" s="361">
+      <c r="I29" s="352">
         <v>3.42</v>
       </c>
-      <c r="J29" s="363">
+      <c r="J29" s="357">
         <v>1.23</v>
       </c>
-      <c r="K29" s="364">
+      <c r="K29" s="358">
         <v>10.14</v>
       </c>
-      <c r="L29" s="360">
+      <c r="L29" s="359">
         <v>-0.87</v>
       </c>
-      <c r="M29" s="352">
+      <c r="M29" s="361">
         <v>5.63</v>
       </c>
-      <c r="N29" s="353">
+      <c r="N29" s="360">
         <v>-0.83</v>
       </c>
-      <c r="O29" s="355">
+      <c r="O29" s="353">
         <v>-0.62</v>
       </c>
       <c r="P29" s="362">
         <v>-6.58</v>
       </c>
-      <c r="Q29" s="356">
+      <c r="Q29" s="363">
         <v>-16.49</v>
       </c>
-      <c r="R29" s="357">
+      <c r="R29" s="364">
         <v>-10.75</v>
       </c>
-      <c r="S29" s="354">
+      <c r="S29" s="355">
         <v>0.63</v>
       </c>
-      <c r="T29" s="358">
-        <v>16.49</v>
+      <c r="T29" s="354">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="30">
@@ -10674,7 +10722,7 @@
       <c r="C30" t="str">
         <v>603130</v>
       </c>
-      <c r="D30" s="366" t="str">
+      <c r="D30" s="372" t="str">
         <v>净买: 297.33万</v>
       </c>
       <c r="E30">
@@ -10689,41 +10737,41 @@
       <c r="H30">
         <v>-0.93</v>
       </c>
-      <c r="I30" s="372">
+      <c r="I30" s="376">
         <v>-8.65</v>
       </c>
-      <c r="J30" s="367">
+      <c r="J30" s="373">
         <v>-3.96</v>
       </c>
-      <c r="K30" s="373">
+      <c r="K30" s="365">
         <v>-6.7</v>
       </c>
-      <c r="L30" s="377">
+      <c r="L30" s="366">
         <v>-2.84</v>
       </c>
       <c r="M30" s="374">
         <v>-5.33</v>
       </c>
-      <c r="N30" s="368">
+      <c r="N30" s="375">
         <v>-7.23</v>
       </c>
-      <c r="O30" s="365">
+      <c r="O30" s="367">
         <v>-9.19</v>
       </c>
-      <c r="P30" s="369">
+      <c r="P30" s="370">
         <v>-11.19</v>
       </c>
-      <c r="Q30" s="370">
+      <c r="Q30" s="368">
         <v>-10.76</v>
       </c>
-      <c r="R30" s="371">
+      <c r="R30" s="377">
         <v>-1.83</v>
       </c>
-      <c r="S30" s="375">
+      <c r="S30" s="369">
         <v>2.97</v>
       </c>
-      <c r="T30" s="376">
-        <v>23.55</v>
+      <c r="T30" s="371">
+        <v>19.59</v>
       </c>
     </row>
     <row r="31">
@@ -10736,7 +10784,7 @@
       <c r="C31" t="str">
         <v>000695</v>
       </c>
-      <c r="D31" s="383" t="str">
+      <c r="D31" s="378" t="str">
         <v>净买: 1731.47万</v>
       </c>
       <c r="E31">
@@ -10754,38 +10802,38 @@
       <c r="I31" s="384">
         <v>-7.67</v>
       </c>
-      <c r="J31" s="378">
+      <c r="J31" s="379">
         <v>-10.54</v>
       </c>
-      <c r="K31" s="379">
+      <c r="K31" s="380">
         <v>-16.08</v>
       </c>
-      <c r="L31" s="380">
+      <c r="L31" s="385">
         <v>-21.88</v>
       </c>
-      <c r="M31" s="382">
+      <c r="M31" s="386">
         <v>-23.96</v>
       </c>
-      <c r="N31" s="385">
+      <c r="N31" s="381">
         <v>-24.6</v>
       </c>
-      <c r="O31" s="388">
+      <c r="O31" s="389">
         <v>-28.17</v>
       </c>
-      <c r="P31" s="386">
+      <c r="P31" s="387">
         <v>-28.81</v>
       </c>
-      <c r="Q31" s="381">
+      <c r="Q31" s="382">
         <v>-30.62</v>
       </c>
-      <c r="R31" s="389">
+      <c r="R31" s="388">
         <v>-32.37</v>
       </c>
-      <c r="S31" s="390">
+      <c r="S31" s="383">
         <v>-32.16</v>
       </c>
-      <c r="T31" s="387">
-        <v>-21.88</v>
+      <c r="T31" s="390">
+        <v>-20.39</v>
       </c>
     </row>
     <row r="32">
@@ -10813,41 +10861,41 @@
       <c r="H32">
         <v>1.28</v>
       </c>
-      <c r="I32" s="399">
+      <c r="I32" s="400">
         <v>28.31</v>
       </c>
-      <c r="J32" s="403">
+      <c r="J32" s="391">
         <v>29.11</v>
       </c>
-      <c r="K32" s="400">
+      <c r="K32" s="401">
         <v>15.45</v>
       </c>
-      <c r="L32" s="394">
+      <c r="L32" s="396">
         <v>17.04</v>
       </c>
-      <c r="M32" s="401">
+      <c r="M32" s="402">
         <v>25.35</v>
       </c>
-      <c r="N32" s="395">
+      <c r="N32" s="399">
         <v>62.96</v>
       </c>
-      <c r="O32" s="391">
+      <c r="O32" s="397">
         <v>42.07</v>
       </c>
-      <c r="P32" s="402">
+      <c r="P32" s="392">
         <v>32.35</v>
       </c>
-      <c r="Q32" s="392">
+      <c r="Q32" s="393">
         <v>36.62</v>
       </c>
-      <c r="R32" s="393">
+      <c r="R32" s="403">
         <v>27.7</v>
       </c>
-      <c r="S32" s="396">
+      <c r="S32" s="394">
         <v>27.7</v>
       </c>
-      <c r="T32" s="397">
-        <v>-16.62</v>
+      <c r="T32" s="395">
+        <v>-17.98</v>
       </c>
     </row>
     <row r="33">
@@ -10860,7 +10908,7 @@
       <c r="C33" t="str">
         <v>920765</v>
       </c>
-      <c r="D33" s="408" t="str">
+      <c r="D33" s="414" t="str">
         <v>净卖: -3268.70万</v>
       </c>
       <c r="E33">
@@ -10878,38 +10926,38 @@
       <c r="I33" s="415">
         <v>2.35</v>
       </c>
-      <c r="J33" s="409">
+      <c r="J33" s="416">
         <v>-1.45</v>
       </c>
-      <c r="K33" s="413">
+      <c r="K33" s="408">
         <v>-5.92</v>
       </c>
-      <c r="L33" s="410">
+      <c r="L33" s="404">
         <v>-10.71</v>
       </c>
       <c r="M33" s="411">
         <v>-10.51</v>
       </c>
-      <c r="N33" s="416">
+      <c r="N33" s="409">
         <v>-12.16</v>
       </c>
-      <c r="O33" s="406">
+      <c r="O33" s="412">
         <v>-14.08</v>
       </c>
-      <c r="P33" s="412">
+      <c r="P33" s="405">
         <v>-16.59</v>
       </c>
-      <c r="Q33" s="404">
+      <c r="Q33" s="410">
         <v>-19.14</v>
       </c>
       <c r="R33" s="407">
         <v>-18.63</v>
       </c>
-      <c r="S33" s="405">
+      <c r="S33" s="406">
         <v>-18.86</v>
       </c>
-      <c r="T33" s="414">
-        <v>-44.04</v>
+      <c r="T33" s="413">
+        <v>-46.59</v>
       </c>
     </row>
     <row r="34">
@@ -10922,7 +10970,7 @@
       <c r="C34" t="str">
         <v>603458</v>
       </c>
-      <c r="D34" s="427" t="str">
+      <c r="D34" s="428" t="str">
         <v>净买: 2084.50万</v>
       </c>
       <c r="E34">
@@ -10937,41 +10985,41 @@
       <c r="H34">
         <v>5.37</v>
       </c>
-      <c r="I34" s="423">
+      <c r="I34" s="420">
         <v>4.4</v>
       </c>
-      <c r="J34" s="428">
+      <c r="J34" s="429">
         <v>0.2</v>
       </c>
-      <c r="K34" s="429">
+      <c r="K34" s="424">
         <v>10.2</v>
       </c>
       <c r="L34" s="426">
         <v>14</v>
       </c>
-      <c r="M34" s="420">
+      <c r="M34" s="421">
         <v>13.9</v>
       </c>
-      <c r="N34" s="424">
+      <c r="N34" s="417">
         <v>20.5</v>
       </c>
-      <c r="O34" s="417">
+      <c r="O34" s="425">
         <v>20.4</v>
       </c>
-      <c r="P34" s="418">
+      <c r="P34" s="422">
         <v>21.7</v>
       </c>
-      <c r="Q34" s="425">
+      <c r="Q34" s="418">
         <v>19.2</v>
       </c>
-      <c r="R34" s="419">
+      <c r="R34" s="423">
         <v>31.1</v>
       </c>
-      <c r="S34" s="421">
+      <c r="S34" s="427">
         <v>27.9</v>
       </c>
-      <c r="T34" s="422">
-        <v>15</v>
+      <c r="T34" s="419">
+        <v>16</v>
       </c>
     </row>
     <row r="35">
@@ -10984,7 +11032,7 @@
       <c r="C35" t="str">
         <v>920179</v>
       </c>
-      <c r="D35" s="438" t="str">
+      <c r="D35" s="441" t="str">
         <v>净买: 1651.86万</v>
       </c>
       <c r="E35">
@@ -10999,41 +11047,41 @@
       <c r="H35">
         <v>5.59</v>
       </c>
-      <c r="I35" s="439">
+      <c r="I35" s="431">
         <v>15.88</v>
       </c>
-      <c r="J35" s="440">
+      <c r="J35" s="435">
         <v>19.24</v>
       </c>
-      <c r="K35" s="442">
+      <c r="K35" s="432">
         <v>13.24</v>
       </c>
-      <c r="L35" s="432">
+      <c r="L35" s="436">
         <v>17.03</v>
       </c>
-      <c r="M35" s="433">
+      <c r="M35" s="442">
         <v>8.58</v>
       </c>
       <c r="N35" s="430">
         <v>8.97</v>
       </c>
-      <c r="O35" s="434">
+      <c r="O35" s="433">
         <v>10.54</v>
       </c>
-      <c r="P35" s="435">
+      <c r="P35" s="437">
         <v>7.38</v>
       </c>
-      <c r="Q35" s="431">
+      <c r="Q35" s="439">
         <v>13.87</v>
       </c>
-      <c r="R35" s="436">
+      <c r="R35" s="434">
         <v>36.96</v>
       </c>
-      <c r="S35" s="437">
+      <c r="S35" s="438">
         <v>37.84</v>
       </c>
-      <c r="T35" s="441">
-        <v>22.4</v>
+      <c r="T35" s="440">
+        <v>22.43</v>
       </c>
     </row>
     <row r="36">
@@ -11046,7 +11094,7 @@
       <c r="C36" t="str">
         <v>603488</v>
       </c>
-      <c r="D36" s="455" t="str">
+      <c r="D36" s="452" t="str">
         <v>净买: 3230.20万</v>
       </c>
       <c r="E36">
@@ -11061,41 +11109,41 @@
       <c r="H36">
         <v>-0.94</v>
       </c>
-      <c r="I36" s="449">
+      <c r="I36" s="446">
         <v>11.07</v>
       </c>
-      <c r="J36" s="443">
+      <c r="J36" s="455">
         <v>9.74</v>
       </c>
-      <c r="K36" s="444">
+      <c r="K36" s="443">
         <v>7.38</v>
       </c>
-      <c r="L36" s="445">
+      <c r="L36" s="447">
         <v>2.93</v>
       </c>
-      <c r="M36" s="446">
+      <c r="M36" s="444">
         <v>-3.12</v>
       </c>
-      <c r="N36" s="450">
+      <c r="N36" s="448">
         <v>-5.01</v>
       </c>
-      <c r="O36" s="451">
+      <c r="O36" s="454">
         <v>-4.92</v>
       </c>
-      <c r="P36" s="452">
+      <c r="P36" s="449">
         <v>-5.11</v>
       </c>
-      <c r="Q36" s="447">
+      <c r="Q36" s="445">
         <v>-5.3</v>
       </c>
-      <c r="R36" s="453">
+      <c r="R36" s="450">
         <v>-8.89</v>
       </c>
-      <c r="S36" s="448">
+      <c r="S36" s="451">
         <v>0.19</v>
       </c>
-      <c r="T36" s="454">
-        <v>1.7</v>
+      <c r="T36" s="453">
+        <v>8.61</v>
       </c>
     </row>
     <row r="37">
@@ -11108,7 +11156,7 @@
       <c r="C37" t="str">
         <v>688115</v>
       </c>
-      <c r="D37" s="466" t="str">
+      <c r="D37" s="465" t="str">
         <v>净买: 534.48万</v>
       </c>
       <c r="E37">
@@ -11123,41 +11171,41 @@
       <c r="H37">
         <v>-0.49</v>
       </c>
-      <c r="I37" s="467">
+      <c r="I37" s="463">
         <v>-15.96</v>
       </c>
-      <c r="J37" s="459">
+      <c r="J37" s="466">
         <v>-24.38</v>
       </c>
-      <c r="K37" s="460">
+      <c r="K37" s="467">
         <v>-27.28</v>
       </c>
-      <c r="L37" s="461">
+      <c r="L37" s="457">
         <v>-26.26</v>
       </c>
-      <c r="M37" s="468">
+      <c r="M37" s="461">
         <v>-29.33</v>
       </c>
-      <c r="N37" s="456">
+      <c r="N37" s="462">
         <v>-33.51</v>
       </c>
-      <c r="O37" s="463">
+      <c r="O37" s="468">
         <v>-34.12</v>
       </c>
-      <c r="P37" s="464">
+      <c r="P37" s="458">
         <v>-35.51</v>
       </c>
-      <c r="Q37" s="457">
+      <c r="Q37" s="464">
         <v>-35.8</v>
       </c>
-      <c r="R37" s="458">
+      <c r="R37" s="456">
         <v>-33.88</v>
       </c>
-      <c r="S37" s="462">
+      <c r="S37" s="459">
         <v>-35.38</v>
       </c>
-      <c r="T37" s="465">
-        <v>-30.88</v>
+      <c r="T37" s="460">
+        <v>-27.22</v>
       </c>
     </row>
     <row r="38">
@@ -11170,7 +11218,7 @@
       <c r="C38" t="str">
         <v>600671</v>
       </c>
-      <c r="D38" s="473" t="str">
+      <c r="D38" s="479" t="str">
         <v>净卖: -271.42万</v>
       </c>
       <c r="E38">
@@ -11185,41 +11233,41 @@
       <c r="H38">
         <v>-1.3</v>
       </c>
-      <c r="I38" s="477">
+      <c r="I38" s="473">
         <v>-8.5</v>
       </c>
-      <c r="J38" s="481">
+      <c r="J38" s="474">
         <v>-11.05</v>
       </c>
-      <c r="K38" s="469">
+      <c r="K38" s="480">
         <v>-13.41</v>
       </c>
-      <c r="L38" s="474">
+      <c r="L38" s="478">
         <v>-13.14</v>
       </c>
-      <c r="M38" s="475">
+      <c r="M38" s="481">
         <v>-15.18</v>
       </c>
-      <c r="N38" s="478">
+      <c r="N38" s="469">
         <v>-15.68</v>
       </c>
       <c r="O38" s="470">
         <v>-13.05</v>
       </c>
-      <c r="P38" s="471">
+      <c r="P38" s="475">
         <v>-15.68</v>
       </c>
-      <c r="Q38" s="479">
+      <c r="Q38" s="471">
         <v>-14.45</v>
       </c>
       <c r="R38" s="476">
         <v>-13.27</v>
       </c>
-      <c r="S38" s="472">
+      <c r="S38" s="477">
         <v>-11.23</v>
       </c>
-      <c r="T38" s="480">
-        <v>-12.91</v>
+      <c r="T38" s="472">
+        <v>-12.41</v>
       </c>
     </row>
     <row r="39">
@@ -11232,7 +11280,7 @@
       <c r="C39" t="str">
         <v>300017</v>
       </c>
-      <c r="D39" s="491" t="str">
+      <c r="D39" s="492" t="str">
         <v>净买: 3.37亿</v>
       </c>
       <c r="E39">
@@ -11247,41 +11295,41 @@
       <c r="H39">
         <v>15.07</v>
       </c>
-      <c r="I39" s="492">
+      <c r="I39" s="484">
         <v>0.06</v>
       </c>
       <c r="J39" s="487">
         <v>7.83</v>
       </c>
-      <c r="K39" s="493">
+      <c r="K39" s="485">
         <v>6.29</v>
       </c>
-      <c r="L39" s="489">
+      <c r="L39" s="493">
         <v>8.34</v>
       </c>
-      <c r="M39" s="482">
+      <c r="M39" s="494">
         <v>23.94</v>
       </c>
-      <c r="N39" s="483">
+      <c r="N39" s="482">
         <v>7.32</v>
       </c>
-      <c r="O39" s="484">
+      <c r="O39" s="488">
         <v>15.34</v>
       </c>
-      <c r="P39" s="494">
+      <c r="P39" s="486">
         <v>15.08</v>
       </c>
-      <c r="Q39" s="488">
+      <c r="Q39" s="489">
         <v>21.31</v>
       </c>
-      <c r="R39" s="485">
+      <c r="R39" s="483">
         <v>19.9</v>
       </c>
-      <c r="S39" s="486">
+      <c r="S39" s="490">
         <v>31.26</v>
       </c>
-      <c r="T39" s="490">
-        <v>14.25</v>
+      <c r="T39" s="491">
+        <v>8.41</v>
       </c>
     </row>
     <row r="40">
@@ -11294,7 +11342,7 @@
       <c r="C40" t="str">
         <v>301486</v>
       </c>
-      <c r="D40" s="496" t="str">
+      <c r="D40" s="495" t="str">
         <v>净买: 6753.30万</v>
       </c>
       <c r="E40">
@@ -11309,27 +11357,29 @@
       <c r="H40">
         <v>-3.8</v>
       </c>
-      <c r="I40" s="497">
+      <c r="I40" s="496">
         <v>24.74</v>
       </c>
-      <c r="J40" s="498">
+      <c r="J40" s="497">
         <v>27.42</v>
       </c>
-      <c r="K40" s="499">
+      <c r="K40" s="498">
         <v>22.58</v>
       </c>
-      <c r="L40" s="500">
+      <c r="L40" s="499">
         <v>17.3</v>
       </c>
-      <c r="M40" t="str"/>
+      <c r="M40" s="500">
+        <v>25.35</v>
+      </c>
       <c r="N40" t="str"/>
       <c r="O40" t="str"/>
       <c r="P40" t="str"/>
       <c r="Q40" t="str"/>
       <c r="R40" t="str"/>
       <c r="S40" t="str"/>
-      <c r="T40" s="495">
-        <v>17.3</v>
+      <c r="T40" s="501">
+        <v>25.35</v>
       </c>
     </row>
     <row r="41">
@@ -11342,7 +11392,7 @@
       <c r="C41" t="str">
         <v>600734</v>
       </c>
-      <c r="D41" s="501" t="str">
+      <c r="D41" s="504" t="str">
         <v>净卖: -404.86万</v>
       </c>
       <c r="E41">
@@ -11357,27 +11407,29 @@
       <c r="H41">
         <v>-10.1</v>
       </c>
-      <c r="I41" s="502">
+      <c r="I41" s="505">
         <v>0</v>
       </c>
-      <c r="J41" s="503">
+      <c r="J41" s="506">
         <v>-4.35</v>
       </c>
-      <c r="K41" s="504">
+      <c r="K41" s="507">
         <v>-10.14</v>
       </c>
-      <c r="L41" s="505">
+      <c r="L41" s="508">
         <v>-13.41</v>
       </c>
-      <c r="M41" t="str"/>
+      <c r="M41" s="502">
+        <v>-15.22</v>
+      </c>
       <c r="N41" t="str"/>
       <c r="O41" t="str"/>
       <c r="P41" t="str"/>
       <c r="Q41" t="str"/>
       <c r="R41" t="str"/>
       <c r="S41" t="str"/>
-      <c r="T41" s="506">
-        <v>-13.41</v>
+      <c r="T41" s="503">
+        <v>-15.22</v>
       </c>
     </row>
     <row r="42">
@@ -11390,7 +11442,7 @@
       <c r="C42" t="str">
         <v>603169</v>
       </c>
-      <c r="D42" s="510" t="str">
+      <c r="D42" s="513" t="str">
         <v>净卖: -374.20万</v>
       </c>
       <c r="E42">
@@ -11405,13 +11457,15 @@
       <c r="H42">
         <v>-10</v>
       </c>
-      <c r="I42" s="507">
+      <c r="I42" s="509">
         <v>0</v>
       </c>
-      <c r="J42" s="508">
+      <c r="J42" s="510">
         <v>-6.69</v>
       </c>
-      <c r="K42" t="str"/>
+      <c r="K42" s="511">
+        <v>-5.22</v>
+      </c>
       <c r="L42" t="str"/>
       <c r="M42" t="str"/>
       <c r="N42" t="str"/>
@@ -11420,8 +11474,8 @@
       <c r="Q42" t="str"/>
       <c r="R42" t="str"/>
       <c r="S42" t="str"/>
-      <c r="T42" s="509">
-        <v>-6.69</v>
+      <c r="T42" s="512">
+        <v>-5.22</v>
       </c>
     </row>
     <row r="43">
@@ -11442,13 +11496,13 @@
         <v>41</v>
       </c>
       <c r="K43">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L43">
         <v>40</v>
       </c>
       <c r="M43">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N43">
         <v>38</v>
@@ -11483,40 +11537,40 @@
       <c r="F44" t="str"/>
       <c r="G44" t="str"/>
       <c r="H44" t="str"/>
-      <c r="I44" s="513">
+      <c r="I44" s="522">
         <v>53.66</v>
       </c>
-      <c r="J44" s="522">
+      <c r="J44" s="514">
         <v>58.54</v>
       </c>
-      <c r="K44" s="511">
-        <v>55</v>
-      </c>
-      <c r="L44" s="514">
+      <c r="K44" s="515">
+        <v>53.66</v>
+      </c>
+      <c r="L44" s="523">
         <v>52.5</v>
       </c>
-      <c r="M44" s="515">
+      <c r="M44" s="516">
         <v>50</v>
       </c>
-      <c r="N44" s="519">
+      <c r="N44" s="524">
         <v>44.74</v>
       </c>
-      <c r="O44" s="516">
+      <c r="O44" s="520">
         <v>44.74</v>
       </c>
       <c r="P44" s="517">
         <v>50</v>
       </c>
-      <c r="Q44" s="520">
+      <c r="Q44" s="521">
         <v>44.74</v>
       </c>
-      <c r="R44" s="512">
+      <c r="R44" s="518">
         <v>39.47</v>
       </c>
-      <c r="S44" s="521">
+      <c r="S44" s="519">
         <v>50</v>
       </c>
-      <c r="T44" s="518">
+      <c r="T44" s="525">
         <v>51.22</v>
       </c>
     </row>
@@ -11531,41 +11585,41 @@
       <c r="F45" t="str"/>
       <c r="G45" t="str"/>
       <c r="H45" t="str"/>
-      <c r="I45" s="529">
+      <c r="I45" s="533">
         <v>3.45</v>
       </c>
-      <c r="J45" s="530">
+      <c r="J45" s="536">
         <v>2.93</v>
       </c>
-      <c r="K45" s="527">
-        <v>0.95</v>
-      </c>
-      <c r="L45" s="524">
+      <c r="K45" s="531">
+        <v>0.8</v>
+      </c>
+      <c r="L45" s="534">
         <v>-0.04</v>
       </c>
-      <c r="M45" s="531">
-        <v>-0.18</v>
-      </c>
-      <c r="N45" s="525">
+      <c r="M45" s="526">
+        <v>0.08</v>
+      </c>
+      <c r="N45" s="535">
         <v>0.5</v>
       </c>
-      <c r="O45" s="534">
+      <c r="O45" s="527">
         <v>0.7</v>
       </c>
-      <c r="P45" s="532">
+      <c r="P45" s="528">
         <v>-0.65</v>
       </c>
-      <c r="Q45" s="533">
+      <c r="Q45" s="529">
         <v>-0.47</v>
       </c>
-      <c r="R45" s="526">
+      <c r="R45" s="530">
         <v>-0.13</v>
       </c>
-      <c r="S45" s="523">
+      <c r="S45" s="537">
         <v>0.43</v>
       </c>
-      <c r="T45" s="528">
-        <v>15.68</v>
+      <c r="T45" s="532">
+        <v>16.16</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/小鳄鱼/index.xlsx
+++ b/youzi/小鳄鱼/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="539">
+  <fills count="542">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,54 +39,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF7D4D8"/>
         <bgColor/>
       </patternFill>
@@ -99,6 +87,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC12937"/>
         <bgColor/>
       </patternFill>
@@ -111,13 +111,1255 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FA94B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C788"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA91D2B"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF76C788"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15664"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4E0BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9ED7AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A712F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A143"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,31 +1371,493 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2FA94B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6707C"/>
+        <fgColor rgb="FFDD3B4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBEE4C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9818B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1E2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F2E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9858F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -165,49 +1869,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2D"/>
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -219,7 +1923,1039 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CDD1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EFDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CD95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B96B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8790"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04D5B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -243,31 +2979,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B76"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -315,97 +3045,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE15664"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -417,73 +3069,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB4E0BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -495,67 +3111,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -567,421 +3135,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3747"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A712F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FFF2B5BA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -993,55 +3147,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505E"/>
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1053,103 +3177,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
+        <fgColor rgb="FF8DD09D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1161,31 +3195,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF74C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
+        <fgColor rgb="FFE15260"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D7"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1197,445 +3225,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A143"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBEE4C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3B4A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9818B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1E2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F2E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1647,1620 +3267,39 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9858F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF8F0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAEFDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CDD1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EFDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CD95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8790"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF54B96B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04D5B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15260"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF1F9F2"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D7"/>
+        <fgColor rgb="FFE8F5EB"/>
         <bgColor/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="538">
+  <borders count="541">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -7031,7 +7070,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="538">
+  <cellXfs count="541">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -8642,6 +8681,15 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="537" fillId="538" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="538" fillId="539" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="539" fillId="540" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="540" fillId="541" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -8986,7 +9034,7 @@
       <c r="C2" t="str">
         <v>603881</v>
       </c>
-      <c r="D2" s="1" t="str">
+      <c r="D2" s="6" t="str">
         <v>净买: 1.27亿</v>
       </c>
       <c r="E2">
@@ -9001,13 +9049,13 @@
       <c r="H2">
         <v>8.87</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="7">
         <v>1.04</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="13">
         <v>11.14</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="2">
         <v>0.03</v>
       </c>
       <c r="L2" s="11">
@@ -9016,26 +9064,26 @@
       <c r="M2" s="3">
         <v>8.74</v>
       </c>
-      <c r="N2" s="6">
+      <c r="N2" s="8">
         <v>19.61</v>
       </c>
-      <c r="O2" s="7">
+      <c r="O2" s="12">
         <v>25.9</v>
       </c>
-      <c r="P2" s="12">
+      <c r="P2" s="1">
         <v>21.45</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="4">
         <v>15.56</v>
       </c>
-      <c r="R2" s="13">
+      <c r="R2" s="9">
         <v>9.81</v>
       </c>
-      <c r="S2" s="8">
+      <c r="S2" s="5">
         <v>-0.74</v>
       </c>
-      <c r="T2" s="4">
-        <v>10.52</v>
+      <c r="T2" s="10">
+        <v>8.47</v>
       </c>
     </row>
     <row r="3">
@@ -9048,7 +9096,7 @@
       <c r="C3" t="str">
         <v>603881</v>
       </c>
-      <c r="D3" s="21" t="str">
+      <c r="D3" s="22" t="str">
         <v>净卖: -9150.08万</v>
       </c>
       <c r="E3">
@@ -9063,41 +9111,41 @@
       <c r="H3">
         <v>-4.56</v>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="16">
         <v>-5.7</v>
       </c>
-      <c r="J3" s="24">
+      <c r="J3" s="17">
         <v>1.34</v>
       </c>
-      <c r="K3" s="25">
+      <c r="K3" s="23">
         <v>2.51</v>
       </c>
       <c r="L3" s="19">
         <v>12.77</v>
       </c>
-      <c r="M3" s="22">
+      <c r="M3" s="25">
         <v>18.69</v>
       </c>
       <c r="N3" s="26">
         <v>14.5</v>
       </c>
-      <c r="O3" s="15">
+      <c r="O3" s="24">
         <v>8.94</v>
       </c>
-      <c r="P3" s="20">
+      <c r="P3" s="14">
         <v>3.52</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="Q3" s="20">
         <v>-6.42</v>
       </c>
-      <c r="R3" s="17">
+      <c r="R3" s="15">
         <v>-4.83</v>
       </c>
-      <c r="S3" s="14">
+      <c r="S3" s="18">
         <v>-3.18</v>
       </c>
-      <c r="T3" s="18">
-        <v>4.19</v>
+      <c r="T3" s="21">
+        <v>2.26</v>
       </c>
     </row>
     <row r="4">
@@ -9125,41 +9173,41 @@
       <c r="H4">
         <v>0.22</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="39">
         <v>9.8</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="27">
         <v>13.04</v>
       </c>
-      <c r="K4" s="38">
+      <c r="K4" s="34">
         <v>17.87</v>
       </c>
-      <c r="L4" s="39">
+      <c r="L4" s="28">
         <v>11.31</v>
       </c>
-      <c r="M4" s="27">
+      <c r="M4" s="29">
         <v>12.39</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="31">
         <v>15.13</v>
       </c>
-      <c r="O4" s="31">
+      <c r="O4" s="35">
         <v>7.93</v>
       </c>
       <c r="P4" s="32">
         <v>8.36</v>
       </c>
-      <c r="Q4" s="29">
+      <c r="Q4" s="36">
         <v>9.44</v>
       </c>
       <c r="R4" s="33">
         <v>11.38</v>
       </c>
-      <c r="S4" s="34">
+      <c r="S4" s="37">
         <v>11.1</v>
       </c>
-      <c r="T4" s="37">
-        <v>5.91</v>
+      <c r="T4" s="38">
+        <v>5.76</v>
       </c>
     </row>
     <row r="5">
@@ -9190,38 +9238,38 @@
       <c r="I5" s="42">
         <v>11.82</v>
       </c>
-      <c r="J5" s="43">
+      <c r="J5" s="47">
         <v>12.21</v>
       </c>
-      <c r="K5" s="49">
+      <c r="K5" s="50">
         <v>5.32</v>
       </c>
-      <c r="L5" s="52">
+      <c r="L5" s="43">
         <v>15.84</v>
       </c>
       <c r="M5" s="44">
         <v>10.91</v>
       </c>
-      <c r="N5" s="40">
+      <c r="N5" s="45">
         <v>18.96</v>
       </c>
-      <c r="O5" s="45">
+      <c r="O5" s="51">
         <v>22.6</v>
       </c>
-      <c r="P5" s="46">
+      <c r="P5" s="52">
         <v>15.71</v>
       </c>
-      <c r="Q5" s="47">
+      <c r="Q5" s="48">
         <v>4.16</v>
       </c>
-      <c r="R5" s="50">
+      <c r="R5" s="49">
         <v>-6.23</v>
       </c>
-      <c r="S5" s="48">
+      <c r="S5" s="46">
         <v>-8.18</v>
       </c>
-      <c r="T5" s="51">
-        <v>134.68</v>
+      <c r="T5" s="40">
+        <v>127.66</v>
       </c>
     </row>
     <row r="6">
@@ -9255,35 +9303,35 @@
       <c r="J6" s="65">
         <v>4.08</v>
       </c>
-      <c r="K6" s="53">
+      <c r="K6" s="60">
         <v>4.08</v>
       </c>
-      <c r="L6" s="55">
+      <c r="L6" s="53">
         <v>4.08</v>
       </c>
-      <c r="M6" s="56">
+      <c r="M6" s="54">
         <v>7.06</v>
       </c>
-      <c r="N6" s="60">
+      <c r="N6" s="61">
         <v>5.02</v>
       </c>
-      <c r="O6" s="54">
+      <c r="O6" s="55">
         <v>-5.49</v>
       </c>
       <c r="P6" s="57">
         <v>-14.6</v>
       </c>
-      <c r="Q6" s="58">
+      <c r="Q6" s="56">
         <v>-9.26</v>
       </c>
-      <c r="R6" s="61">
+      <c r="R6" s="58">
         <v>-5.81</v>
       </c>
-      <c r="S6" s="59">
+      <c r="S6" s="62">
         <v>3.61</v>
       </c>
-      <c r="T6" s="62">
-        <v>513.66</v>
+      <c r="T6" s="59">
+        <v>504.71</v>
       </c>
     </row>
     <row r="7">
@@ -9296,7 +9344,7 @@
       <c r="C7" t="str">
         <v>603011</v>
       </c>
-      <c r="D7" s="76" t="str">
+      <c r="D7" s="77" t="str">
         <v>净卖: -2450.00万</v>
       </c>
       <c r="E7">
@@ -9311,41 +9359,41 @@
       <c r="H7">
         <v>-0.78</v>
       </c>
-      <c r="I7" s="77">
+      <c r="I7" s="66">
         <v>10.9</v>
       </c>
-      <c r="J7" s="69">
+      <c r="J7" s="73">
         <v>5.29</v>
       </c>
-      <c r="K7" s="66">
+      <c r="K7" s="67">
         <v>-1.74</v>
       </c>
-      <c r="L7" s="73">
+      <c r="L7" s="69">
         <v>-11.53</v>
       </c>
-      <c r="M7" s="70">
+      <c r="M7" s="74">
         <v>-20.38</v>
       </c>
-      <c r="N7" s="74">
+      <c r="N7" s="75">
         <v>-24.17</v>
       </c>
-      <c r="O7" s="71">
+      <c r="O7" s="68">
         <v>-21.8</v>
       </c>
-      <c r="P7" s="78">
+      <c r="P7" s="70">
         <v>-20.46</v>
       </c>
-      <c r="Q7" s="67">
+      <c r="Q7" s="76">
         <v>-12.48</v>
       </c>
-      <c r="R7" s="75">
+      <c r="R7" s="78">
         <v>-15.24</v>
       </c>
-      <c r="S7" s="72">
+      <c r="S7" s="71">
         <v>-22.12</v>
       </c>
-      <c r="T7" s="68">
-        <v>67.22</v>
+      <c r="T7" s="72">
+        <v>62.56</v>
       </c>
     </row>
     <row r="8">
@@ -9358,7 +9406,7 @@
       <c r="C8" t="str">
         <v>000989</v>
       </c>
-      <c r="D8" s="87" t="str">
+      <c r="D8" s="80" t="str">
         <v>净卖: -4522.23万</v>
       </c>
       <c r="E8">
@@ -9373,41 +9421,41 @@
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="88">
+      <c r="I8" s="87">
         <v>-6.8</v>
       </c>
-      <c r="J8" s="81">
+      <c r="J8" s="88">
         <v>-8.95</v>
       </c>
-      <c r="K8" s="89">
+      <c r="K8" s="84">
         <v>-12.73</v>
       </c>
-      <c r="L8" s="82">
+      <c r="L8" s="79">
         <v>-12.41</v>
       </c>
-      <c r="M8" s="83">
+      <c r="M8" s="81">
         <v>-9.82</v>
       </c>
-      <c r="N8" s="90">
+      <c r="N8" s="85">
         <v>-6.8</v>
       </c>
-      <c r="O8" s="91">
+      <c r="O8" s="89">
         <v>-1.29</v>
       </c>
-      <c r="P8" s="84">
+      <c r="P8" s="90">
         <v>-3.78</v>
       </c>
-      <c r="Q8" s="85">
+      <c r="Q8" s="86">
         <v>-6.36</v>
       </c>
-      <c r="R8" s="79">
+      <c r="R8" s="82">
         <v>-5.83</v>
       </c>
-      <c r="S8" s="86">
+      <c r="S8" s="91">
         <v>-8.2</v>
       </c>
-      <c r="T8" s="80">
-        <v>7.12</v>
+      <c r="T8" s="83">
+        <v>5.93</v>
       </c>
     </row>
     <row r="9">
@@ -9420,7 +9468,7 @@
       <c r="C9" t="str">
         <v>603488</v>
       </c>
-      <c r="D9" s="94" t="str">
+      <c r="D9" s="96" t="str">
         <v>净卖: -414.45万</v>
       </c>
       <c r="E9">
@@ -9435,41 +9483,41 @@
       <c r="H9">
         <v>-0.82</v>
       </c>
-      <c r="I9" s="103">
+      <c r="I9" s="97">
         <v>10.89</v>
       </c>
       <c r="J9" s="98">
         <v>2.01</v>
       </c>
-      <c r="K9" s="104">
+      <c r="K9" s="93">
         <v>-0.12</v>
       </c>
-      <c r="L9" s="93">
+      <c r="L9" s="102">
         <v>-4.5</v>
       </c>
       <c r="M9" s="99">
         <v>-4.73</v>
       </c>
-      <c r="N9" s="100">
+      <c r="N9" s="103">
         <v>-6.27</v>
       </c>
-      <c r="O9" s="95">
+      <c r="O9" s="94">
         <v>-5.56</v>
       </c>
-      <c r="P9" s="101">
+      <c r="P9" s="100">
         <v>-9.11</v>
       </c>
-      <c r="Q9" s="92">
+      <c r="Q9" s="95">
         <v>-8.52</v>
       </c>
-      <c r="R9" s="102">
+      <c r="R9" s="101">
         <v>-7.1</v>
       </c>
-      <c r="S9" s="96">
+      <c r="S9" s="104">
         <v>-7.81</v>
       </c>
-      <c r="T9" s="97">
-        <v>35.86</v>
+      <c r="T9" s="92">
+        <v>29.7</v>
       </c>
     </row>
     <row r="10">
@@ -9482,7 +9530,7 @@
       <c r="C10" t="str">
         <v>603429</v>
       </c>
-      <c r="D10" s="108" t="str">
+      <c r="D10" s="113" t="str">
         <v>净卖: -775.14万</v>
       </c>
       <c r="E10">
@@ -9500,38 +9548,38 @@
       <c r="I10" s="109">
         <v>-9.58</v>
       </c>
-      <c r="J10" s="117">
+      <c r="J10" s="116">
         <v>-17.02</v>
       </c>
       <c r="K10" s="110">
         <v>-15.53</v>
       </c>
-      <c r="L10" s="113">
+      <c r="L10" s="111">
         <v>-17.02</v>
       </c>
-      <c r="M10" s="105">
+      <c r="M10" s="117">
         <v>-25.3</v>
       </c>
-      <c r="N10" s="111">
+      <c r="N10" s="112">
         <v>-26.33</v>
       </c>
-      <c r="O10" s="115">
+      <c r="O10" s="105">
         <v>-22.79</v>
       </c>
       <c r="P10" s="106">
         <v>-22.7</v>
       </c>
-      <c r="Q10" s="112">
+      <c r="Q10" s="107">
         <v>-24.47</v>
       </c>
-      <c r="R10" s="114">
+      <c r="R10" s="108">
         <v>-23.91</v>
       </c>
-      <c r="S10" s="107">
+      <c r="S10" s="114">
         <v>-24.74</v>
       </c>
-      <c r="T10" s="116">
-        <v>-9.12</v>
+      <c r="T10" s="115">
+        <v>-8.19</v>
       </c>
     </row>
     <row r="11">
@@ -9544,7 +9592,7 @@
       <c r="C11" t="str">
         <v>600735</v>
       </c>
-      <c r="D11" s="127" t="str">
+      <c r="D11" s="119" t="str">
         <v>净买: 1079.52万</v>
       </c>
       <c r="E11">
@@ -9559,41 +9607,41 @@
       <c r="H11">
         <v>-5.01</v>
       </c>
-      <c r="I11" s="122">
+      <c r="I11" s="120">
         <v>5.4</v>
       </c>
-      <c r="J11" s="128">
+      <c r="J11" s="123">
         <v>4.08</v>
       </c>
-      <c r="K11" s="129">
+      <c r="K11" s="127">
         <v>1.32</v>
       </c>
-      <c r="L11" s="130">
+      <c r="L11" s="121">
         <v>2.37</v>
       </c>
-      <c r="M11" s="123">
+      <c r="M11" s="128">
         <v>7.64</v>
       </c>
-      <c r="N11" s="125">
+      <c r="N11" s="124">
         <v>6.19</v>
       </c>
-      <c r="O11" s="118">
+      <c r="O11" s="129">
         <v>3.43</v>
       </c>
-      <c r="P11" s="124">
+      <c r="P11" s="130">
         <v>8.7</v>
       </c>
-      <c r="Q11" s="119">
+      <c r="Q11" s="118">
         <v>10.28</v>
       </c>
-      <c r="R11" s="126">
+      <c r="R11" s="125">
         <v>6.59</v>
       </c>
-      <c r="S11" s="120">
+      <c r="S11" s="122">
         <v>3.43</v>
       </c>
-      <c r="T11" s="121">
-        <v>-6.85</v>
+      <c r="T11" s="126">
+        <v>-2.24</v>
       </c>
     </row>
     <row r="12">
@@ -9606,7 +9654,7 @@
       <c r="C12" t="str">
         <v>603429</v>
       </c>
-      <c r="D12" s="138" t="str">
+      <c r="D12" s="141" t="str">
         <v>净买: 2015.22万</v>
       </c>
       <c r="E12">
@@ -9621,41 +9669,41 @@
       <c r="H12">
         <v>-4.22</v>
       </c>
-      <c r="I12" s="133">
+      <c r="I12" s="138">
         <v>-4.19</v>
       </c>
-      <c r="J12" s="141">
+      <c r="J12" s="142">
         <v>-2.47</v>
       </c>
-      <c r="K12" s="134">
+      <c r="K12" s="133">
         <v>-4.19</v>
       </c>
-      <c r="L12" s="142">
+      <c r="L12" s="143">
         <v>-13.75</v>
       </c>
-      <c r="M12" s="136">
+      <c r="M12" s="134">
         <v>-14.93</v>
       </c>
-      <c r="N12" s="137">
+      <c r="N12" s="131">
         <v>-10.85</v>
       </c>
-      <c r="O12" s="135">
+      <c r="O12" s="132">
         <v>-10.74</v>
       </c>
       <c r="P12" s="139">
         <v>-12.78</v>
       </c>
-      <c r="Q12" s="143">
+      <c r="Q12" s="140">
         <v>-12.14</v>
       </c>
-      <c r="R12" s="140">
+      <c r="R12" s="135">
         <v>-13.1</v>
       </c>
-      <c r="S12" s="131">
+      <c r="S12" s="136">
         <v>-14.18</v>
       </c>
-      <c r="T12" s="132">
-        <v>4.94</v>
+      <c r="T12" s="137">
+        <v>6.02</v>
       </c>
     </row>
     <row r="13">
@@ -9668,7 +9716,7 @@
       <c r="C13" t="str">
         <v>603429</v>
       </c>
-      <c r="D13" s="146" t="str">
+      <c r="D13" s="148" t="str">
         <v>净卖: -2033.97万</v>
       </c>
       <c r="E13">
@@ -9683,41 +9731,41 @@
       <c r="H13">
         <v>-0.45</v>
       </c>
-      <c r="I13" s="151">
+      <c r="I13" s="149">
         <v>-9.57</v>
       </c>
-      <c r="J13" s="155">
+      <c r="J13" s="144">
         <v>-10.81</v>
       </c>
-      <c r="K13" s="149">
+      <c r="K13" s="153">
         <v>-6.53</v>
       </c>
-      <c r="L13" s="147">
+      <c r="L13" s="154">
         <v>-6.42</v>
       </c>
-      <c r="M13" s="148">
+      <c r="M13" s="150">
         <v>-8.56</v>
       </c>
-      <c r="N13" s="156">
+      <c r="N13" s="155">
         <v>-7.88</v>
       </c>
-      <c r="O13" s="144">
+      <c r="O13" s="145">
         <v>-8.9</v>
       </c>
-      <c r="P13" s="145">
+      <c r="P13" s="146">
         <v>-10.02</v>
       </c>
-      <c r="Q13" s="152">
+      <c r="Q13" s="156">
         <v>-8.78</v>
       </c>
-      <c r="R13" s="153">
+      <c r="R13" s="151">
         <v>-8.78</v>
       </c>
-      <c r="S13" s="154">
+      <c r="S13" s="152">
         <v>-5.86</v>
       </c>
-      <c r="T13" s="150">
-        <v>10.02</v>
+      <c r="T13" s="147">
+        <v>11.15</v>
       </c>
     </row>
     <row r="14">
@@ -9730,7 +9778,7 @@
       <c r="C14" t="str">
         <v>600735</v>
       </c>
-      <c r="D14" s="158" t="str">
+      <c r="D14" s="161" t="str">
         <v>净买: 450.48万</v>
       </c>
       <c r="E14">
@@ -9745,41 +9793,41 @@
       <c r="H14">
         <v>-9.95</v>
       </c>
-      <c r="I14" s="169">
+      <c r="I14" s="157">
         <v>0</v>
       </c>
-      <c r="J14" s="162">
+      <c r="J14" s="165">
         <v>-0.12</v>
       </c>
-      <c r="K14" s="159">
+      <c r="K14" s="166">
         <v>0.6</v>
       </c>
-      <c r="L14" s="160">
+      <c r="L14" s="158">
         <v>2.04</v>
       </c>
-      <c r="M14" s="164">
+      <c r="M14" s="167">
         <v>-0.96</v>
       </c>
-      <c r="N14" s="165">
+      <c r="N14" s="168">
         <v>-3.72</v>
       </c>
-      <c r="O14" s="163">
+      <c r="O14" s="169">
         <v>2.4</v>
       </c>
-      <c r="P14" s="166">
+      <c r="P14" s="162">
         <v>2.88</v>
       </c>
-      <c r="Q14" s="167">
+      <c r="Q14" s="163">
         <v>3.48</v>
       </c>
-      <c r="R14" s="157">
+      <c r="R14" s="164">
         <v>2.76</v>
       </c>
-      <c r="S14" s="168">
+      <c r="S14" s="159">
         <v>4.32</v>
       </c>
-      <c r="T14" s="161">
-        <v>-15.13</v>
+      <c r="T14" s="160">
+        <v>-10.92</v>
       </c>
     </row>
     <row r="15">
@@ -9792,7 +9840,7 @@
       <c r="C15" t="str">
         <v>605198</v>
       </c>
-      <c r="D15" s="181" t="str">
+      <c r="D15" s="175" t="str">
         <v>净买: 424.10万</v>
       </c>
       <c r="E15">
@@ -9807,41 +9855,41 @@
       <c r="H15">
         <v>-3.44</v>
       </c>
-      <c r="I15" s="172">
+      <c r="I15" s="180">
         <v>-6.79</v>
       </c>
-      <c r="J15" s="182">
+      <c r="J15" s="181">
         <v>-11.34</v>
       </c>
-      <c r="K15" s="170">
+      <c r="K15" s="182">
         <v>-12.86</v>
       </c>
-      <c r="L15" s="173">
+      <c r="L15" s="172">
         <v>-11.52</v>
       </c>
-      <c r="M15" s="179">
+      <c r="M15" s="170">
         <v>-11.25</v>
       </c>
-      <c r="N15" s="175">
+      <c r="N15" s="176">
         <v>-11.47</v>
       </c>
-      <c r="O15" s="174">
+      <c r="O15" s="179">
         <v>-11.43</v>
       </c>
-      <c r="P15" s="180">
+      <c r="P15" s="171">
         <v>-11.41</v>
       </c>
-      <c r="Q15" s="176">
+      <c r="Q15" s="177">
         <v>-9.78</v>
       </c>
-      <c r="R15" s="177">
+      <c r="R15" s="178">
         <v>-11.65</v>
       </c>
-      <c r="S15" s="178">
+      <c r="S15" s="173">
         <v>-11.96</v>
       </c>
-      <c r="T15" s="171">
-        <v>1.32</v>
+      <c r="T15" s="174">
+        <v>1.1</v>
       </c>
     </row>
     <row r="16">
@@ -9854,7 +9902,7 @@
       <c r="C16" t="str">
         <v>600208</v>
       </c>
-      <c r="D16" s="192" t="str">
+      <c r="D16" s="190" t="str">
         <v>净卖: -1100.93万</v>
       </c>
       <c r="E16">
@@ -9869,41 +9917,41 @@
       <c r="H16">
         <v>9.93</v>
       </c>
-      <c r="I16" s="187">
+      <c r="I16" s="194">
         <v>0</v>
       </c>
-      <c r="J16" s="189">
+      <c r="J16" s="183">
         <v>10.04</v>
       </c>
-      <c r="K16" s="183">
+      <c r="K16" s="195">
         <v>7.23</v>
       </c>
-      <c r="L16" s="184">
+      <c r="L16" s="191">
         <v>11.24</v>
       </c>
-      <c r="M16" s="193">
+      <c r="M16" s="188">
         <v>0.2</v>
       </c>
-      <c r="N16" s="190">
+      <c r="N16" s="184">
         <v>-4.42</v>
       </c>
       <c r="O16" s="185">
         <v>-2.81</v>
       </c>
-      <c r="P16" s="194">
+      <c r="P16" s="192">
         <v>3.41</v>
       </c>
-      <c r="Q16" s="195">
+      <c r="Q16" s="189">
         <v>0.4</v>
       </c>
       <c r="R16" s="186">
         <v>-5.82</v>
       </c>
-      <c r="S16" s="191">
+      <c r="S16" s="193">
         <v>-3.21</v>
       </c>
-      <c r="T16" s="188">
-        <v>-14.46</v>
+      <c r="T16" s="187">
+        <v>-17.47</v>
       </c>
     </row>
     <row r="17">
@@ -9931,41 +9979,41 @@
       <c r="H17">
         <v>9.98</v>
       </c>
-      <c r="I17" s="205">
+      <c r="I17" s="201">
         <v>0</v>
       </c>
-      <c r="J17" s="207">
+      <c r="J17" s="208">
         <v>-3.03</v>
       </c>
-      <c r="K17" s="208">
+      <c r="K17" s="198">
         <v>-5.43</v>
       </c>
-      <c r="L17" s="206">
+      <c r="L17" s="205">
         <v>-8.3</v>
       </c>
-      <c r="M17" s="200">
+      <c r="M17" s="206">
         <v>-9.54</v>
       </c>
-      <c r="N17" s="197">
+      <c r="N17" s="207">
         <v>-11.64</v>
       </c>
-      <c r="O17" s="198">
+      <c r="O17" s="202">
         <v>-10.4</v>
       </c>
-      <c r="P17" s="201">
+      <c r="P17" s="199">
         <v>-12.57</v>
       </c>
-      <c r="Q17" s="202">
+      <c r="Q17" s="196">
         <v>-13.03</v>
       </c>
-      <c r="R17" s="199">
+      <c r="R17" s="197">
         <v>-14.82</v>
       </c>
-      <c r="S17" s="203">
+      <c r="S17" s="200">
         <v>-21.26</v>
       </c>
-      <c r="T17" s="196">
-        <v>27.08</v>
+      <c r="T17" s="203">
+        <v>22.81</v>
       </c>
     </row>
     <row r="18">
@@ -9996,10 +10044,10 @@
       <c r="I18" s="218">
         <v>7.01</v>
       </c>
-      <c r="J18" s="209">
+      <c r="J18" s="213">
         <v>5.38</v>
       </c>
-      <c r="K18" s="213">
+      <c r="K18" s="209">
         <v>3.49</v>
       </c>
       <c r="L18" s="210">
@@ -10008,26 +10056,26 @@
       <c r="M18" s="214">
         <v>9.01</v>
       </c>
-      <c r="N18" s="221">
+      <c r="N18" s="215">
         <v>4.46</v>
       </c>
-      <c r="O18" s="211">
+      <c r="O18" s="219">
         <v>10.34</v>
       </c>
-      <c r="P18" s="215">
+      <c r="P18" s="216">
         <v>3.06</v>
       </c>
-      <c r="Q18" s="212">
+      <c r="Q18" s="211">
         <v>1.01</v>
       </c>
-      <c r="R18" s="219">
+      <c r="R18" s="220">
         <v>-6.11</v>
       </c>
-      <c r="S18" s="216">
+      <c r="S18" s="212">
         <v>-3.86</v>
       </c>
-      <c r="T18" s="220">
-        <v>-14.34</v>
+      <c r="T18" s="221">
+        <v>-17.22</v>
       </c>
     </row>
     <row r="19">
@@ -10040,7 +10088,7 @@
       <c r="C19" t="str">
         <v>000061</v>
       </c>
-      <c r="D19" s="224" t="str">
+      <c r="D19" s="231" t="str">
         <v>净买: 2178.30万</v>
       </c>
       <c r="E19">
@@ -10055,41 +10103,41 @@
       <c r="H19">
         <v>5.09</v>
       </c>
-      <c r="I19" s="229">
+      <c r="I19" s="232">
         <v>4.72</v>
       </c>
-      <c r="J19" s="230">
+      <c r="J19" s="222">
         <v>8.94</v>
       </c>
-      <c r="K19" s="231">
+      <c r="K19" s="233">
         <v>3.73</v>
       </c>
-      <c r="L19" s="234">
+      <c r="L19" s="225">
         <v>-1.99</v>
       </c>
-      <c r="M19" s="222">
+      <c r="M19" s="226">
         <v>-1.49</v>
       </c>
-      <c r="N19" s="232">
+      <c r="N19" s="227">
         <v>-0.25</v>
       </c>
-      <c r="O19" s="233">
+      <c r="O19" s="228">
         <v>-0.12</v>
       </c>
-      <c r="P19" s="225">
+      <c r="P19" s="229">
         <v>3.11</v>
       </c>
       <c r="Q19" s="223">
         <v>4.84</v>
       </c>
-      <c r="R19" s="226">
+      <c r="R19" s="230">
         <v>15.28</v>
       </c>
-      <c r="S19" s="227">
+      <c r="S19" s="234">
         <v>14.53</v>
       </c>
-      <c r="T19" s="228">
-        <v>-8.07</v>
+      <c r="T19" s="224">
+        <v>-10.06</v>
       </c>
     </row>
     <row r="20">
@@ -10102,7 +10150,7 @@
       <c r="C20" t="str">
         <v>837174</v>
       </c>
-      <c r="D20" s="237" t="str">
+      <c r="D20" s="240" t="str">
         <v>净买: 1878.87万</v>
       </c>
       <c r="E20">
@@ -10120,37 +10168,37 @@
       <c r="I20" s="246">
         <v>31.1</v>
       </c>
-      <c r="J20" s="245">
+      <c r="J20" s="241">
         <v>25.62</v>
       </c>
-      <c r="K20" s="247">
+      <c r="K20" s="242">
         <v>0.1</v>
       </c>
       <c r="L20" s="238">
         <v>-14.6</v>
       </c>
-      <c r="M20" s="235">
+      <c r="M20" s="247">
         <v>-15.25</v>
       </c>
-      <c r="N20" s="239">
+      <c r="N20" s="243">
         <v>-17.98</v>
       </c>
-      <c r="O20" s="240">
+      <c r="O20" s="236">
         <v>-19.46</v>
       </c>
-      <c r="P20" s="243">
+      <c r="P20" s="237">
         <v>-18.77</v>
       </c>
-      <c r="Q20" s="241">
+      <c r="Q20" s="244">
         <v>-23.13</v>
       </c>
-      <c r="R20" s="236">
+      <c r="R20" s="239">
         <v>-22.25</v>
       </c>
-      <c r="S20" s="244">
+      <c r="S20" s="245">
         <v>-22.58</v>
       </c>
-      <c r="T20" s="242">
+      <c r="T20" s="235">
         <v>-29.79</v>
       </c>
     </row>
@@ -10164,7 +10212,7 @@
       <c r="C21" t="str">
         <v>002050</v>
       </c>
-      <c r="D21" s="251" t="str">
+      <c r="D21" s="252" t="str">
         <v>净买: 2.36亿</v>
       </c>
       <c r="E21">
@@ -10179,41 +10227,41 @@
       <c r="H21">
         <v>2.54</v>
       </c>
-      <c r="I21" s="252">
+      <c r="I21" s="249">
         <v>7.27</v>
       </c>
-      <c r="J21" s="253">
+      <c r="J21" s="250">
         <v>8.13</v>
       </c>
       <c r="K21" s="256">
         <v>6.42</v>
       </c>
-      <c r="L21" s="254">
+      <c r="L21" s="251">
         <v>10.42</v>
       </c>
-      <c r="M21" s="248">
+      <c r="M21" s="257">
         <v>9.59</v>
       </c>
-      <c r="N21" s="255">
+      <c r="N21" s="253">
         <v>13.28</v>
       </c>
-      <c r="O21" s="249">
+      <c r="O21" s="259">
         <v>24.62</v>
       </c>
-      <c r="P21" s="257">
+      <c r="P21" s="254">
         <v>33.1</v>
       </c>
-      <c r="Q21" s="258">
+      <c r="Q21" s="260">
         <v>44.7</v>
       </c>
-      <c r="R21" s="250">
+      <c r="R21" s="255">
         <v>32.31</v>
       </c>
-      <c r="S21" s="259">
+      <c r="S21" s="258">
         <v>36.5</v>
       </c>
-      <c r="T21" s="260">
-        <v>45.84</v>
+      <c r="T21" s="248">
+        <v>40.28</v>
       </c>
     </row>
     <row r="22">
@@ -10226,7 +10274,7 @@
       <c r="C22" t="str">
         <v>603429</v>
       </c>
-      <c r="D22" s="263" t="str">
+      <c r="D22" s="270" t="str">
         <v>净买: 1423.30万</v>
       </c>
       <c r="E22">
@@ -10241,41 +10289,41 @@
       <c r="H22">
         <v>-0.38</v>
       </c>
-      <c r="I22" s="269">
+      <c r="I22" s="264">
         <v>-6.68</v>
       </c>
-      <c r="J22" s="266">
+      <c r="J22" s="271">
         <v>-8.22</v>
       </c>
-      <c r="K22" s="272">
+      <c r="K22" s="265">
         <v>-10.52</v>
       </c>
-      <c r="L22" s="270">
+      <c r="L22" s="272">
         <v>-8.76</v>
       </c>
-      <c r="M22" s="273">
+      <c r="M22" s="261">
         <v>-10.37</v>
       </c>
-      <c r="N22" s="261">
+      <c r="N22" s="273">
         <v>-10.68</v>
       </c>
-      <c r="O22" s="267">
+      <c r="O22" s="262">
         <v>-12.75</v>
       </c>
-      <c r="P22" s="262">
+      <c r="P22" s="263">
         <v>-9.75</v>
       </c>
-      <c r="Q22" s="264">
+      <c r="Q22" s="266">
         <v>-0.69</v>
       </c>
-      <c r="R22" s="271">
+      <c r="R22" s="267">
         <v>-0.92</v>
       </c>
       <c r="S22" s="268">
         <v>2</v>
       </c>
-      <c r="T22" s="265">
-        <v>-24.96</v>
+      <c r="T22" s="269">
+        <v>-24.19</v>
       </c>
     </row>
     <row r="23">
@@ -10288,7 +10336,7 @@
       <c r="C23" t="str">
         <v>002475</v>
       </c>
-      <c r="D23" s="278" t="str">
+      <c r="D23" s="277" t="str">
         <v>净买: 2.00亿</v>
       </c>
       <c r="E23">
@@ -10303,41 +10351,41 @@
       <c r="H23">
         <v>-1.85</v>
       </c>
-      <c r="I23" s="279">
+      <c r="I23" s="283">
         <v>12.08</v>
       </c>
-      <c r="J23" s="285">
+      <c r="J23" s="284">
         <v>11.67</v>
       </c>
       <c r="K23" s="280">
         <v>11.74</v>
       </c>
-      <c r="L23" s="282">
+      <c r="L23" s="278">
         <v>11</v>
       </c>
-      <c r="M23" s="286">
+      <c r="M23" s="285">
         <v>10.19</v>
       </c>
-      <c r="N23" s="283">
+      <c r="N23" s="281">
         <v>12.52</v>
       </c>
-      <c r="O23" s="284">
+      <c r="O23" s="286">
         <v>17.39</v>
       </c>
-      <c r="P23" s="274">
+      <c r="P23" s="276">
         <v>29.13</v>
       </c>
-      <c r="Q23" s="275">
+      <c r="Q23" s="279">
         <v>39.19</v>
       </c>
-      <c r="R23" s="276">
+      <c r="R23" s="274">
         <v>48.73</v>
       </c>
-      <c r="S23" s="281">
+      <c r="S23" s="282">
         <v>45.64</v>
       </c>
-      <c r="T23" s="277">
-        <v>52.48</v>
+      <c r="T23" s="275">
+        <v>48.05</v>
       </c>
     </row>
     <row r="24">
@@ -10350,7 +10398,7 @@
       <c r="C24" t="str">
         <v>002146</v>
       </c>
-      <c r="D24" s="299" t="str">
+      <c r="D24" s="288" t="str">
         <v>净买: 2134.01万</v>
       </c>
       <c r="E24">
@@ -10365,41 +10413,41 @@
       <c r="H24">
         <v>0.5</v>
       </c>
-      <c r="I24" s="296">
+      <c r="I24" s="291">
         <v>-9</v>
       </c>
-      <c r="J24" s="287">
+      <c r="J24" s="297">
         <v>-11</v>
       </c>
-      <c r="K24" s="297">
+      <c r="K24" s="294">
         <v>-14.5</v>
       </c>
-      <c r="L24" s="291">
+      <c r="L24" s="292">
         <v>-17.5</v>
       </c>
-      <c r="M24" s="294">
+      <c r="M24" s="295">
         <v>-16.5</v>
       </c>
       <c r="N24" s="298">
         <v>-19</v>
       </c>
-      <c r="O24" s="292">
+      <c r="O24" s="299">
         <v>-20</v>
       </c>
-      <c r="P24" s="293">
+      <c r="P24" s="296">
         <v>-19.5</v>
       </c>
-      <c r="Q24" s="288">
+      <c r="Q24" s="287">
         <v>-19.5</v>
       </c>
-      <c r="R24" s="289">
+      <c r="R24" s="293">
         <v>-19</v>
       </c>
-      <c r="S24" s="290">
+      <c r="S24" s="289">
         <v>-18.5</v>
       </c>
-      <c r="T24" s="295">
-        <v>-36.5</v>
+      <c r="T24" s="290">
+        <v>-37</v>
       </c>
     </row>
     <row r="25">
@@ -10412,7 +10460,7 @@
       <c r="C25" t="str">
         <v>002743</v>
       </c>
-      <c r="D25" s="308" t="str">
+      <c r="D25" s="305" t="str">
         <v>净卖: -133.27万</v>
       </c>
       <c r="E25">
@@ -10427,19 +10475,19 @@
       <c r="H25">
         <v>-9.98</v>
       </c>
-      <c r="I25" s="309">
+      <c r="I25" s="311">
         <v>0</v>
       </c>
-      <c r="J25" s="305">
+      <c r="J25" s="306">
         <v>-5.83</v>
       </c>
-      <c r="K25" s="301">
+      <c r="K25" s="307">
         <v>-3.38</v>
       </c>
-      <c r="L25" s="302">
+      <c r="L25" s="300">
         <v>0.75</v>
       </c>
-      <c r="M25" s="310">
+      <c r="M25" s="301">
         <v>1.88</v>
       </c>
       <c r="N25" s="303">
@@ -10448,20 +10496,20 @@
       <c r="O25" s="304">
         <v>3.95</v>
       </c>
-      <c r="P25" s="306">
+      <c r="P25" s="308">
         <v>0.75</v>
       </c>
-      <c r="Q25" s="311">
+      <c r="Q25" s="302">
         <v>-0.19</v>
       </c>
-      <c r="R25" s="300">
+      <c r="R25" s="309">
         <v>1.5</v>
       </c>
-      <c r="S25" s="312">
+      <c r="S25" s="310">
         <v>5.83</v>
       </c>
-      <c r="T25" s="307">
-        <v>-0.38</v>
+      <c r="T25" s="312">
+        <v>0.38</v>
       </c>
     </row>
     <row r="26">
@@ -10474,7 +10522,7 @@
       <c r="C26" t="str">
         <v>601011</v>
       </c>
-      <c r="D26" s="320" t="str">
+      <c r="D26" s="314" t="str">
         <v>净卖: -479.33万</v>
       </c>
       <c r="E26">
@@ -10489,41 +10537,41 @@
       <c r="H26">
         <v>3.37</v>
       </c>
-      <c r="I26" s="316">
+      <c r="I26" s="322">
         <v>6.51</v>
       </c>
-      <c r="J26" s="321">
+      <c r="J26" s="323">
         <v>17.26</v>
       </c>
-      <c r="K26" s="322">
+      <c r="K26" s="319">
         <v>28.99</v>
       </c>
-      <c r="L26" s="325">
+      <c r="L26" s="315">
         <v>16.94</v>
       </c>
-      <c r="M26" s="313">
+      <c r="M26" s="324">
         <v>28.66</v>
       </c>
-      <c r="N26" s="323">
+      <c r="N26" s="316">
         <v>30.29</v>
       </c>
       <c r="O26" s="317">
         <v>43.32</v>
       </c>
-      <c r="P26" s="314">
+      <c r="P26" s="325">
         <v>33.55</v>
       </c>
-      <c r="Q26" s="318">
+      <c r="Q26" s="313">
         <v>25.08</v>
       </c>
-      <c r="R26" s="324">
+      <c r="R26" s="318">
         <v>29.97</v>
       </c>
-      <c r="S26" s="315">
+      <c r="S26" s="320">
         <v>21.5</v>
       </c>
-      <c r="T26" s="319">
-        <v>0.98</v>
+      <c r="T26" s="321">
+        <v>1.3</v>
       </c>
     </row>
     <row r="27">
@@ -10536,7 +10584,7 @@
       <c r="C27" t="str">
         <v>601011</v>
       </c>
-      <c r="D27" s="331" t="str">
+      <c r="D27" s="334" t="str">
         <v>净卖: -659.33万</v>
       </c>
       <c r="E27">
@@ -10551,41 +10599,41 @@
       <c r="H27">
         <v>10.09</v>
       </c>
-      <c r="I27" s="336">
+      <c r="I27" s="335">
         <v>0</v>
       </c>
       <c r="J27" s="337">
         <v>10</v>
       </c>
-      <c r="K27" s="332">
+      <c r="K27" s="338">
         <v>-0.28</v>
       </c>
-      <c r="L27" s="327">
+      <c r="L27" s="336">
         <v>9.72</v>
       </c>
-      <c r="M27" s="334">
+      <c r="M27" s="328">
         <v>11.11</v>
       </c>
-      <c r="N27" s="328">
+      <c r="N27" s="332">
         <v>22.22</v>
       </c>
-      <c r="O27" s="338">
+      <c r="O27" s="329">
         <v>13.89</v>
       </c>
-      <c r="P27" s="329">
+      <c r="P27" s="326">
         <v>6.67</v>
       </c>
-      <c r="Q27" s="326">
+      <c r="Q27" s="333">
         <v>10.83</v>
       </c>
-      <c r="R27" s="330">
+      <c r="R27" s="327">
         <v>3.61</v>
       </c>
-      <c r="S27" s="335">
+      <c r="S27" s="330">
         <v>4.17</v>
       </c>
-      <c r="T27" s="333">
-        <v>-13.89</v>
+      <c r="T27" s="331">
+        <v>-13.61</v>
       </c>
     </row>
     <row r="28">
@@ -10598,7 +10646,7 @@
       <c r="C28" t="str">
         <v>920765</v>
       </c>
-      <c r="D28" s="345" t="str">
+      <c r="D28" s="342" t="str">
         <v>净卖: -291.63万</v>
       </c>
       <c r="E28">
@@ -10613,41 +10661,41 @@
       <c r="H28">
         <v>-0.26</v>
       </c>
-      <c r="I28" s="346">
+      <c r="I28" s="347">
         <v>21.66</v>
       </c>
-      <c r="J28" s="342">
+      <c r="J28" s="348">
         <v>16.41</v>
       </c>
-      <c r="K28" s="339">
+      <c r="K28" s="343">
         <v>26.65</v>
       </c>
-      <c r="L28" s="340">
+      <c r="L28" s="351">
         <v>21.66</v>
       </c>
-      <c r="M28" s="343">
+      <c r="M28" s="339">
         <v>16.11</v>
       </c>
       <c r="N28" s="349">
         <v>14.53</v>
       </c>
-      <c r="O28" s="347">
+      <c r="O28" s="345">
         <v>11.07</v>
       </c>
-      <c r="P28" s="344">
+      <c r="P28" s="340">
         <v>10.15</v>
       </c>
-      <c r="Q28" s="350">
+      <c r="Q28" s="341">
         <v>9.63</v>
       </c>
-      <c r="R28" s="351">
+      <c r="R28" s="344">
         <v>8.67</v>
       </c>
-      <c r="S28" s="348">
+      <c r="S28" s="346">
         <v>9.1</v>
       </c>
-      <c r="T28" s="341">
-        <v>-40.39</v>
+      <c r="T28" s="350">
+        <v>-42.01</v>
       </c>
     </row>
     <row r="29">
@@ -10660,7 +10708,7 @@
       <c r="C29" t="str">
         <v>688233</v>
       </c>
-      <c r="D29" s="356" t="str">
+      <c r="D29" s="359" t="str">
         <v>净买: 4489.13万</v>
       </c>
       <c r="E29">
@@ -10675,41 +10723,41 @@
       <c r="H29">
         <v>16.03</v>
       </c>
-      <c r="I29" s="352">
+      <c r="I29" s="362">
         <v>3.42</v>
       </c>
-      <c r="J29" s="357">
+      <c r="J29" s="363">
         <v>1.23</v>
       </c>
-      <c r="K29" s="358">
+      <c r="K29" s="357">
         <v>10.14</v>
       </c>
-      <c r="L29" s="359">
+      <c r="L29" s="364">
         <v>-0.87</v>
       </c>
-      <c r="M29" s="361">
+      <c r="M29" s="352">
         <v>5.63</v>
       </c>
-      <c r="N29" s="360">
+      <c r="N29" s="354">
         <v>-0.83</v>
       </c>
-      <c r="O29" s="353">
+      <c r="O29" s="358">
         <v>-0.62</v>
       </c>
-      <c r="P29" s="362">
+      <c r="P29" s="360">
         <v>-6.58</v>
       </c>
-      <c r="Q29" s="363">
+      <c r="Q29" s="353">
         <v>-16.49</v>
       </c>
-      <c r="R29" s="364">
+      <c r="R29" s="355">
         <v>-10.75</v>
       </c>
-      <c r="S29" s="355">
+      <c r="S29" s="356">
         <v>0.63</v>
       </c>
-      <c r="T29" s="354">
-        <v>-0.86</v>
+      <c r="T29" s="361">
+        <v>-3.48</v>
       </c>
     </row>
     <row r="30">
@@ -10722,7 +10770,7 @@
       <c r="C30" t="str">
         <v>603130</v>
       </c>
-      <c r="D30" s="372" t="str">
+      <c r="D30" s="367" t="str">
         <v>净买: 297.33万</v>
       </c>
       <c r="E30">
@@ -10737,41 +10785,41 @@
       <c r="H30">
         <v>-0.93</v>
       </c>
-      <c r="I30" s="376">
+      <c r="I30" s="368">
         <v>-8.65</v>
       </c>
-      <c r="J30" s="373">
+      <c r="J30" s="372">
         <v>-3.96</v>
       </c>
-      <c r="K30" s="365">
+      <c r="K30" s="369">
         <v>-6.7</v>
       </c>
-      <c r="L30" s="366">
+      <c r="L30" s="370">
         <v>-2.84</v>
       </c>
-      <c r="M30" s="374">
+      <c r="M30" s="373">
         <v>-5.33</v>
       </c>
       <c r="N30" s="375">
         <v>-7.23</v>
       </c>
-      <c r="O30" s="367">
+      <c r="O30" s="365">
         <v>-9.19</v>
       </c>
-      <c r="P30" s="370">
+      <c r="P30" s="374">
         <v>-11.19</v>
       </c>
-      <c r="Q30" s="368">
+      <c r="Q30" s="371">
         <v>-10.76</v>
       </c>
-      <c r="R30" s="377">
+      <c r="R30" s="376">
         <v>-1.83</v>
       </c>
-      <c r="S30" s="369">
+      <c r="S30" s="377">
         <v>2.97</v>
       </c>
-      <c r="T30" s="371">
-        <v>19.59</v>
+      <c r="T30" s="366">
+        <v>17.54</v>
       </c>
     </row>
     <row r="31">
@@ -10784,7 +10832,7 @@
       <c r="C31" t="str">
         <v>000695</v>
       </c>
-      <c r="D31" s="378" t="str">
+      <c r="D31" s="387" t="str">
         <v>净买: 1731.47万</v>
       </c>
       <c r="E31">
@@ -10799,41 +10847,41 @@
       <c r="H31">
         <v>-2.44</v>
       </c>
-      <c r="I31" s="384">
+      <c r="I31" s="389">
         <v>-7.67</v>
       </c>
-      <c r="J31" s="379">
+      <c r="J31" s="388">
         <v>-10.54</v>
       </c>
-      <c r="K31" s="380">
+      <c r="K31" s="381">
         <v>-16.08</v>
       </c>
-      <c r="L31" s="385">
+      <c r="L31" s="390">
         <v>-21.88</v>
       </c>
-      <c r="M31" s="386">
+      <c r="M31" s="382">
         <v>-23.96</v>
       </c>
-      <c r="N31" s="381">
+      <c r="N31" s="383">
         <v>-24.6</v>
       </c>
-      <c r="O31" s="389">
+      <c r="O31" s="384">
         <v>-28.17</v>
       </c>
-      <c r="P31" s="387">
+      <c r="P31" s="378">
         <v>-28.81</v>
       </c>
-      <c r="Q31" s="382">
+      <c r="Q31" s="385">
         <v>-30.62</v>
       </c>
-      <c r="R31" s="388">
+      <c r="R31" s="386">
         <v>-32.37</v>
       </c>
-      <c r="S31" s="383">
+      <c r="S31" s="379">
         <v>-32.16</v>
       </c>
-      <c r="T31" s="390">
-        <v>-20.39</v>
+      <c r="T31" s="380">
+        <v>-19.81</v>
       </c>
     </row>
     <row r="32">
@@ -10846,7 +10894,7 @@
       <c r="C32" t="str">
         <v>920407</v>
       </c>
-      <c r="D32" s="398" t="str">
+      <c r="D32" s="399" t="str">
         <v>净买: 722.34万</v>
       </c>
       <c r="E32">
@@ -10861,41 +10909,41 @@
       <c r="H32">
         <v>1.28</v>
       </c>
-      <c r="I32" s="400">
+      <c r="I32" s="395">
         <v>28.31</v>
       </c>
-      <c r="J32" s="391">
+      <c r="J32" s="396">
         <v>29.11</v>
       </c>
-      <c r="K32" s="401">
+      <c r="K32" s="402">
         <v>15.45</v>
       </c>
-      <c r="L32" s="396">
+      <c r="L32" s="400">
         <v>17.04</v>
       </c>
-      <c r="M32" s="402">
+      <c r="M32" s="397">
         <v>25.35</v>
       </c>
-      <c r="N32" s="399">
+      <c r="N32" s="398">
         <v>62.96</v>
       </c>
-      <c r="O32" s="397">
+      <c r="O32" s="403">
         <v>42.07</v>
       </c>
-      <c r="P32" s="392">
+      <c r="P32" s="391">
         <v>32.35</v>
       </c>
-      <c r="Q32" s="393">
+      <c r="Q32" s="392">
         <v>36.62</v>
       </c>
-      <c r="R32" s="403">
+      <c r="R32" s="393">
         <v>27.7</v>
       </c>
-      <c r="S32" s="394">
+      <c r="S32" s="401">
         <v>27.7</v>
       </c>
-      <c r="T32" s="395">
-        <v>-17.98</v>
+      <c r="T32" s="394">
+        <v>-19.3</v>
       </c>
     </row>
     <row r="33">
@@ -10908,7 +10956,7 @@
       <c r="C33" t="str">
         <v>920765</v>
       </c>
-      <c r="D33" s="414" t="str">
+      <c r="D33" s="406" t="str">
         <v>净卖: -3268.70万</v>
       </c>
       <c r="E33">
@@ -10923,41 +10971,41 @@
       <c r="H33">
         <v>-10.08</v>
       </c>
-      <c r="I33" s="415">
+      <c r="I33" s="407">
         <v>2.35</v>
       </c>
-      <c r="J33" s="416">
+      <c r="J33" s="409">
         <v>-1.45</v>
       </c>
-      <c r="K33" s="408">
+      <c r="K33" s="413">
         <v>-5.92</v>
       </c>
-      <c r="L33" s="404">
+      <c r="L33" s="414">
         <v>-10.71</v>
       </c>
-      <c r="M33" s="411">
+      <c r="M33" s="415">
         <v>-10.51</v>
       </c>
-      <c r="N33" s="409">
+      <c r="N33" s="410">
         <v>-12.16</v>
       </c>
-      <c r="O33" s="412">
+      <c r="O33" s="416">
         <v>-14.08</v>
       </c>
-      <c r="P33" s="405">
+      <c r="P33" s="411">
         <v>-16.59</v>
       </c>
-      <c r="Q33" s="410">
+      <c r="Q33" s="412">
         <v>-19.14</v>
       </c>
-      <c r="R33" s="407">
+      <c r="R33" s="408">
         <v>-18.63</v>
       </c>
-      <c r="S33" s="406">
+      <c r="S33" s="404">
         <v>-18.86</v>
       </c>
-      <c r="T33" s="413">
-        <v>-46.59</v>
+      <c r="T33" s="405">
+        <v>-48.04</v>
       </c>
     </row>
     <row r="34">
@@ -10970,7 +11018,7 @@
       <c r="C34" t="str">
         <v>603458</v>
       </c>
-      <c r="D34" s="428" t="str">
+      <c r="D34" s="417" t="str">
         <v>净买: 2084.50万</v>
       </c>
       <c r="E34">
@@ -10985,41 +11033,41 @@
       <c r="H34">
         <v>5.37</v>
       </c>
-      <c r="I34" s="420">
+      <c r="I34" s="424">
         <v>4.4</v>
       </c>
-      <c r="J34" s="429">
+      <c r="J34" s="418">
         <v>0.2</v>
       </c>
-      <c r="K34" s="424">
+      <c r="K34" s="425">
         <v>10.2</v>
       </c>
-      <c r="L34" s="426">
+      <c r="L34" s="429">
         <v>14</v>
       </c>
-      <c r="M34" s="421">
+      <c r="M34" s="419">
         <v>13.9</v>
       </c>
-      <c r="N34" s="417">
+      <c r="N34" s="426">
         <v>20.5</v>
       </c>
-      <c r="O34" s="425">
+      <c r="O34" s="427">
         <v>20.4</v>
       </c>
-      <c r="P34" s="422">
+      <c r="P34" s="421">
         <v>21.7</v>
       </c>
-      <c r="Q34" s="418">
+      <c r="Q34" s="420">
         <v>19.2</v>
       </c>
-      <c r="R34" s="423">
+      <c r="R34" s="428">
         <v>31.1</v>
       </c>
-      <c r="S34" s="427">
+      <c r="S34" s="422">
         <v>27.9</v>
       </c>
-      <c r="T34" s="419">
-        <v>16</v>
+      <c r="T34" s="423">
+        <v>12</v>
       </c>
     </row>
     <row r="35">
@@ -11032,7 +11080,7 @@
       <c r="C35" t="str">
         <v>920179</v>
       </c>
-      <c r="D35" s="441" t="str">
+      <c r="D35" s="439" t="str">
         <v>净买: 1651.86万</v>
       </c>
       <c r="E35">
@@ -11050,38 +11098,38 @@
       <c r="I35" s="431">
         <v>15.88</v>
       </c>
-      <c r="J35" s="435">
+      <c r="J35" s="434">
         <v>19.24</v>
       </c>
       <c r="K35" s="432">
         <v>13.24</v>
       </c>
-      <c r="L35" s="436">
+      <c r="L35" s="433">
         <v>17.03</v>
       </c>
       <c r="M35" s="442">
         <v>8.58</v>
       </c>
-      <c r="N35" s="430">
+      <c r="N35" s="435">
         <v>8.97</v>
       </c>
-      <c r="O35" s="433">
+      <c r="O35" s="440">
         <v>10.54</v>
       </c>
-      <c r="P35" s="437">
+      <c r="P35" s="441">
         <v>7.38</v>
       </c>
-      <c r="Q35" s="439">
+      <c r="Q35" s="430">
         <v>13.87</v>
       </c>
-      <c r="R35" s="434">
+      <c r="R35" s="436">
         <v>36.96</v>
       </c>
-      <c r="S35" s="438">
+      <c r="S35" s="437">
         <v>37.84</v>
       </c>
-      <c r="T35" s="440">
-        <v>22.43</v>
+      <c r="T35" s="438">
+        <v>17.77</v>
       </c>
     </row>
     <row r="36">
@@ -11094,7 +11142,7 @@
       <c r="C36" t="str">
         <v>603488</v>
       </c>
-      <c r="D36" s="452" t="str">
+      <c r="D36" s="451" t="str">
         <v>净买: 3230.20万</v>
       </c>
       <c r="E36">
@@ -11109,41 +11157,41 @@
       <c r="H36">
         <v>-0.94</v>
       </c>
-      <c r="I36" s="446">
+      <c r="I36" s="444">
         <v>11.07</v>
       </c>
-      <c r="J36" s="455">
+      <c r="J36" s="445">
         <v>9.74</v>
       </c>
-      <c r="K36" s="443">
+      <c r="K36" s="449">
         <v>7.38</v>
       </c>
-      <c r="L36" s="447">
+      <c r="L36" s="453">
         <v>2.93</v>
       </c>
-      <c r="M36" s="444">
+      <c r="M36" s="446">
         <v>-3.12</v>
       </c>
-      <c r="N36" s="448">
+      <c r="N36" s="454">
         <v>-5.01</v>
       </c>
-      <c r="O36" s="454">
+      <c r="O36" s="455">
         <v>-4.92</v>
       </c>
-      <c r="P36" s="449">
+      <c r="P36" s="447">
         <v>-5.11</v>
       </c>
-      <c r="Q36" s="445">
+      <c r="Q36" s="448">
         <v>-5.3</v>
       </c>
       <c r="R36" s="450">
         <v>-8.89</v>
       </c>
-      <c r="S36" s="451">
+      <c r="S36" s="443">
         <v>0.19</v>
       </c>
-      <c r="T36" s="453">
-        <v>8.61</v>
+      <c r="T36" s="452">
+        <v>3.69</v>
       </c>
     </row>
     <row r="37">
@@ -11156,7 +11204,7 @@
       <c r="C37" t="str">
         <v>688115</v>
       </c>
-      <c r="D37" s="465" t="str">
+      <c r="D37" s="461" t="str">
         <v>净买: 534.48万</v>
       </c>
       <c r="E37">
@@ -11171,41 +11219,41 @@
       <c r="H37">
         <v>-0.49</v>
       </c>
-      <c r="I37" s="463">
+      <c r="I37" s="456">
         <v>-15.96</v>
       </c>
-      <c r="J37" s="466">
+      <c r="J37" s="457">
         <v>-24.38</v>
       </c>
-      <c r="K37" s="467">
+      <c r="K37" s="462">
         <v>-27.28</v>
       </c>
-      <c r="L37" s="457">
+      <c r="L37" s="465">
         <v>-26.26</v>
       </c>
-      <c r="M37" s="461">
+      <c r="M37" s="463">
         <v>-29.33</v>
       </c>
-      <c r="N37" s="462">
+      <c r="N37" s="458">
         <v>-33.51</v>
       </c>
-      <c r="O37" s="468">
+      <c r="O37" s="467">
         <v>-34.12</v>
       </c>
-      <c r="P37" s="458">
+      <c r="P37" s="464">
         <v>-35.51</v>
       </c>
-      <c r="Q37" s="464">
+      <c r="Q37" s="468">
         <v>-35.8</v>
       </c>
-      <c r="R37" s="456">
+      <c r="R37" s="459">
         <v>-33.88</v>
       </c>
-      <c r="S37" s="459">
+      <c r="S37" s="460">
         <v>-35.38</v>
       </c>
-      <c r="T37" s="460">
-        <v>-27.22</v>
+      <c r="T37" s="466">
+        <v>-27.72</v>
       </c>
     </row>
     <row r="38">
@@ -11218,7 +11266,7 @@
       <c r="C38" t="str">
         <v>600671</v>
       </c>
-      <c r="D38" s="479" t="str">
+      <c r="D38" s="481" t="str">
         <v>净卖: -271.42万</v>
       </c>
       <c r="E38">
@@ -11233,41 +11281,41 @@
       <c r="H38">
         <v>-1.3</v>
       </c>
-      <c r="I38" s="473">
+      <c r="I38" s="471">
         <v>-8.5</v>
       </c>
-      <c r="J38" s="474">
+      <c r="J38" s="469">
         <v>-11.05</v>
       </c>
-      <c r="K38" s="480">
+      <c r="K38" s="470">
         <v>-13.41</v>
       </c>
-      <c r="L38" s="478">
+      <c r="L38" s="473">
         <v>-13.14</v>
       </c>
-      <c r="M38" s="481">
+      <c r="M38" s="474">
         <v>-15.18</v>
       </c>
-      <c r="N38" s="469">
+      <c r="N38" s="472">
         <v>-15.68</v>
       </c>
-      <c r="O38" s="470">
+      <c r="O38" s="477">
         <v>-13.05</v>
       </c>
-      <c r="P38" s="475">
+      <c r="P38" s="478">
         <v>-15.68</v>
       </c>
-      <c r="Q38" s="471">
+      <c r="Q38" s="475">
         <v>-14.45</v>
       </c>
-      <c r="R38" s="476">
+      <c r="R38" s="479">
         <v>-13.27</v>
       </c>
-      <c r="S38" s="477">
+      <c r="S38" s="476">
         <v>-11.23</v>
       </c>
-      <c r="T38" s="472">
-        <v>-12.41</v>
+      <c r="T38" s="480">
+        <v>-11.45</v>
       </c>
     </row>
     <row r="39">
@@ -11280,7 +11328,7 @@
       <c r="C39" t="str">
         <v>300017</v>
       </c>
-      <c r="D39" s="492" t="str">
+      <c r="D39" s="487" t="str">
         <v>净买: 3.37亿</v>
       </c>
       <c r="E39">
@@ -11295,41 +11343,41 @@
       <c r="H39">
         <v>15.07</v>
       </c>
-      <c r="I39" s="484">
+      <c r="I39" s="491">
         <v>0.06</v>
       </c>
-      <c r="J39" s="487">
+      <c r="J39" s="492">
         <v>7.83</v>
       </c>
-      <c r="K39" s="485">
+      <c r="K39" s="482">
         <v>6.29</v>
       </c>
-      <c r="L39" s="493">
+      <c r="L39" s="488">
         <v>8.34</v>
       </c>
-      <c r="M39" s="494">
+      <c r="M39" s="483">
         <v>23.94</v>
       </c>
-      <c r="N39" s="482">
+      <c r="N39" s="484">
         <v>7.32</v>
       </c>
-      <c r="O39" s="488">
+      <c r="O39" s="489">
         <v>15.34</v>
       </c>
-      <c r="P39" s="486">
+      <c r="P39" s="493">
         <v>15.08</v>
       </c>
-      <c r="Q39" s="489">
+      <c r="Q39" s="485">
         <v>21.31</v>
       </c>
-      <c r="R39" s="483">
+      <c r="R39" s="490">
         <v>19.9</v>
       </c>
-      <c r="S39" s="490">
+      <c r="S39" s="486">
         <v>31.26</v>
       </c>
-      <c r="T39" s="491">
-        <v>8.41</v>
+      <c r="T39" s="494">
+        <v>3.66</v>
       </c>
     </row>
     <row r="40">
@@ -11342,7 +11390,7 @@
       <c r="C40" t="str">
         <v>301486</v>
       </c>
-      <c r="D40" s="495" t="str">
+      <c r="D40" s="496" t="str">
         <v>净买: 6753.30万</v>
       </c>
       <c r="E40">
@@ -11357,29 +11405,31 @@
       <c r="H40">
         <v>-3.8</v>
       </c>
-      <c r="I40" s="496">
+      <c r="I40" s="497">
         <v>24.74</v>
       </c>
-      <c r="J40" s="497">
+      <c r="J40" s="498">
         <v>27.42</v>
       </c>
-      <c r="K40" s="498">
+      <c r="K40" s="499">
         <v>22.58</v>
       </c>
-      <c r="L40" s="499">
+      <c r="L40" s="500">
         <v>17.3</v>
       </c>
-      <c r="M40" s="500">
+      <c r="M40" s="501">
         <v>25.35</v>
       </c>
-      <c r="N40" t="str"/>
+      <c r="N40" s="502">
+        <v>21.04</v>
+      </c>
       <c r="O40" t="str"/>
       <c r="P40" t="str"/>
       <c r="Q40" t="str"/>
       <c r="R40" t="str"/>
       <c r="S40" t="str"/>
-      <c r="T40" s="501">
-        <v>25.35</v>
+      <c r="T40" s="495">
+        <v>21.04</v>
       </c>
     </row>
     <row r="41">
@@ -11392,7 +11442,7 @@
       <c r="C41" t="str">
         <v>600734</v>
       </c>
-      <c r="D41" s="504" t="str">
+      <c r="D41" s="505" t="str">
         <v>净卖: -404.86万</v>
       </c>
       <c r="E41">
@@ -11407,29 +11457,31 @@
       <c r="H41">
         <v>-10.1</v>
       </c>
-      <c r="I41" s="505">
+      <c r="I41" s="506">
         <v>0</v>
       </c>
-      <c r="J41" s="506">
+      <c r="J41" s="507">
         <v>-4.35</v>
       </c>
-      <c r="K41" s="507">
+      <c r="K41" s="508">
         <v>-10.14</v>
       </c>
-      <c r="L41" s="508">
+      <c r="L41" s="509">
         <v>-13.41</v>
       </c>
-      <c r="M41" s="502">
+      <c r="M41" s="510">
         <v>-15.22</v>
       </c>
-      <c r="N41" t="str"/>
+      <c r="N41" s="503">
+        <v>-14.86</v>
+      </c>
       <c r="O41" t="str"/>
       <c r="P41" t="str"/>
       <c r="Q41" t="str"/>
       <c r="R41" t="str"/>
       <c r="S41" t="str"/>
-      <c r="T41" s="503">
-        <v>-15.22</v>
+      <c r="T41" s="504">
+        <v>-14.86</v>
       </c>
     </row>
     <row r="42">
@@ -11442,7 +11494,7 @@
       <c r="C42" t="str">
         <v>603169</v>
       </c>
-      <c r="D42" s="513" t="str">
+      <c r="D42" s="512" t="str">
         <v>净卖: -374.20万</v>
       </c>
       <c r="E42">
@@ -11457,16 +11509,18 @@
       <c r="H42">
         <v>-10</v>
       </c>
-      <c r="I42" s="509">
+      <c r="I42" s="513">
         <v>0</v>
       </c>
-      <c r="J42" s="510">
+      <c r="J42" s="514">
         <v>-6.69</v>
       </c>
-      <c r="K42" s="511">
+      <c r="K42" s="515">
         <v>-5.22</v>
       </c>
-      <c r="L42" t="str"/>
+      <c r="L42" s="516">
+        <v>-6.8</v>
+      </c>
       <c r="M42" t="str"/>
       <c r="N42" t="str"/>
       <c r="O42" t="str"/>
@@ -11474,8 +11528,8 @@
       <c r="Q42" t="str"/>
       <c r="R42" t="str"/>
       <c r="S42" t="str"/>
-      <c r="T42" s="512">
-        <v>-5.22</v>
+      <c r="T42" s="511">
+        <v>-6.8</v>
       </c>
     </row>
     <row r="43">
@@ -11499,13 +11553,13 @@
         <v>41</v>
       </c>
       <c r="L43">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M43">
         <v>40</v>
       </c>
       <c r="N43">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O43">
         <v>38</v>
@@ -11537,41 +11591,41 @@
       <c r="F44" t="str"/>
       <c r="G44" t="str"/>
       <c r="H44" t="str"/>
-      <c r="I44" s="522">
+      <c r="I44" s="525">
         <v>53.66</v>
       </c>
-      <c r="J44" s="514">
+      <c r="J44" s="527">
         <v>58.54</v>
       </c>
-      <c r="K44" s="515">
+      <c r="K44" s="517">
         <v>53.66</v>
       </c>
-      <c r="L44" s="523">
-        <v>52.5</v>
-      </c>
-      <c r="M44" s="516">
+      <c r="L44" s="518">
+        <v>51.22</v>
+      </c>
+      <c r="M44" s="523">
         <v>50</v>
       </c>
-      <c r="N44" s="524">
-        <v>44.74</v>
+      <c r="N44" s="519">
+        <v>45</v>
       </c>
       <c r="O44" s="520">
         <v>44.74</v>
       </c>
-      <c r="P44" s="517">
+      <c r="P44" s="526">
         <v>50</v>
       </c>
-      <c r="Q44" s="521">
+      <c r="Q44" s="524">
         <v>44.74</v>
       </c>
-      <c r="R44" s="518">
+      <c r="R44" s="521">
         <v>39.47</v>
       </c>
-      <c r="S44" s="519">
+      <c r="S44" s="528">
         <v>50</v>
       </c>
-      <c r="T44" s="525">
-        <v>51.22</v>
+      <c r="T44" s="522">
+        <v>53.66</v>
       </c>
     </row>
     <row r="45">
@@ -11585,41 +11639,41 @@
       <c r="F45" t="str"/>
       <c r="G45" t="str"/>
       <c r="H45" t="str"/>
-      <c r="I45" s="533">
+      <c r="I45" s="535">
         <v>3.45</v>
       </c>
       <c r="J45" s="536">
         <v>2.93</v>
       </c>
-      <c r="K45" s="531">
+      <c r="K45" s="538">
         <v>0.8</v>
       </c>
-      <c r="L45" s="534">
-        <v>-0.04</v>
-      </c>
-      <c r="M45" s="526">
+      <c r="L45" s="540">
+        <v>-0.21</v>
+      </c>
+      <c r="M45" s="531">
         <v>0.08</v>
       </c>
-      <c r="N45" s="535">
-        <v>0.5</v>
-      </c>
-      <c r="O45" s="527">
+      <c r="N45" s="537">
+        <v>0.63</v>
+      </c>
+      <c r="O45" s="532">
         <v>0.7</v>
       </c>
-      <c r="P45" s="528">
+      <c r="P45" s="533">
         <v>-0.65</v>
       </c>
       <c r="Q45" s="529">
         <v>-0.47</v>
       </c>
-      <c r="R45" s="530">
+      <c r="R45" s="539">
         <v>-0.13</v>
       </c>
-      <c r="S45" s="537">
+      <c r="S45" s="530">
         <v>0.43</v>
       </c>
-      <c r="T45" s="532">
-        <v>16.16</v>
+      <c r="T45" s="534">
+        <v>14.38</v>
       </c>
     </row>
   </sheetData>
